--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A703F5F7-5A89-4FEE-9336-BA81F180CF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE03DFCB-CB3E-416B-90DB-1E3D4FD4A888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
   <si>
     <t>H22</t>
   </si>
@@ -77,10 +77,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -112,10 +108,6 @@
     <t>H35</t>
   </si>
   <si>
-    <t>比较</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>H36</t>
   </si>
   <si>
@@ -132,6 +124,48 @@
   </si>
   <si>
     <t>H40</t>
+  </si>
+  <si>
+    <t>H38</t>
+  </si>
+  <si>
+    <t>H39</t>
+  </si>
+  <si>
+    <t>H41</t>
+  </si>
+  <si>
+    <t>H42</t>
+  </si>
+  <si>
+    <t>H43</t>
+  </si>
+  <si>
+    <t>H37</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>mak</t>
+  </si>
+  <si>
+    <t>gen</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>H22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H36</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -653,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="13"/>
@@ -672,20 +706,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>17</v>
+      <c r="A1" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>24</v>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
@@ -697,22 +731,22 @@
         <v>13</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
@@ -724,10 +758,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>15</v>
@@ -736,10 +770,10 @@
         <v>14</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>11</v>
@@ -751,12 +785,12 @@
         <v>13</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -766,22 +800,22 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(F2:H2)</f>
-        <v>391.68</v>
+        <v>502.81999999999994</v>
       </c>
       <c r="E2" s="5">
-        <v>372.69</v>
+        <v>369.63</v>
       </c>
       <c r="F2" s="8">
-        <v>140.16</v>
+        <v>174.9</v>
       </c>
       <c r="G2" s="8">
-        <v>115.45</v>
+        <v>144.88999999999999</v>
       </c>
       <c r="H2" s="8">
-        <v>136.07</v>
+        <v>183.03</v>
       </c>
       <c r="I2" s="7">
-        <v>223.78</v>
+        <v>293.08999999999997</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>0</v>
@@ -793,58 +827,57 @@
         <v>1</v>
       </c>
       <c r="M2" s="4">
-        <f>SUM(O2:Q2)</f>
-        <v>32.869999999999997</v>
+        <v>41.709999999999994</v>
       </c>
       <c r="N2" s="5">
-        <v>68.569999999999993</v>
+        <v>93.96</v>
       </c>
       <c r="O2" s="8">
-        <v>4.99</v>
+        <v>6.59</v>
       </c>
       <c r="P2" s="8">
-        <v>12.19</v>
+        <v>15.56</v>
       </c>
       <c r="Q2" s="8">
-        <v>15.69</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="R2" s="7">
-        <v>26.66</v>
+        <v>33.96</v>
       </c>
       <c r="S2" s="16" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T2" s="5">
-        <f t="shared" ref="T2:T16" si="0">ROUND(B2/K2,3)</f>
+        <f>ROUND(B2/K2,3)</f>
         <v>1</v>
       </c>
       <c r="U2" s="5">
-        <f t="shared" ref="U2:U16" si="1">ROUND(C2/L2,3)</f>
+        <f>ROUND(C2/L2,3)</f>
         <v>1</v>
       </c>
       <c r="V2" s="4">
-        <f t="shared" ref="V2:V16" si="2">ROUND(D2/M2,3)</f>
-        <v>11.916</v>
+        <f>ROUND(D2/M2,3)</f>
+        <v>12.055</v>
       </c>
       <c r="W2" s="5">
-        <f t="shared" ref="W2:W14" si="3">ROUND(E2/N2,3)</f>
-        <v>5.4349999999999996</v>
+        <f>ROUND(E2/N2,3)</f>
+        <v>3.9340000000000002</v>
       </c>
       <c r="X2" s="8">
-        <f t="shared" ref="X2:X14" si="4">ROUND(F2/O2,3)</f>
-        <v>28.088000000000001</v>
+        <f>ROUND(F2/O2,3)</f>
+        <v>26.54</v>
       </c>
       <c r="Y2" s="8">
-        <f t="shared" ref="Y2:Y14" si="5">ROUND(G2/P2,3)</f>
-        <v>9.4710000000000001</v>
+        <f>ROUND(G2/P2,3)</f>
+        <v>9.3119999999999994</v>
       </c>
       <c r="Z2" s="8">
-        <f t="shared" ref="Z2:Z14" si="6">ROUND(H2/Q2,3)</f>
-        <v>8.6720000000000006</v>
+        <f>ROUND(H2/Q2,3)</f>
+        <v>9.3569999999999993</v>
       </c>
       <c r="AA2" s="7">
-        <f t="shared" ref="AA2:AA14" si="7">ROUND(I2/R2,3)</f>
-        <v>8.3940000000000001</v>
+        <f>ROUND(I2/R2,3)</f>
+        <v>8.6300000000000008</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -853,95 +886,92 @@
       </c>
       <c r="B3" s="2">
         <f>D$2/D3</f>
-        <v>1.5574996023540639</v>
+        <v>1.5134695843241126</v>
       </c>
       <c r="C3" s="2">
         <f>D2/D3</f>
-        <v>1.5574996023540639</v>
+        <v>1.5134695843241126</v>
       </c>
       <c r="D3" s="6">
-        <f t="shared" ref="D3:D14" si="8">SUM(F3:H3)</f>
-        <v>251.48000000000002</v>
+        <f t="shared" ref="D3:D14" si="0">SUM(F3:H3)</f>
+        <v>332.23</v>
       </c>
       <c r="E3" s="5">
-        <v>365.53</v>
+        <v>360.67</v>
       </c>
       <c r="F3" s="8">
-        <v>134.85</v>
+        <v>175.4</v>
       </c>
       <c r="G3" s="8">
-        <v>114.51</v>
+        <v>153.86000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>2.12</v>
+        <v>2.97</v>
       </c>
       <c r="I3" s="7">
-        <v>219.12</v>
+        <v>295.49</v>
       </c>
       <c r="J3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="2">
-        <f>M$2/M3</f>
-        <v>1.8697383390216151</v>
+        <v>1.4359982525120139</v>
       </c>
       <c r="L3" s="2">
-        <f>M2/M3</f>
-        <v>1.8697383390216151</v>
+        <v>1.8221930974224549</v>
       </c>
       <c r="M3" s="6">
-        <f t="shared" ref="M3:M16" si="9">SUM(O3:Q3)</f>
-        <v>17.580000000000002</v>
+        <v>22.89</v>
       </c>
       <c r="N3" s="5">
-        <v>68.42</v>
+        <v>89.09</v>
       </c>
       <c r="O3" s="8">
-        <v>4.8600000000000003</v>
+        <v>6.74</v>
       </c>
       <c r="P3" s="8">
-        <v>12.26</v>
+        <v>15.54</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="R3" s="7">
-        <v>26.59</v>
+        <v>33.75</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="2">
-        <f t="shared" si="0"/>
-        <v>0.83299999999999996</v>
+        <f>ROUND(B3/K3,3)</f>
+        <v>1.054</v>
       </c>
       <c r="U3" s="2">
-        <f t="shared" si="1"/>
-        <v>0.83299999999999996</v>
+        <f>ROUND(C3/L3,3)</f>
+        <v>0.83099999999999996</v>
       </c>
       <c r="V3" s="6">
-        <f t="shared" si="2"/>
-        <v>14.305</v>
+        <f>ROUND(D3/M3,3)</f>
+        <v>14.513999999999999</v>
       </c>
       <c r="W3" s="5">
-        <f t="shared" si="3"/>
-        <v>5.3419999999999996</v>
+        <f>ROUND(E3/N3,3)</f>
+        <v>4.048</v>
       </c>
       <c r="X3" s="8">
-        <f t="shared" si="4"/>
-        <v>27.747</v>
+        <f>ROUND(F3/O3,3)</f>
+        <v>26.024000000000001</v>
       </c>
       <c r="Y3" s="8">
-        <f t="shared" si="5"/>
-        <v>9.34</v>
+        <f>ROUND(G3/P3,3)</f>
+        <v>9.9009999999999998</v>
       </c>
       <c r="Z3" s="1">
-        <f t="shared" si="6"/>
-        <v>4.609</v>
+        <f>ROUND(H3/Q3,3)</f>
+        <v>4.8689999999999998</v>
       </c>
       <c r="AA3" s="7">
-        <f t="shared" si="7"/>
-        <v>8.2409999999999997</v>
+        <f>ROUND(I3/R3,3)</f>
+        <v>8.7550000000000008</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -949,96 +979,93 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B12" si="10">D$2/D4</f>
-        <v>1.9913569576490926</v>
+        <f t="shared" ref="B4:B12" si="1">D$2/D4</f>
+        <v>2.0672614397894993</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C12" si="11">D3/D4</f>
-        <v>1.2785601708271901</v>
+        <f t="shared" ref="C4:C12" si="2">D3/D4</f>
+        <v>1.3659088105907988</v>
       </c>
       <c r="D4" s="6">
-        <f t="shared" si="8"/>
-        <v>196.69</v>
+        <f t="shared" si="0"/>
+        <v>243.23000000000002</v>
       </c>
       <c r="E4" s="5">
-        <v>369.35</v>
+        <v>358.84</v>
       </c>
       <c r="F4" s="1">
-        <v>72.650000000000006</v>
+        <v>91.11</v>
       </c>
       <c r="G4" s="8">
-        <v>121.84</v>
+        <v>149.25</v>
       </c>
       <c r="H4" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.87</v>
       </c>
       <c r="I4" s="7">
-        <v>215.94</v>
+        <v>295.82</v>
       </c>
       <c r="J4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="2">
-        <f t="shared" ref="K4:K12" si="12">M$2/M4</f>
-        <v>2.0030469226081657</v>
+        <v>1.5644930985245118</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L12" si="13">M3/M4</f>
-        <v>1.0712979890310788</v>
+        <v>1.0894811994288434</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" si="9"/>
-        <v>16.41</v>
+        <v>21.01</v>
       </c>
       <c r="N4" s="5">
-        <v>69.11</v>
+        <v>89.15</v>
       </c>
       <c r="O4" s="1">
-        <v>3.65</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="P4" s="8">
-        <v>12.29</v>
+        <v>15.64</v>
       </c>
       <c r="Q4" s="8">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="R4" s="7">
-        <v>26.68</v>
+        <v>33.96</v>
       </c>
       <c r="S4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <f t="shared" si="0"/>
-        <v>0.99399999999999999</v>
+        <f>ROUND(B4/K4,3)</f>
+        <v>1.321</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" si="1"/>
-        <v>1.1930000000000001</v>
+        <f>ROUND(C4/L4,3)</f>
+        <v>1.254</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="2"/>
-        <v>11.986000000000001</v>
+        <f>ROUND(D4/M4,3)</f>
+        <v>11.577</v>
       </c>
       <c r="W4" s="5">
-        <f t="shared" si="3"/>
-        <v>5.3440000000000003</v>
+        <f>ROUND(E4/N4,3)</f>
+        <v>4.0250000000000004</v>
       </c>
       <c r="X4" s="1">
-        <f t="shared" si="4"/>
-        <v>19.904</v>
+        <f>ROUND(F4/O4,3)</f>
+        <v>19.100999999999999</v>
       </c>
       <c r="Y4" s="8">
-        <f t="shared" si="5"/>
-        <v>9.9139999999999997</v>
+        <f>ROUND(G4/P4,3)</f>
+        <v>9.5429999999999993</v>
       </c>
       <c r="Z4" s="8">
-        <f t="shared" si="6"/>
-        <v>4.681</v>
+        <f>ROUND(H4/Q4,3)</f>
+        <v>4.7830000000000004</v>
       </c>
       <c r="AA4" s="7">
-        <f t="shared" si="7"/>
-        <v>8.0939999999999994</v>
+        <f>ROUND(I4/R4,3)</f>
+        <v>8.7110000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1046,96 +1073,93 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" si="10"/>
-        <v>2.2487082328625561</v>
+        <f t="shared" si="1"/>
+        <v>2.2113642360805694</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="11"/>
-        <v>1.1292341256171776</v>
+        <f t="shared" si="2"/>
+        <v>1.0697070982496262</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" si="8"/>
-        <v>174.18</v>
+        <f t="shared" si="0"/>
+        <v>227.38000000000002</v>
       </c>
       <c r="E5" s="5">
-        <v>364.67</v>
+        <v>373.6</v>
       </c>
       <c r="F5" s="8">
-        <v>73.83</v>
+        <v>92.29</v>
       </c>
       <c r="G5" s="1">
-        <v>98.15</v>
+        <v>132.24</v>
       </c>
       <c r="H5" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.85</v>
       </c>
       <c r="I5" s="7">
-        <v>217.76</v>
+        <v>297.08999999999997</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="12"/>
-        <v>3.6280353200882991</v>
+        <v>2.7075782537067541</v>
       </c>
       <c r="L5" s="2">
-        <f t="shared" si="13"/>
-        <v>1.811258278145695</v>
+        <v>1.7306425041186162</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="9"/>
-        <v>9.0600000000000023</v>
+        <v>12.14</v>
       </c>
       <c r="N5" s="5">
-        <v>65.209999999999994</v>
+        <v>89.78</v>
       </c>
       <c r="O5" s="8">
-        <v>3.66</v>
+        <v>4.82</v>
       </c>
       <c r="P5" s="1">
-        <v>4.9400000000000004</v>
+        <v>6.71</v>
       </c>
       <c r="Q5" s="8">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="R5" s="7">
-        <v>26.2</v>
+        <v>34.090000000000003</v>
       </c>
       <c r="S5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.62</v>
+        <f>ROUND(B5/K5,3)</f>
+        <v>0.81699999999999995</v>
       </c>
       <c r="U5" s="2">
-        <f t="shared" si="1"/>
-        <v>0.623</v>
+        <f>ROUND(C5/L5,3)</f>
+        <v>0.61799999999999999</v>
       </c>
       <c r="V5" s="6">
-        <f t="shared" si="2"/>
-        <v>19.225000000000001</v>
+        <f>ROUND(D5/M5,3)</f>
+        <v>18.73</v>
       </c>
       <c r="W5" s="5">
-        <f t="shared" si="3"/>
-        <v>5.5919999999999996</v>
+        <f>ROUND(E5/N5,3)</f>
+        <v>4.1609999999999996</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="4"/>
-        <v>20.172000000000001</v>
+        <f>ROUND(F5/O5,3)</f>
+        <v>19.146999999999998</v>
       </c>
       <c r="Y5" s="1">
-        <f t="shared" si="5"/>
-        <v>19.867999999999999</v>
+        <f>ROUND(G5/P5,3)</f>
+        <v>19.707999999999998</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" si="6"/>
-        <v>4.7830000000000004</v>
+        <f>ROUND(H5/Q5,3)</f>
+        <v>4.6719999999999997</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" si="7"/>
-        <v>8.3109999999999999</v>
+        <f>ROUND(I5/R5,3)</f>
+        <v>8.7149999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1143,96 +1167,93 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" si="10"/>
-        <v>2.260779220779221</v>
+        <f t="shared" si="1"/>
+        <v>2.2125319017864999</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" si="11"/>
-        <v>1.0053679653679655</v>
+        <f t="shared" si="2"/>
+        <v>1.0005280295696561</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" si="8"/>
-        <v>173.25</v>
+        <f t="shared" si="0"/>
+        <v>227.26</v>
       </c>
       <c r="E6" s="5">
-        <v>355.68</v>
+        <v>372.01</v>
       </c>
       <c r="F6" s="8">
-        <v>73.319999999999993</v>
+        <v>93</v>
       </c>
       <c r="G6" s="8">
-        <v>97.66</v>
+        <v>131.47</v>
       </c>
       <c r="H6" s="8">
-        <v>2.27</v>
+        <v>2.79</v>
       </c>
       <c r="I6" s="3">
-        <v>79.650000000000006</v>
+        <v>112.14</v>
       </c>
       <c r="J6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="5">
-        <f t="shared" si="12"/>
-        <v>3.6280353200882995</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="L6" s="5">
-        <f t="shared" si="13"/>
-        <v>1.0000000000000002</v>
+        <v>1.0024772914946325</v>
       </c>
       <c r="M6" s="4">
-        <f t="shared" si="9"/>
-        <v>9.06</v>
+        <v>12.110000000000001</v>
       </c>
       <c r="N6" s="5">
-        <v>67.66</v>
+        <v>89.96</v>
       </c>
       <c r="O6" s="8">
-        <v>3.66</v>
+        <v>4.79</v>
       </c>
       <c r="P6" s="8">
-        <v>4.92</v>
+        <v>6.69</v>
       </c>
       <c r="Q6" s="8">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="R6" s="3">
-        <v>4.4800000000000004</v>
+        <v>6.1</v>
       </c>
       <c r="S6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="T6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.623</v>
+        <f>ROUND(B6/K6,3)</f>
+        <v>0.81499999999999995</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" si="1"/>
-        <v>1.0049999999999999</v>
+        <f>ROUND(C6/L6,3)</f>
+        <v>0.998</v>
       </c>
       <c r="V6" s="4">
-        <f t="shared" si="2"/>
-        <v>19.123000000000001</v>
+        <f>ROUND(D6/M6,3)</f>
+        <v>18.765999999999998</v>
       </c>
       <c r="W6" s="5">
-        <f t="shared" si="3"/>
-        <v>5.2569999999999997</v>
+        <f>ROUND(E6/N6,3)</f>
+        <v>4.1349999999999998</v>
       </c>
       <c r="X6" s="8">
-        <f t="shared" si="4"/>
-        <v>20.033000000000001</v>
+        <f>ROUND(F6/O6,3)</f>
+        <v>19.414999999999999</v>
       </c>
       <c r="Y6" s="8">
-        <f t="shared" si="5"/>
-        <v>19.850000000000001</v>
+        <f>ROUND(G6/P6,3)</f>
+        <v>19.652000000000001</v>
       </c>
       <c r="Z6" s="8">
-        <f t="shared" si="6"/>
-        <v>4.7290000000000001</v>
+        <f>ROUND(H6/Q6,3)</f>
+        <v>4.4290000000000003</v>
       </c>
       <c r="AA6" s="3">
-        <f t="shared" si="7"/>
-        <v>17.779</v>
+        <f>ROUND(I6/R6,3)</f>
+        <v>18.384</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1240,96 +1261,93 @@
         <v>5</v>
       </c>
       <c r="B7" s="5">
-        <f t="shared" si="10"/>
-        <v>2.1988435412339302</v>
+        <f t="shared" si="1"/>
+        <v>2.1726656008296241</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" si="11"/>
-        <v>0.97260427777465885</v>
+        <f t="shared" si="2"/>
+        <v>0.98198159270621777</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" si="8"/>
-        <v>178.13000000000002</v>
+        <f t="shared" si="0"/>
+        <v>231.43</v>
       </c>
       <c r="E7" s="5">
-        <v>361.32</v>
+        <v>524.05999999999995</v>
       </c>
       <c r="F7" s="8">
-        <v>79.7</v>
+        <v>98.24</v>
       </c>
       <c r="G7" s="8">
-        <v>97.35</v>
+        <v>131.75</v>
       </c>
       <c r="H7" s="1">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="I7" s="7">
-        <v>80.17</v>
+        <v>112.99</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="12"/>
-        <v>3.6932584269662918</v>
+        <v>2.81180496150556</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="13"/>
-        <v>1.0179775280898877</v>
+        <v>1.0359281437125749</v>
       </c>
       <c r="M7" s="4">
-        <f t="shared" si="9"/>
-        <v>8.9</v>
+        <v>11.69</v>
       </c>
       <c r="N7" s="5">
-        <v>76.17</v>
+        <v>100.86</v>
       </c>
       <c r="O7" s="8">
-        <v>3.68</v>
+        <v>4.71</v>
       </c>
       <c r="P7" s="8">
-        <v>5.03</v>
+        <v>6.71</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R7" s="7">
-        <v>4.4800000000000004</v>
+        <v>6.05</v>
       </c>
       <c r="S7" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.59499999999999997</v>
+        <f>ROUND(B7/K7,3)</f>
+        <v>0.77300000000000002</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" si="1"/>
-        <v>0.95499999999999996</v>
+        <f>ROUND(C7/L7,3)</f>
+        <v>0.94799999999999995</v>
       </c>
       <c r="V7" s="4">
-        <f t="shared" si="2"/>
-        <v>20.015000000000001</v>
+        <f>ROUND(D7/M7,3)</f>
+        <v>19.797000000000001</v>
       </c>
       <c r="W7" s="5">
-        <f t="shared" si="3"/>
-        <v>4.7439999999999998</v>
+        <f>ROUND(E7/N7,3)</f>
+        <v>5.1959999999999997</v>
       </c>
       <c r="X7" s="8">
-        <f t="shared" si="4"/>
-        <v>21.658000000000001</v>
+        <f>ROUND(F7/O7,3)</f>
+        <v>20.858000000000001</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" si="5"/>
-        <v>19.353999999999999</v>
+        <f>ROUND(G7/P7,3)</f>
+        <v>19.635000000000002</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" si="6"/>
-        <v>5.6840000000000002</v>
+        <f>ROUND(H7/Q7,3)</f>
+        <v>5.3330000000000002</v>
       </c>
       <c r="AA7" s="7">
-        <f t="shared" si="7"/>
-        <v>17.895</v>
+        <f>ROUND(I7/R7,3)</f>
+        <v>18.675999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1337,96 +1355,93 @@
         <v>6</v>
       </c>
       <c r="B8" s="5">
-        <f t="shared" si="10"/>
-        <v>2.1740674955595027</v>
+        <f t="shared" si="1"/>
+        <v>2.1582110052365007</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" si="11"/>
-        <v>0.98873223801065735</v>
+        <f t="shared" si="2"/>
+        <v>0.99334706841789</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" si="8"/>
-        <v>180.16</v>
+        <f t="shared" si="0"/>
+        <v>232.98</v>
       </c>
       <c r="E8" s="5">
-        <v>468.52</v>
+        <v>667.66</v>
       </c>
       <c r="F8" s="8">
-        <v>80.599999999999994</v>
+        <v>98.75</v>
       </c>
       <c r="G8" s="8">
-        <v>98.54</v>
+        <v>132.88</v>
       </c>
       <c r="H8" s="8">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="I8" s="7">
-        <v>82.18</v>
+        <v>114.88</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="12"/>
-        <v>3.7912341407151091</v>
+        <v>2.8287435456110153</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="13"/>
-        <v>1.0265282583621684</v>
+        <v>1.0060240963855422</v>
       </c>
       <c r="M8" s="4">
-        <f t="shared" si="9"/>
-        <v>8.67</v>
+        <v>11.62</v>
       </c>
       <c r="N8" s="5">
-        <v>89.32</v>
+        <v>121.4</v>
       </c>
       <c r="O8" s="8">
-        <v>3.56</v>
+        <v>4.75</v>
       </c>
       <c r="P8" s="8">
-        <v>4.93</v>
+        <v>6.6</v>
       </c>
       <c r="Q8" s="8">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="R8" s="7">
-        <v>4.4800000000000004</v>
+        <v>6.02</v>
       </c>
       <c r="S8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.57299999999999995</v>
+        <f>ROUND(B8/K8,3)</f>
+        <v>0.76300000000000001</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="1"/>
-        <v>0.96299999999999997</v>
+        <f>ROUND(C8/L8,3)</f>
+        <v>0.98699999999999999</v>
       </c>
       <c r="V8" s="4">
-        <f t="shared" si="2"/>
-        <v>20.78</v>
+        <f>ROUND(D8/M8,3)</f>
+        <v>20.05</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" si="3"/>
-        <v>5.2450000000000001</v>
+        <f>ROUND(E8/N8,3)</f>
+        <v>5.5</v>
       </c>
       <c r="X8" s="8">
-        <f t="shared" si="4"/>
-        <v>22.64</v>
+        <f>ROUND(F8/O8,3)</f>
+        <v>20.789000000000001</v>
       </c>
       <c r="Y8" s="8">
-        <f t="shared" si="5"/>
-        <v>19.988</v>
+        <f>ROUND(G8/P8,3)</f>
+        <v>20.132999999999999</v>
       </c>
       <c r="Z8" s="8">
-        <f t="shared" si="6"/>
-        <v>5.6669999999999998</v>
+        <f>ROUND(H8/Q8,3)</f>
+        <v>5</v>
       </c>
       <c r="AA8" s="7">
-        <f t="shared" si="7"/>
-        <v>18.344000000000001</v>
+        <f>ROUND(I8/R8,3)</f>
+        <v>19.082999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1434,96 +1449,93 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" si="10"/>
-        <v>2.2244434348023625</v>
+        <f t="shared" si="1"/>
+        <v>2.1661138155343984</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" si="11"/>
-        <v>1.0231712857791913</v>
+        <f t="shared" si="2"/>
+        <v>1.0036617412656701</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="8"/>
-        <v>176.08</v>
+        <f t="shared" si="0"/>
+        <v>232.13</v>
       </c>
       <c r="E9" s="5">
-        <v>465.99</v>
+        <v>669.91</v>
       </c>
       <c r="F9" s="8">
-        <v>78.61</v>
+        <v>100.22</v>
       </c>
       <c r="G9" s="8">
-        <v>96.48</v>
+        <v>130.52000000000001</v>
       </c>
       <c r="H9" s="8">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="I9" s="7">
-        <v>78.36</v>
+        <v>112.53</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="12"/>
-        <v>3.6002190580503837</v>
+        <v>2.81180496150556</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="13"/>
-        <v>0.94961664841182925</v>
+        <v>0.99401197604790414</v>
       </c>
       <c r="M9" s="4">
-        <f t="shared" si="9"/>
-        <v>9.129999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="N9" s="5">
-        <v>89.84</v>
+        <v>123.25</v>
       </c>
       <c r="O9" s="8">
-        <v>3.77</v>
+        <v>4.75</v>
       </c>
       <c r="P9" s="8">
-        <v>5.16</v>
+        <v>6.66</v>
       </c>
       <c r="Q9" s="8">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R9" s="7">
-        <v>4.67</v>
+        <v>6.05</v>
       </c>
       <c r="S9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="T9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.61799999999999999</v>
+        <f>ROUND(B9/K9,3)</f>
+        <v>0.77</v>
       </c>
       <c r="U9" s="5">
-        <f t="shared" si="1"/>
-        <v>1.077</v>
+        <f>ROUND(C9/L9,3)</f>
+        <v>1.01</v>
       </c>
       <c r="V9" s="4">
-        <f t="shared" si="2"/>
-        <v>19.286000000000001</v>
+        <f>ROUND(D9/M9,3)</f>
+        <v>19.856999999999999</v>
       </c>
       <c r="W9" s="5">
-        <f t="shared" si="3"/>
-        <v>5.1870000000000003</v>
+        <f>ROUND(E9/N9,3)</f>
+        <v>5.4349999999999996</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="4"/>
-        <v>20.850999999999999</v>
+        <f>ROUND(F9/O9,3)</f>
+        <v>21.099</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="5"/>
-        <v>18.698</v>
+        <f>ROUND(G9/P9,3)</f>
+        <v>19.597999999999999</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" si="6"/>
-        <v>4.95</v>
+        <f>ROUND(H9/Q9,3)</f>
+        <v>4.9640000000000004</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" si="7"/>
-        <v>16.779</v>
+        <f>ROUND(I9/R9,3)</f>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1531,96 +1543,93 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <f t="shared" si="10"/>
-        <v>2.2100095920555214</v>
+        <f t="shared" si="1"/>
+        <v>2.1769926830324287</v>
       </c>
       <c r="C10" s="5">
-        <f t="shared" si="11"/>
-        <v>0.99351125655927341</v>
+        <f t="shared" si="2"/>
+        <v>1.0050222972680436</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="8"/>
-        <v>177.23</v>
+        <f t="shared" si="0"/>
+        <v>230.96999999999997</v>
       </c>
       <c r="E10" s="2">
-        <v>241.42</v>
+        <v>338.85</v>
       </c>
       <c r="F10" s="8">
-        <v>79.81</v>
+        <v>98.21</v>
       </c>
       <c r="G10" s="8">
-        <v>96.38</v>
+        <v>131.38999999999999</v>
       </c>
       <c r="H10" s="8">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="I10" s="7">
-        <v>78.36</v>
+        <v>112.43</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="K10" s="5">
-        <f t="shared" si="12"/>
-        <v>3.6808510638297869</v>
+        <v>2.8458874458874459</v>
       </c>
       <c r="L10" s="5">
-        <f t="shared" si="13"/>
-        <v>1.0223964165733481</v>
+        <v>1.0121212121212122</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" si="9"/>
-        <v>8.93</v>
+        <v>11.549999999999999</v>
       </c>
       <c r="N10" s="2">
-        <v>77.58</v>
+        <v>101.72</v>
       </c>
       <c r="O10" s="8">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P10" s="8">
-        <v>5.08</v>
+        <v>6.57</v>
       </c>
       <c r="Q10" s="8">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R10" s="7">
-        <v>4.55</v>
+        <v>5.97</v>
       </c>
       <c r="S10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f>ROUND(B10/K10,3)</f>
+        <v>0.76500000000000001</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" si="1"/>
-        <v>0.97199999999999998</v>
+        <f>ROUND(C10/L10,3)</f>
+        <v>0.99299999999999999</v>
       </c>
       <c r="V10" s="4">
-        <f t="shared" si="2"/>
-        <v>19.847000000000001</v>
+        <f>ROUND(D10/M10,3)</f>
+        <v>19.997</v>
       </c>
       <c r="W10" s="2">
-        <f t="shared" si="3"/>
-        <v>3.1120000000000001</v>
+        <f>ROUND(E10/N10,3)</f>
+        <v>3.331</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" si="4"/>
-        <v>21.866</v>
+        <f>ROUND(F10/O10,3)</f>
+        <v>20.896000000000001</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" si="5"/>
-        <v>18.972000000000001</v>
+        <f>ROUND(G10/P10,3)</f>
+        <v>19.998000000000001</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" si="6"/>
-        <v>5.2</v>
+        <f>ROUND(H10/Q10,3)</f>
+        <v>4.8929999999999998</v>
       </c>
       <c r="AA10" s="7">
-        <f t="shared" si="7"/>
-        <v>17.222000000000001</v>
+        <f>ROUND(I10/R10,3)</f>
+        <v>18.832000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1628,96 +1637,93 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <f t="shared" si="10"/>
-        <v>2.7175466592659405</v>
+        <f t="shared" si="1"/>
+        <v>2.6913236632232507</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="11"/>
-        <v>1.2296537847776312</v>
+        <f t="shared" si="2"/>
+        <v>1.23625756034898</v>
       </c>
       <c r="D11" s="6">
-        <f t="shared" si="8"/>
-        <v>144.13</v>
+        <f t="shared" si="0"/>
+        <v>186.83</v>
       </c>
       <c r="E11" s="5">
-        <v>206.67</v>
+        <v>290.02999999999997</v>
       </c>
       <c r="F11" s="1">
-        <v>42.84</v>
+        <v>53.19</v>
       </c>
       <c r="G11" s="8">
-        <v>100.16</v>
+        <v>132.06</v>
       </c>
       <c r="H11" s="8">
-        <v>1.1299999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="I11" s="7">
-        <v>89.04</v>
+        <v>111.93</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" si="12"/>
-        <v>4.0183374083129584</v>
+        <v>3.1394460362941738</v>
       </c>
       <c r="L11" s="2">
-        <f t="shared" si="13"/>
-        <v>1.0916870415647921</v>
+        <v>1.1031518624641834</v>
       </c>
       <c r="M11" s="6">
-        <f t="shared" si="9"/>
-        <v>8.18</v>
+        <v>10.469999999999999</v>
       </c>
       <c r="N11" s="5">
-        <v>74.05</v>
+        <v>99.82</v>
       </c>
       <c r="O11" s="1">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="P11" s="8">
-        <v>6.57</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="Q11" s="8">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R11" s="7">
-        <v>6.04</v>
+        <v>7.81</v>
       </c>
       <c r="S11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="T11" s="2">
-        <f t="shared" si="0"/>
-        <v>0.67600000000000005</v>
+        <f>ROUND(B11/K11,3)</f>
+        <v>0.85699999999999998</v>
       </c>
       <c r="U11" s="2">
-        <f t="shared" si="1"/>
-        <v>1.1259999999999999</v>
+        <f>ROUND(C11/L11,3)</f>
+        <v>1.121</v>
       </c>
       <c r="V11" s="6">
-        <f t="shared" si="2"/>
-        <v>17.62</v>
+        <f>ROUND(D11/M11,3)</f>
+        <v>17.844000000000001</v>
       </c>
       <c r="W11" s="5">
-        <f t="shared" si="3"/>
-        <v>2.7909999999999999</v>
+        <f>ROUND(E11/N11,3)</f>
+        <v>2.9060000000000001</v>
       </c>
       <c r="X11" s="1">
-        <f t="shared" si="4"/>
-        <v>30.169</v>
+        <f>ROUND(F11/O11,3)</f>
+        <v>29.065999999999999</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" si="5"/>
-        <v>15.244999999999999</v>
+        <f>ROUND(G11/P11,3)</f>
+        <v>15.778</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" si="6"/>
-        <v>5.9470000000000001</v>
+        <f>ROUND(H11/Q11,3)</f>
+        <v>5.8520000000000003</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" si="7"/>
-        <v>14.742000000000001</v>
+        <f>ROUND(I11/R11,3)</f>
+        <v>14.332000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1725,873 +1731,1151 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" si="10"/>
-        <v>2.9690721649484533</v>
+        <f t="shared" si="1"/>
+        <v>2.9142227889185115</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="11"/>
-        <v>1.0925560946027895</v>
+        <f t="shared" si="2"/>
+        <v>1.0828213747536803</v>
       </c>
       <c r="D12" s="6">
-        <f t="shared" si="8"/>
-        <v>131.92000000000002</v>
+        <f t="shared" si="0"/>
+        <v>172.54</v>
       </c>
       <c r="E12" s="5">
-        <v>209.07</v>
+        <v>290.17</v>
       </c>
       <c r="F12" s="8">
-        <v>43.17</v>
+        <v>52.21</v>
       </c>
       <c r="G12" s="1">
-        <v>87.7</v>
+        <v>118.92</v>
       </c>
       <c r="H12" s="8">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="I12" s="3">
-        <v>71.48</v>
+        <v>93.93</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="K12" s="2">
-        <f t="shared" si="12"/>
-        <v>5.2009493670886071</v>
+        <v>3.853458382180539</v>
       </c>
       <c r="L12" s="2">
-        <f t="shared" si="13"/>
-        <v>1.2943037974683542</v>
+        <v>1.227432590855803</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" si="9"/>
-        <v>6.32</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="N12" s="5">
-        <v>73.63</v>
+        <v>100.42</v>
       </c>
       <c r="O12" s="8">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="P12" s="1">
-        <v>4.83</v>
+        <v>6.46</v>
       </c>
       <c r="Q12" s="8">
-        <v>0.19</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R12" s="3">
-        <v>4.04</v>
+        <v>5.44</v>
       </c>
       <c r="S12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="T12" s="2">
-        <f t="shared" si="0"/>
-        <v>0.57099999999999995</v>
+        <f>ROUND(B12/K12,3)</f>
+        <v>0.75600000000000001</v>
       </c>
       <c r="U12" s="2">
-        <f t="shared" si="1"/>
-        <v>0.84399999999999997</v>
+        <f>ROUND(C12/L12,3)</f>
+        <v>0.88200000000000001</v>
       </c>
       <c r="V12" s="6">
-        <f t="shared" si="2"/>
-        <v>20.873000000000001</v>
+        <f>ROUND(D12/M12,3)</f>
+        <v>20.227</v>
       </c>
       <c r="W12" s="5">
-        <f t="shared" si="3"/>
-        <v>2.839</v>
+        <f>ROUND(E12/N12,3)</f>
+        <v>2.89</v>
       </c>
       <c r="X12" s="8">
-        <f t="shared" si="4"/>
-        <v>33.207999999999998</v>
+        <f>ROUND(F12/O12,3)</f>
+        <v>29.167999999999999</v>
       </c>
       <c r="Y12" s="1">
-        <f t="shared" si="5"/>
-        <v>18.157</v>
+        <f>ROUND(G12/P12,3)</f>
+        <v>18.408999999999999</v>
       </c>
       <c r="Z12" s="8">
-        <f t="shared" si="6"/>
-        <v>5.5259999999999998</v>
+        <f>ROUND(H12/Q12,3)</f>
+        <v>5.0359999999999996</v>
       </c>
       <c r="AA12" s="3">
-        <f t="shared" si="7"/>
-        <v>17.693000000000001</v>
+        <f>ROUND(I12/R12,3)</f>
+        <v>17.266999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" ref="B13:B14" si="14">D$2/D13</f>
-        <v>3.3684210526315788</v>
+        <f t="shared" ref="B13:B14" si="3">D$2/D13</f>
+        <v>3.3354560530679929</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" ref="C13:C14" si="15">D12/D13</f>
-        <v>1.1345029239766082</v>
+        <f t="shared" ref="C13:C14" si="4">D12/D13</f>
+        <v>1.1445439469320067</v>
       </c>
       <c r="D13" s="6">
-        <f t="shared" si="8"/>
-        <v>116.28</v>
+        <f t="shared" si="0"/>
+        <v>150.75</v>
       </c>
       <c r="E13" s="5">
-        <v>221.39</v>
+        <v>292.87</v>
       </c>
       <c r="F13" s="1">
-        <v>25.59</v>
+        <v>30.74</v>
       </c>
       <c r="G13" s="8">
-        <v>89.09</v>
+        <v>118.51</v>
       </c>
       <c r="H13" s="8">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="7">
-        <v>71.73</v>
+        <v>94.27</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" ref="K13:K14" si="16">M$2/M13</f>
-        <v>5.6188034188034184</v>
+        <v>4.1345911949685537</v>
       </c>
       <c r="L13" s="2">
-        <f t="shared" ref="L13:L14" si="17">M12/M13</f>
-        <v>1.0803418803418805</v>
+        <v>1.0729559748427673</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="9"/>
-        <v>5.85</v>
+        <v>7.9499999999999993</v>
       </c>
       <c r="N13" s="5">
-        <v>75.28</v>
+        <v>101.89</v>
       </c>
       <c r="O13" s="1">
-        <v>0.89</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P13" s="8">
-        <v>4.7699999999999996</v>
+        <v>6.52</v>
       </c>
       <c r="Q13" s="8">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R13" s="7">
-        <v>4</v>
+        <v>5.47</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T13" s="2">
-        <f t="shared" si="0"/>
-        <v>0.59899999999999998</v>
+        <f>ROUND(B13/K13,3)</f>
+        <v>0.80700000000000005</v>
       </c>
       <c r="U13" s="2">
-        <f t="shared" si="1"/>
-        <v>1.05</v>
+        <f>ROUND(C13/L13,3)</f>
+        <v>1.0669999999999999</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" si="2"/>
-        <v>19.876999999999999</v>
+        <f>ROUND(D13/M13,3)</f>
+        <v>18.962</v>
       </c>
       <c r="W13" s="5">
-        <f t="shared" si="3"/>
-        <v>2.9409999999999998</v>
+        <f>ROUND(E13/N13,3)</f>
+        <v>2.8740000000000001</v>
       </c>
       <c r="X13" s="1">
-        <f t="shared" si="4"/>
-        <v>28.753</v>
+        <f>ROUND(F13/O13,3)</f>
+        <v>26.5</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="5"/>
-        <v>18.677</v>
+        <f>ROUND(G13/P13,3)</f>
+        <v>18.175999999999998</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="6"/>
-        <v>8.4209999999999994</v>
+        <f>ROUND(H13/Q13,3)</f>
+        <v>5.556</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" si="7"/>
-        <v>17.933</v>
+        <f>ROUND(I13/R13,3)</f>
+        <v>17.234000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="5">
-        <f t="shared" si="14"/>
-        <v>3.3888215954317356</v>
+        <f t="shared" si="3"/>
+        <v>3.3443298969072162</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" si="15"/>
-        <v>1.0060564111437966</v>
+        <f t="shared" si="4"/>
+        <v>1.0026604589291652</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="8"/>
-        <v>115.58</v>
+        <f t="shared" si="0"/>
+        <v>150.35</v>
       </c>
       <c r="E14" s="5">
-        <v>210.13</v>
+        <v>293.14</v>
       </c>
       <c r="F14" s="1">
-        <v>25.46</v>
+        <v>30.84</v>
       </c>
       <c r="G14" s="8">
-        <v>89.08</v>
+        <v>118.09</v>
       </c>
       <c r="H14" s="8">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="I14" s="7">
-        <v>72.56</v>
+        <v>93.68</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K14" s="5">
-        <f t="shared" si="16"/>
-        <v>5.7165217391304344</v>
+        <v>4.2087067861715743</v>
       </c>
       <c r="L14" s="5">
-        <f t="shared" si="17"/>
-        <v>1.017391304347826</v>
+        <v>1.0179257362355951</v>
       </c>
       <c r="M14" s="4">
-        <f t="shared" si="9"/>
-        <v>5.75</v>
+        <v>7.8100000000000005</v>
       </c>
       <c r="N14" s="5">
-        <v>73.13</v>
+        <v>100.03</v>
       </c>
       <c r="O14" s="1">
-        <v>0.84</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P14" s="8">
-        <v>4.72</v>
+        <v>6.41</v>
       </c>
       <c r="Q14" s="8">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R14" s="7">
-        <v>3.94</v>
+        <v>5.35</v>
       </c>
       <c r="S14" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.59299999999999997</v>
+        <f>ROUND(B14/K14,3)</f>
+        <v>0.79500000000000004</v>
       </c>
       <c r="U14" s="5">
-        <f t="shared" si="1"/>
-        <v>0.98899999999999999</v>
+        <f>ROUND(C14/L14,3)</f>
+        <v>0.98499999999999999</v>
       </c>
       <c r="V14" s="4">
-        <f t="shared" si="2"/>
-        <v>20.100999999999999</v>
+        <f>ROUND(D14/M14,3)</f>
+        <v>19.251000000000001</v>
       </c>
       <c r="W14" s="5">
-        <f t="shared" si="3"/>
-        <v>2.8730000000000002</v>
+        <f>ROUND(E14/N14,3)</f>
+        <v>2.931</v>
       </c>
       <c r="X14" s="1">
-        <f t="shared" si="4"/>
-        <v>30.31</v>
+        <f>ROUND(F14/O14,3)</f>
+        <v>27.292000000000002</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" si="5"/>
-        <v>18.873000000000001</v>
+        <f>ROUND(G14/P14,3)</f>
+        <v>18.422999999999998</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="6"/>
-        <v>5.4740000000000002</v>
+        <f>ROUND(H14/Q14,3)</f>
+        <v>5.2590000000000003</v>
       </c>
       <c r="AA14" s="7">
-        <f t="shared" si="7"/>
-        <v>18.416</v>
+        <f>ROUND(I14/R14,3)</f>
+        <v>17.510000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2">
-        <f t="shared" ref="B15" si="18">D$2/D15</f>
-        <v>4.0077765271666834</v>
+        <f t="shared" ref="B15" si="5">D$2/D15</f>
+        <v>4.2789549825546755</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15" si="19">D14/D15</f>
-        <v>1.1826460656911899</v>
+        <f t="shared" ref="C15" si="6">D14/D15</f>
+        <v>1.2794655773976682</v>
       </c>
       <c r="D15" s="6">
-        <f>SUM(F15:H15)</f>
-        <v>97.73</v>
+        <f t="shared" ref="D15:D20" si="7">SUM(F15:H15)</f>
+        <v>117.51</v>
       </c>
       <c r="E15" s="5">
-        <v>209.57</v>
+        <v>298.74</v>
       </c>
       <c r="F15" s="8">
-        <v>26.2</v>
+        <v>30.98</v>
       </c>
       <c r="G15" s="1">
-        <v>70.55</v>
+        <v>85.1</v>
       </c>
       <c r="H15" s="8">
-        <v>0.98</v>
+        <v>1.43</v>
       </c>
       <c r="I15" s="3">
-        <v>50.26</v>
+        <v>64.790000000000006</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" ref="K15" si="20">M$2/M15</f>
-        <v>6.0422794117647047</v>
+        <v>4.533793103448275</v>
       </c>
       <c r="L15" s="2">
-        <f t="shared" ref="L15" si="21">M14/M15</f>
-        <v>1.056985294117647</v>
+        <v>1.0772413793103448</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="9"/>
-        <v>5.44</v>
+        <v>7.2500000000000009</v>
       </c>
       <c r="N15" s="5">
-        <v>75.37</v>
+        <v>99.74</v>
       </c>
       <c r="O15" s="8">
-        <v>0.87</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P15" s="1">
-        <v>4.37</v>
+        <v>5.82</v>
       </c>
       <c r="Q15" s="8">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R15" s="3">
-        <v>3.76</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="S15" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T15" s="2">
-        <f t="shared" si="0"/>
-        <v>0.66300000000000003</v>
+        <f>ROUND(B15/K15,3)</f>
+        <v>0.94399999999999995</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" si="1"/>
-        <v>1.119</v>
+        <f>ROUND(C15/L15,3)</f>
+        <v>1.1879999999999999</v>
       </c>
       <c r="V15" s="6">
-        <f t="shared" si="2"/>
-        <v>17.965</v>
+        <f>ROUND(D15/M15,3)</f>
+        <v>16.207999999999998</v>
       </c>
       <c r="W15" s="5">
-        <f t="shared" ref="W15:AA19" si="22">ROUND(E15/N15,3)</f>
-        <v>2.7810000000000001</v>
+        <f>ROUND(E15/N15,3)</f>
+        <v>2.9950000000000001</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" si="22"/>
-        <v>30.114999999999998</v>
+        <f>ROUND(F15/O15,3)</f>
+        <v>26.939</v>
       </c>
       <c r="Y15" s="1">
-        <f t="shared" si="22"/>
-        <v>16.143999999999998</v>
+        <f>ROUND(G15/P15,3)</f>
+        <v>14.622</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="22"/>
-        <v>4.9000000000000004</v>
+        <f>ROUND(H15/Q15,3)</f>
+        <v>5.1070000000000002</v>
       </c>
       <c r="AA15" s="3">
-        <f t="shared" si="22"/>
-        <v>13.367000000000001</v>
+        <f>ROUND(I15/R15,3)</f>
+        <v>12.804</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" ref="B16" si="23">D$2/D16</f>
-        <v>4.0634920634920633</v>
+        <f t="shared" ref="B16" si="8">D$2/D16</f>
+        <v>4.3257054370268406</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16" si="24">D15/D16</f>
-        <v>1.0139018570391121</v>
+        <f t="shared" ref="C16" si="9">D15/D16</f>
+        <v>1.0109256710254646</v>
       </c>
       <c r="D16" s="4">
-        <f>SUM(F16:H16)</f>
-        <v>96.39</v>
+        <f t="shared" si="7"/>
+        <v>116.24</v>
       </c>
       <c r="E16" s="1">
-        <v>208.68</v>
+        <v>293.04000000000002</v>
       </c>
       <c r="F16" s="8">
-        <v>25.49</v>
+        <v>30.81</v>
       </c>
       <c r="G16" s="8">
-        <v>69.89</v>
+        <v>83.82</v>
       </c>
       <c r="H16" s="8">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="I16" s="7">
-        <v>49.77</v>
+        <v>63.86</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16" si="25">M$2/M16</f>
-        <v>6.1210428305400368</v>
+        <v>4.5589459084604709</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16" si="26">M15/M16</f>
-        <v>1.0130353817504656</v>
+        <v>1.0055478502080446</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" si="9"/>
-        <v>5.37</v>
+        <v>7.21</v>
       </c>
       <c r="N16" s="1">
-        <v>10.34</v>
+        <v>13.94</v>
       </c>
       <c r="O16" s="8">
-        <v>0.8</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P16" s="8">
-        <v>4.37</v>
+        <v>5.8</v>
       </c>
       <c r="Q16" s="8">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R16" s="7">
-        <v>3.7</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="S16" s="18" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.66400000000000003</v>
+        <f>ROUND(B16/K16,3)</f>
+        <v>0.94899999999999995</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" si="1"/>
-        <v>1.0009999999999999</v>
+        <f>ROUND(C16/L16,3)</f>
+        <v>1.0049999999999999</v>
       </c>
       <c r="V16" s="4">
-        <f t="shared" si="2"/>
-        <v>17.95</v>
+        <f>ROUND(D16/M16,3)</f>
+        <v>16.122</v>
       </c>
       <c r="W16" s="1">
-        <f t="shared" si="22"/>
-        <v>20.181999999999999</v>
+        <f>ROUND(E16/N16,3)</f>
+        <v>21.021999999999998</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="22"/>
-        <v>31.863</v>
+        <f>ROUND(F16/O16,3)</f>
+        <v>27.265000000000001</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" si="22"/>
-        <v>15.993</v>
+        <f>ROUND(G16/P16,3)</f>
+        <v>14.452</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" si="22"/>
-        <v>5.05</v>
+        <f>ROUND(H16/Q16,3)</f>
+        <v>5.75</v>
       </c>
       <c r="AA16" s="7">
-        <f t="shared" si="22"/>
-        <v>13.451000000000001</v>
+        <f>ROUND(I16/R16,3)</f>
+        <v>12.721</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5">
-        <f t="shared" ref="B17" si="27">D$2/D17</f>
-        <v>4.0945013589797208</v>
+        <f t="shared" ref="B17" si="10">D$2/D17</f>
+        <v>4.3421416234887733</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17" si="28">D16/D17</f>
-        <v>1.0076311938114155</v>
+        <f t="shared" ref="C17" si="11">D16/D17</f>
+        <v>1.0037996545768566</v>
       </c>
       <c r="D17" s="4">
-        <f>SUM(F17:H17)</f>
-        <v>95.659999999999982</v>
+        <f t="shared" si="7"/>
+        <v>115.8</v>
       </c>
       <c r="E17" s="19">
-        <v>205.93</v>
+        <v>293.16000000000003</v>
       </c>
       <c r="F17" s="19">
-        <v>24.74</v>
+        <v>30.57</v>
       </c>
       <c r="G17" s="14">
-        <v>69.959999999999994</v>
+        <v>83.77</v>
       </c>
       <c r="H17" s="19">
-        <v>0.96</v>
+        <v>1.46</v>
       </c>
       <c r="I17" s="19">
-        <v>48.83</v>
+        <v>64.06</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" ref="K17" si="29">M$2/M17</f>
-        <v>7.2083333333333321</v>
+        <v>4.957767722473605</v>
       </c>
       <c r="L17" s="5">
-        <f t="shared" ref="L17" si="30">M16/M17</f>
-        <v>1.1776315789473684</v>
+        <v>1.0874811463046758</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" ref="M17" si="31">SUM(O17:Q17)</f>
-        <v>4.5600000000000005</v>
+        <v>6.629999999999999</v>
       </c>
       <c r="N17" s="19">
-        <v>10.66</v>
+        <v>13.86</v>
       </c>
       <c r="O17" s="19">
-        <v>0.82</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P17" s="14">
-        <v>3.55</v>
+        <v>5.21</v>
       </c>
       <c r="Q17" s="19">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R17" s="19">
-        <v>2.95</v>
+        <v>4.26</v>
       </c>
       <c r="S17" s="18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" ref="T17" si="32">ROUND(B17/K17,3)</f>
-        <v>0.56799999999999995</v>
+        <f>ROUND(B17/K17,3)</f>
+        <v>0.876</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" ref="U17" si="33">ROUND(C17/L17,3)</f>
-        <v>0.85599999999999998</v>
+        <f>ROUND(C17/L17,3)</f>
+        <v>0.92300000000000004</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" ref="V17" si="34">ROUND(D17/M17,3)</f>
-        <v>20.978000000000002</v>
+        <f>ROUND(D17/M17,3)</f>
+        <v>17.466000000000001</v>
       </c>
       <c r="W17" s="19">
-        <f t="shared" si="22"/>
-        <v>19.318000000000001</v>
+        <f>ROUND(E17/N17,3)</f>
+        <v>21.152000000000001</v>
       </c>
       <c r="X17" s="19">
-        <f t="shared" si="22"/>
-        <v>30.170999999999999</v>
+        <f>ROUND(F17/O17,3)</f>
+        <v>26.582999999999998</v>
       </c>
       <c r="Y17" s="14">
-        <f t="shared" si="22"/>
-        <v>19.707000000000001</v>
+        <f>ROUND(G17/P17,3)</f>
+        <v>16.079000000000001</v>
       </c>
       <c r="Z17" s="19">
-        <f t="shared" si="22"/>
-        <v>5.0529999999999999</v>
+        <f>ROUND(H17/Q17,3)</f>
+        <v>5.407</v>
       </c>
       <c r="AA17" s="19">
-        <f t="shared" si="22"/>
-        <v>16.553000000000001</v>
+        <f>ROUND(I17/R17,3)</f>
+        <v>15.038</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5">
-        <f t="shared" ref="B18" si="35">D$2/D18</f>
-        <v>4.0685571829230289</v>
+        <f t="shared" ref="B18" si="12">D$2/D18</f>
+        <v>4.3432668221473598</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18" si="36">D17/D18</f>
-        <v>0.99366365430559866</v>
+        <f t="shared" ref="C18" si="13">D17/D18</f>
+        <v>1.0002591344908005</v>
       </c>
       <c r="D18" s="4">
-        <f>SUM(F18:H18)</f>
-        <v>96.27</v>
+        <f t="shared" si="7"/>
+        <v>115.77000000000001</v>
       </c>
       <c r="E18" s="19">
-        <v>204.06</v>
+        <v>298.27</v>
       </c>
       <c r="F18" s="19">
-        <v>25.06</v>
+        <v>30.43</v>
       </c>
       <c r="G18" s="14">
-        <v>70.22</v>
+        <v>83.93</v>
       </c>
       <c r="H18" s="19">
-        <v>0.99</v>
+        <v>1.41</v>
       </c>
       <c r="I18" s="15">
-        <v>49.89</v>
+        <v>63.83</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="5">
-        <f t="shared" ref="K18" si="37">M$2/M18</f>
-        <v>7.6264501160092797</v>
+        <v>5.3621533442088092</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" ref="L18" si="38">M17/M18</f>
-        <v>1.0580046403712298</v>
+        <v>1.0815660685154975</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" ref="M18" si="39">SUM(O18:Q18)</f>
-        <v>4.3100000000000005</v>
+        <v>6.129999999999999</v>
       </c>
       <c r="N18" s="19">
-        <v>10.47</v>
+        <v>13.93</v>
       </c>
       <c r="O18" s="19">
-        <v>0.82</v>
+        <v>1.18</v>
       </c>
       <c r="P18" s="14">
-        <v>3.3</v>
+        <v>4.68</v>
       </c>
       <c r="Q18" s="19">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R18" s="15">
-        <v>2.63</v>
+        <v>3.98</v>
       </c>
       <c r="S18" s="18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18" si="40">ROUND(B18/K18,3)</f>
-        <v>0.53300000000000003</v>
+        <f>ROUND(B18/K18,3)</f>
+        <v>0.81</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" ref="U18" si="41">ROUND(C18/L18,3)</f>
-        <v>0.93899999999999995</v>
+        <f>ROUND(C18/L18,3)</f>
+        <v>0.92500000000000004</v>
       </c>
       <c r="V18" s="4">
-        <f t="shared" ref="V18" si="42">ROUND(D18/M18,3)</f>
-        <v>22.335999999999999</v>
+        <f>ROUND(D18/M18,3)</f>
+        <v>18.885999999999999</v>
       </c>
       <c r="W18" s="19">
-        <f t="shared" si="22"/>
-        <v>19.489999999999998</v>
+        <f>ROUND(E18/N18,3)</f>
+        <v>21.411999999999999</v>
       </c>
       <c r="X18" s="19">
-        <f t="shared" si="22"/>
-        <v>30.561</v>
+        <f>ROUND(F18/O18,3)</f>
+        <v>25.788</v>
       </c>
       <c r="Y18" s="14">
-        <f t="shared" si="22"/>
-        <v>21.279</v>
+        <f>ROUND(G18/P18,3)</f>
+        <v>17.934000000000001</v>
       </c>
       <c r="Z18" s="19">
-        <f t="shared" si="22"/>
-        <v>5.2110000000000003</v>
+        <f>ROUND(H18/Q18,3)</f>
+        <v>5.2220000000000004</v>
       </c>
       <c r="AA18" s="15">
-        <f t="shared" si="22"/>
-        <v>18.97</v>
+        <f>ROUND(I18/R18,3)</f>
+        <v>16.038</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5">
-        <f t="shared" ref="B19" si="43">D$2/D19</f>
-        <v>4.184615384615384</v>
+        <f t="shared" ref="B19" si="14">D$2/D19</f>
+        <v>4.4906671429847274</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19" si="44">D18/D19</f>
-        <v>1.0285256410256409</v>
+        <f t="shared" ref="C19" si="15">D18/D19</f>
+        <v>1.0339376618737164</v>
       </c>
       <c r="D19" s="4">
-        <f>SUM(F19:H19)</f>
-        <v>93.600000000000009</v>
+        <f t="shared" si="7"/>
+        <v>111.97</v>
       </c>
       <c r="E19" s="9">
-        <v>210.23</v>
+        <v>292.86</v>
       </c>
       <c r="F19" s="9">
-        <v>26.34</v>
+        <v>30.8</v>
       </c>
       <c r="G19" s="14">
-        <v>66.260000000000005</v>
+        <v>79.72</v>
       </c>
       <c r="H19" s="9">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="I19" s="10">
-        <v>50.19</v>
+        <v>62.95</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" ref="K19" si="45">M$2/M19</f>
-        <v>8.3426395939086291</v>
+        <v>6.0870370370370361</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" ref="L19" si="46">M18/M19</f>
-        <v>1.0939086294416245</v>
+        <v>1.1351851851851849</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" ref="M19" si="47">SUM(O19:Q19)</f>
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="N19" s="9">
-        <v>10.27</v>
+        <v>13.88</v>
       </c>
       <c r="O19" s="9">
-        <v>0.84</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P19" s="14">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q19" s="9">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="R19" s="10">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="S19" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T19" s="5">
-        <f t="shared" ref="T19" si="48">ROUND(B19/K19,3)</f>
-        <v>0.502</v>
+        <f>ROUND(B19/K19,3)</f>
+        <v>0.73799999999999999</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" ref="U19" si="49">ROUND(C19/L19,3)</f>
-        <v>0.94</v>
+        <f>ROUND(C19/L19,3)</f>
+        <v>0.91100000000000003</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" ref="V19" si="50">ROUND(D19/M19,3)</f>
-        <v>23.756</v>
-      </c>
-      <c r="W19" s="19">
-        <f t="shared" si="22"/>
-        <v>20.47</v>
-      </c>
-      <c r="X19" s="19">
-        <f t="shared" si="22"/>
-        <v>31.356999999999999</v>
+        <f>ROUND(D19/M19,3)</f>
+        <v>20.734999999999999</v>
+      </c>
+      <c r="W19" s="9">
+        <f>ROUND(E19/N19,3)</f>
+        <v>21.099</v>
+      </c>
+      <c r="X19" s="9">
+        <f>ROUND(F19/O19,3)</f>
+        <v>26.552</v>
       </c>
       <c r="Y19" s="14">
-        <f t="shared" si="22"/>
-        <v>22.692</v>
-      </c>
-      <c r="Z19" s="19">
-        <f t="shared" si="22"/>
-        <v>5.556</v>
-      </c>
-      <c r="AA19" s="20">
-        <f t="shared" si="22"/>
-        <v>20.076000000000001</v>
+        <f>ROUND(G19/P19,3)</f>
+        <v>20.081</v>
+      </c>
+      <c r="Z19" s="9">
+        <f>ROUND(H19/Q19,3)</f>
+        <v>5.37</v>
+      </c>
+      <c r="AA19" s="10">
+        <f>ROUND(I19/R19,3)</f>
+        <v>17.731999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5">
-        <f t="shared" ref="B20" si="51">D$2/D20</f>
-        <v>4.8278072229754709</v>
+        <f t="shared" ref="B20" si="16">D$2/D20</f>
+        <v>4.9858205255329686</v>
       </c>
       <c r="C20" s="5">
-        <f t="shared" ref="C20" si="52">D19/D20</f>
-        <v>1.15370393196105</v>
+        <f t="shared" ref="C20" si="17">D19/D20</f>
+        <v>1.1102627664848785</v>
       </c>
       <c r="D20" s="4">
-        <f>SUM(F20:H20)</f>
-        <v>81.13000000000001</v>
+        <f t="shared" si="7"/>
+        <v>100.85000000000001</v>
       </c>
       <c r="E20" s="9">
-        <v>208.06</v>
+        <v>297.58999999999997</v>
       </c>
       <c r="F20" s="9">
-        <v>24.71</v>
+        <v>30.73</v>
       </c>
       <c r="G20" s="14">
-        <v>55.38</v>
+        <v>68.73</v>
       </c>
       <c r="H20" s="9">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="I20" s="15">
-        <v>42.98</v>
+        <v>54.16</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K20" s="5">
-        <f t="shared" ref="K20" si="53">M$2/M20</f>
-        <v>8.2795969773299749</v>
+        <v>6.0870370370370361</v>
       </c>
       <c r="L20" s="5">
-        <f t="shared" ref="L20" si="54">M19/M20</f>
-        <v>0.9924433249370278</v>
+        <v>1</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" ref="M20" si="55">SUM(O20:Q20)</f>
-        <v>3.9699999999999998</v>
+        <v>5.4</v>
       </c>
       <c r="N20" s="9">
-        <v>10.65</v>
+        <v>13.8</v>
       </c>
       <c r="O20" s="9">
-        <v>0.88</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P20" s="14">
-        <v>2.9</v>
+        <v>3.99</v>
       </c>
       <c r="Q20" s="9">
-        <v>0.19</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R20" s="15">
-        <v>2.52</v>
+        <v>3.54</v>
       </c>
       <c r="S20" s="18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T20" s="5">
-        <f t="shared" ref="T20" si="56">ROUND(B20/K20,3)</f>
-        <v>0.58299999999999996</v>
+        <f>ROUND(B20/K20,3)</f>
+        <v>0.81899999999999995</v>
       </c>
       <c r="U20" s="5">
-        <f t="shared" ref="U20" si="57">ROUND(C20/L20,3)</f>
-        <v>1.1619999999999999</v>
+        <f>ROUND(C20/L20,3)</f>
+        <v>1.1100000000000001</v>
       </c>
       <c r="V20" s="4">
-        <f t="shared" ref="V20" si="58">ROUND(D20/M20,3)</f>
-        <v>20.436</v>
-      </c>
-      <c r="W20" s="19">
-        <f t="shared" ref="W20" si="59">ROUND(E20/N20,3)</f>
-        <v>19.536000000000001</v>
-      </c>
-      <c r="X20" s="19">
-        <f t="shared" ref="X20" si="60">ROUND(F20/O20,3)</f>
-        <v>28.08</v>
+        <f>ROUND(D20/M20,3)</f>
+        <v>18.675999999999998</v>
+      </c>
+      <c r="W20" s="9">
+        <f>ROUND(E20/N20,3)</f>
+        <v>21.564</v>
+      </c>
+      <c r="X20" s="9">
+        <f>ROUND(F20/O20,3)</f>
+        <v>27.195</v>
       </c>
       <c r="Y20" s="14">
-        <f t="shared" ref="Y20" si="61">ROUND(G20/P20,3)</f>
-        <v>19.097000000000001</v>
-      </c>
-      <c r="Z20" s="19">
-        <f t="shared" ref="Z20" si="62">ROUND(H20/Q20,3)</f>
-        <v>5.4740000000000002</v>
+        <f>ROUND(G20/P20,3)</f>
+        <v>17.225999999999999</v>
+      </c>
+      <c r="Z20" s="9">
+        <f>ROUND(H20/Q20,3)</f>
+        <v>4.9640000000000004</v>
       </c>
       <c r="AA20" s="15">
-        <f t="shared" ref="AA20" si="63">ROUND(I20/R20,3)</f>
-        <v>17.056000000000001</v>
-      </c>
+        <f>ROUND(I20/R20,3)</f>
+        <v>15.298999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="5">
+        <f t="shared" ref="B21:B23" si="18">D$2/D21</f>
+        <v>7.0206646188215585</v>
+      </c>
+      <c r="C21" s="5">
+        <f t="shared" ref="C21:C23" si="19">D20/D21</f>
+        <v>1.4081262217257753</v>
+      </c>
+      <c r="D21" s="4">
+        <f t="shared" ref="D21:D23" si="20">SUM(F21:H21)</f>
+        <v>71.61999999999999</v>
+      </c>
+      <c r="E21" s="14">
+        <v>308.72000000000003</v>
+      </c>
+      <c r="F21" s="14">
+        <v>27.33</v>
+      </c>
+      <c r="G21" s="14">
+        <v>43.3</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0.99</v>
+      </c>
+      <c r="I21" s="15">
+        <v>35.18</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="5">
+        <v>7.5389908256880727</v>
+      </c>
+      <c r="L21" s="5">
+        <v>1.238532110091743</v>
+      </c>
+      <c r="M21" s="4">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="N21" s="14">
+        <v>11.45</v>
+      </c>
+      <c r="O21" s="14">
+        <v>0.85</v>
+      </c>
+      <c r="P21" s="14">
+        <v>3.28</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>0.23</v>
+      </c>
+      <c r="R21" s="15">
+        <v>3.08</v>
+      </c>
+      <c r="S21" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" s="5">
+        <f t="shared" ref="T21:T23" si="21">ROUND(B21/K21,3)</f>
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="U21" s="5">
+        <f t="shared" ref="U21:U23" si="22">ROUND(C21/L21,3)</f>
+        <v>1.137</v>
+      </c>
+      <c r="V21" s="4">
+        <f t="shared" ref="V21:V23" si="23">ROUND(D21/M21,3)</f>
+        <v>16.427</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" ref="W21:W23" si="24">ROUND(E21/N21,3)</f>
+        <v>26.962</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" ref="X21:X23" si="25">ROUND(F21/O21,3)</f>
+        <v>32.152999999999999</v>
+      </c>
+      <c r="Y21" s="14">
+        <f t="shared" ref="Y21:Y23" si="26">ROUND(G21/P21,3)</f>
+        <v>13.201000000000001</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" ref="Z21:Z23" si="27">ROUND(H21/Q21,3)</f>
+        <v>4.3040000000000003</v>
+      </c>
+      <c r="AA21" s="15">
+        <f t="shared" ref="AA21:AA23" si="28">ROUND(I21/R21,3)</f>
+        <v>11.422000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="5">
+        <f t="shared" si="18"/>
+        <v>9.6566160937199896</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="19"/>
+        <v>1.3754561167658916</v>
+      </c>
+      <c r="D22" s="4">
+        <f t="shared" si="20"/>
+        <v>52.070000000000007</v>
+      </c>
+      <c r="E22" s="14">
+        <v>310.76</v>
+      </c>
+      <c r="F22" s="14">
+        <v>27.44</v>
+      </c>
+      <c r="G22" s="14">
+        <v>23.6</v>
+      </c>
+      <c r="H22" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="I22" s="15">
+        <v>21.37</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="5">
+        <v>9.3380681818181817</v>
+      </c>
+      <c r="L22" s="5">
+        <v>1.2386363636363638</v>
+      </c>
+      <c r="M22" s="4">
+        <v>3.52</v>
+      </c>
+      <c r="N22" s="9">
+        <v>11.2</v>
+      </c>
+      <c r="O22" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="P22" s="14">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="R22" s="14">
+        <v>2.16</v>
+      </c>
+      <c r="S22" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" s="5">
+        <f t="shared" si="21"/>
+        <v>1.034</v>
+      </c>
+      <c r="U22" s="5">
+        <f t="shared" si="22"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="V22" s="4">
+        <f t="shared" si="23"/>
+        <v>14.792999999999999</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="24"/>
+        <v>27.745999999999999</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="25"/>
+        <v>32.667000000000002</v>
+      </c>
+      <c r="Y22" s="14">
+        <f t="shared" si="26"/>
+        <v>9.6329999999999991</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="27"/>
+        <v>4.4779999999999998</v>
+      </c>
+      <c r="AA22" s="15">
+        <f t="shared" si="28"/>
+        <v>9.8940000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="5">
+        <f t="shared" si="18"/>
+        <v>9.5829998094149023</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" si="19"/>
+        <v>0.99237659615018103</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" si="20"/>
+        <v>52.470000000000006</v>
+      </c>
+      <c r="E23" s="19">
+        <v>313.47000000000003</v>
+      </c>
+      <c r="F23" s="19">
+        <v>27.85</v>
+      </c>
+      <c r="G23" s="19">
+        <v>23.63</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0.99</v>
+      </c>
+      <c r="I23" s="20">
+        <v>21.36</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1.4448351648351647</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0.15472527472527473</v>
+      </c>
+      <c r="M23" s="4">
+        <v>22.75</v>
+      </c>
+      <c r="N23" s="9">
+        <v>11.41</v>
+      </c>
+      <c r="O23" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="P23" s="9">
+        <v>21.69</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>0.22</v>
+      </c>
+      <c r="R23" s="9">
+        <v>21.18</v>
+      </c>
+      <c r="S23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="21"/>
+        <v>6.633</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="22"/>
+        <v>6.4139999999999997</v>
+      </c>
+      <c r="V23" s="4">
+        <f t="shared" si="23"/>
+        <v>2.306</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="24"/>
+        <v>27.472999999999999</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="25"/>
+        <v>33.155000000000001</v>
+      </c>
+      <c r="Y23" s="14">
+        <f t="shared" si="26"/>
+        <v>1.089</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="27"/>
+        <v>4.5</v>
+      </c>
+      <c r="AA23" s="15">
+        <f t="shared" si="28"/>
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="16"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="G24" s="14"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="4"/>
+      <c r="P24" s="14"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE03DFCB-CB3E-416B-90DB-1E3D4FD4A888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA6578F-C9E8-4E62-8CE8-0C1C33E13539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
-  <si>
-    <t>H22</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
   <si>
     <t>H23</t>
   </si>
@@ -81,12 +78,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>第一</t>
-  </si>
-  <si>
-    <t>上一</t>
-  </si>
-  <si>
     <t>总计</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -108,9 +99,6 @@
     <t>H35</t>
   </si>
   <si>
-    <t>H36</t>
-  </si>
-  <si>
     <t>H37</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -123,15 +111,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>H40</t>
-  </si>
-  <si>
-    <t>H38</t>
-  </si>
-  <si>
-    <t>H39</t>
-  </si>
-  <si>
     <t>H41</t>
   </si>
   <si>
@@ -139,21 +118,6 @@
   </si>
   <si>
     <t>H43</t>
-  </si>
-  <si>
-    <t>H37</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>mak</t>
-  </si>
-  <si>
-    <t>gen</t>
-  </si>
-  <si>
-    <t>总计</t>
   </si>
   <si>
     <t>H22</t>
@@ -165,6 +129,10 @@
   </si>
   <si>
     <t>H36</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -309,7 +277,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -342,9 +310,6 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -687,110 +652,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.625" style="13"/>
+    <col min="1" max="1" width="7.625" style="12"/>
     <col min="2" max="3" width="7.625" style="9"/>
     <col min="4" max="4" width="7.625" style="9" customWidth="1"/>
     <col min="5" max="8" width="7.625" style="9"/>
     <col min="9" max="9" width="7.625" style="10"/>
-    <col min="10" max="10" width="7.625" style="13"/>
+    <col min="10" max="10" width="7.625" style="12"/>
     <col min="11" max="17" width="7.625" style="9"/>
     <col min="18" max="18" width="7.625" style="10"/>
-    <col min="19" max="19" width="7.625" style="13"/>
+    <col min="19" max="19" width="7.625" style="12"/>
     <col min="20" max="26" width="7.625" style="9"/>
     <col min="27" max="27" width="7.625" style="10"/>
-    <col min="28" max="28" width="7.625" style="13"/>
+    <col min="28" max="28" width="7.625" style="12"/>
     <col min="29" max="16384" width="7.625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
+      <c r="A2" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -817,8 +782,8 @@
       <c r="I2" s="7">
         <v>293.08999999999997</v>
       </c>
-      <c r="J2" s="16" t="s">
-        <v>0</v>
+      <c r="J2" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="K2" s="5">
         <v>1</v>
@@ -844,45 +809,45 @@
       <c r="R2" s="7">
         <v>33.96</v>
       </c>
-      <c r="S2" s="16" t="s">
-        <v>40</v>
+      <c r="S2" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="T2" s="5">
-        <f>ROUND(B2/K2,3)</f>
+        <f t="shared" ref="T2:T20" si="0">ROUND(B2/K2,3)</f>
         <v>1</v>
       </c>
       <c r="U2" s="5">
-        <f>ROUND(C2/L2,3)</f>
+        <f t="shared" ref="U2:U20" si="1">ROUND(C2/L2,3)</f>
         <v>1</v>
       </c>
       <c r="V2" s="4">
-        <f>ROUND(D2/M2,3)</f>
+        <f t="shared" ref="V2:V20" si="2">ROUND(D2/M2,3)</f>
         <v>12.055</v>
       </c>
       <c r="W2" s="5">
-        <f>ROUND(E2/N2,3)</f>
+        <f t="shared" ref="W2:W20" si="3">ROUND(E2/N2,3)</f>
         <v>3.9340000000000002</v>
       </c>
       <c r="X2" s="8">
-        <f>ROUND(F2/O2,3)</f>
+        <f t="shared" ref="X2:X20" si="4">ROUND(F2/O2,3)</f>
         <v>26.54</v>
       </c>
       <c r="Y2" s="8">
-        <f>ROUND(G2/P2,3)</f>
+        <f t="shared" ref="Y2:Y20" si="5">ROUND(G2/P2,3)</f>
         <v>9.3119999999999994</v>
       </c>
       <c r="Z2" s="8">
-        <f>ROUND(H2/Q2,3)</f>
+        <f t="shared" ref="Z2:Z20" si="6">ROUND(H2/Q2,3)</f>
         <v>9.3569999999999993</v>
       </c>
       <c r="AA2" s="7">
-        <f>ROUND(I2/R2,3)</f>
+        <f t="shared" ref="AA2:AA20" si="7">ROUND(I2/R2,3)</f>
         <v>8.6300000000000008</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>1</v>
+      <c r="A3" s="15" t="s">
+        <v>0</v>
       </c>
       <c r="B3" s="2">
         <f>D$2/D3</f>
@@ -893,7 +858,7 @@
         <v>1.5134695843241126</v>
       </c>
       <c r="D3" s="6">
-        <f t="shared" ref="D3:D14" si="0">SUM(F3:H3)</f>
+        <f t="shared" ref="D3:D14" si="8">SUM(F3:H3)</f>
         <v>332.23</v>
       </c>
       <c r="E3" s="5">
@@ -911,13 +876,15 @@
       <c r="I3" s="7">
         <v>295.49</v>
       </c>
-      <c r="J3" s="16" t="s">
-        <v>1</v>
+      <c r="J3" s="15" t="s">
+        <v>0</v>
       </c>
       <c r="K3" s="2">
-        <v>1.4359982525120139</v>
+        <f>M$2/M3</f>
+        <v>1.8221930974224549</v>
       </c>
       <c r="L3" s="2">
+        <f>M2/M3</f>
         <v>1.8221930974224549</v>
       </c>
       <c r="M3" s="6">
@@ -938,56 +905,56 @@
       <c r="R3" s="7">
         <v>33.75</v>
       </c>
-      <c r="S3" s="16" t="s">
-        <v>1</v>
+      <c r="S3" s="15" t="s">
+        <v>0</v>
       </c>
       <c r="T3" s="2">
-        <f>ROUND(B3/K3,3)</f>
-        <v>1.054</v>
+        <f t="shared" si="0"/>
+        <v>0.83099999999999996</v>
       </c>
       <c r="U3" s="2">
-        <f>ROUND(C3/L3,3)</f>
+        <f t="shared" si="1"/>
         <v>0.83099999999999996</v>
       </c>
       <c r="V3" s="6">
-        <f>ROUND(D3/M3,3)</f>
+        <f t="shared" si="2"/>
         <v>14.513999999999999</v>
       </c>
       <c r="W3" s="5">
-        <f>ROUND(E3/N3,3)</f>
+        <f t="shared" si="3"/>
         <v>4.048</v>
       </c>
       <c r="X3" s="8">
-        <f>ROUND(F3/O3,3)</f>
+        <f t="shared" si="4"/>
         <v>26.024000000000001</v>
       </c>
       <c r="Y3" s="8">
-        <f>ROUND(G3/P3,3)</f>
+        <f t="shared" si="5"/>
         <v>9.9009999999999998</v>
       </c>
       <c r="Z3" s="1">
-        <f>ROUND(H3/Q3,3)</f>
+        <f t="shared" si="6"/>
         <v>4.8689999999999998</v>
       </c>
       <c r="AA3" s="7">
-        <f>ROUND(I3/R3,3)</f>
+        <f t="shared" si="7"/>
         <v>8.7550000000000008</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
-        <v>2</v>
+      <c r="A4" s="15" t="s">
+        <v>1</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B12" si="1">D$2/D4</f>
+        <f t="shared" ref="B4:B23" si="9">D$2/D4</f>
         <v>2.0672614397894993</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C12" si="2">D3/D4</f>
+        <f t="shared" ref="C4:C23" si="10">D3/D4</f>
         <v>1.3659088105907988</v>
       </c>
       <c r="D4" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>243.23000000000002</v>
       </c>
       <c r="E4" s="5">
@@ -1005,16 +972,19 @@
       <c r="I4" s="7">
         <v>295.82</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>2</v>
+      <c r="J4" s="15" t="s">
+        <v>1</v>
       </c>
       <c r="K4" s="2">
-        <v>1.5644930985245118</v>
+        <f t="shared" ref="K4:K23" si="11">M$2/M4</f>
+        <v>1.9852451213707754</v>
       </c>
       <c r="L4" s="2">
+        <f t="shared" ref="L4:L23" si="12">M3/M4</f>
         <v>1.0894811994288434</v>
       </c>
       <c r="M4" s="6">
+        <f t="shared" ref="M4:M23" si="13">SUM(O4:Q4)</f>
         <v>21.01</v>
       </c>
       <c r="N4" s="5">
@@ -1032,56 +1002,56 @@
       <c r="R4" s="7">
         <v>33.96</v>
       </c>
-      <c r="S4" s="16" t="s">
-        <v>2</v>
+      <c r="S4" s="15" t="s">
+        <v>1</v>
       </c>
       <c r="T4" s="2">
-        <f>ROUND(B4/K4,3)</f>
-        <v>1.321</v>
+        <f t="shared" si="0"/>
+        <v>1.0409999999999999</v>
       </c>
       <c r="U4" s="2">
-        <f>ROUND(C4/L4,3)</f>
+        <f t="shared" si="1"/>
         <v>1.254</v>
       </c>
       <c r="V4" s="6">
-        <f>ROUND(D4/M4,3)</f>
+        <f t="shared" si="2"/>
         <v>11.577</v>
       </c>
       <c r="W4" s="5">
-        <f>ROUND(E4/N4,3)</f>
+        <f t="shared" si="3"/>
         <v>4.0250000000000004</v>
       </c>
       <c r="X4" s="1">
-        <f>ROUND(F4/O4,3)</f>
+        <f t="shared" si="4"/>
         <v>19.100999999999999</v>
       </c>
       <c r="Y4" s="8">
-        <f>ROUND(G4/P4,3)</f>
+        <f t="shared" si="5"/>
         <v>9.5429999999999993</v>
       </c>
       <c r="Z4" s="8">
-        <f>ROUND(H4/Q4,3)</f>
+        <f t="shared" si="6"/>
         <v>4.7830000000000004</v>
       </c>
       <c r="AA4" s="7">
-        <f>ROUND(I4/R4,3)</f>
+        <f t="shared" si="7"/>
         <v>8.7110000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
-        <v>3</v>
+      <c r="A5" s="15" t="s">
+        <v>2</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.2113642360805694</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.0697070982496262</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>227.38000000000002</v>
       </c>
       <c r="E5" s="5">
@@ -1099,16 +1069,19 @@
       <c r="I5" s="7">
         <v>297.08999999999997</v>
       </c>
-      <c r="J5" s="16" t="s">
-        <v>3</v>
+      <c r="J5" s="15" t="s">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
-        <v>2.7075782537067541</v>
+        <f t="shared" si="11"/>
+        <v>3.435749588138385</v>
       </c>
       <c r="L5" s="2">
+        <f t="shared" si="12"/>
         <v>1.7306425041186162</v>
       </c>
       <c r="M5" s="6">
+        <f t="shared" si="13"/>
         <v>12.14</v>
       </c>
       <c r="N5" s="5">
@@ -1126,56 +1099,56 @@
       <c r="R5" s="7">
         <v>34.090000000000003</v>
       </c>
-      <c r="S5" s="16" t="s">
-        <v>3</v>
+      <c r="S5" s="15" t="s">
+        <v>2</v>
       </c>
       <c r="T5" s="2">
-        <f>ROUND(B5/K5,3)</f>
-        <v>0.81699999999999995</v>
+        <f t="shared" si="0"/>
+        <v>0.64400000000000002</v>
       </c>
       <c r="U5" s="2">
-        <f>ROUND(C5/L5,3)</f>
+        <f t="shared" si="1"/>
         <v>0.61799999999999999</v>
       </c>
       <c r="V5" s="6">
-        <f>ROUND(D5/M5,3)</f>
+        <f t="shared" si="2"/>
         <v>18.73</v>
       </c>
       <c r="W5" s="5">
-        <f>ROUND(E5/N5,3)</f>
+        <f t="shared" si="3"/>
         <v>4.1609999999999996</v>
       </c>
       <c r="X5" s="8">
-        <f>ROUND(F5/O5,3)</f>
+        <f t="shared" si="4"/>
         <v>19.146999999999998</v>
       </c>
       <c r="Y5" s="1">
-        <f>ROUND(G5/P5,3)</f>
+        <f t="shared" si="5"/>
         <v>19.707999999999998</v>
       </c>
       <c r="Z5" s="8">
-        <f>ROUND(H5/Q5,3)</f>
+        <f t="shared" si="6"/>
         <v>4.6719999999999997</v>
       </c>
       <c r="AA5" s="7">
-        <f>ROUND(I5/R5,3)</f>
+        <f t="shared" si="7"/>
         <v>8.7149999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>4</v>
+      <c r="A6" s="15" t="s">
+        <v>3</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.2125319017864999</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.0005280295696561</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>227.26</v>
       </c>
       <c r="E6" s="5">
@@ -1193,16 +1166,19 @@
       <c r="I6" s="3">
         <v>112.14</v>
       </c>
-      <c r="J6" s="16" t="s">
-        <v>4</v>
+      <c r="J6" s="15" t="s">
+        <v>3</v>
       </c>
       <c r="K6" s="5">
-        <v>2.714285714285714</v>
+        <f t="shared" si="11"/>
+        <v>3.444260941370767</v>
       </c>
       <c r="L6" s="5">
+        <f t="shared" si="12"/>
         <v>1.0024772914946325</v>
       </c>
       <c r="M6" s="4">
+        <f t="shared" si="13"/>
         <v>12.110000000000001</v>
       </c>
       <c r="N6" s="5">
@@ -1220,56 +1196,56 @@
       <c r="R6" s="3">
         <v>6.1</v>
       </c>
-      <c r="S6" s="16" t="s">
-        <v>4</v>
+      <c r="S6" s="15" t="s">
+        <v>3</v>
       </c>
       <c r="T6" s="5">
-        <f>ROUND(B6/K6,3)</f>
-        <v>0.81499999999999995</v>
+        <f t="shared" si="0"/>
+        <v>0.64200000000000002</v>
       </c>
       <c r="U6" s="5">
-        <f>ROUND(C6/L6,3)</f>
+        <f t="shared" si="1"/>
         <v>0.998</v>
       </c>
       <c r="V6" s="4">
-        <f>ROUND(D6/M6,3)</f>
+        <f t="shared" si="2"/>
         <v>18.765999999999998</v>
       </c>
       <c r="W6" s="5">
-        <f>ROUND(E6/N6,3)</f>
+        <f t="shared" si="3"/>
         <v>4.1349999999999998</v>
       </c>
       <c r="X6" s="8">
-        <f>ROUND(F6/O6,3)</f>
+        <f t="shared" si="4"/>
         <v>19.414999999999999</v>
       </c>
       <c r="Y6" s="8">
-        <f>ROUND(G6/P6,3)</f>
+        <f t="shared" si="5"/>
         <v>19.652000000000001</v>
       </c>
       <c r="Z6" s="8">
-        <f>ROUND(H6/Q6,3)</f>
+        <f t="shared" si="6"/>
         <v>4.4290000000000003</v>
       </c>
       <c r="AA6" s="3">
-        <f>ROUND(I6/R6,3)</f>
+        <f t="shared" si="7"/>
         <v>18.384</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
-        <v>5</v>
+      <c r="A7" s="15" t="s">
+        <v>4</v>
       </c>
       <c r="B7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.1726656008296241</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.98198159270621777</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>231.43</v>
       </c>
       <c r="E7" s="5">
@@ -1287,16 +1263,19 @@
       <c r="I7" s="7">
         <v>112.99</v>
       </c>
-      <c r="J7" s="16" t="s">
-        <v>5</v>
+      <c r="J7" s="15" t="s">
+        <v>4</v>
       </c>
       <c r="K7" s="5">
-        <v>2.81180496150556</v>
+        <f t="shared" si="11"/>
+        <v>3.5680068434559447</v>
       </c>
       <c r="L7" s="5">
+        <f t="shared" si="12"/>
         <v>1.0359281437125749</v>
       </c>
       <c r="M7" s="4">
+        <f t="shared" si="13"/>
         <v>11.69</v>
       </c>
       <c r="N7" s="5">
@@ -1314,56 +1293,56 @@
       <c r="R7" s="7">
         <v>6.05</v>
       </c>
-      <c r="S7" s="16" t="s">
-        <v>5</v>
+      <c r="S7" s="15" t="s">
+        <v>4</v>
       </c>
       <c r="T7" s="5">
-        <f>ROUND(B7/K7,3)</f>
-        <v>0.77300000000000002</v>
+        <f t="shared" si="0"/>
+        <v>0.60899999999999999</v>
       </c>
       <c r="U7" s="5">
-        <f>ROUND(C7/L7,3)</f>
+        <f t="shared" si="1"/>
         <v>0.94799999999999995</v>
       </c>
       <c r="V7" s="4">
-        <f>ROUND(D7/M7,3)</f>
+        <f t="shared" si="2"/>
         <v>19.797000000000001</v>
       </c>
       <c r="W7" s="5">
-        <f>ROUND(E7/N7,3)</f>
+        <f t="shared" si="3"/>
         <v>5.1959999999999997</v>
       </c>
       <c r="X7" s="8">
-        <f>ROUND(F7/O7,3)</f>
+        <f t="shared" si="4"/>
         <v>20.858000000000001</v>
       </c>
       <c r="Y7" s="8">
-        <f>ROUND(G7/P7,3)</f>
+        <f t="shared" si="5"/>
         <v>19.635000000000002</v>
       </c>
       <c r="Z7" s="1">
-        <f>ROUND(H7/Q7,3)</f>
+        <f t="shared" si="6"/>
         <v>5.3330000000000002</v>
       </c>
       <c r="AA7" s="7">
-        <f>ROUND(I7/R7,3)</f>
+        <f t="shared" si="7"/>
         <v>18.675999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
-        <v>6</v>
+      <c r="A8" s="15" t="s">
+        <v>5</v>
       </c>
       <c r="B8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.1582110052365007</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.99334706841789</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>232.98</v>
       </c>
       <c r="E8" s="5">
@@ -1381,16 +1360,19 @@
       <c r="I8" s="7">
         <v>114.88</v>
       </c>
-      <c r="J8" s="16" t="s">
-        <v>6</v>
+      <c r="J8" s="15" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="5">
-        <v>2.8287435456110153</v>
+        <f t="shared" si="11"/>
+        <v>3.5895008605851975</v>
       </c>
       <c r="L8" s="5">
+        <f t="shared" si="12"/>
         <v>1.0060240963855422</v>
       </c>
       <c r="M8" s="4">
+        <f t="shared" si="13"/>
         <v>11.62</v>
       </c>
       <c r="N8" s="5">
@@ -1408,56 +1390,56 @@
       <c r="R8" s="7">
         <v>6.02</v>
       </c>
-      <c r="S8" s="16" t="s">
-        <v>6</v>
+      <c r="S8" s="15" t="s">
+        <v>5</v>
       </c>
       <c r="T8" s="5">
-        <f>ROUND(B8/K8,3)</f>
-        <v>0.76300000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.60099999999999998</v>
       </c>
       <c r="U8" s="5">
-        <f>ROUND(C8/L8,3)</f>
+        <f t="shared" si="1"/>
         <v>0.98699999999999999</v>
       </c>
       <c r="V8" s="4">
-        <f>ROUND(D8/M8,3)</f>
+        <f t="shared" si="2"/>
         <v>20.05</v>
       </c>
       <c r="W8" s="5">
-        <f>ROUND(E8/N8,3)</f>
+        <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
       <c r="X8" s="8">
-        <f>ROUND(F8/O8,3)</f>
+        <f t="shared" si="4"/>
         <v>20.789000000000001</v>
       </c>
       <c r="Y8" s="8">
-        <f>ROUND(G8/P8,3)</f>
+        <f t="shared" si="5"/>
         <v>20.132999999999999</v>
       </c>
       <c r="Z8" s="8">
-        <f>ROUND(H8/Q8,3)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AA8" s="7">
-        <f>ROUND(I8/R8,3)</f>
+        <f t="shared" si="7"/>
         <v>19.082999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
-        <v>7</v>
+      <c r="A9" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.1661138155343984</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.0036617412656701</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>232.13</v>
       </c>
       <c r="E9" s="5">
@@ -1475,16 +1457,19 @@
       <c r="I9" s="7">
         <v>112.53</v>
       </c>
-      <c r="J9" s="16" t="s">
-        <v>7</v>
+      <c r="J9" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="K9" s="5">
-        <v>2.81180496150556</v>
+        <f t="shared" si="11"/>
+        <v>3.5680068434559447</v>
       </c>
       <c r="L9" s="5">
+        <f t="shared" si="12"/>
         <v>0.99401197604790414</v>
       </c>
       <c r="M9" s="4">
+        <f t="shared" si="13"/>
         <v>11.69</v>
       </c>
       <c r="N9" s="5">
@@ -1502,56 +1487,56 @@
       <c r="R9" s="7">
         <v>6.05</v>
       </c>
-      <c r="S9" s="16" t="s">
-        <v>7</v>
+      <c r="S9" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="T9" s="5">
-        <f>ROUND(B9/K9,3)</f>
-        <v>0.77</v>
+        <f t="shared" si="0"/>
+        <v>0.60699999999999998</v>
       </c>
       <c r="U9" s="5">
-        <f>ROUND(C9/L9,3)</f>
+        <f t="shared" si="1"/>
         <v>1.01</v>
       </c>
       <c r="V9" s="4">
-        <f>ROUND(D9/M9,3)</f>
+        <f t="shared" si="2"/>
         <v>19.856999999999999</v>
       </c>
       <c r="W9" s="5">
-        <f>ROUND(E9/N9,3)</f>
+        <f t="shared" si="3"/>
         <v>5.4349999999999996</v>
       </c>
       <c r="X9" s="8">
-        <f>ROUND(F9/O9,3)</f>
+        <f t="shared" si="4"/>
         <v>21.099</v>
       </c>
       <c r="Y9" s="8">
-        <f>ROUND(G9/P9,3)</f>
+        <f t="shared" si="5"/>
         <v>19.597999999999999</v>
       </c>
       <c r="Z9" s="8">
-        <f>ROUND(H9/Q9,3)</f>
+        <f t="shared" si="6"/>
         <v>4.9640000000000004</v>
       </c>
       <c r="AA9" s="7">
-        <f>ROUND(I9/R9,3)</f>
+        <f t="shared" si="7"/>
         <v>18.600000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
-        <v>8</v>
+      <c r="A10" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="B10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.1769926830324287</v>
       </c>
       <c r="C10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.0050222972680436</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>230.96999999999997</v>
       </c>
       <c r="E10" s="2">
@@ -1569,16 +1554,19 @@
       <c r="I10" s="7">
         <v>112.43</v>
       </c>
-      <c r="J10" s="16" t="s">
-        <v>8</v>
+      <c r="J10" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="K10" s="5">
-        <v>2.8458874458874459</v>
+        <f t="shared" si="11"/>
+        <v>3.6112554112554109</v>
       </c>
       <c r="L10" s="5">
+        <f t="shared" si="12"/>
         <v>1.0121212121212122</v>
       </c>
       <c r="M10" s="4">
+        <f t="shared" si="13"/>
         <v>11.549999999999999</v>
       </c>
       <c r="N10" s="2">
@@ -1596,56 +1584,56 @@
       <c r="R10" s="7">
         <v>5.97</v>
       </c>
-      <c r="S10" s="16" t="s">
-        <v>8</v>
+      <c r="S10" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="T10" s="5">
-        <f>ROUND(B10/K10,3)</f>
-        <v>0.76500000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.60299999999999998</v>
       </c>
       <c r="U10" s="5">
-        <f>ROUND(C10/L10,3)</f>
+        <f t="shared" si="1"/>
         <v>0.99299999999999999</v>
       </c>
       <c r="V10" s="4">
-        <f>ROUND(D10/M10,3)</f>
+        <f t="shared" si="2"/>
         <v>19.997</v>
       </c>
       <c r="W10" s="2">
-        <f>ROUND(E10/N10,3)</f>
+        <f t="shared" si="3"/>
         <v>3.331</v>
       </c>
       <c r="X10" s="8">
-        <f>ROUND(F10/O10,3)</f>
+        <f t="shared" si="4"/>
         <v>20.896000000000001</v>
       </c>
       <c r="Y10" s="8">
-        <f>ROUND(G10/P10,3)</f>
+        <f t="shared" si="5"/>
         <v>19.998000000000001</v>
       </c>
       <c r="Z10" s="8">
-        <f>ROUND(H10/Q10,3)</f>
+        <f t="shared" si="6"/>
         <v>4.8929999999999998</v>
       </c>
       <c r="AA10" s="7">
-        <f>ROUND(I10/R10,3)</f>
+        <f t="shared" si="7"/>
         <v>18.832000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
-        <v>9</v>
+      <c r="A11" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="B11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.6913236632232507</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.23625756034898</v>
       </c>
       <c r="D11" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>186.83</v>
       </c>
       <c r="E11" s="5">
@@ -1663,16 +1651,19 @@
       <c r="I11" s="7">
         <v>111.93</v>
       </c>
-      <c r="J11" s="16" t="s">
-        <v>9</v>
+      <c r="J11" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="K11" s="2">
-        <v>3.1394460362941738</v>
+        <f t="shared" si="11"/>
+        <v>3.9837631327602674</v>
       </c>
       <c r="L11" s="2">
+        <f t="shared" si="12"/>
         <v>1.1031518624641834</v>
       </c>
       <c r="M11" s="6">
+        <f t="shared" si="13"/>
         <v>10.469999999999999</v>
       </c>
       <c r="N11" s="5">
@@ -1690,56 +1681,56 @@
       <c r="R11" s="7">
         <v>7.81</v>
       </c>
-      <c r="S11" s="16" t="s">
-        <v>9</v>
+      <c r="S11" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="T11" s="2">
-        <f>ROUND(B11/K11,3)</f>
-        <v>0.85699999999999998</v>
+        <f t="shared" si="0"/>
+        <v>0.67600000000000005</v>
       </c>
       <c r="U11" s="2">
-        <f>ROUND(C11/L11,3)</f>
+        <f t="shared" si="1"/>
         <v>1.121</v>
       </c>
       <c r="V11" s="6">
-        <f>ROUND(D11/M11,3)</f>
+        <f t="shared" si="2"/>
         <v>17.844000000000001</v>
       </c>
       <c r="W11" s="5">
-        <f>ROUND(E11/N11,3)</f>
+        <f t="shared" si="3"/>
         <v>2.9060000000000001</v>
       </c>
       <c r="X11" s="1">
-        <f>ROUND(F11/O11,3)</f>
+        <f t="shared" si="4"/>
         <v>29.065999999999999</v>
       </c>
       <c r="Y11" s="8">
-        <f>ROUND(G11/P11,3)</f>
+        <f t="shared" si="5"/>
         <v>15.778</v>
       </c>
       <c r="Z11" s="8">
-        <f>ROUND(H11/Q11,3)</f>
+        <f t="shared" si="6"/>
         <v>5.8520000000000003</v>
       </c>
       <c r="AA11" s="7">
-        <f>ROUND(I11/R11,3)</f>
+        <f t="shared" si="7"/>
         <v>14.332000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
-        <v>10</v>
+      <c r="A12" s="15" t="s">
+        <v>9</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>2.9142227889185115</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.0828213747536803</v>
       </c>
       <c r="D12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>172.54</v>
       </c>
       <c r="E12" s="5">
@@ -1757,16 +1748,19 @@
       <c r="I12" s="3">
         <v>93.93</v>
       </c>
-      <c r="J12" s="16" t="s">
-        <v>10</v>
+      <c r="J12" s="15" t="s">
+        <v>9</v>
       </c>
       <c r="K12" s="2">
-        <v>3.853458382180539</v>
+        <f t="shared" si="11"/>
+        <v>4.8898007033997652</v>
       </c>
       <c r="L12" s="2">
+        <f t="shared" si="12"/>
         <v>1.227432590855803</v>
       </c>
       <c r="M12" s="6">
+        <f t="shared" si="13"/>
         <v>8.5299999999999994</v>
       </c>
       <c r="N12" s="5">
@@ -1784,56 +1778,56 @@
       <c r="R12" s="3">
         <v>5.44</v>
       </c>
-      <c r="S12" s="16" t="s">
-        <v>10</v>
+      <c r="S12" s="15" t="s">
+        <v>9</v>
       </c>
       <c r="T12" s="2">
-        <f>ROUND(B12/K12,3)</f>
-        <v>0.75600000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.59599999999999997</v>
       </c>
       <c r="U12" s="2">
-        <f>ROUND(C12/L12,3)</f>
+        <f t="shared" si="1"/>
         <v>0.88200000000000001</v>
       </c>
       <c r="V12" s="6">
-        <f>ROUND(D12/M12,3)</f>
+        <f t="shared" si="2"/>
         <v>20.227</v>
       </c>
       <c r="W12" s="5">
-        <f>ROUND(E12/N12,3)</f>
+        <f t="shared" si="3"/>
         <v>2.89</v>
       </c>
       <c r="X12" s="8">
-        <f>ROUND(F12/O12,3)</f>
+        <f t="shared" si="4"/>
         <v>29.167999999999999</v>
       </c>
       <c r="Y12" s="1">
-        <f>ROUND(G12/P12,3)</f>
+        <f t="shared" si="5"/>
         <v>18.408999999999999</v>
       </c>
       <c r="Z12" s="8">
-        <f>ROUND(H12/Q12,3)</f>
+        <f t="shared" si="6"/>
         <v>5.0359999999999996</v>
       </c>
       <c r="AA12" s="3">
-        <f>ROUND(I12/R12,3)</f>
+        <f t="shared" si="7"/>
         <v>17.266999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
-        <v>21</v>
+      <c r="A13" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" ref="B13:B14" si="3">D$2/D13</f>
+        <f t="shared" si="9"/>
         <v>3.3354560530679929</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" ref="C13:C14" si="4">D12/D13</f>
+        <f t="shared" si="10"/>
         <v>1.1445439469320067</v>
       </c>
       <c r="D13" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>150.75</v>
       </c>
       <c r="E13" s="5">
@@ -1851,16 +1845,19 @@
       <c r="I13" s="7">
         <v>94.27</v>
       </c>
-      <c r="J13" s="17" t="s">
-        <v>21</v>
+      <c r="J13" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="K13" s="2">
-        <v>4.1345911949685537</v>
+        <f t="shared" si="11"/>
+        <v>5.2465408805031446</v>
       </c>
       <c r="L13" s="2">
+        <f t="shared" si="12"/>
         <v>1.0729559748427673</v>
       </c>
       <c r="M13" s="6">
+        <f t="shared" si="13"/>
         <v>7.9499999999999993</v>
       </c>
       <c r="N13" s="5">
@@ -1878,56 +1875,56 @@
       <c r="R13" s="7">
         <v>5.47</v>
       </c>
-      <c r="S13" s="17" t="s">
-        <v>21</v>
+      <c r="S13" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="T13" s="2">
-        <f>ROUND(B13/K13,3)</f>
-        <v>0.80700000000000005</v>
+        <f t="shared" si="0"/>
+        <v>0.63600000000000001</v>
       </c>
       <c r="U13" s="2">
-        <f>ROUND(C13/L13,3)</f>
+        <f t="shared" si="1"/>
         <v>1.0669999999999999</v>
       </c>
       <c r="V13" s="6">
-        <f>ROUND(D13/M13,3)</f>
+        <f t="shared" si="2"/>
         <v>18.962</v>
       </c>
       <c r="W13" s="5">
-        <f>ROUND(E13/N13,3)</f>
+        <f t="shared" si="3"/>
         <v>2.8740000000000001</v>
       </c>
       <c r="X13" s="1">
-        <f>ROUND(F13/O13,3)</f>
+        <f t="shared" si="4"/>
         <v>26.5</v>
       </c>
       <c r="Y13" s="8">
-        <f>ROUND(G13/P13,3)</f>
+        <f t="shared" si="5"/>
         <v>18.175999999999998</v>
       </c>
       <c r="Z13" s="8">
-        <f>ROUND(H13/Q13,3)</f>
+        <f t="shared" si="6"/>
         <v>5.556</v>
       </c>
       <c r="AA13" s="7">
-        <f>ROUND(I13/R13,3)</f>
+        <f t="shared" si="7"/>
         <v>17.234000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
-        <v>22</v>
+      <c r="A14" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="B14" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>3.3443298969072162</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1.0026604589291652</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>150.35</v>
       </c>
       <c r="E14" s="5">
@@ -1945,16 +1942,19 @@
       <c r="I14" s="7">
         <v>93.68</v>
       </c>
-      <c r="J14" s="18" t="s">
-        <v>22</v>
+      <c r="J14" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="K14" s="5">
-        <v>4.2087067861715743</v>
+        <f t="shared" si="11"/>
+        <v>5.3405889884763109</v>
       </c>
       <c r="L14" s="5">
+        <f t="shared" si="12"/>
         <v>1.0179257362355951</v>
       </c>
       <c r="M14" s="4">
+        <f t="shared" si="13"/>
         <v>7.8100000000000005</v>
       </c>
       <c r="N14" s="5">
@@ -1972,56 +1972,56 @@
       <c r="R14" s="7">
         <v>5.35</v>
       </c>
-      <c r="S14" s="18" t="s">
-        <v>22</v>
+      <c r="S14" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="T14" s="5">
-        <f>ROUND(B14/K14,3)</f>
-        <v>0.79500000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.626</v>
       </c>
       <c r="U14" s="5">
-        <f>ROUND(C14/L14,3)</f>
+        <f t="shared" si="1"/>
         <v>0.98499999999999999</v>
       </c>
       <c r="V14" s="4">
-        <f>ROUND(D14/M14,3)</f>
+        <f t="shared" si="2"/>
         <v>19.251000000000001</v>
       </c>
       <c r="W14" s="5">
-        <f>ROUND(E14/N14,3)</f>
+        <f t="shared" si="3"/>
         <v>2.931</v>
       </c>
       <c r="X14" s="1">
-        <f>ROUND(F14/O14,3)</f>
+        <f t="shared" si="4"/>
         <v>27.292000000000002</v>
       </c>
       <c r="Y14" s="8">
-        <f>ROUND(G14/P14,3)</f>
+        <f t="shared" si="5"/>
         <v>18.422999999999998</v>
       </c>
       <c r="Z14" s="8">
-        <f>ROUND(H14/Q14,3)</f>
+        <f t="shared" si="6"/>
         <v>5.2590000000000003</v>
       </c>
       <c r="AA14" s="7">
-        <f>ROUND(I14/R14,3)</f>
+        <f t="shared" si="7"/>
         <v>17.510000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18" t="s">
-        <v>24</v>
+      <c r="A15" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="B15" s="2">
-        <f t="shared" ref="B15" si="5">D$2/D15</f>
+        <f t="shared" si="9"/>
         <v>4.2789549825546755</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15" si="6">D14/D15</f>
+        <f t="shared" si="10"/>
         <v>1.2794655773976682</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" ref="D15:D20" si="7">SUM(F15:H15)</f>
+        <f t="shared" ref="D15:D20" si="14">SUM(F15:H15)</f>
         <v>117.51</v>
       </c>
       <c r="E15" s="5">
@@ -2039,16 +2039,19 @@
       <c r="I15" s="3">
         <v>64.790000000000006</v>
       </c>
-      <c r="J15" s="18" t="s">
-        <v>24</v>
+      <c r="J15" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="K15" s="2">
-        <v>4.533793103448275</v>
+        <f t="shared" si="11"/>
+        <v>5.7531034482758603</v>
       </c>
       <c r="L15" s="2">
+        <f t="shared" si="12"/>
         <v>1.0772413793103448</v>
       </c>
       <c r="M15" s="6">
+        <f t="shared" si="13"/>
         <v>7.2500000000000009</v>
       </c>
       <c r="N15" s="5">
@@ -2066,56 +2069,56 @@
       <c r="R15" s="3">
         <v>5.0599999999999996</v>
       </c>
-      <c r="S15" s="18" t="s">
-        <v>24</v>
+      <c r="S15" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="T15" s="2">
-        <f>ROUND(B15/K15,3)</f>
-        <v>0.94399999999999995</v>
+        <f t="shared" si="0"/>
+        <v>0.74399999999999999</v>
       </c>
       <c r="U15" s="2">
-        <f>ROUND(C15/L15,3)</f>
+        <f t="shared" si="1"/>
         <v>1.1879999999999999</v>
       </c>
       <c r="V15" s="6">
-        <f>ROUND(D15/M15,3)</f>
+        <f t="shared" si="2"/>
         <v>16.207999999999998</v>
       </c>
       <c r="W15" s="5">
-        <f>ROUND(E15/N15,3)</f>
+        <f t="shared" si="3"/>
         <v>2.9950000000000001</v>
       </c>
       <c r="X15" s="8">
-        <f>ROUND(F15/O15,3)</f>
+        <f t="shared" si="4"/>
         <v>26.939</v>
       </c>
       <c r="Y15" s="1">
-        <f>ROUND(G15/P15,3)</f>
+        <f t="shared" si="5"/>
         <v>14.622</v>
       </c>
       <c r="Z15" s="8">
-        <f>ROUND(H15/Q15,3)</f>
+        <f t="shared" si="6"/>
         <v>5.1070000000000002</v>
       </c>
       <c r="AA15" s="3">
-        <f>ROUND(I15/R15,3)</f>
+        <f t="shared" si="7"/>
         <v>12.804</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18" t="s">
-        <v>42</v>
+      <c r="A16" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" ref="B16" si="8">D$2/D16</f>
+        <f t="shared" si="9"/>
         <v>4.3257054370268406</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16" si="9">D15/D16</f>
+        <f t="shared" si="10"/>
         <v>1.0109256710254646</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>116.24</v>
       </c>
       <c r="E16" s="1">
@@ -2133,16 +2136,19 @@
       <c r="I16" s="7">
         <v>63.86</v>
       </c>
-      <c r="J16" s="18" t="s">
-        <v>25</v>
+      <c r="J16" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="K16" s="5">
-        <v>4.5589459084604709</v>
+        <f t="shared" si="11"/>
+        <v>5.7850208044382789</v>
       </c>
       <c r="L16" s="5">
+        <f t="shared" si="12"/>
         <v>1.0055478502080446</v>
       </c>
       <c r="M16" s="4">
+        <f t="shared" si="13"/>
         <v>7.21</v>
       </c>
       <c r="N16" s="1">
@@ -2160,722 +2166,720 @@
       <c r="R16" s="7">
         <v>5.0199999999999996</v>
       </c>
-      <c r="S16" s="18" t="s">
-        <v>42</v>
+      <c r="S16" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="T16" s="5">
-        <f>ROUND(B16/K16,3)</f>
-        <v>0.94899999999999995</v>
+        <f t="shared" si="0"/>
+        <v>0.748</v>
       </c>
       <c r="U16" s="5">
-        <f>ROUND(C16/L16,3)</f>
+        <f t="shared" si="1"/>
         <v>1.0049999999999999</v>
       </c>
       <c r="V16" s="4">
-        <f>ROUND(D16/M16,3)</f>
+        <f t="shared" si="2"/>
         <v>16.122</v>
       </c>
       <c r="W16" s="1">
-        <f>ROUND(E16/N16,3)</f>
+        <f t="shared" si="3"/>
         <v>21.021999999999998</v>
       </c>
       <c r="X16" s="8">
-        <f>ROUND(F16/O16,3)</f>
+        <f t="shared" si="4"/>
         <v>27.265000000000001</v>
       </c>
       <c r="Y16" s="8">
-        <f>ROUND(G16/P16,3)</f>
+        <f t="shared" si="5"/>
         <v>14.452</v>
       </c>
       <c r="Z16" s="8">
-        <f>ROUND(H16/Q16,3)</f>
+        <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
       <c r="AA16" s="7">
-        <f>ROUND(I16/R16,3)</f>
+        <f t="shared" si="7"/>
         <v>12.721</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18" t="s">
-        <v>26</v>
+      <c r="A17" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="B17" s="5">
-        <f t="shared" ref="B17" si="10">D$2/D17</f>
+        <f t="shared" si="9"/>
         <v>4.3421416234887733</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17" si="11">D16/D17</f>
+        <f t="shared" si="10"/>
         <v>1.0037996545768566</v>
       </c>
       <c r="D17" s="4">
+        <f t="shared" si="14"/>
+        <v>115.8</v>
+      </c>
+      <c r="E17" s="18">
+        <v>293.16000000000003</v>
+      </c>
+      <c r="F17" s="18">
+        <v>30.57</v>
+      </c>
+      <c r="G17" s="13">
+        <v>83.77</v>
+      </c>
+      <c r="H17" s="18">
+        <v>1.46</v>
+      </c>
+      <c r="I17" s="18">
+        <v>64.06</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="5">
+        <f t="shared" si="11"/>
+        <v>6.291101055806938</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="12"/>
+        <v>1.0874811463046758</v>
+      </c>
+      <c r="M17" s="4">
+        <f t="shared" si="13"/>
+        <v>6.629999999999999</v>
+      </c>
+      <c r="N17" s="18">
+        <v>13.86</v>
+      </c>
+      <c r="O17" s="18">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P17" s="13">
+        <v>5.21</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>0.27</v>
+      </c>
+      <c r="R17" s="18">
+        <v>4.26</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="T17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.69</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="1"/>
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="V17" s="4">
+        <f t="shared" si="2"/>
+        <v>17.466000000000001</v>
+      </c>
+      <c r="W17" s="18">
+        <f t="shared" si="3"/>
+        <v>21.152000000000001</v>
+      </c>
+      <c r="X17" s="18">
+        <f t="shared" si="4"/>
+        <v>26.582999999999998</v>
+      </c>
+      <c r="Y17" s="13">
+        <f t="shared" si="5"/>
+        <v>16.079000000000001</v>
+      </c>
+      <c r="Z17" s="18">
+        <f t="shared" si="6"/>
+        <v>5.407</v>
+      </c>
+      <c r="AA17" s="18">
         <f t="shared" si="7"/>
-        <v>115.8</v>
-      </c>
-      <c r="E17" s="19">
-        <v>293.16000000000003</v>
-      </c>
-      <c r="F17" s="19">
-        <v>30.57</v>
-      </c>
-      <c r="G17" s="14">
-        <v>83.77</v>
-      </c>
-      <c r="H17" s="19">
-        <v>1.46</v>
-      </c>
-      <c r="I17" s="19">
-        <v>64.06</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="5">
-        <v>4.957767722473605</v>
-      </c>
-      <c r="L17" s="5">
-        <v>1.0874811463046758</v>
-      </c>
-      <c r="M17" s="4">
-        <v>6.629999999999999</v>
-      </c>
-      <c r="N17" s="19">
-        <v>13.86</v>
-      </c>
-      <c r="O17" s="19">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="P17" s="14">
-        <v>5.21</v>
-      </c>
-      <c r="Q17" s="19">
-        <v>0.27</v>
-      </c>
-      <c r="R17" s="19">
-        <v>4.26</v>
-      </c>
-      <c r="S17" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" s="5">
-        <f>ROUND(B17/K17,3)</f>
-        <v>0.876</v>
-      </c>
-      <c r="U17" s="5">
-        <f>ROUND(C17/L17,3)</f>
-        <v>0.92300000000000004</v>
-      </c>
-      <c r="V17" s="4">
-        <f>ROUND(D17/M17,3)</f>
-        <v>17.466000000000001</v>
-      </c>
-      <c r="W17" s="19">
-        <f>ROUND(E17/N17,3)</f>
-        <v>21.152000000000001</v>
-      </c>
-      <c r="X17" s="19">
-        <f>ROUND(F17/O17,3)</f>
-        <v>26.582999999999998</v>
-      </c>
-      <c r="Y17" s="14">
-        <f>ROUND(G17/P17,3)</f>
-        <v>16.079000000000001</v>
-      </c>
-      <c r="Z17" s="19">
-        <f>ROUND(H17/Q17,3)</f>
-        <v>5.407</v>
-      </c>
-      <c r="AA17" s="19">
-        <f>ROUND(I17/R17,3)</f>
         <v>15.038</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
-        <v>27</v>
+      <c r="A18" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="B18" s="5">
-        <f t="shared" ref="B18" si="12">D$2/D18</f>
+        <f t="shared" si="9"/>
         <v>4.3432668221473598</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18" si="13">D17/D18</f>
+        <f t="shared" si="10"/>
         <v>1.0002591344908005</v>
       </c>
       <c r="D18" s="4">
+        <f t="shared" si="14"/>
+        <v>115.77000000000001</v>
+      </c>
+      <c r="E18" s="18">
+        <v>298.27</v>
+      </c>
+      <c r="F18" s="18">
+        <v>30.43</v>
+      </c>
+      <c r="G18" s="13">
+        <v>83.93</v>
+      </c>
+      <c r="H18" s="18">
+        <v>1.41</v>
+      </c>
+      <c r="I18" s="14">
+        <v>63.83</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" si="11"/>
+        <v>6.8042414355628056</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="12"/>
+        <v>1.0815660685154975</v>
+      </c>
+      <c r="M18" s="4">
+        <f t="shared" si="13"/>
+        <v>6.129999999999999</v>
+      </c>
+      <c r="N18" s="18">
+        <v>13.93</v>
+      </c>
+      <c r="O18" s="18">
+        <v>1.18</v>
+      </c>
+      <c r="P18" s="13">
+        <v>4.68</v>
+      </c>
+      <c r="Q18" s="18">
+        <v>0.27</v>
+      </c>
+      <c r="R18" s="14">
+        <v>3.98</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="U18" s="5">
+        <f t="shared" si="1"/>
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="V18" s="4">
+        <f t="shared" si="2"/>
+        <v>18.885999999999999</v>
+      </c>
+      <c r="W18" s="18">
+        <f t="shared" si="3"/>
+        <v>21.411999999999999</v>
+      </c>
+      <c r="X18" s="18">
+        <f t="shared" si="4"/>
+        <v>25.788</v>
+      </c>
+      <c r="Y18" s="13">
+        <f t="shared" si="5"/>
+        <v>17.934000000000001</v>
+      </c>
+      <c r="Z18" s="18">
+        <f t="shared" si="6"/>
+        <v>5.2220000000000004</v>
+      </c>
+      <c r="AA18" s="14">
         <f t="shared" si="7"/>
-        <v>115.77000000000001</v>
-      </c>
-      <c r="E18" s="19">
-        <v>298.27</v>
-      </c>
-      <c r="F18" s="19">
-        <v>30.43</v>
-      </c>
-      <c r="G18" s="14">
-        <v>83.93</v>
-      </c>
-      <c r="H18" s="19">
-        <v>1.41</v>
-      </c>
-      <c r="I18" s="15">
-        <v>63.83</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" s="5">
-        <v>5.3621533442088092</v>
-      </c>
-      <c r="L18" s="5">
-        <v>1.0815660685154975</v>
-      </c>
-      <c r="M18" s="4">
-        <v>6.129999999999999</v>
-      </c>
-      <c r="N18" s="19">
-        <v>13.93</v>
-      </c>
-      <c r="O18" s="19">
-        <v>1.18</v>
-      </c>
-      <c r="P18" s="14">
-        <v>4.68</v>
-      </c>
-      <c r="Q18" s="19">
-        <v>0.27</v>
-      </c>
-      <c r="R18" s="15">
-        <v>3.98</v>
-      </c>
-      <c r="S18" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="T18" s="5">
-        <f>ROUND(B18/K18,3)</f>
-        <v>0.81</v>
-      </c>
-      <c r="U18" s="5">
-        <f>ROUND(C18/L18,3)</f>
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="V18" s="4">
-        <f>ROUND(D18/M18,3)</f>
-        <v>18.885999999999999</v>
-      </c>
-      <c r="W18" s="19">
-        <f>ROUND(E18/N18,3)</f>
-        <v>21.411999999999999</v>
-      </c>
-      <c r="X18" s="19">
-        <f>ROUND(F18/O18,3)</f>
-        <v>25.788</v>
-      </c>
-      <c r="Y18" s="14">
-        <f>ROUND(G18/P18,3)</f>
-        <v>17.934000000000001</v>
-      </c>
-      <c r="Z18" s="19">
-        <f>ROUND(H18/Q18,3)</f>
-        <v>5.2220000000000004</v>
-      </c>
-      <c r="AA18" s="15">
-        <f>ROUND(I18/R18,3)</f>
         <v>16.038</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
-        <v>28</v>
+      <c r="A19" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="B19" s="5">
-        <f t="shared" ref="B19" si="14">D$2/D19</f>
-        <v>4.4906671429847274</v>
+        <f t="shared" si="9"/>
+        <v>4.497495527728085</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19" si="15">D18/D19</f>
-        <v>1.0339376618737164</v>
+        <f t="shared" si="10"/>
+        <v>1.0355098389982111</v>
       </c>
       <c r="D19" s="4">
+        <f t="shared" si="14"/>
+        <v>111.8</v>
+      </c>
+      <c r="E19" s="9">
+        <v>297.63</v>
+      </c>
+      <c r="F19" s="9">
+        <v>30.51</v>
+      </c>
+      <c r="G19" s="13">
+        <v>79.83</v>
+      </c>
+      <c r="H19" s="9">
+        <v>1.46</v>
+      </c>
+      <c r="I19" s="10">
+        <v>63.53</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="11"/>
+        <v>7.6955719557195561</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="12"/>
+        <v>1.1309963099630995</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" si="13"/>
+        <v>5.42</v>
+      </c>
+      <c r="N19" s="9">
+        <v>13.89</v>
+      </c>
+      <c r="O19" s="9">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="P19" s="13">
+        <v>4.01</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R19" s="10">
+        <v>3.59</v>
+      </c>
+      <c r="S19" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="1"/>
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="V19" s="4">
+        <f t="shared" si="2"/>
+        <v>20.626999999999999</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" si="3"/>
+        <v>21.428000000000001</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="Y19" s="13">
+        <f t="shared" si="5"/>
+        <v>19.908000000000001</v>
+      </c>
+      <c r="Z19" s="9">
+        <f t="shared" si="6"/>
+        <v>5.2140000000000004</v>
+      </c>
+      <c r="AA19" s="10">
         <f t="shared" si="7"/>
-        <v>111.97</v>
-      </c>
-      <c r="E19" s="9">
-        <v>292.86</v>
-      </c>
-      <c r="F19" s="9">
-        <v>30.8</v>
-      </c>
-      <c r="G19" s="14">
-        <v>79.72</v>
-      </c>
-      <c r="H19" s="9">
-        <v>1.45</v>
-      </c>
-      <c r="I19" s="10">
-        <v>62.95</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="5">
-        <v>6.0870370370370361</v>
-      </c>
-      <c r="L19" s="5">
-        <v>1.1351851851851849</v>
-      </c>
-      <c r="M19" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="N19" s="9">
-        <v>13.88</v>
-      </c>
-      <c r="O19" s="9">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="P19" s="14">
-        <v>3.97</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>0.27</v>
-      </c>
-      <c r="R19" s="10">
-        <v>3.55</v>
-      </c>
-      <c r="S19" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="T19" s="5">
-        <f>ROUND(B19/K19,3)</f>
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="U19" s="5">
-        <f>ROUND(C19/L19,3)</f>
-        <v>0.91100000000000003</v>
-      </c>
-      <c r="V19" s="4">
-        <f>ROUND(D19/M19,3)</f>
-        <v>20.734999999999999</v>
-      </c>
-      <c r="W19" s="9">
-        <f>ROUND(E19/N19,3)</f>
-        <v>21.099</v>
-      </c>
-      <c r="X19" s="9">
-        <f>ROUND(F19/O19,3)</f>
-        <v>26.552</v>
-      </c>
-      <c r="Y19" s="14">
-        <f>ROUND(G19/P19,3)</f>
-        <v>20.081</v>
-      </c>
-      <c r="Z19" s="9">
-        <f>ROUND(H19/Q19,3)</f>
-        <v>5.37</v>
-      </c>
-      <c r="AA19" s="10">
-        <f>ROUND(I19/R19,3)</f>
-        <v>17.731999999999999</v>
+        <v>17.696000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5">
-        <f t="shared" ref="B20" si="16">D$2/D20</f>
-        <v>4.9858205255329686</v>
-      </c>
-      <c r="C20" s="5">
-        <f t="shared" ref="C20" si="17">D19/D20</f>
-        <v>1.1102627664848785</v>
+      <c r="A20" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2">
+        <f t="shared" si="9"/>
+        <v>5.0825836450015158</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" si="10"/>
+        <v>1.1300919842312747</v>
       </c>
       <c r="D20" s="4">
+        <f t="shared" si="14"/>
+        <v>98.929999999999993</v>
+      </c>
+      <c r="E20" s="9">
+        <v>293.52</v>
+      </c>
+      <c r="F20" s="9">
+        <v>30.99</v>
+      </c>
+      <c r="G20" s="13">
+        <v>66.48</v>
+      </c>
+      <c r="H20" s="9">
+        <v>1.46</v>
+      </c>
+      <c r="I20" s="14">
+        <v>48.15</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="11"/>
+        <v>9.0871459694989092</v>
+      </c>
+      <c r="L20" s="2">
+        <f t="shared" si="12"/>
+        <v>1.1808278867102397</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" si="13"/>
+        <v>4.59</v>
+      </c>
+      <c r="N20" s="9">
+        <v>14.07</v>
+      </c>
+      <c r="O20" s="9">
+        <v>1.17</v>
+      </c>
+      <c r="P20" s="13">
+        <v>3.15</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>0.27</v>
+      </c>
+      <c r="R20" s="14">
+        <v>3.02</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="T20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="U20" s="2">
+        <f t="shared" si="1"/>
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="V20" s="4">
+        <f t="shared" si="2"/>
+        <v>21.553000000000001</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="3"/>
+        <v>20.861000000000001</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="4"/>
+        <v>26.486999999999998</v>
+      </c>
+      <c r="Y20" s="13">
+        <f t="shared" si="5"/>
+        <v>21.105</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="6"/>
+        <v>5.407</v>
+      </c>
+      <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>100.85000000000001</v>
-      </c>
-      <c r="E20" s="9">
-        <v>297.58999999999997</v>
-      </c>
-      <c r="F20" s="9">
-        <v>30.73</v>
-      </c>
-      <c r="G20" s="14">
-        <v>68.73</v>
-      </c>
-      <c r="H20" s="9">
-        <v>1.39</v>
-      </c>
-      <c r="I20" s="15">
-        <v>54.16</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="5">
-        <v>6.0870370370370361</v>
-      </c>
-      <c r="L20" s="5">
-        <v>1</v>
-      </c>
-      <c r="M20" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="N20" s="9">
-        <v>13.8</v>
-      </c>
-      <c r="O20" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="P20" s="14">
-        <v>3.99</v>
-      </c>
-      <c r="Q20" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="R20" s="15">
-        <v>3.54</v>
-      </c>
-      <c r="S20" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="T20" s="5">
-        <f>ROUND(B20/K20,3)</f>
-        <v>0.81899999999999995</v>
-      </c>
-      <c r="U20" s="5">
-        <f>ROUND(C20/L20,3)</f>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="V20" s="4">
-        <f>ROUND(D20/M20,3)</f>
-        <v>18.675999999999998</v>
-      </c>
-      <c r="W20" s="9">
-        <f>ROUND(E20/N20,3)</f>
-        <v>21.564</v>
-      </c>
-      <c r="X20" s="9">
-        <f>ROUND(F20/O20,3)</f>
-        <v>27.195</v>
-      </c>
-      <c r="Y20" s="14">
-        <f>ROUND(G20/P20,3)</f>
-        <v>17.225999999999999</v>
-      </c>
-      <c r="Z20" s="9">
-        <f>ROUND(H20/Q20,3)</f>
-        <v>4.9640000000000004</v>
-      </c>
-      <c r="AA20" s="15">
-        <f>ROUND(I20/R20,3)</f>
-        <v>15.298999999999999</v>
+        <v>15.944000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="5">
-        <f t="shared" ref="B21:B23" si="18">D$2/D21</f>
-        <v>7.0206646188215585</v>
-      </c>
-      <c r="C21" s="5">
-        <f t="shared" ref="C21:C23" si="19">D20/D21</f>
-        <v>1.4081262217257753</v>
+      <c r="A21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2">
+        <f t="shared" si="9"/>
+        <v>7.1728958630527799</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" si="10"/>
+        <v>1.4112696148359483</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" ref="D21:D23" si="20">SUM(F21:H21)</f>
-        <v>71.61999999999999</v>
-      </c>
-      <c r="E21" s="14">
-        <v>308.72000000000003</v>
-      </c>
-      <c r="F21" s="14">
-        <v>27.33</v>
-      </c>
-      <c r="G21" s="14">
-        <v>43.3</v>
-      </c>
-      <c r="H21" s="14">
-        <v>0.99</v>
-      </c>
-      <c r="I21" s="15">
-        <v>35.18</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" s="5">
-        <v>7.5389908256880727</v>
-      </c>
-      <c r="L21" s="5">
-        <v>1.238532110091743</v>
+        <f t="shared" ref="D21:D23" si="15">SUM(F21:H21)</f>
+        <v>70.100000000000009</v>
+      </c>
+      <c r="E21" s="13">
+        <v>309.2</v>
+      </c>
+      <c r="F21" s="13">
+        <v>27.26</v>
+      </c>
+      <c r="G21" s="13">
+        <v>41.8</v>
+      </c>
+      <c r="H21" s="13">
+        <v>1.04</v>
+      </c>
+      <c r="I21" s="14">
+        <v>29.72</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="11"/>
+        <v>11.883190883190881</v>
+      </c>
+      <c r="L21" s="2">
+        <f t="shared" si="12"/>
+        <v>1.3076923076923075</v>
       </c>
       <c r="M21" s="4">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="N21" s="14">
-        <v>11.45</v>
-      </c>
-      <c r="O21" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="P21" s="14">
-        <v>3.28</v>
-      </c>
-      <c r="Q21" s="14">
+        <f t="shared" si="13"/>
+        <v>3.5100000000000002</v>
+      </c>
+      <c r="N21" s="13">
+        <v>11.48</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0.83</v>
+      </c>
+      <c r="P21" s="13">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q21" s="13">
         <v>0.23</v>
       </c>
-      <c r="R21" s="15">
-        <v>3.08</v>
-      </c>
-      <c r="S21" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="T21" s="5">
-        <f t="shared" ref="T21:T23" si="21">ROUND(B21/K21,3)</f>
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="U21" s="5">
-        <f t="shared" ref="U21:U23" si="22">ROUND(C21/L21,3)</f>
-        <v>1.137</v>
+      <c r="R21" s="14">
+        <v>2.17</v>
+      </c>
+      <c r="S21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="T21" s="2">
+        <f t="shared" ref="T21:T23" si="16">ROUND(B21/K21,3)</f>
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="U21" s="2">
+        <f t="shared" ref="U21:U23" si="17">ROUND(C21/L21,3)</f>
+        <v>1.079</v>
       </c>
       <c r="V21" s="4">
-        <f t="shared" ref="V21:V23" si="23">ROUND(D21/M21,3)</f>
-        <v>16.427</v>
-      </c>
-      <c r="W21" s="9">
-        <f t="shared" ref="W21:W23" si="24">ROUND(E21/N21,3)</f>
-        <v>26.962</v>
-      </c>
-      <c r="X21" s="9">
-        <f t="shared" ref="X21:X23" si="25">ROUND(F21/O21,3)</f>
-        <v>32.152999999999999</v>
-      </c>
-      <c r="Y21" s="14">
-        <f t="shared" ref="Y21:Y23" si="26">ROUND(G21/P21,3)</f>
-        <v>13.201000000000001</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" ref="Z21:Z23" si="27">ROUND(H21/Q21,3)</f>
-        <v>4.3040000000000003</v>
-      </c>
-      <c r="AA21" s="15">
-        <f t="shared" ref="AA21:AA23" si="28">ROUND(I21/R21,3)</f>
-        <v>11.422000000000001</v>
+        <f t="shared" ref="V21:V23" si="18">ROUND(D21/M21,3)</f>
+        <v>19.972000000000001</v>
+      </c>
+      <c r="W21" s="13">
+        <f t="shared" ref="W21:W23" si="19">ROUND(E21/N21,3)</f>
+        <v>26.934000000000001</v>
+      </c>
+      <c r="X21" s="13">
+        <f t="shared" ref="X21:X23" si="20">ROUND(F21/O21,3)</f>
+        <v>32.843000000000004</v>
+      </c>
+      <c r="Y21" s="13">
+        <f t="shared" ref="Y21:Y23" si="21">ROUND(G21/P21,3)</f>
+        <v>17.061</v>
+      </c>
+      <c r="Z21" s="13">
+        <f t="shared" ref="Z21:Z23" si="22">ROUND(H21/Q21,3)</f>
+        <v>4.5220000000000002</v>
+      </c>
+      <c r="AA21" s="14">
+        <f t="shared" ref="AA21:AA23" si="23">ROUND(I21/R21,3)</f>
+        <v>13.696</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
-        <v>33</v>
+      <c r="A22" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B22" s="5">
+        <f t="shared" si="9"/>
+        <v>7.0799774711348897</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="10"/>
+        <v>0.98704590256265834</v>
+      </c>
+      <c r="D22" s="4">
+        <f t="shared" si="15"/>
+        <v>71.02000000000001</v>
+      </c>
+      <c r="E22" s="18">
+        <v>310.51</v>
+      </c>
+      <c r="F22" s="13">
+        <v>27.93</v>
+      </c>
+      <c r="G22" s="13">
+        <v>42.19</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="I22" s="14">
+        <v>30.45</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="5">
+        <f t="shared" si="11"/>
+        <v>11.917142857142855</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="12"/>
+        <v>1.0028571428571429</v>
+      </c>
+      <c r="M22" s="4">
+        <f t="shared" si="13"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="N22" s="18">
+        <v>11.59</v>
+      </c>
+      <c r="O22" s="13">
+        <v>0.83</v>
+      </c>
+      <c r="P22" s="13">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="R22" s="14">
+        <v>2.17</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="T22" s="5">
+        <f t="shared" si="16"/>
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="U22" s="5">
+        <f t="shared" si="17"/>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="V22" s="4">
         <f t="shared" si="18"/>
-        <v>9.6566160937199896</v>
-      </c>
-      <c r="C22" s="5">
+        <v>20.291</v>
+      </c>
+      <c r="W22" s="18">
         <f t="shared" si="19"/>
-        <v>1.3754561167658916</v>
-      </c>
-      <c r="D22" s="4">
+        <v>26.791</v>
+      </c>
+      <c r="X22" s="13">
         <f t="shared" si="20"/>
-        <v>52.070000000000007</v>
-      </c>
-      <c r="E22" s="14">
-        <v>310.76</v>
-      </c>
-      <c r="F22" s="14">
-        <v>27.44</v>
-      </c>
-      <c r="G22" s="14">
-        <v>23.6</v>
-      </c>
-      <c r="H22" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="I22" s="15">
-        <v>21.37</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K22" s="5">
-        <v>9.3380681818181817</v>
-      </c>
-      <c r="L22" s="5">
-        <v>1.2386363636363638</v>
-      </c>
-      <c r="M22" s="4">
-        <v>3.52</v>
-      </c>
-      <c r="N22" s="9">
-        <v>11.2</v>
-      </c>
-      <c r="O22" s="9">
-        <v>0.84</v>
-      </c>
-      <c r="P22" s="14">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>0.23</v>
-      </c>
-      <c r="R22" s="14">
-        <v>2.16</v>
-      </c>
-      <c r="S22" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" s="5">
+        <v>33.651000000000003</v>
+      </c>
+      <c r="Y22" s="13">
         <f t="shared" si="21"/>
-        <v>1.034</v>
-      </c>
-      <c r="U22" s="5">
+        <v>17.22</v>
+      </c>
+      <c r="Z22" s="9">
         <f t="shared" si="22"/>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="V22" s="4">
+        <v>4.0910000000000002</v>
+      </c>
+      <c r="AA22" s="14">
         <f t="shared" si="23"/>
-        <v>14.792999999999999</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" si="24"/>
-        <v>27.745999999999999</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" si="25"/>
-        <v>32.667000000000002</v>
-      </c>
-      <c r="Y22" s="14">
-        <f t="shared" si="26"/>
-        <v>9.6329999999999991</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="27"/>
-        <v>4.4779999999999998</v>
-      </c>
-      <c r="AA22" s="15">
-        <f t="shared" si="28"/>
-        <v>9.8940000000000001</v>
+        <v>14.032</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>34</v>
+      <c r="A23" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="B23" s="5">
+        <f t="shared" si="9"/>
+        <v>7.1647192932459385</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" si="10"/>
+        <v>1.0119692220005703</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" si="15"/>
+        <v>70.179999999999993</v>
+      </c>
+      <c r="E23" s="18">
+        <v>307.02999999999997</v>
+      </c>
+      <c r="F23" s="18">
+        <v>27.29</v>
+      </c>
+      <c r="G23" s="18">
+        <v>41.97</v>
+      </c>
+      <c r="H23" s="18">
+        <v>0.92</v>
+      </c>
+      <c r="I23" s="19">
+        <v>30.32</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="11"/>
+        <v>11.849431818181817</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="12"/>
+        <v>0.99431818181818199</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="13"/>
+        <v>3.52</v>
+      </c>
+      <c r="N23" s="18">
+        <v>11.08</v>
+      </c>
+      <c r="O23" s="18">
+        <v>0.84</v>
+      </c>
+      <c r="P23" s="18">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>0.23</v>
+      </c>
+      <c r="R23" s="19">
+        <v>2.17</v>
+      </c>
+      <c r="S23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="16"/>
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="17"/>
+        <v>1.018</v>
+      </c>
+      <c r="V23" s="4">
         <f t="shared" si="18"/>
-        <v>9.5829998094149023</v>
-      </c>
-      <c r="C23" s="5">
+        <v>19.937999999999999</v>
+      </c>
+      <c r="W23" s="18">
         <f t="shared" si="19"/>
-        <v>0.99237659615018103</v>
-      </c>
-      <c r="D23" s="4">
+        <v>27.71</v>
+      </c>
+      <c r="X23" s="18">
         <f t="shared" si="20"/>
-        <v>52.470000000000006</v>
-      </c>
-      <c r="E23" s="19">
-        <v>313.47000000000003</v>
-      </c>
-      <c r="F23" s="19">
-        <v>27.85</v>
-      </c>
-      <c r="G23" s="19">
-        <v>23.63</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0.99</v>
-      </c>
-      <c r="I23" s="20">
-        <v>21.36</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="5">
-        <v>1.4448351648351647</v>
-      </c>
-      <c r="L23" s="5">
-        <v>0.15472527472527473</v>
-      </c>
-      <c r="M23" s="4">
-        <v>22.75</v>
-      </c>
-      <c r="N23" s="9">
-        <v>11.41</v>
-      </c>
-      <c r="O23" s="9">
-        <v>0.84</v>
-      </c>
-      <c r="P23" s="9">
-        <v>21.69</v>
-      </c>
-      <c r="Q23" s="14">
-        <v>0.22</v>
-      </c>
-      <c r="R23" s="9">
-        <v>21.18</v>
-      </c>
-      <c r="S23" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="T23" s="5">
+        <v>32.488</v>
+      </c>
+      <c r="Y23" s="18">
         <f t="shared" si="21"/>
-        <v>6.633</v>
-      </c>
-      <c r="U23" s="5">
+        <v>17.131</v>
+      </c>
+      <c r="Z23" s="18">
         <f t="shared" si="22"/>
-        <v>6.4139999999999997</v>
-      </c>
-      <c r="V23" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="19">
         <f t="shared" si="23"/>
-        <v>2.306</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="24"/>
-        <v>27.472999999999999</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="25"/>
-        <v>33.155000000000001</v>
-      </c>
-      <c r="Y23" s="14">
-        <f t="shared" si="26"/>
-        <v>1.089</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="27"/>
-        <v>4.5</v>
-      </c>
-      <c r="AA23" s="15">
-        <f t="shared" si="28"/>
-        <v>1.008</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="4"/>
-      <c r="G24" s="14"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="4"/>
-      <c r="P24" s="14"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="15"/>
+        <v>13.972</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA6578F-C9E8-4E62-8CE8-0C1C33E13539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF35255-8AFC-4E24-85FE-8AB7830C90B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -2402,95 +2402,95 @@
       </c>
       <c r="B19" s="5">
         <f t="shared" si="9"/>
-        <v>4.497495527728085</v>
+        <v>4.4505222163214722</v>
       </c>
       <c r="C19" s="5">
         <f t="shared" si="10"/>
-        <v>1.0355098389982111</v>
+        <v>1.0246946362187999</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="14"/>
-        <v>111.8</v>
+        <v>112.98</v>
       </c>
       <c r="E19" s="9">
-        <v>297.63</v>
+        <v>297.26</v>
       </c>
       <c r="F19" s="9">
-        <v>30.51</v>
+        <v>31.06</v>
       </c>
       <c r="G19" s="13">
-        <v>79.83</v>
+        <v>80.38</v>
       </c>
       <c r="H19" s="9">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="I19" s="10">
-        <v>63.53</v>
+        <v>63.89</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>24</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="11"/>
-        <v>7.6955719557195561</v>
+        <v>7.7240740740740721</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="12"/>
-        <v>1.1309963099630995</v>
+        <v>1.1351851851851849</v>
       </c>
       <c r="M19" s="4">
         <f t="shared" si="13"/>
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="N19" s="9">
-        <v>13.89</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="O19" s="9">
-        <v>1.1299999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P19" s="13">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="Q19" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R19" s="10">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="S19" s="17" t="s">
         <v>24</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="0"/>
-        <v>0.58399999999999996</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="1"/>
-        <v>0.91600000000000004</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="2"/>
-        <v>20.626999999999999</v>
+        <v>20.922000000000001</v>
       </c>
       <c r="W19" s="9">
         <f t="shared" si="3"/>
-        <v>21.428000000000001</v>
+        <v>17.663</v>
       </c>
       <c r="X19" s="9">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>27.245999999999999</v>
       </c>
       <c r="Y19" s="13">
         <f t="shared" si="5"/>
-        <v>19.908000000000001</v>
+        <v>20.196000000000002</v>
       </c>
       <c r="Z19" s="9">
         <f t="shared" si="6"/>
-        <v>5.2140000000000004</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" s="10">
         <f t="shared" si="7"/>
-        <v>17.696000000000002</v>
+        <v>17.946999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2499,192 +2499,192 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.0825836450015158</v>
+        <v>5.0975263584752621</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1300919842312747</v>
-      </c>
-      <c r="D20" s="4">
+        <v>1.1453771289537711</v>
+      </c>
+      <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>98.929999999999993</v>
-      </c>
-      <c r="E20" s="9">
-        <v>293.52</v>
+        <v>98.640000000000015</v>
+      </c>
+      <c r="E20" s="13">
+        <v>298.05</v>
       </c>
       <c r="F20" s="9">
-        <v>30.99</v>
+        <v>31.04</v>
       </c>
       <c r="G20" s="13">
-        <v>66.48</v>
+        <v>66.17</v>
       </c>
       <c r="H20" s="9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="I20" s="14">
-        <v>48.15</v>
+        <v>47.91</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>29</v>
       </c>
       <c r="K20" s="2">
         <f t="shared" si="11"/>
-        <v>9.0871459694989092</v>
+        <v>9.0871459694989074</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="12"/>
-        <v>1.1808278867102397</v>
-      </c>
-      <c r="M20" s="4">
+        <v>1.1764705882352939</v>
+      </c>
+      <c r="M20" s="6">
         <f t="shared" si="13"/>
-        <v>4.59</v>
-      </c>
-      <c r="N20" s="9">
-        <v>14.07</v>
+        <v>4.5900000000000007</v>
+      </c>
+      <c r="N20" s="13">
+        <v>13.93</v>
       </c>
       <c r="O20" s="9">
-        <v>1.17</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P20" s="13">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="Q20" s="9">
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R20" s="14">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="S20" s="17" t="s">
         <v>29</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
-        <v>0.55900000000000005</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.95699999999999996</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="2"/>
-        <v>21.553000000000001</v>
+        <v>21.49</v>
       </c>
       <c r="W20" s="9">
         <f t="shared" si="3"/>
-        <v>20.861000000000001</v>
+        <v>21.396000000000001</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>26.486999999999998</v>
+        <v>26.991</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>21.105</v>
+        <v>20.94</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>5.407</v>
+        <v>5.1070000000000002</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.944000000000001</v>
+        <v>15.811999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="5">
         <f t="shared" si="9"/>
-        <v>7.1728958630527799</v>
-      </c>
-      <c r="C21" s="2">
+        <v>5.1618930294630934</v>
+      </c>
+      <c r="C21" s="5">
         <f t="shared" si="10"/>
-        <v>1.4112696148359483</v>
+        <v>1.012627040344934</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" ref="D21:D23" si="15">SUM(F21:H21)</f>
-        <v>70.100000000000009</v>
-      </c>
-      <c r="E21" s="13">
-        <v>309.2</v>
-      </c>
-      <c r="F21" s="13">
-        <v>27.26</v>
-      </c>
-      <c r="G21" s="13">
-        <v>41.8</v>
-      </c>
-      <c r="H21" s="13">
-        <v>1.04</v>
-      </c>
-      <c r="I21" s="14">
-        <v>29.72</v>
+        <v>97.41</v>
+      </c>
+      <c r="E21" s="18">
+        <v>292.64999999999998</v>
+      </c>
+      <c r="F21" s="18">
+        <v>30.63</v>
+      </c>
+      <c r="G21" s="18">
+        <v>65.34</v>
+      </c>
+      <c r="H21" s="18">
+        <v>1.44</v>
+      </c>
+      <c r="I21" s="19">
+        <v>46.92</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="5">
         <f t="shared" si="11"/>
-        <v>11.883190883190881</v>
-      </c>
-      <c r="L21" s="2">
+        <v>8.9698924731182768</v>
+      </c>
+      <c r="L21" s="5">
         <f t="shared" si="12"/>
-        <v>1.3076923076923075</v>
+        <v>0.98709677419354847</v>
       </c>
       <c r="M21" s="4">
         <f t="shared" si="13"/>
-        <v>3.5100000000000002</v>
-      </c>
-      <c r="N21" s="13">
-        <v>11.48</v>
-      </c>
-      <c r="O21" s="13">
-        <v>0.83</v>
-      </c>
-      <c r="P21" s="13">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0.23</v>
-      </c>
-      <c r="R21" s="14">
-        <v>2.17</v>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="N21" s="18">
+        <v>13.93</v>
+      </c>
+      <c r="O21" s="18">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="P21" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="Q21" s="18">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R21" s="19">
+        <v>3.1</v>
       </c>
       <c r="S21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" ref="T21:T23" si="16">ROUND(B21/K21,3)</f>
-        <v>0.60399999999999998</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" ref="U21:U23" si="17">ROUND(C21/L21,3)</f>
-        <v>1.079</v>
+        <v>1.026</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" ref="V21:V23" si="18">ROUND(D21/M21,3)</f>
-        <v>19.972000000000001</v>
+        <v>20.948</v>
       </c>
       <c r="W21" s="13">
         <f t="shared" ref="W21:W23" si="19">ROUND(E21/N21,3)</f>
-        <v>26.934000000000001</v>
+        <v>21.009</v>
       </c>
       <c r="X21" s="13">
         <f t="shared" ref="X21:X23" si="20">ROUND(F21/O21,3)</f>
-        <v>32.843000000000004</v>
+        <v>26.405000000000001</v>
       </c>
       <c r="Y21" s="13">
         <f t="shared" ref="Y21:Y23" si="21">ROUND(G21/P21,3)</f>
-        <v>17.061</v>
+        <v>20.419</v>
       </c>
       <c r="Z21" s="13">
         <f t="shared" ref="Z21:Z23" si="22">ROUND(H21/Q21,3)</f>
-        <v>4.5220000000000002</v>
+        <v>4.9660000000000002</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" ref="AA21:AA23" si="23">ROUND(I21/R21,3)</f>
-        <v>13.696</v>
+        <v>15.135</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2693,95 +2693,95 @@
       </c>
       <c r="B22" s="5">
         <f t="shared" si="9"/>
-        <v>7.0799774711348897</v>
+        <v>5.1058082859463854</v>
       </c>
       <c r="C22" s="5">
         <f t="shared" si="10"/>
-        <v>0.98704590256265834</v>
+        <v>0.98913484971567833</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="15"/>
-        <v>71.02000000000001</v>
+        <v>98.47999999999999</v>
       </c>
       <c r="E22" s="18">
-        <v>310.51</v>
-      </c>
-      <c r="F22" s="13">
-        <v>27.93</v>
-      </c>
-      <c r="G22" s="13">
-        <v>42.19</v>
+        <v>293.38</v>
+      </c>
+      <c r="F22" s="18">
+        <v>30.58</v>
+      </c>
+      <c r="G22" s="18">
+        <v>66.489999999999995</v>
       </c>
       <c r="H22" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="I22" s="14">
-        <v>30.45</v>
+        <v>1.41</v>
+      </c>
+      <c r="I22" s="19">
+        <v>48.2</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>26</v>
       </c>
       <c r="K22" s="5">
         <f t="shared" si="11"/>
-        <v>11.917142857142855</v>
+        <v>9.0477223427331861</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="12"/>
-        <v>1.0028571428571429</v>
+        <v>1.0086767895878526</v>
       </c>
       <c r="M22" s="4">
         <f t="shared" si="13"/>
-        <v>3.5000000000000004</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="N22" s="18">
-        <v>11.59</v>
-      </c>
-      <c r="O22" s="13">
-        <v>0.83</v>
-      </c>
-      <c r="P22" s="13">
-        <v>2.4500000000000002</v>
+        <v>14.53</v>
+      </c>
+      <c r="O22" s="18">
+        <v>1.17</v>
+      </c>
+      <c r="P22" s="18">
+        <v>3.16</v>
       </c>
       <c r="Q22" s="9">
-        <v>0.22</v>
-      </c>
-      <c r="R22" s="14">
-        <v>2.17</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R22" s="19">
+        <v>3.03</v>
       </c>
       <c r="S22" s="17" t="s">
         <v>26</v>
       </c>
       <c r="T22" s="5">
         <f t="shared" si="16"/>
-        <v>0.59399999999999997</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="U22" s="5">
         <f t="shared" si="17"/>
-        <v>0.98399999999999999</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="18"/>
-        <v>20.291</v>
+        <v>21.361999999999998</v>
       </c>
       <c r="W22" s="18">
         <f t="shared" si="19"/>
-        <v>26.791</v>
+        <v>20.190999999999999</v>
       </c>
       <c r="X22" s="13">
         <f t="shared" si="20"/>
-        <v>33.651000000000003</v>
+        <v>26.137</v>
       </c>
       <c r="Y22" s="13">
         <f t="shared" si="21"/>
-        <v>17.22</v>
+        <v>21.041</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="22"/>
-        <v>4.0910000000000002</v>
+        <v>5.0359999999999996</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" si="23"/>
-        <v>14.032</v>
+        <v>15.907999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2790,95 +2790,95 @@
       </c>
       <c r="B23" s="5">
         <f t="shared" si="9"/>
-        <v>7.1647192932459385</v>
+        <v>5.0631356358876234</v>
       </c>
       <c r="C23" s="5">
         <f t="shared" si="10"/>
-        <v>1.0119692220005703</v>
+        <v>0.9916423320914306</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="15"/>
-        <v>70.179999999999993</v>
+        <v>99.310000000000016</v>
       </c>
       <c r="E23" s="18">
-        <v>307.02999999999997</v>
+        <v>297.35000000000002</v>
       </c>
       <c r="F23" s="18">
-        <v>27.29</v>
+        <v>31.04</v>
       </c>
       <c r="G23" s="18">
-        <v>41.97</v>
+        <v>66.760000000000005</v>
       </c>
       <c r="H23" s="18">
-        <v>0.92</v>
+        <v>1.51</v>
       </c>
       <c r="I23" s="19">
-        <v>30.32</v>
+        <v>48.14</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>27</v>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="11"/>
-        <v>11.849431818181817</v>
+        <v>9.1269146608315079</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="12"/>
-        <v>0.99431818181818199</v>
+        <v>1.0087527352297594</v>
       </c>
       <c r="M23" s="4">
         <f t="shared" si="13"/>
-        <v>3.52</v>
+        <v>4.57</v>
       </c>
       <c r="N23" s="18">
-        <v>11.08</v>
+        <v>13.77</v>
       </c>
       <c r="O23" s="18">
-        <v>0.84</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P23" s="18">
-        <v>2.4500000000000002</v>
+        <v>3.17</v>
       </c>
       <c r="Q23" s="18">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="R23" s="19">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="S23" s="17" t="s">
         <v>27</v>
       </c>
       <c r="T23" s="5">
         <f t="shared" si="16"/>
-        <v>0.60499999999999998</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" si="17"/>
-        <v>1.018</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="18"/>
-        <v>19.937999999999999</v>
+        <v>21.731000000000002</v>
       </c>
       <c r="W23" s="18">
         <f t="shared" si="19"/>
-        <v>27.71</v>
+        <v>21.594000000000001</v>
       </c>
       <c r="X23" s="18">
         <f t="shared" si="20"/>
-        <v>32.488</v>
+        <v>27.469000000000001</v>
       </c>
       <c r="Y23" s="18">
         <f t="shared" si="21"/>
-        <v>17.131</v>
+        <v>21.06</v>
       </c>
       <c r="Z23" s="18">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>5.593</v>
       </c>
       <c r="AA23" s="19">
         <f t="shared" si="23"/>
-        <v>13.972</v>
+        <v>15.836</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF35255-8AFC-4E24-85FE-8AB7830C90B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F027053-5596-4AA9-955E-FB315FA5AA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="30">
   <si>
     <t>H23</t>
   </si>
@@ -112,12 +112,6 @@
   </si>
   <si>
     <t>H41</t>
-  </si>
-  <si>
-    <t>H42</t>
-  </si>
-  <si>
-    <t>H43</t>
   </si>
   <si>
     <t>H22</t>
@@ -277,7 +271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -333,9 +327,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -652,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -699,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -755,7 +746,7 @@
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -783,7 +774,7 @@
         <v>293.08999999999997</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K2" s="5">
         <v>1</v>
@@ -810,7 +801,7 @@
         <v>33.96</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T2" s="5">
         <f t="shared" ref="T2:T20" si="0">ROUND(B2/K2,3)</f>
@@ -946,11 +937,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B23" si="9">D$2/D4</f>
+        <f t="shared" ref="B4:B21" si="9">D$2/D4</f>
         <v>2.0672614397894993</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C23" si="10">D3/D4</f>
+        <f t="shared" ref="C4:C21" si="10">D3/D4</f>
         <v>1.3659088105907988</v>
       </c>
       <c r="D4" s="6">
@@ -976,15 +967,15 @@
         <v>1</v>
       </c>
       <c r="K4" s="2">
-        <f t="shared" ref="K4:K23" si="11">M$2/M4</f>
+        <f t="shared" ref="K4:K21" si="11">M$2/M4</f>
         <v>1.9852451213707754</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L23" si="12">M3/M4</f>
+        <f t="shared" ref="L4:L21" si="12">M3/M4</f>
         <v>1.0894811994288434</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" ref="M4:M23" si="13">SUM(O4:Q4)</f>
+        <f t="shared" ref="M4:M21" si="13">SUM(O4:Q4)</f>
         <v>21.01</v>
       </c>
       <c r="N4" s="5">
@@ -2107,7 +2098,7 @@
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" s="5">
         <f t="shared" si="9"/>
@@ -2137,7 +2128,7 @@
         <v>63.86</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="11"/>
@@ -2167,7 +2158,7 @@
         <v>5.0199999999999996</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T16" s="5">
         <f t="shared" si="0"/>
@@ -2305,67 +2296,67 @@
       </c>
       <c r="B18" s="5">
         <f t="shared" si="9"/>
-        <v>4.3432668221473598</v>
+        <v>4.3105015002143157</v>
       </c>
       <c r="C18" s="5">
         <f t="shared" si="10"/>
-        <v>1.0002591344908005</v>
+        <v>0.99271324474924982</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="14"/>
-        <v>115.77000000000001</v>
+        <v>116.65</v>
       </c>
       <c r="E18" s="18">
-        <v>298.27</v>
+        <v>296.22000000000003</v>
       </c>
       <c r="F18" s="18">
-        <v>30.43</v>
+        <v>31.01</v>
       </c>
       <c r="G18" s="13">
-        <v>83.93</v>
+        <v>84.19</v>
       </c>
       <c r="H18" s="18">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="I18" s="14">
-        <v>63.83</v>
+        <v>64.33</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K18" s="5">
         <f t="shared" si="11"/>
-        <v>6.8042414355628056</v>
+        <v>6.749190938511326</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="12"/>
-        <v>1.0815660685154975</v>
+        <v>1.0728155339805825</v>
       </c>
       <c r="M18" s="4">
         <f t="shared" si="13"/>
-        <v>6.129999999999999</v>
+        <v>6.18</v>
       </c>
       <c r="N18" s="18">
-        <v>13.93</v>
+        <v>14.18</v>
       </c>
       <c r="O18" s="18">
-        <v>1.18</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P18" s="13">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="Q18" s="18">
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R18" s="14">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="S18" s="17" t="s">
         <v>23</v>
       </c>
       <c r="T18" s="5">
         <f t="shared" si="0"/>
-        <v>0.63800000000000001</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="1"/>
@@ -2373,27 +2364,27 @@
       </c>
       <c r="V18" s="4">
         <f t="shared" si="2"/>
-        <v>18.885999999999999</v>
+        <v>18.875</v>
       </c>
       <c r="W18" s="18">
         <f t="shared" si="3"/>
-        <v>21.411999999999999</v>
+        <v>20.89</v>
       </c>
       <c r="X18" s="18">
         <f t="shared" si="4"/>
-        <v>25.788</v>
+        <v>27.202000000000002</v>
       </c>
       <c r="Y18" s="13">
         <f t="shared" si="5"/>
-        <v>17.934000000000001</v>
+        <v>17.687000000000001</v>
       </c>
       <c r="Z18" s="18">
         <f t="shared" si="6"/>
-        <v>5.2220000000000004</v>
+        <v>5.1790000000000003</v>
       </c>
       <c r="AA18" s="14">
         <f t="shared" si="7"/>
-        <v>16.038</v>
+        <v>16.286000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2402,160 +2393,160 @@
       </c>
       <c r="B19" s="5">
         <f t="shared" si="9"/>
-        <v>4.4505222163214722</v>
+        <v>4.4446212322107304</v>
       </c>
       <c r="C19" s="5">
         <f t="shared" si="10"/>
-        <v>1.0246946362187999</v>
+        <v>1.0311146468664367</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="14"/>
-        <v>112.98</v>
+        <v>113.13000000000001</v>
       </c>
       <c r="E19" s="9">
-        <v>297.26</v>
+        <v>294.64</v>
       </c>
       <c r="F19" s="9">
-        <v>31.06</v>
+        <v>30.59</v>
       </c>
       <c r="G19" s="13">
-        <v>80.38</v>
+        <v>81.010000000000005</v>
       </c>
       <c r="H19" s="9">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I19" s="10">
-        <v>63.89</v>
+        <v>63.79</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>24</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="11"/>
-        <v>7.7240740740740721</v>
+        <v>7.6252285191956117</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="12"/>
-        <v>1.1351851851851849</v>
+        <v>1.129798903107861</v>
       </c>
       <c r="M19" s="4">
         <f t="shared" si="13"/>
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
       <c r="N19" s="9">
-        <v>16.829999999999998</v>
+        <v>14.02</v>
       </c>
       <c r="O19" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="P19" s="13">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R19" s="10">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="S19" s="17" t="s">
         <v>24</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="0"/>
-        <v>0.57599999999999996</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="1"/>
-        <v>0.90300000000000002</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="2"/>
-        <v>20.922000000000001</v>
+        <v>20.681999999999999</v>
       </c>
       <c r="W19" s="9">
         <f t="shared" si="3"/>
-        <v>17.663</v>
+        <v>21.015999999999998</v>
       </c>
       <c r="X19" s="9">
         <f t="shared" si="4"/>
-        <v>27.245999999999999</v>
+        <v>25.923999999999999</v>
       </c>
       <c r="Y19" s="13">
         <f t="shared" si="5"/>
-        <v>20.196000000000002</v>
+        <v>20.253</v>
       </c>
       <c r="Z19" s="9">
         <f t="shared" si="6"/>
-        <v>5.5</v>
+        <v>5.2759999999999998</v>
       </c>
       <c r="AA19" s="10">
         <f t="shared" si="7"/>
-        <v>17.946999999999999</v>
+        <v>17.818000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.0975263584752621</v>
+        <v>5.0453542042946014</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1453771289537711</v>
+        <v>1.1351595424443108</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>98.640000000000015</v>
+        <v>99.66</v>
       </c>
       <c r="E20" s="13">
-        <v>298.05</v>
+        <v>297.94</v>
       </c>
       <c r="F20" s="9">
-        <v>31.04</v>
+        <v>31.28</v>
       </c>
       <c r="G20" s="13">
-        <v>66.17</v>
+        <v>66.989999999999995</v>
       </c>
       <c r="H20" s="9">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="I20" s="14">
-        <v>47.91</v>
+        <v>48.31</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K20" s="2">
         <f t="shared" si="11"/>
-        <v>9.0871459694989074</v>
+        <v>8.989224137931032</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="12"/>
-        <v>1.1764705882352939</v>
+        <v>1.1788793103448274</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="13"/>
-        <v>4.5900000000000007</v>
+        <v>4.6400000000000006</v>
       </c>
       <c r="N20" s="13">
-        <v>13.93</v>
+        <v>13.85</v>
       </c>
       <c r="O20" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="P20" s="13">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="Q20" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R20" s="14">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
@@ -2563,322 +2554,128 @@
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.97399999999999998</v>
-      </c>
-      <c r="V20" s="4">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="V20" s="6">
         <f t="shared" si="2"/>
-        <v>21.49</v>
-      </c>
-      <c r="W20" s="9">
+        <v>21.478000000000002</v>
+      </c>
+      <c r="W20" s="13">
         <f t="shared" si="3"/>
-        <v>21.396000000000001</v>
+        <v>21.512</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>26.991</v>
+        <v>26.507999999999999</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>20.94</v>
+        <v>21.065999999999999</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>5.1070000000000002</v>
+        <v>4.9640000000000004</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.811999999999999</v>
+        <v>15.685</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="2">
         <f t="shared" si="9"/>
-        <v>5.1618930294630934</v>
-      </c>
-      <c r="C21" s="5">
+        <v>5.6049492810166086</v>
+      </c>
+      <c r="C21" s="2">
         <f t="shared" si="10"/>
-        <v>1.012627040344934</v>
-      </c>
-      <c r="D21" s="4">
-        <f t="shared" ref="D21:D23" si="15">SUM(F21:H21)</f>
-        <v>97.41</v>
+        <v>1.1109129417010366</v>
+      </c>
+      <c r="D21" s="6">
+        <f t="shared" ref="D21" si="15">SUM(F21:H21)</f>
+        <v>89.71</v>
       </c>
       <c r="E21" s="18">
-        <v>292.64999999999998</v>
+        <v>297.38</v>
       </c>
       <c r="F21" s="18">
-        <v>30.63</v>
-      </c>
-      <c r="G21" s="18">
-        <v>65.34</v>
+        <v>30.52</v>
+      </c>
+      <c r="G21" s="13">
+        <v>57.78</v>
       </c>
       <c r="H21" s="18">
-        <v>1.44</v>
-      </c>
-      <c r="I21" s="19">
-        <v>46.92</v>
+        <v>1.41</v>
+      </c>
+      <c r="I21" s="14">
+        <v>45.42</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="2">
         <f t="shared" si="11"/>
-        <v>8.9698924731182768</v>
-      </c>
-      <c r="L21" s="5">
+        <v>10.94750656167979</v>
+      </c>
+      <c r="L21" s="2">
         <f t="shared" si="12"/>
-        <v>0.98709677419354847</v>
-      </c>
-      <c r="M21" s="4">
+        <v>1.2178477690288716</v>
+      </c>
+      <c r="M21" s="6">
         <f t="shared" si="13"/>
-        <v>4.6500000000000004</v>
+        <v>3.8099999999999996</v>
       </c>
       <c r="N21" s="18">
-        <v>13.93</v>
+        <v>14.01</v>
       </c>
       <c r="O21" s="18">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="P21" s="18">
-        <v>3.2</v>
+        <v>1.17</v>
+      </c>
+      <c r="P21" s="13">
+        <v>2.36</v>
       </c>
       <c r="Q21" s="18">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="R21" s="19">
-        <v>3.1</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R21" s="14">
+        <v>1.88</v>
       </c>
       <c r="S21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="2">
-        <f t="shared" ref="T21:T23" si="16">ROUND(B21/K21,3)</f>
-        <v>0.57499999999999996</v>
+        <f t="shared" ref="T21" si="16">ROUND(B21/K21,3)</f>
+        <v>0.51200000000000001</v>
       </c>
       <c r="U21" s="2">
-        <f t="shared" ref="U21:U23" si="17">ROUND(C21/L21,3)</f>
-        <v>1.026</v>
-      </c>
-      <c r="V21" s="4">
-        <f t="shared" ref="V21:V23" si="18">ROUND(D21/M21,3)</f>
-        <v>20.948</v>
-      </c>
-      <c r="W21" s="13">
-        <f t="shared" ref="W21:W23" si="19">ROUND(E21/N21,3)</f>
-        <v>21.009</v>
-      </c>
-      <c r="X21" s="13">
-        <f t="shared" ref="X21:X23" si="20">ROUND(F21/O21,3)</f>
-        <v>26.405000000000001</v>
+        <f t="shared" ref="U21" si="17">ROUND(C21/L21,3)</f>
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="V21" s="6">
+        <f t="shared" ref="V21" si="18">ROUND(D21/M21,3)</f>
+        <v>23.545999999999999</v>
+      </c>
+      <c r="W21" s="18">
+        <f t="shared" ref="W21" si="19">ROUND(E21/N21,3)</f>
+        <v>21.225999999999999</v>
+      </c>
+      <c r="X21" s="18">
+        <f t="shared" ref="X21" si="20">ROUND(F21/O21,3)</f>
+        <v>26.085000000000001</v>
       </c>
       <c r="Y21" s="13">
-        <f t="shared" ref="Y21:Y23" si="21">ROUND(G21/P21,3)</f>
-        <v>20.419</v>
-      </c>
-      <c r="Z21" s="13">
-        <f t="shared" ref="Z21:Z23" si="22">ROUND(H21/Q21,3)</f>
-        <v>4.9660000000000002</v>
+        <f t="shared" ref="Y21" si="21">ROUND(G21/P21,3)</f>
+        <v>24.483000000000001</v>
+      </c>
+      <c r="Z21" s="18">
+        <f t="shared" ref="Z21" si="22">ROUND(H21/Q21,3)</f>
+        <v>5.0359999999999996</v>
       </c>
       <c r="AA21" s="14">
-        <f t="shared" ref="AA21:AA23" si="23">ROUND(I21/R21,3)</f>
-        <v>15.135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="5">
-        <f t="shared" si="9"/>
-        <v>5.1058082859463854</v>
-      </c>
-      <c r="C22" s="5">
-        <f t="shared" si="10"/>
-        <v>0.98913484971567833</v>
-      </c>
-      <c r="D22" s="4">
-        <f t="shared" si="15"/>
-        <v>98.47999999999999</v>
-      </c>
-      <c r="E22" s="18">
-        <v>293.38</v>
-      </c>
-      <c r="F22" s="18">
-        <v>30.58</v>
-      </c>
-      <c r="G22" s="18">
-        <v>66.489999999999995</v>
-      </c>
-      <c r="H22" s="9">
-        <v>1.41</v>
-      </c>
-      <c r="I22" s="19">
-        <v>48.2</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="5">
-        <f t="shared" si="11"/>
-        <v>9.0477223427331861</v>
-      </c>
-      <c r="L22" s="5">
-        <f t="shared" si="12"/>
-        <v>1.0086767895878526</v>
-      </c>
-      <c r="M22" s="4">
-        <f t="shared" si="13"/>
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="N22" s="18">
-        <v>14.53</v>
-      </c>
-      <c r="O22" s="18">
-        <v>1.17</v>
-      </c>
-      <c r="P22" s="18">
-        <v>3.16</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="R22" s="19">
-        <v>3.03</v>
-      </c>
-      <c r="S22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="T22" s="5">
-        <f t="shared" si="16"/>
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="U22" s="5">
-        <f t="shared" si="17"/>
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="V22" s="4">
-        <f t="shared" si="18"/>
-        <v>21.361999999999998</v>
-      </c>
-      <c r="W22" s="18">
-        <f t="shared" si="19"/>
-        <v>20.190999999999999</v>
-      </c>
-      <c r="X22" s="13">
-        <f t="shared" si="20"/>
-        <v>26.137</v>
-      </c>
-      <c r="Y22" s="13">
-        <f t="shared" si="21"/>
-        <v>21.041</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="22"/>
-        <v>5.0359999999999996</v>
-      </c>
-      <c r="AA22" s="14">
-        <f t="shared" si="23"/>
-        <v>15.907999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="5">
-        <f t="shared" si="9"/>
-        <v>5.0631356358876234</v>
-      </c>
-      <c r="C23" s="5">
-        <f t="shared" si="10"/>
-        <v>0.9916423320914306</v>
-      </c>
-      <c r="D23" s="4">
-        <f t="shared" si="15"/>
-        <v>99.310000000000016</v>
-      </c>
-      <c r="E23" s="18">
-        <v>297.35000000000002</v>
-      </c>
-      <c r="F23" s="18">
-        <v>31.04</v>
-      </c>
-      <c r="G23" s="18">
-        <v>66.760000000000005</v>
-      </c>
-      <c r="H23" s="18">
-        <v>1.51</v>
-      </c>
-      <c r="I23" s="19">
-        <v>48.14</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="5">
-        <f t="shared" si="11"/>
-        <v>9.1269146608315079</v>
-      </c>
-      <c r="L23" s="5">
-        <f t="shared" si="12"/>
-        <v>1.0087527352297594</v>
-      </c>
-      <c r="M23" s="4">
-        <f t="shared" si="13"/>
-        <v>4.57</v>
-      </c>
-      <c r="N23" s="18">
-        <v>13.77</v>
-      </c>
-      <c r="O23" s="18">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="P23" s="18">
-        <v>3.17</v>
-      </c>
-      <c r="Q23" s="18">
-        <v>0.27</v>
-      </c>
-      <c r="R23" s="19">
-        <v>3.04</v>
-      </c>
-      <c r="S23" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T23" s="5">
-        <f t="shared" si="16"/>
-        <v>0.55500000000000005</v>
-      </c>
-      <c r="U23" s="5">
-        <f t="shared" si="17"/>
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="V23" s="4">
-        <f t="shared" si="18"/>
-        <v>21.731000000000002</v>
-      </c>
-      <c r="W23" s="18">
-        <f t="shared" si="19"/>
-        <v>21.594000000000001</v>
-      </c>
-      <c r="X23" s="18">
-        <f t="shared" si="20"/>
-        <v>27.469000000000001</v>
-      </c>
-      <c r="Y23" s="18">
-        <f t="shared" si="21"/>
-        <v>21.06</v>
-      </c>
-      <c r="Z23" s="18">
-        <f t="shared" si="22"/>
-        <v>5.593</v>
-      </c>
-      <c r="AA23" s="19">
-        <f t="shared" si="23"/>
-        <v>15.836</v>
+        <f t="shared" ref="AA21" si="23">ROUND(I21/R21,3)</f>
+        <v>24.16</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F027053-5596-4AA9-955E-FB315FA5AA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BB4089-8124-4587-BA4E-6201C4A7FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="31">
   <si>
     <t>H23</t>
   </si>
@@ -127,6 +127,10 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H42</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -643,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2490,95 +2494,95 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.0453542042946014</v>
+        <v>5.1042533752918473</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1351595424443108</v>
+        <v>1.1484113287991067</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>99.66</v>
-      </c>
-      <c r="E20" s="13">
-        <v>297.94</v>
+        <v>98.51</v>
+      </c>
+      <c r="E20" s="18">
+        <v>303.99</v>
       </c>
       <c r="F20" s="9">
-        <v>31.28</v>
+        <v>30.92</v>
       </c>
       <c r="G20" s="13">
-        <v>66.989999999999995</v>
+        <v>66.17</v>
       </c>
       <c r="H20" s="9">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="I20" s="14">
-        <v>48.31</v>
+        <v>48.2</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="K20" s="2">
         <f t="shared" si="11"/>
-        <v>8.989224137931032</v>
+        <v>8.9892241379310338</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="12"/>
-        <v>1.1788793103448274</v>
+        <v>1.1788793103448276</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="13"/>
-        <v>4.6400000000000006</v>
-      </c>
-      <c r="N20" s="13">
-        <v>13.85</v>
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="N20" s="18">
+        <v>14.29</v>
       </c>
       <c r="O20" s="9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P20" s="13">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="Q20" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R20" s="14">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="S20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
-        <v>0.56100000000000005</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.96299999999999997</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="2"/>
-        <v>21.478000000000002</v>
-      </c>
-      <c r="W20" s="13">
+        <v>21.231000000000002</v>
+      </c>
+      <c r="W20" s="18">
         <f t="shared" si="3"/>
-        <v>21.512</v>
+        <v>21.273</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>26.507999999999999</v>
+        <v>25.983000000000001</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>21.065999999999999</v>
+        <v>20.873999999999999</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>4.9640000000000004</v>
+        <v>5.0709999999999997</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.685</v>
+        <v>15.803000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2587,95 +2591,192 @@
       </c>
       <c r="B21" s="2">
         <f t="shared" si="9"/>
-        <v>5.6049492810166086</v>
+        <v>5.5751191928151682</v>
       </c>
       <c r="C21" s="2">
         <f t="shared" si="10"/>
-        <v>1.1109129417010366</v>
+        <v>1.0922496950881475</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" ref="D21" si="15">SUM(F21:H21)</f>
-        <v>89.71</v>
+        <v>90.189999999999984</v>
       </c>
       <c r="E21" s="18">
-        <v>297.38</v>
+        <v>310</v>
       </c>
       <c r="F21" s="18">
-        <v>30.52</v>
+        <v>30.97</v>
       </c>
       <c r="G21" s="13">
-        <v>57.78</v>
+        <v>57.73</v>
       </c>
       <c r="H21" s="18">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="I21" s="14">
-        <v>45.42</v>
+        <v>45.9</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="2">
         <f t="shared" si="11"/>
-        <v>10.94750656167979</v>
+        <v>10.640306122448978</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="12"/>
-        <v>1.2178477690288716</v>
+        <v>1.1836734693877551</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="13"/>
-        <v>3.8099999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="N21" s="18">
-        <v>14.01</v>
+        <v>14.51</v>
       </c>
       <c r="O21" s="18">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="P21" s="13">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" s="18">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R21" s="14">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="S21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" ref="T21" si="16">ROUND(B21/K21,3)</f>
-        <v>0.51200000000000001</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" ref="U21" si="17">ROUND(C21/L21,3)</f>
-        <v>0.91200000000000003</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="V21" s="6">
         <f t="shared" ref="V21" si="18">ROUND(D21/M21,3)</f>
-        <v>23.545999999999999</v>
+        <v>23.007999999999999</v>
       </c>
       <c r="W21" s="18">
         <f t="shared" ref="W21" si="19">ROUND(E21/N21,3)</f>
-        <v>21.225999999999999</v>
+        <v>21.364999999999998</v>
       </c>
       <c r="X21" s="18">
         <f t="shared" ref="X21" si="20">ROUND(F21/O21,3)</f>
-        <v>26.085000000000001</v>
+        <v>25.594999999999999</v>
       </c>
       <c r="Y21" s="13">
         <f t="shared" ref="Y21" si="21">ROUND(G21/P21,3)</f>
-        <v>24.483000000000001</v>
+        <v>23.855</v>
       </c>
       <c r="Z21" s="18">
         <f t="shared" ref="Z21" si="22">ROUND(H21/Q21,3)</f>
-        <v>5.0359999999999996</v>
+        <v>5.1379999999999999</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" ref="AA21" si="23">ROUND(I21/R21,3)</f>
-        <v>24.16</v>
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="2">
+        <f t="shared" ref="B22" si="24">D$2/D22</f>
+        <v>7.1301758366420867</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" ref="C22" si="25">D21/D22</f>
+        <v>1.2789279636982416</v>
+      </c>
+      <c r="D22" s="6">
+        <f t="shared" ref="D22" si="26">SUM(F22:H22)</f>
+        <v>70.52</v>
+      </c>
+      <c r="E22" s="9">
+        <v>294.91000000000003</v>
+      </c>
+      <c r="F22" s="9">
+        <v>30.52</v>
+      </c>
+      <c r="G22" s="13">
+        <v>38.43</v>
+      </c>
+      <c r="H22" s="9">
+        <v>1.57</v>
+      </c>
+      <c r="I22" s="14">
+        <v>27.83</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" ref="K22" si="27">M$2/M22</f>
+        <v>13.116352201257861</v>
+      </c>
+      <c r="L22" s="2">
+        <f t="shared" ref="L22" si="28">M21/M22</f>
+        <v>1.2327044025157234</v>
+      </c>
+      <c r="M22" s="6">
+        <f t="shared" ref="M22" si="29">SUM(O22:Q22)</f>
+        <v>3.1799999999999997</v>
+      </c>
+      <c r="N22" s="9">
+        <v>13.81</v>
+      </c>
+      <c r="O22" s="9">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="P22" s="13">
+        <v>1.76</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R22" s="14">
+        <v>1.34</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="T22" s="2">
+        <f t="shared" ref="T22" si="30">ROUND(B22/K22,3)</f>
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="U22" s="2">
+        <f t="shared" ref="U22" si="31">ROUND(C22/L22,3)</f>
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="V22" s="6">
+        <f t="shared" ref="V22" si="32">ROUND(D22/M22,3)</f>
+        <v>22.175999999999998</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" ref="W22" si="33">ROUND(E22/N22,3)</f>
+        <v>21.355</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" ref="X22" si="34">ROUND(F22/O22,3)</f>
+        <v>26.771999999999998</v>
+      </c>
+      <c r="Y22" s="13">
+        <f t="shared" ref="Y22" si="35">ROUND(G22/P22,3)</f>
+        <v>21.835000000000001</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22" si="36">ROUND(H22/Q22,3)</f>
+        <v>5.6070000000000002</v>
+      </c>
+      <c r="AA22" s="14">
+        <f t="shared" ref="AA22" si="37">ROUND(I22/R22,3)</f>
+        <v>20.768999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BB4089-8124-4587-BA4E-6201C4A7FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2B738B-C50D-4B78-B9D3-8915A9275B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
   <si>
     <t>H23</t>
   </si>
@@ -131,6 +131,10 @@
   </si>
   <si>
     <t>H42</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H43</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -647,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2494,95 +2498,95 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.1042533752918473</v>
+        <v>5.1125571936959835</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1484113287991067</v>
+        <v>1.1502796136248095</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>98.51</v>
+        <v>98.35</v>
       </c>
       <c r="E20" s="18">
-        <v>303.99</v>
+        <v>298.58999999999997</v>
       </c>
       <c r="F20" s="9">
-        <v>30.92</v>
+        <v>30.47</v>
       </c>
       <c r="G20" s="13">
-        <v>66.17</v>
+        <v>66.5</v>
       </c>
       <c r="H20" s="9">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="I20" s="14">
-        <v>48.2</v>
+        <v>48.19</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="K20" s="2">
         <f t="shared" si="11"/>
-        <v>8.9892241379310338</v>
+        <v>9.0281385281385269</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="12"/>
-        <v>1.1788793103448276</v>
+        <v>1.1839826839826839</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="13"/>
-        <v>4.6399999999999997</v>
+        <v>4.62</v>
       </c>
       <c r="N20" s="18">
-        <v>14.29</v>
+        <v>14.67</v>
       </c>
       <c r="O20" s="9">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P20" s="13">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="Q20" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R20" s="14">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="S20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
-        <v>0.56799999999999995</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.97399999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="2"/>
-        <v>21.231000000000002</v>
+        <v>21.288</v>
       </c>
       <c r="W20" s="18">
         <f t="shared" si="3"/>
-        <v>21.273</v>
+        <v>20.353999999999999</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>25.983000000000001</v>
+        <v>26.042999999999999</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>20.873999999999999</v>
+        <v>21.044</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>5.0709999999999997</v>
+        <v>4.7590000000000003</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.803000000000001</v>
+        <v>15.904</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2591,95 +2595,95 @@
       </c>
       <c r="B21" s="2">
         <f t="shared" si="9"/>
-        <v>5.5751191928151682</v>
+        <v>5.5813075813075814</v>
       </c>
       <c r="C21" s="2">
         <f t="shared" si="10"/>
-        <v>1.0922496950881475</v>
+        <v>1.0916860916860918</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" ref="D21" si="15">SUM(F21:H21)</f>
-        <v>90.189999999999984</v>
+        <v>90.089999999999989</v>
       </c>
       <c r="E21" s="18">
-        <v>310</v>
+        <v>297.12</v>
       </c>
       <c r="F21" s="18">
-        <v>30.97</v>
+        <v>31.05</v>
       </c>
       <c r="G21" s="13">
-        <v>57.73</v>
+        <v>57.41</v>
       </c>
       <c r="H21" s="18">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="I21" s="14">
-        <v>45.9</v>
+        <v>44.34</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="2">
         <f t="shared" si="11"/>
-        <v>10.640306122448978</v>
+        <v>10.976315789473682</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="12"/>
-        <v>1.1836734693877551</v>
+        <v>1.2157894736842105</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="13"/>
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="N21" s="18">
-        <v>14.51</v>
+        <v>13.86</v>
       </c>
       <c r="O21" s="18">
-        <v>1.21</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P21" s="13">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" s="18">
         <v>0.28999999999999998</v>
       </c>
       <c r="R21" s="14">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="S21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" ref="T21" si="16">ROUND(B21/K21,3)</f>
-        <v>0.52400000000000002</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" ref="U21" si="17">ROUND(C21/L21,3)</f>
-        <v>0.92300000000000004</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="V21" s="6">
         <f t="shared" ref="V21" si="18">ROUND(D21/M21,3)</f>
-        <v>23.007999999999999</v>
+        <v>23.707999999999998</v>
       </c>
       <c r="W21" s="18">
         <f t="shared" ref="W21" si="19">ROUND(E21/N21,3)</f>
-        <v>21.364999999999998</v>
+        <v>21.437000000000001</v>
       </c>
       <c r="X21" s="18">
         <f t="shared" ref="X21" si="20">ROUND(F21/O21,3)</f>
-        <v>25.594999999999999</v>
+        <v>26.766999999999999</v>
       </c>
       <c r="Y21" s="13">
         <f t="shared" ref="Y21" si="21">ROUND(G21/P21,3)</f>
-        <v>23.855</v>
+        <v>24.43</v>
       </c>
       <c r="Z21" s="18">
         <f t="shared" ref="Z21" si="22">ROUND(H21/Q21,3)</f>
-        <v>5.1379999999999999</v>
+        <v>5.6210000000000004</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" ref="AA21" si="23">ROUND(I21/R21,3)</f>
-        <v>23.66</v>
+        <v>23.337</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2688,51 +2692,51 @@
       </c>
       <c r="B22" s="2">
         <f t="shared" ref="B22" si="24">D$2/D22</f>
-        <v>7.1301758366420867</v>
+        <v>7.1291648943711898</v>
       </c>
       <c r="C22" s="2">
         <f t="shared" ref="C22" si="25">D21/D22</f>
-        <v>1.2789279636982416</v>
+        <v>1.277328796256912</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22" si="26">SUM(F22:H22)</f>
-        <v>70.52</v>
+        <v>70.529999999999987</v>
       </c>
       <c r="E22" s="9">
-        <v>294.91000000000003</v>
+        <v>298.99</v>
       </c>
       <c r="F22" s="9">
-        <v>30.52</v>
+        <v>30.56</v>
       </c>
       <c r="G22" s="13">
-        <v>38.43</v>
+        <v>38.4</v>
       </c>
       <c r="H22" s="9">
         <v>1.57</v>
       </c>
       <c r="I22" s="14">
-        <v>27.83</v>
+        <v>27.43</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" ref="K22" si="27">M$2/M22</f>
-        <v>13.116352201257861</v>
+        <f t="shared" ref="K22:K23" si="27">M$2/M22</f>
+        <v>13.034374999999997</v>
       </c>
       <c r="L22" s="2">
-        <f t="shared" ref="L22" si="28">M21/M22</f>
-        <v>1.2327044025157234</v>
+        <f t="shared" ref="L22:L23" si="28">M21/M22</f>
+        <v>1.1874999999999998</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" ref="M22" si="29">SUM(O22:Q22)</f>
-        <v>3.1799999999999997</v>
+        <f t="shared" ref="M22:M23" si="29">SUM(O22:Q22)</f>
+        <v>3.2</v>
       </c>
       <c r="N22" s="9">
-        <v>13.81</v>
+        <v>13.98</v>
       </c>
       <c r="O22" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P22" s="13">
         <v>1.76</v>
@@ -2748,27 +2752,27 @@
       </c>
       <c r="T22" s="2">
         <f t="shared" ref="T22" si="30">ROUND(B22/K22,3)</f>
-        <v>0.54400000000000004</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="U22" s="2">
         <f t="shared" ref="U22" si="31">ROUND(C22/L22,3)</f>
-        <v>1.0369999999999999</v>
+        <v>1.0760000000000001</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22" si="32">ROUND(D22/M22,3)</f>
-        <v>22.175999999999998</v>
+        <v>22.041</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" ref="W22" si="33">ROUND(E22/N22,3)</f>
-        <v>21.355</v>
+        <v>21.387</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" ref="X22" si="34">ROUND(F22/O22,3)</f>
-        <v>26.771999999999998</v>
+        <v>26.344999999999999</v>
       </c>
       <c r="Y22" s="13">
         <f t="shared" ref="Y22" si="35">ROUND(G22/P22,3)</f>
-        <v>21.835000000000001</v>
+        <v>21.818000000000001</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" ref="Z22" si="36">ROUND(H22/Q22,3)</f>
@@ -2776,7 +2780,104 @@
       </c>
       <c r="AA22" s="14">
         <f t="shared" ref="AA22" si="37">ROUND(I22/R22,3)</f>
-        <v>20.768999999999998</v>
+        <v>20.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="5">
+        <f t="shared" ref="B23" si="38">D$2/D23</f>
+        <v>6.867249385413821</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" ref="C23" si="39">D22/D23</f>
+        <v>0.96326140398798121</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" ref="D23" si="40">SUM(F23:H23)</f>
+        <v>73.22</v>
+      </c>
+      <c r="E23" s="13">
+        <v>249.18</v>
+      </c>
+      <c r="F23" s="9">
+        <v>31.08</v>
+      </c>
+      <c r="G23" s="9">
+        <v>40.54</v>
+      </c>
+      <c r="H23" s="9">
+        <v>1.6</v>
+      </c>
+      <c r="I23" s="10">
+        <v>28.46</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="27"/>
+        <v>13.116352201257861</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="28"/>
+        <v>1.0062893081761008</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="29"/>
+        <v>3.1799999999999997</v>
+      </c>
+      <c r="N23" s="13">
+        <v>11.59</v>
+      </c>
+      <c r="O23" s="9">
+        <v>1.17</v>
+      </c>
+      <c r="P23" s="9">
+        <v>1.72</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R23" s="10">
+        <v>1.33</v>
+      </c>
+      <c r="S23" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" ref="T23" si="41">ROUND(B23/K23,3)</f>
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" ref="U23" si="42">ROUND(C23/L23,3)</f>
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="V23" s="6">
+        <f t="shared" ref="V23" si="43">ROUND(D23/M23,3)</f>
+        <v>23.024999999999999</v>
+      </c>
+      <c r="W23" s="13">
+        <f t="shared" ref="W23" si="44">ROUND(E23/N23,3)</f>
+        <v>21.5</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" ref="X23" si="45">ROUND(F23/O23,3)</f>
+        <v>26.564</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" ref="Y23" si="46">ROUND(G23/P23,3)</f>
+        <v>23.57</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" ref="Z23" si="47">ROUND(H23/Q23,3)</f>
+        <v>5.5170000000000003</v>
+      </c>
+      <c r="AA23" s="10">
+        <f t="shared" ref="AA23" si="48">ROUND(I23/R23,3)</f>
+        <v>21.398</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2B738B-C50D-4B78-B9D3-8915A9275B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E2ACE4-D005-4648-972D-1B84E11DF018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="33">
   <si>
     <t>H23</t>
   </si>
@@ -135,6 +135,10 @@
   </si>
   <si>
     <t>H43</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H44</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2498,30 +2502,30 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.1125571936959835</v>
+        <v>5.1544848795489484</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1502796136248095</v>
+        <v>1.1597129677088673</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>98.35</v>
+        <v>97.55</v>
       </c>
       <c r="E20" s="18">
-        <v>298.58999999999997</v>
+        <v>299.93</v>
       </c>
       <c r="F20" s="9">
-        <v>30.47</v>
+        <v>30.56</v>
       </c>
       <c r="G20" s="13">
-        <v>66.5</v>
+        <v>65.53</v>
       </c>
       <c r="H20" s="9">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="I20" s="14">
-        <v>48.19</v>
+        <v>47.15</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>27</v>
@@ -2539,54 +2543,54 @@
         <v>4.62</v>
       </c>
       <c r="N20" s="18">
-        <v>14.67</v>
+        <v>15.78</v>
       </c>
       <c r="O20" s="9">
-        <v>1.17</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P20" s="13">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R20" s="14">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="S20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
-        <v>0.56599999999999995</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.97199999999999998</v>
+        <v>0.98</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="2"/>
-        <v>21.288</v>
+        <v>21.114999999999998</v>
       </c>
       <c r="W20" s="18">
         <f t="shared" si="3"/>
-        <v>20.353999999999999</v>
+        <v>19.007000000000001</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>26.042999999999999</v>
+        <v>26.806999999999999</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>21.044</v>
+        <v>20.478000000000002</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>4.7590000000000003</v>
+        <v>5.2140000000000004</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.904</v>
+        <v>15.308</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2595,95 +2599,95 @@
       </c>
       <c r="B21" s="2">
         <f t="shared" si="9"/>
-        <v>5.5813075813075814</v>
+        <v>5.5844069302532198</v>
       </c>
       <c r="C21" s="2">
         <f t="shared" si="10"/>
-        <v>1.0916860916860918</v>
+        <v>1.083407374500222</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" ref="D21" si="15">SUM(F21:H21)</f>
-        <v>90.089999999999989</v>
+        <v>90.04</v>
       </c>
       <c r="E21" s="18">
-        <v>297.12</v>
+        <v>294.04000000000002</v>
       </c>
       <c r="F21" s="18">
-        <v>31.05</v>
+        <v>30.85</v>
       </c>
       <c r="G21" s="13">
-        <v>57.41</v>
+        <v>57.77</v>
       </c>
       <c r="H21" s="18">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="I21" s="14">
-        <v>44.34</v>
+        <v>44.64</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="2">
         <f t="shared" si="11"/>
-        <v>10.976315789473682</v>
+        <v>11.034391534391531</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="12"/>
-        <v>1.2157894736842105</v>
+        <v>1.2222222222222221</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="13"/>
-        <v>3.8</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="N21" s="18">
-        <v>13.86</v>
+        <v>13.8</v>
       </c>
       <c r="O21" s="18">
         <v>1.1599999999999999</v>
       </c>
       <c r="P21" s="13">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" s="18">
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R21" s="14">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" ref="T21" si="16">ROUND(B21/K21,3)</f>
-        <v>0.50800000000000001</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" ref="U21" si="17">ROUND(C21/L21,3)</f>
-        <v>0.89800000000000002</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="V21" s="6">
         <f t="shared" ref="V21" si="18">ROUND(D21/M21,3)</f>
-        <v>23.707999999999998</v>
+        <v>23.82</v>
       </c>
       <c r="W21" s="18">
         <f t="shared" ref="W21" si="19">ROUND(E21/N21,3)</f>
-        <v>21.437000000000001</v>
+        <v>21.306999999999999</v>
       </c>
       <c r="X21" s="18">
         <f t="shared" ref="X21" si="20">ROUND(F21/O21,3)</f>
-        <v>26.766999999999999</v>
+        <v>26.594999999999999</v>
       </c>
       <c r="Y21" s="13">
         <f t="shared" ref="Y21" si="21">ROUND(G21/P21,3)</f>
-        <v>24.43</v>
+        <v>24.687999999999999</v>
       </c>
       <c r="Z21" s="18">
         <f t="shared" ref="Z21" si="22">ROUND(H21/Q21,3)</f>
-        <v>5.6210000000000004</v>
+        <v>5.0709999999999997</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" ref="AA21" si="23">ROUND(I21/R21,3)</f>
-        <v>23.337</v>
+        <v>23.619</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2692,51 +2696,51 @@
       </c>
       <c r="B22" s="2">
         <f t="shared" ref="B22" si="24">D$2/D22</f>
-        <v>7.1291648943711898</v>
+        <v>7.0969654199011991</v>
       </c>
       <c r="C22" s="2">
         <f t="shared" ref="C22" si="25">D21/D22</f>
-        <v>1.277328796256912</v>
+        <v>1.2708539167254767</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22" si="26">SUM(F22:H22)</f>
-        <v>70.529999999999987</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="E22" s="9">
-        <v>298.99</v>
+        <v>292.88</v>
       </c>
       <c r="F22" s="9">
-        <v>30.56</v>
+        <v>31.07</v>
       </c>
       <c r="G22" s="13">
-        <v>38.4</v>
+        <v>38.159999999999997</v>
       </c>
       <c r="H22" s="9">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="I22" s="14">
-        <v>27.43</v>
+        <v>27.31</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" ref="K22:K23" si="27">M$2/M22</f>
-        <v>13.034374999999997</v>
+        <f t="shared" ref="K22:K24" si="27">M$2/M22</f>
+        <v>12.913312693498449</v>
       </c>
       <c r="L22" s="2">
-        <f t="shared" ref="L22:L23" si="28">M21/M22</f>
-        <v>1.1874999999999998</v>
+        <f t="shared" ref="L22:L24" si="28">M21/M22</f>
+        <v>1.1702786377708978</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" ref="M22:M23" si="29">SUM(O22:Q22)</f>
-        <v>3.2</v>
+        <f t="shared" ref="M22:M24" si="29">SUM(O22:Q22)</f>
+        <v>3.2300000000000004</v>
       </c>
       <c r="N22" s="9">
-        <v>13.98</v>
+        <v>13.67</v>
       </c>
       <c r="O22" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="P22" s="13">
         <v>1.76</v>
@@ -2745,42 +2749,42 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="R22" s="14">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="T22" s="2">
         <f t="shared" ref="T22" si="30">ROUND(B22/K22,3)</f>
-        <v>0.54700000000000004</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="U22" s="2">
         <f t="shared" ref="U22" si="31">ROUND(C22/L22,3)</f>
-        <v>1.0760000000000001</v>
+        <v>1.0860000000000001</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22" si="32">ROUND(D22/M22,3)</f>
-        <v>22.041</v>
+        <v>21.934999999999999</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" ref="W22" si="33">ROUND(E22/N22,3)</f>
-        <v>21.387</v>
+        <v>21.425000000000001</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" ref="X22" si="34">ROUND(F22/O22,3)</f>
-        <v>26.344999999999999</v>
+        <v>26.109000000000002</v>
       </c>
       <c r="Y22" s="13">
         <f t="shared" ref="Y22" si="35">ROUND(G22/P22,3)</f>
-        <v>21.818000000000001</v>
+        <v>21.681999999999999</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" ref="Z22" si="36">ROUND(H22/Q22,3)</f>
-        <v>5.6070000000000002</v>
+        <v>5.7859999999999996</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" ref="AA22" si="37">ROUND(I22/R22,3)</f>
-        <v>20.47</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2789,30 +2793,30 @@
       </c>
       <c r="B23" s="5">
         <f t="shared" ref="B23" si="38">D$2/D23</f>
-        <v>6.867249385413821</v>
+        <v>6.9182718767198663</v>
       </c>
       <c r="C23" s="5">
         <f t="shared" ref="C23" si="39">D22/D23</f>
-        <v>0.96326140398798121</v>
+        <v>0.9748211337369288</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" ref="D23" si="40">SUM(F23:H23)</f>
-        <v>73.22</v>
+        <v>72.680000000000007</v>
       </c>
       <c r="E23" s="13">
-        <v>249.18</v>
+        <v>245.49</v>
       </c>
       <c r="F23" s="9">
-        <v>31.08</v>
+        <v>30.67</v>
       </c>
       <c r="G23" s="9">
-        <v>40.54</v>
+        <v>40.42</v>
       </c>
       <c r="H23" s="9">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I23" s="10">
-        <v>28.46</v>
+        <v>28.89</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>31</v>
@@ -2823,61 +2827,158 @@
       </c>
       <c r="L23" s="5">
         <f t="shared" si="28"/>
-        <v>1.0062893081761008</v>
+        <v>1.0157232704402519</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="29"/>
         <v>3.1799999999999997</v>
       </c>
       <c r="N23" s="13">
-        <v>11.59</v>
+        <v>11.52</v>
       </c>
       <c r="O23" s="9">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P23" s="9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R23" s="10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S23" s="17" t="s">
         <v>31</v>
       </c>
       <c r="T23" s="5">
         <f t="shared" ref="T23" si="41">ROUND(B23/K23,3)</f>
-        <v>0.52400000000000002</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" ref="U23" si="42">ROUND(C23/L23,3)</f>
-        <v>0.95699999999999996</v>
+        <v>0.96</v>
       </c>
       <c r="V23" s="6">
         <f t="shared" ref="V23" si="43">ROUND(D23/M23,3)</f>
-        <v>23.024999999999999</v>
+        <v>22.855</v>
       </c>
       <c r="W23" s="13">
         <f t="shared" ref="W23" si="44">ROUND(E23/N23,3)</f>
-        <v>21.5</v>
+        <v>21.31</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" ref="X23" si="45">ROUND(F23/O23,3)</f>
-        <v>26.564</v>
+        <v>25.773</v>
       </c>
       <c r="Y23" s="9">
         <f t="shared" ref="Y23" si="46">ROUND(G23/P23,3)</f>
-        <v>23.57</v>
+        <v>23.637</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" ref="Z23" si="47">ROUND(H23/Q23,3)</f>
-        <v>5.5170000000000003</v>
+        <v>5.6790000000000003</v>
       </c>
       <c r="AA23" s="10">
         <f t="shared" ref="AA23" si="48">ROUND(I23/R23,3)</f>
-        <v>21.398</v>
+        <v>22.053000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" ref="B24" si="49">D$2/D24</f>
+        <v>7.9901477832512304</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24" si="50">D23/D24</f>
+        <v>1.154934053710472</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" ref="D24" si="51">SUM(F24:H24)</f>
+        <v>62.93</v>
+      </c>
+      <c r="E24" s="9">
+        <v>244.43</v>
+      </c>
+      <c r="F24" s="9">
+        <v>31.14</v>
+      </c>
+      <c r="G24" s="13">
+        <v>30.27</v>
+      </c>
+      <c r="H24" s="9">
+        <v>1.52</v>
+      </c>
+      <c r="I24" s="14">
+        <v>21.93</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="2">
+        <f t="shared" si="27"/>
+        <v>15.057761732851981</v>
+      </c>
+      <c r="L24" s="2">
+        <f t="shared" si="28"/>
+        <v>1.1480144404332127</v>
+      </c>
+      <c r="M24" s="6">
+        <f t="shared" si="29"/>
+        <v>2.7700000000000005</v>
+      </c>
+      <c r="N24" s="9">
+        <v>11.6</v>
+      </c>
+      <c r="O24" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="P24" s="13">
+        <v>1.38</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R24" s="14">
+        <v>1.02</v>
+      </c>
+      <c r="S24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="2">
+        <f t="shared" ref="T24" si="52">ROUND(B24/K24,3)</f>
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="U24" s="2">
+        <f t="shared" ref="U24" si="53">ROUND(C24/L24,3)</f>
+        <v>1.006</v>
+      </c>
+      <c r="V24" s="6">
+        <f t="shared" ref="V24" si="54">ROUND(D24/M24,3)</f>
+        <v>22.718</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" ref="W24" si="55">ROUND(E24/N24,3)</f>
+        <v>21.071999999999999</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" ref="X24" si="56">ROUND(F24/O24,3)</f>
+        <v>28.053999999999998</v>
+      </c>
+      <c r="Y24" s="13">
+        <f t="shared" ref="Y24" si="57">ROUND(G24/P24,3)</f>
+        <v>21.934999999999999</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" ref="Z24" si="58">ROUND(H24/Q24,3)</f>
+        <v>5.4290000000000003</v>
+      </c>
+      <c r="AA24" s="14">
+        <f t="shared" ref="AA24" si="59">ROUND(I24/R24,3)</f>
+        <v>21.5</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E2ACE4-D005-4648-972D-1B84E11DF018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40F3EE1-8130-4EFB-AB8F-8DD5C2028172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="34">
   <si>
     <t>H23</t>
   </si>
@@ -139,6 +139,10 @@
   </si>
   <si>
     <t>H44</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H45</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2502,95 +2506,95 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.1544848795489484</v>
+        <v>5.110998170359828</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1597129677088673</v>
+        <v>1.1499288473266924</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>97.55</v>
+        <v>98.38000000000001</v>
       </c>
       <c r="E20" s="18">
-        <v>299.93</v>
+        <v>293.24</v>
       </c>
       <c r="F20" s="9">
-        <v>30.56</v>
+        <v>30.45</v>
       </c>
       <c r="G20" s="13">
-        <v>65.53</v>
+        <v>66.5</v>
       </c>
       <c r="H20" s="9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="I20" s="14">
-        <v>47.15</v>
+        <v>48.2</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="K20" s="2">
         <f t="shared" si="11"/>
-        <v>9.0281385281385269</v>
+        <v>9.0477223427331879</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="12"/>
-        <v>1.1839826839826839</v>
+        <v>1.1865509761388287</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="13"/>
-        <v>4.62</v>
+        <v>4.6099999999999994</v>
       </c>
       <c r="N20" s="18">
-        <v>15.78</v>
+        <v>13.7</v>
       </c>
       <c r="O20" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P20" s="13">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q20" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="R20" s="14">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="S20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
-        <v>0.57099999999999995</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="2"/>
-        <v>21.114999999999998</v>
+        <v>21.341000000000001</v>
       </c>
       <c r="W20" s="18">
         <f t="shared" si="3"/>
-        <v>19.007000000000001</v>
+        <v>21.404</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>26.806999999999999</v>
+        <v>26.25</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>20.478000000000002</v>
+        <v>20.911999999999999</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>5.2140000000000004</v>
+        <v>5.2960000000000003</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.308</v>
+        <v>15.855</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2599,54 +2603,54 @@
       </c>
       <c r="B21" s="2">
         <f t="shared" si="9"/>
-        <v>5.5844069302532198</v>
+        <v>5.6130832775173021</v>
       </c>
       <c r="C21" s="2">
         <f t="shared" si="10"/>
-        <v>1.083407374500222</v>
+        <v>1.0982362134405002</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" ref="D21" si="15">SUM(F21:H21)</f>
-        <v>90.04</v>
+        <v>89.58</v>
       </c>
       <c r="E21" s="18">
-        <v>294.04000000000002</v>
+        <v>294.22000000000003</v>
       </c>
       <c r="F21" s="18">
-        <v>30.85</v>
+        <v>30.48</v>
       </c>
       <c r="G21" s="13">
-        <v>57.77</v>
+        <v>57.69</v>
       </c>
       <c r="H21" s="18">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I21" s="14">
-        <v>44.64</v>
+        <v>44.44</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="2">
         <f t="shared" si="11"/>
-        <v>11.034391534391531</v>
+        <v>10.976315789473682</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="12"/>
-        <v>1.2222222222222221</v>
+        <v>1.213157894736842</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="13"/>
-        <v>3.7800000000000002</v>
+        <v>3.8</v>
       </c>
       <c r="N21" s="18">
-        <v>13.8</v>
+        <v>13.74</v>
       </c>
       <c r="O21" s="18">
-        <v>1.1599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="P21" s="13">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" s="18">
         <v>0.28000000000000003</v>
@@ -2659,35 +2663,35 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" ref="T21" si="16">ROUND(B21/K21,3)</f>
-        <v>0.50600000000000001</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" ref="U21" si="17">ROUND(C21/L21,3)</f>
-        <v>0.88600000000000001</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="V21" s="6">
         <f t="shared" ref="V21" si="18">ROUND(D21/M21,3)</f>
-        <v>23.82</v>
+        <v>23.574000000000002</v>
       </c>
       <c r="W21" s="18">
         <f t="shared" ref="W21" si="19">ROUND(E21/N21,3)</f>
-        <v>21.306999999999999</v>
+        <v>21.413</v>
       </c>
       <c r="X21" s="18">
         <f t="shared" ref="X21" si="20">ROUND(F21/O21,3)</f>
-        <v>26.594999999999999</v>
+        <v>26.050999999999998</v>
       </c>
       <c r="Y21" s="13">
         <f t="shared" ref="Y21" si="21">ROUND(G21/P21,3)</f>
-        <v>24.687999999999999</v>
+        <v>24.548999999999999</v>
       </c>
       <c r="Z21" s="18">
         <f t="shared" ref="Z21" si="22">ROUND(H21/Q21,3)</f>
-        <v>5.0709999999999997</v>
+        <v>5.0359999999999996</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" ref="AA21" si="23">ROUND(I21/R21,3)</f>
-        <v>23.619</v>
+        <v>23.513000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2696,54 +2700,54 @@
       </c>
       <c r="B22" s="2">
         <f t="shared" ref="B22" si="24">D$2/D22</f>
-        <v>7.0969654199011991</v>
+        <v>7.1954779622209495</v>
       </c>
       <c r="C22" s="2">
         <f t="shared" ref="C22" si="25">D21/D22</f>
-        <v>1.2708539167254767</v>
+        <v>1.2819118488838008</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22" si="26">SUM(F22:H22)</f>
-        <v>70.849999999999994</v>
+        <v>69.88</v>
       </c>
       <c r="E22" s="9">
-        <v>292.88</v>
+        <v>292.68</v>
       </c>
       <c r="F22" s="9">
-        <v>31.07</v>
+        <v>30.4</v>
       </c>
       <c r="G22" s="13">
-        <v>38.159999999999997</v>
+        <v>37.909999999999997</v>
       </c>
       <c r="H22" s="9">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="I22" s="14">
-        <v>27.31</v>
+        <v>26.96</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="2">
         <f t="shared" ref="K22:K24" si="27">M$2/M22</f>
-        <v>12.913312693498449</v>
+        <v>13.075235109717864</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" ref="L22:L24" si="28">M21/M22</f>
-        <v>1.1702786377708978</v>
+        <v>1.1912225705329151</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" ref="M22:M24" si="29">SUM(O22:Q22)</f>
-        <v>3.2300000000000004</v>
+        <v>3.1900000000000004</v>
       </c>
       <c r="N22" s="9">
-        <v>13.67</v>
+        <v>13.98</v>
       </c>
       <c r="O22" s="9">
-        <v>1.19</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P22" s="13">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" s="9">
         <v>0.28000000000000003</v>
@@ -2760,31 +2764,31 @@
       </c>
       <c r="U22" s="2">
         <f t="shared" ref="U22" si="31">ROUND(C22/L22,3)</f>
-        <v>1.0860000000000001</v>
+        <v>1.0760000000000001</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22" si="32">ROUND(D22/M22,3)</f>
-        <v>21.934999999999999</v>
+        <v>21.905999999999999</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" ref="W22" si="33">ROUND(E22/N22,3)</f>
-        <v>21.425000000000001</v>
+        <v>20.936</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" ref="X22" si="34">ROUND(F22/O22,3)</f>
-        <v>26.109000000000002</v>
+        <v>26.207000000000001</v>
       </c>
       <c r="Y22" s="13">
         <f t="shared" ref="Y22" si="35">ROUND(G22/P22,3)</f>
-        <v>21.681999999999999</v>
+        <v>21.663</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" ref="Z22" si="36">ROUND(H22/Q22,3)</f>
-        <v>5.7859999999999996</v>
+        <v>5.6070000000000002</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" ref="AA22" si="37">ROUND(I22/R22,3)</f>
-        <v>20.23</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2793,95 +2797,95 @@
       </c>
       <c r="B23" s="5">
         <f t="shared" ref="B23" si="38">D$2/D23</f>
-        <v>6.9182718767198663</v>
+        <v>6.8373674190916507</v>
       </c>
       <c r="C23" s="5">
         <f t="shared" ref="C23" si="39">D22/D23</f>
-        <v>0.9748211337369288</v>
+        <v>0.95023116671199348</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" ref="D23" si="40">SUM(F23:H23)</f>
-        <v>72.680000000000007</v>
+        <v>73.539999999999992</v>
       </c>
       <c r="E23" s="13">
-        <v>245.49</v>
+        <v>244.68</v>
       </c>
       <c r="F23" s="9">
-        <v>30.67</v>
+        <v>30.89</v>
       </c>
       <c r="G23" s="9">
-        <v>40.42</v>
+        <v>40.619999999999997</v>
       </c>
       <c r="H23" s="9">
-        <v>1.59</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="I23" s="10">
-        <v>28.89</v>
+        <v>28.79</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>31</v>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="27"/>
-        <v>13.116352201257861</v>
+        <v>13.368589743589743</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="28"/>
-        <v>1.0157232704402519</v>
+        <v>1.0224358974358976</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="29"/>
-        <v>3.1799999999999997</v>
+        <v>3.1199999999999997</v>
       </c>
       <c r="N23" s="13">
-        <v>11.52</v>
+        <v>11.49</v>
       </c>
       <c r="O23" s="9">
-        <v>1.19</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P23" s="9">
         <v>1.71</v>
       </c>
       <c r="Q23" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="R23" s="10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S23" s="17" t="s">
         <v>31</v>
       </c>
       <c r="T23" s="5">
         <f t="shared" ref="T23" si="41">ROUND(B23/K23,3)</f>
-        <v>0.52700000000000002</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" ref="U23" si="42">ROUND(C23/L23,3)</f>
-        <v>0.96</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="V23" s="6">
         <f t="shared" ref="V23" si="43">ROUND(D23/M23,3)</f>
-        <v>22.855</v>
+        <v>23.571000000000002</v>
       </c>
       <c r="W23" s="13">
         <f t="shared" ref="W23" si="44">ROUND(E23/N23,3)</f>
-        <v>21.31</v>
+        <v>21.295000000000002</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" ref="X23" si="45">ROUND(F23/O23,3)</f>
-        <v>25.773</v>
+        <v>27.096</v>
       </c>
       <c r="Y23" s="9">
         <f t="shared" ref="Y23" si="46">ROUND(G23/P23,3)</f>
-        <v>23.637</v>
+        <v>23.754000000000001</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" ref="Z23" si="47">ROUND(H23/Q23,3)</f>
-        <v>5.6790000000000003</v>
+        <v>7.5190000000000001</v>
       </c>
       <c r="AA23" s="10">
         <f t="shared" ref="AA23" si="48">ROUND(I23/R23,3)</f>
-        <v>22.053000000000001</v>
+        <v>22.146000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2890,51 +2894,51 @@
       </c>
       <c r="B24" s="2">
         <f t="shared" ref="B24" si="49">D$2/D24</f>
-        <v>7.9901477832512304</v>
+        <v>8.1165456012913637</v>
       </c>
       <c r="C24" s="2">
         <f t="shared" ref="C24" si="50">D23/D24</f>
-        <v>1.154934053710472</v>
+        <v>1.1870863599677159</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" ref="D24" si="51">SUM(F24:H24)</f>
-        <v>62.93</v>
+        <v>61.949999999999996</v>
       </c>
       <c r="E24" s="9">
-        <v>244.43</v>
+        <v>244.04</v>
       </c>
       <c r="F24" s="9">
-        <v>31.14</v>
+        <v>30.65</v>
       </c>
       <c r="G24" s="13">
-        <v>30.27</v>
+        <v>29.9</v>
       </c>
       <c r="H24" s="9">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="I24" s="14">
-        <v>21.93</v>
+        <v>21.71</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="K24" s="2">
         <f t="shared" si="27"/>
-        <v>15.057761732851981</v>
+        <v>14.843416370106761</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="28"/>
-        <v>1.1480144404332127</v>
+        <v>1.1103202846975089</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="29"/>
-        <v>2.7700000000000005</v>
+        <v>2.8099999999999996</v>
       </c>
       <c r="N24" s="9">
-        <v>11.6</v>
+        <v>11.52</v>
       </c>
       <c r="O24" s="9">
-        <v>1.1100000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P24" s="13">
         <v>1.38</v>
@@ -2943,42 +2947,139 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="R24" s="14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="S24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="T24" s="2">
         <f t="shared" ref="T24" si="52">ROUND(B24/K24,3)</f>
-        <v>0.53100000000000003</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="U24" s="2">
         <f t="shared" ref="U24" si="53">ROUND(C24/L24,3)</f>
-        <v>1.006</v>
+        <v>1.069</v>
       </c>
       <c r="V24" s="6">
         <f t="shared" ref="V24" si="54">ROUND(D24/M24,3)</f>
-        <v>22.718</v>
+        <v>22.045999999999999</v>
       </c>
       <c r="W24" s="9">
         <f t="shared" ref="W24" si="55">ROUND(E24/N24,3)</f>
-        <v>21.071999999999999</v>
+        <v>21.184000000000001</v>
       </c>
       <c r="X24" s="9">
         <f t="shared" ref="X24" si="56">ROUND(F24/O24,3)</f>
-        <v>28.053999999999998</v>
+        <v>26.652000000000001</v>
       </c>
       <c r="Y24" s="13">
         <f t="shared" ref="Y24" si="57">ROUND(G24/P24,3)</f>
-        <v>21.934999999999999</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="Z24" s="9">
         <f t="shared" ref="Z24" si="58">ROUND(H24/Q24,3)</f>
-        <v>5.4290000000000003</v>
+        <v>5</v>
       </c>
       <c r="AA24" s="14">
         <f t="shared" ref="AA24" si="59">ROUND(I24/R24,3)</f>
-        <v>21.5</v>
+        <v>21.077999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" ref="B25" si="60">D$2/D25</f>
+        <v>8.3929227174094461</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" ref="C25" si="61">D24/D25</f>
+        <v>1.0340510766149225</v>
+      </c>
+      <c r="D25" s="6">
+        <f t="shared" ref="D25" si="62">SUM(F25:H25)</f>
+        <v>59.91</v>
+      </c>
+      <c r="E25" s="9">
+        <v>243.54</v>
+      </c>
+      <c r="F25" s="9">
+        <v>30.77</v>
+      </c>
+      <c r="G25" s="13">
+        <v>27.63</v>
+      </c>
+      <c r="H25" s="9">
+        <v>1.51</v>
+      </c>
+      <c r="I25" s="14">
+        <v>18.61</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K25" s="2">
+        <f t="shared" ref="K25" si="63">M$2/M25</f>
+        <v>15.680451127819545</v>
+      </c>
+      <c r="L25" s="2">
+        <f t="shared" ref="L25" si="64">M24/M25</f>
+        <v>1.0563909774436089</v>
+      </c>
+      <c r="M25" s="6">
+        <f t="shared" ref="M25" si="65">SUM(O25:Q25)</f>
+        <v>2.66</v>
+      </c>
+      <c r="N25" s="9">
+        <v>11.69</v>
+      </c>
+      <c r="O25" s="9">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="P25" s="13">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R25" s="14">
+        <v>0.91</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="T25" s="2">
+        <f t="shared" ref="T25" si="66">ROUND(B25/K25,3)</f>
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="U25" s="2">
+        <f t="shared" ref="U25" si="67">ROUND(C25/L25,3)</f>
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="V25" s="6">
+        <f t="shared" ref="V25" si="68">ROUND(D25/M25,3)</f>
+        <v>22.523</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" ref="W25" si="69">ROUND(E25/N25,3)</f>
+        <v>20.832999999999998</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" ref="X25" si="70">ROUND(F25/O25,3)</f>
+        <v>26.991</v>
+      </c>
+      <c r="Y25" s="13">
+        <f t="shared" ref="Y25" si="71">ROUND(G25/P25,3)</f>
+        <v>22.282</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" ref="Z25" si="72">ROUND(H25/Q25,3)</f>
+        <v>5.3929999999999998</v>
+      </c>
+      <c r="AA25" s="14">
+        <f t="shared" ref="AA25" si="73">ROUND(I25/R25,3)</f>
+        <v>20.451000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40F3EE1-8130-4EFB-AB8F-8DD5C2028172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99442910-663A-497F-A117-46EC2DCD4AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
   <si>
     <t>H23</t>
   </si>
@@ -143,6 +143,10 @@
   </si>
   <si>
     <t>H45</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H46</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -659,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2506,95 +2510,95 @@
       </c>
       <c r="B20" s="2">
         <f t="shared" si="9"/>
-        <v>5.110998170359828</v>
+        <v>5.1151576805696832</v>
       </c>
       <c r="C20" s="2">
         <f t="shared" si="10"/>
-        <v>1.1499288473266924</v>
+        <v>1.1508646998982706</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="14"/>
-        <v>98.38000000000001</v>
+        <v>98.300000000000011</v>
       </c>
       <c r="E20" s="18">
-        <v>293.24</v>
+        <v>293.48</v>
       </c>
       <c r="F20" s="9">
-        <v>30.45</v>
+        <v>30.47</v>
       </c>
       <c r="G20" s="13">
-        <v>66.5</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H20" s="9">
         <v>1.43</v>
       </c>
       <c r="I20" s="14">
-        <v>48.2</v>
+        <v>47.88</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="K20" s="2">
         <f t="shared" si="11"/>
-        <v>9.0477223427331879</v>
+        <v>9.0281385281385269</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="12"/>
-        <v>1.1865509761388287</v>
+        <v>1.1839826839826839</v>
       </c>
       <c r="M20" s="6">
         <f t="shared" si="13"/>
-        <v>4.6099999999999994</v>
+        <v>4.62</v>
       </c>
       <c r="N20" s="18">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="O20" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="P20" s="13">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="Q20" s="9">
-        <v>0.27</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R20" s="14">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="S20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="0"/>
-        <v>0.56499999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="1"/>
-        <v>0.96899999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="2"/>
-        <v>21.341000000000001</v>
+        <v>21.277000000000001</v>
       </c>
       <c r="W20" s="18">
         <f t="shared" si="3"/>
-        <v>21.404</v>
+        <v>21.266999999999999</v>
       </c>
       <c r="X20" s="9">
         <f t="shared" si="4"/>
-        <v>26.25</v>
+        <v>26.042999999999999</v>
       </c>
       <c r="Y20" s="13">
         <f t="shared" si="5"/>
-        <v>20.911999999999999</v>
+        <v>21.013000000000002</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="6"/>
-        <v>5.2960000000000003</v>
+        <v>4.931</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v>15.855</v>
+        <v>15.802</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2603,54 +2607,54 @@
       </c>
       <c r="B21" s="2">
         <f t="shared" si="9"/>
-        <v>5.6130832775173021</v>
+        <v>5.6281620774569054</v>
       </c>
       <c r="C21" s="2">
         <f t="shared" si="10"/>
-        <v>1.0982362134405002</v>
+        <v>1.1002910230579808</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" ref="D21" si="15">SUM(F21:H21)</f>
-        <v>89.58</v>
+        <v>89.34</v>
       </c>
       <c r="E21" s="18">
-        <v>294.22000000000003</v>
+        <v>294.85000000000002</v>
       </c>
       <c r="F21" s="18">
-        <v>30.48</v>
+        <v>30.53</v>
       </c>
       <c r="G21" s="13">
-        <v>57.69</v>
+        <v>57.4</v>
       </c>
       <c r="H21" s="18">
         <v>1.41</v>
       </c>
       <c r="I21" s="14">
-        <v>44.44</v>
+        <v>44.6</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="2">
         <f t="shared" si="11"/>
-        <v>10.976315789473682</v>
+        <v>11.00527704485488</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="12"/>
-        <v>1.213157894736842</v>
+        <v>1.2189973614775726</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="13"/>
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="N21" s="18">
-        <v>13.74</v>
+        <v>14.3</v>
       </c>
       <c r="O21" s="18">
-        <v>1.17</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P21" s="13">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" s="18">
         <v>0.28000000000000003</v>
@@ -2667,23 +2671,23 @@
       </c>
       <c r="U21" s="2">
         <f t="shared" ref="U21" si="17">ROUND(C21/L21,3)</f>
-        <v>0.90500000000000003</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="V21" s="6">
         <f t="shared" ref="V21" si="18">ROUND(D21/M21,3)</f>
-        <v>23.574000000000002</v>
+        <v>23.573</v>
       </c>
       <c r="W21" s="18">
         <f t="shared" ref="W21" si="19">ROUND(E21/N21,3)</f>
-        <v>21.413</v>
+        <v>20.619</v>
       </c>
       <c r="X21" s="18">
         <f t="shared" ref="X21" si="20">ROUND(F21/O21,3)</f>
-        <v>26.050999999999998</v>
+        <v>26.547999999999998</v>
       </c>
       <c r="Y21" s="13">
         <f t="shared" ref="Y21" si="21">ROUND(G21/P21,3)</f>
-        <v>24.548999999999999</v>
+        <v>24.321999999999999</v>
       </c>
       <c r="Z21" s="18">
         <f t="shared" ref="Z21" si="22">ROUND(H21/Q21,3)</f>
@@ -2691,7 +2695,7 @@
       </c>
       <c r="AA21" s="14">
         <f t="shared" ref="AA21" si="23">ROUND(I21/R21,3)</f>
-        <v>23.513000000000002</v>
+        <v>23.597999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2700,95 +2704,95 @@
       </c>
       <c r="B22" s="2">
         <f t="shared" ref="B22" si="24">D$2/D22</f>
-        <v>7.1954779622209495</v>
+        <v>7.137260468417316</v>
       </c>
       <c r="C22" s="2">
         <f t="shared" ref="C22" si="25">D21/D22</f>
-        <v>1.2819118488838008</v>
+        <v>1.2681334279630945</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22" si="26">SUM(F22:H22)</f>
-        <v>69.88</v>
+        <v>70.45</v>
       </c>
       <c r="E22" s="9">
-        <v>292.68</v>
+        <v>296.97000000000003</v>
       </c>
       <c r="F22" s="9">
         <v>30.4</v>
       </c>
       <c r="G22" s="13">
-        <v>37.909999999999997</v>
+        <v>38.47</v>
       </c>
       <c r="H22" s="9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I22" s="14">
-        <v>26.96</v>
+        <v>27.24</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="2">
         <f t="shared" ref="K22:K24" si="27">M$2/M22</f>
-        <v>13.075235109717864</v>
+        <v>12.677811550151974</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" ref="L22:L24" si="28">M21/M22</f>
-        <v>1.1912225705329151</v>
+        <v>1.1519756838905775</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" ref="M22:M24" si="29">SUM(O22:Q22)</f>
-        <v>3.1900000000000004</v>
+        <v>3.29</v>
       </c>
       <c r="N22" s="9">
-        <v>13.98</v>
+        <v>14.05</v>
       </c>
       <c r="O22" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="P22" s="13">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R22" s="14">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="T22" s="2">
         <f t="shared" ref="T22" si="30">ROUND(B22/K22,3)</f>
-        <v>0.55000000000000004</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="U22" s="2">
         <f t="shared" ref="U22" si="31">ROUND(C22/L22,3)</f>
-        <v>1.0760000000000001</v>
+        <v>1.101</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22" si="32">ROUND(D22/M22,3)</f>
-        <v>21.905999999999999</v>
+        <v>21.413</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" ref="W22" si="33">ROUND(E22/N22,3)</f>
-        <v>20.936</v>
+        <v>21.137</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" ref="X22" si="34">ROUND(F22/O22,3)</f>
-        <v>26.207000000000001</v>
+        <v>24.715</v>
       </c>
       <c r="Y22" s="13">
         <f t="shared" ref="Y22" si="35">ROUND(G22/P22,3)</f>
-        <v>21.663</v>
+        <v>21.611999999999998</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" ref="Z22" si="36">ROUND(H22/Q22,3)</f>
-        <v>5.6070000000000002</v>
+        <v>5.6429999999999998</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" ref="AA22" si="37">ROUND(I22/R22,3)</f>
-        <v>19.97</v>
+        <v>19.597000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2797,95 +2801,95 @@
       </c>
       <c r="B23" s="5">
         <f t="shared" ref="B23" si="38">D$2/D23</f>
-        <v>6.8373674190916507</v>
+        <v>6.9392768423958042</v>
       </c>
       <c r="C23" s="5">
         <f t="shared" ref="C23" si="39">D22/D23</f>
-        <v>0.95023116671199348</v>
+        <v>0.97226055754899265</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" ref="D23" si="40">SUM(F23:H23)</f>
-        <v>73.539999999999992</v>
+        <v>72.459999999999994</v>
       </c>
       <c r="E23" s="13">
-        <v>244.68</v>
+        <v>244.74</v>
       </c>
       <c r="F23" s="9">
-        <v>30.89</v>
+        <v>30.53</v>
       </c>
       <c r="G23" s="9">
-        <v>40.619999999999997</v>
+        <v>40.36</v>
       </c>
       <c r="H23" s="9">
-        <v>2.0299999999999998</v>
+        <v>1.57</v>
       </c>
       <c r="I23" s="10">
-        <v>28.79</v>
+        <v>28.45</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>31</v>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="27"/>
-        <v>13.368589743589743</v>
+        <v>13.241269841269839</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="28"/>
-        <v>1.0224358974358976</v>
+        <v>1.0444444444444443</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="29"/>
-        <v>3.1199999999999997</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="N23" s="13">
-        <v>11.49</v>
+        <v>12.88</v>
       </c>
       <c r="O23" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P23" s="9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q23" s="9">
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R23" s="10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S23" s="17" t="s">
         <v>31</v>
       </c>
       <c r="T23" s="5">
         <f t="shared" ref="T23" si="41">ROUND(B23/K23,3)</f>
-        <v>0.51100000000000001</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" ref="U23" si="42">ROUND(C23/L23,3)</f>
-        <v>0.92900000000000005</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="V23" s="6">
         <f t="shared" ref="V23" si="43">ROUND(D23/M23,3)</f>
-        <v>23.571000000000002</v>
+        <v>23.003</v>
       </c>
       <c r="W23" s="13">
         <f t="shared" ref="W23" si="44">ROUND(E23/N23,3)</f>
-        <v>21.295000000000002</v>
+        <v>19.001999999999999</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" ref="X23" si="45">ROUND(F23/O23,3)</f>
-        <v>27.096</v>
+        <v>26.547999999999998</v>
       </c>
       <c r="Y23" s="9">
         <f t="shared" ref="Y23" si="46">ROUND(G23/P23,3)</f>
-        <v>23.754000000000001</v>
+        <v>23.465</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" ref="Z23" si="47">ROUND(H23/Q23,3)</f>
-        <v>7.5190000000000001</v>
+        <v>5.6070000000000002</v>
       </c>
       <c r="AA23" s="10">
         <f t="shared" ref="AA23" si="48">ROUND(I23/R23,3)</f>
-        <v>22.146000000000001</v>
+        <v>21.718</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2894,95 +2898,95 @@
       </c>
       <c r="B24" s="2">
         <f t="shared" ref="B24" si="49">D$2/D24</f>
-        <v>8.1165456012913637</v>
+        <v>8.0878237091844927</v>
       </c>
       <c r="C24" s="2">
         <f t="shared" ref="C24" si="50">D23/D24</f>
-        <v>1.1870863599677159</v>
+        <v>1.165513913463085</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" ref="D24" si="51">SUM(F24:H24)</f>
-        <v>61.949999999999996</v>
+        <v>62.17</v>
       </c>
       <c r="E24" s="9">
-        <v>244.04</v>
+        <v>250.47</v>
       </c>
       <c r="F24" s="9">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="G24" s="13">
-        <v>29.9</v>
+        <v>30.11</v>
       </c>
       <c r="H24" s="9">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="I24" s="14">
-        <v>21.71</v>
+        <v>21.64</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="K24" s="2">
         <f t="shared" si="27"/>
-        <v>14.843416370106761</v>
+        <v>14.738515901060069</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="28"/>
-        <v>1.1103202846975089</v>
+        <v>1.1130742049469966</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="29"/>
-        <v>2.8099999999999996</v>
+        <v>2.83</v>
       </c>
       <c r="N24" s="9">
-        <v>11.52</v>
+        <v>11.47</v>
       </c>
       <c r="O24" s="9">
         <v>1.1499999999999999</v>
       </c>
       <c r="P24" s="13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R24" s="14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="S24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="T24" s="2">
         <f t="shared" ref="T24" si="52">ROUND(B24/K24,3)</f>
-        <v>0.54700000000000004</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="U24" s="2">
         <f t="shared" ref="U24" si="53">ROUND(C24/L24,3)</f>
-        <v>1.069</v>
+        <v>1.0469999999999999</v>
       </c>
       <c r="V24" s="6">
         <f t="shared" ref="V24" si="54">ROUND(D24/M24,3)</f>
-        <v>22.045999999999999</v>
+        <v>21.968</v>
       </c>
       <c r="W24" s="9">
         <f t="shared" ref="W24" si="55">ROUND(E24/N24,3)</f>
-        <v>21.184000000000001</v>
+        <v>21.837</v>
       </c>
       <c r="X24" s="9">
         <f t="shared" ref="X24" si="56">ROUND(F24/O24,3)</f>
-        <v>26.652000000000001</v>
+        <v>26.6</v>
       </c>
       <c r="Y24" s="13">
         <f t="shared" ref="Y24" si="57">ROUND(G24/P24,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.507000000000001</v>
       </c>
       <c r="Z24" s="9">
         <f t="shared" ref="Z24" si="58">ROUND(H24/Q24,3)</f>
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA24" s="14">
         <f t="shared" ref="AA24" si="59">ROUND(I24/R24,3)</f>
-        <v>21.077999999999999</v>
+        <v>20.808</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2991,54 +2995,54 @@
       </c>
       <c r="B25" s="2">
         <f t="shared" ref="B25" si="60">D$2/D25</f>
-        <v>8.3929227174094461</v>
+        <v>8.4069553586356793</v>
       </c>
       <c r="C25" s="2">
         <f t="shared" ref="C25" si="61">D24/D25</f>
-        <v>1.0340510766149225</v>
+        <v>1.0394582845677982</v>
       </c>
       <c r="D25" s="6">
         <f t="shared" ref="D25" si="62">SUM(F25:H25)</f>
-        <v>59.91</v>
+        <v>59.809999999999995</v>
       </c>
       <c r="E25" s="9">
-        <v>243.54</v>
+        <v>248.62</v>
       </c>
       <c r="F25" s="9">
-        <v>30.77</v>
+        <v>30.49</v>
       </c>
       <c r="G25" s="13">
-        <v>27.63</v>
+        <v>27.86</v>
       </c>
       <c r="H25" s="9">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="I25" s="14">
-        <v>18.61</v>
+        <v>19.07</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" ref="K25" si="63">M$2/M25</f>
+        <f t="shared" ref="K25:K26" si="63">M$2/M25</f>
         <v>15.680451127819545</v>
       </c>
       <c r="L25" s="2">
-        <f t="shared" ref="L25" si="64">M24/M25</f>
-        <v>1.0563909774436089</v>
+        <f t="shared" ref="L25:L26" si="64">M24/M25</f>
+        <v>1.0639097744360901</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" ref="M25" si="65">SUM(O25:Q25)</f>
+        <f t="shared" ref="M25:M26" si="65">SUM(O25:Q25)</f>
         <v>2.66</v>
       </c>
       <c r="N25" s="9">
-        <v>11.69</v>
+        <v>11.82</v>
       </c>
       <c r="O25" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P25" s="13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" s="9">
         <v>0.28000000000000003</v>
@@ -3051,35 +3055,132 @@
       </c>
       <c r="T25" s="2">
         <f t="shared" ref="T25" si="66">ROUND(B25/K25,3)</f>
-        <v>0.53500000000000003</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" ref="U25" si="67">ROUND(C25/L25,3)</f>
-        <v>0.97899999999999998</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="V25" s="6">
         <f t="shared" ref="V25" si="68">ROUND(D25/M25,3)</f>
-        <v>22.523</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" ref="W25" si="69">ROUND(E25/N25,3)</f>
-        <v>20.832999999999998</v>
+        <v>21.033999999999999</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" ref="X25" si="70">ROUND(F25/O25,3)</f>
-        <v>26.991</v>
+        <v>26.981999999999999</v>
       </c>
       <c r="Y25" s="13">
         <f t="shared" ref="Y25" si="71">ROUND(G25/P25,3)</f>
-        <v>22.282</v>
+        <v>22.288</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" ref="Z25" si="72">ROUND(H25/Q25,3)</f>
-        <v>5.3929999999999998</v>
+        <v>5.2140000000000004</v>
       </c>
       <c r="AA25" s="14">
         <f t="shared" ref="AA25" si="73">ROUND(I25/R25,3)</f>
-        <v>20.451000000000001</v>
+        <v>20.956</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="2">
+        <f t="shared" ref="B26" si="74">D$2/D26</f>
+        <v>9.3460966542750903</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" ref="C26" si="75">D25/D26</f>
+        <v>1.1117100371747211</v>
+      </c>
+      <c r="D26" s="6">
+        <f t="shared" ref="D26" si="76">SUM(F26:H26)</f>
+        <v>53.800000000000004</v>
+      </c>
+      <c r="E26" s="9">
+        <v>244</v>
+      </c>
+      <c r="F26" s="9">
+        <v>30.55</v>
+      </c>
+      <c r="G26" s="13">
+        <v>21.79</v>
+      </c>
+      <c r="H26" s="9">
+        <v>1.46</v>
+      </c>
+      <c r="I26" s="14">
+        <v>17.78</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="2">
+        <f t="shared" si="63"/>
+        <v>16.818548387096769</v>
+      </c>
+      <c r="L26" s="2">
+        <f t="shared" si="64"/>
+        <v>1.0725806451612903</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="65"/>
+        <v>2.4800000000000004</v>
+      </c>
+      <c r="N26" s="9">
+        <v>11.81</v>
+      </c>
+      <c r="O26" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P26" s="13">
+        <v>1.05</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R26" s="14">
+        <v>0.88</v>
+      </c>
+      <c r="S26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="T26" s="2">
+        <f t="shared" ref="T26" si="77">ROUND(B26/K26,3)</f>
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="U26" s="2">
+        <f t="shared" ref="U26" si="78">ROUND(C26/L26,3)</f>
+        <v>1.036</v>
+      </c>
+      <c r="V26" s="6">
+        <f t="shared" ref="V26" si="79">ROUND(D26/M26,3)</f>
+        <v>21.693999999999999</v>
+      </c>
+      <c r="W26" s="9">
+        <f t="shared" ref="W26" si="80">ROUND(E26/N26,3)</f>
+        <v>20.66</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" ref="X26" si="81">ROUND(F26/O26,3)</f>
+        <v>26.565000000000001</v>
+      </c>
+      <c r="Y26" s="13">
+        <f t="shared" ref="Y26" si="82">ROUND(G26/P26,3)</f>
+        <v>20.751999999999999</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" ref="Z26" si="83">ROUND(H26/Q26,3)</f>
+        <v>5.2140000000000004</v>
+      </c>
+      <c r="AA26" s="14">
+        <f t="shared" ref="AA26" si="84">ROUND(I26/R26,3)</f>
+        <v>20.204999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99442910-663A-497F-A117-46EC2DCD4AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5291A0-C6BA-4446-9620-8B18DFEB7CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="36">
   <si>
     <t>H23</t>
   </si>
@@ -147,6 +147,10 @@
   </si>
   <si>
     <t>H46</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H47</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -663,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2995,75 +2999,75 @@
       </c>
       <c r="B25" s="2">
         <f t="shared" ref="B25" si="60">D$2/D25</f>
-        <v>8.4069553586356793</v>
+        <v>8.3317315658657822</v>
       </c>
       <c r="C25" s="2">
         <f t="shared" ref="C25" si="61">D24/D25</f>
-        <v>1.0394582845677982</v>
+        <v>1.0301574150787076</v>
       </c>
       <c r="D25" s="6">
         <f t="shared" ref="D25" si="62">SUM(F25:H25)</f>
-        <v>59.809999999999995</v>
+        <v>60.35</v>
       </c>
       <c r="E25" s="9">
-        <v>248.62</v>
+        <v>246.52</v>
       </c>
       <c r="F25" s="9">
-        <v>30.49</v>
+        <v>30.96</v>
       </c>
       <c r="G25" s="13">
-        <v>27.86</v>
+        <v>27.91</v>
       </c>
       <c r="H25" s="9">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="I25" s="14">
-        <v>19.07</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" ref="K25:K26" si="63">M$2/M25</f>
-        <v>15.680451127819545</v>
+        <f t="shared" ref="K25:K27" si="63">M$2/M25</f>
+        <v>15.79924242424242</v>
       </c>
       <c r="L25" s="2">
-        <f t="shared" ref="L25:L26" si="64">M24/M25</f>
-        <v>1.0639097744360901</v>
+        <f t="shared" ref="L25:L27" si="64">M24/M25</f>
+        <v>1.071969696969697</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" ref="M25:M26" si="65">SUM(O25:Q25)</f>
-        <v>2.66</v>
+        <f t="shared" ref="M25:M27" si="65">SUM(O25:Q25)</f>
+        <v>2.64</v>
       </c>
       <c r="N25" s="9">
-        <v>11.82</v>
+        <v>11.72</v>
       </c>
       <c r="O25" s="9">
-        <v>1.1299999999999999</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P25" s="13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Q25" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R25" s="14">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="S25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="T25" s="2">
         <f t="shared" ref="T25" si="66">ROUND(B25/K25,3)</f>
-        <v>0.53600000000000003</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" ref="U25" si="67">ROUND(C25/L25,3)</f>
-        <v>0.97699999999999998</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="V25" s="6">
         <f t="shared" ref="V25" si="68">ROUND(D25/M25,3)</f>
-        <v>22.484999999999999</v>
+        <v>22.86</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" ref="W25" si="69">ROUND(E25/N25,3)</f>
@@ -3071,19 +3075,19 @@
       </c>
       <c r="X25" s="9">
         <f t="shared" ref="X25" si="70">ROUND(F25/O25,3)</f>
-        <v>26.981999999999999</v>
+        <v>27.643000000000001</v>
       </c>
       <c r="Y25" s="13">
         <f t="shared" ref="Y25" si="71">ROUND(G25/P25,3)</f>
-        <v>22.288</v>
+        <v>22.690999999999999</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" ref="Z25" si="72">ROUND(H25/Q25,3)</f>
-        <v>5.2140000000000004</v>
+        <v>5.1029999999999998</v>
       </c>
       <c r="AA25" s="14">
         <f t="shared" ref="AA25" si="73">ROUND(I25/R25,3)</f>
-        <v>20.956</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3092,51 +3096,51 @@
       </c>
       <c r="B26" s="2">
         <f t="shared" ref="B26" si="74">D$2/D26</f>
-        <v>9.3460966542750903</v>
+        <v>9.3097574523236428</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" si="75">D25/D26</f>
-        <v>1.1117100371747211</v>
+        <v>1.1173856693204962</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" ref="D26" si="76">SUM(F26:H26)</f>
-        <v>53.800000000000004</v>
+        <v>54.01</v>
       </c>
       <c r="E26" s="9">
-        <v>244</v>
+        <v>244.97</v>
       </c>
       <c r="F26" s="9">
-        <v>30.55</v>
+        <v>31.1</v>
       </c>
       <c r="G26" s="13">
-        <v>21.79</v>
+        <v>21.48</v>
       </c>
       <c r="H26" s="9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="I26" s="14">
-        <v>17.78</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>34</v>
       </c>
       <c r="K26" s="2">
         <f t="shared" si="63"/>
-        <v>16.818548387096769</v>
+        <v>16.751004016064254</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="64"/>
-        <v>1.0725806451612903</v>
+        <v>1.0602409638554215</v>
       </c>
       <c r="M26" s="6">
         <f t="shared" si="65"/>
-        <v>2.4800000000000004</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="N26" s="9">
-        <v>11.81</v>
+        <v>11.58</v>
       </c>
       <c r="O26" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P26" s="13">
         <v>1.05</v>
@@ -3156,31 +3160,128 @@
       </c>
       <c r="U26" s="2">
         <f t="shared" ref="U26" si="78">ROUND(C26/L26,3)</f>
-        <v>1.036</v>
+        <v>1.054</v>
       </c>
       <c r="V26" s="6">
         <f t="shared" ref="V26" si="79">ROUND(D26/M26,3)</f>
-        <v>21.693999999999999</v>
+        <v>21.690999999999999</v>
       </c>
       <c r="W26" s="9">
         <f t="shared" ref="W26" si="80">ROUND(E26/N26,3)</f>
-        <v>20.66</v>
+        <v>21.155000000000001</v>
       </c>
       <c r="X26" s="9">
         <f t="shared" ref="X26" si="81">ROUND(F26/O26,3)</f>
-        <v>26.565000000000001</v>
+        <v>26.81</v>
       </c>
       <c r="Y26" s="13">
         <f t="shared" ref="Y26" si="82">ROUND(G26/P26,3)</f>
-        <v>20.751999999999999</v>
+        <v>20.457000000000001</v>
       </c>
       <c r="Z26" s="9">
         <f t="shared" ref="Z26" si="83">ROUND(H26/Q26,3)</f>
-        <v>5.2140000000000004</v>
+        <v>5.1070000000000002</v>
       </c>
       <c r="AA26" s="14">
         <f t="shared" ref="AA26" si="84">ROUND(I26/R26,3)</f>
-        <v>20.204999999999998</v>
+        <v>19.898</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="2">
+        <f t="shared" ref="B27" si="85">D$2/D27</f>
+        <v>10.536881810561606</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" ref="C27" si="86">D26/D27</f>
+        <v>1.1318105616093879</v>
+      </c>
+      <c r="D27" s="6">
+        <f t="shared" ref="D27" si="87">SUM(F27:H27)</f>
+        <v>47.720000000000006</v>
+      </c>
+      <c r="E27" s="9">
+        <v>244.09</v>
+      </c>
+      <c r="F27" s="13">
+        <v>25.17</v>
+      </c>
+      <c r="G27" s="9">
+        <v>21.09</v>
+      </c>
+      <c r="H27" s="9">
+        <v>1.46</v>
+      </c>
+      <c r="I27" s="10">
+        <v>17.38</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="2">
+        <f t="shared" si="63"/>
+        <v>18.455752212389381</v>
+      </c>
+      <c r="L27" s="2">
+        <f t="shared" si="64"/>
+        <v>1.101769911504425</v>
+      </c>
+      <c r="M27" s="6">
+        <f t="shared" si="65"/>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="N27" s="9">
+        <v>11.76</v>
+      </c>
+      <c r="O27" s="13">
+        <v>0.94</v>
+      </c>
+      <c r="P27" s="9">
+        <v>1.04</v>
+      </c>
+      <c r="Q27" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R27" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="S27" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="T27" s="2">
+        <f t="shared" ref="T27" si="88">ROUND(B27/K27,3)</f>
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="U27" s="2">
+        <f t="shared" ref="U27" si="89">ROUND(C27/L27,3)</f>
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="V27" s="6">
+        <f t="shared" ref="V27" si="90">ROUND(D27/M27,3)</f>
+        <v>21.114999999999998</v>
+      </c>
+      <c r="W27" s="9">
+        <f t="shared" ref="W27" si="91">ROUND(E27/N27,3)</f>
+        <v>20.756</v>
+      </c>
+      <c r="X27" s="13">
+        <f t="shared" ref="X27" si="92">ROUND(F27/O27,3)</f>
+        <v>26.777000000000001</v>
+      </c>
+      <c r="Y27" s="9">
+        <f t="shared" ref="Y27" si="93">ROUND(G27/P27,3)</f>
+        <v>20.279</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" ref="Z27" si="94">ROUND(H27/Q27,3)</f>
+        <v>5.2140000000000004</v>
+      </c>
+      <c r="AA27" s="10">
+        <f t="shared" ref="AA27" si="95">ROUND(I27/R27,3)</f>
+        <v>19.75</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5291A0-C6BA-4446-9620-8B18DFEB7CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48904AFF-8CE2-42FA-9197-31B2939FD50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
   <si>
     <t>H23</t>
   </si>
@@ -151,6 +151,10 @@
   </si>
   <si>
     <t>H47</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H48</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2999,95 +3003,95 @@
       </c>
       <c r="B25" s="2">
         <f t="shared" ref="B25" si="60">D$2/D25</f>
-        <v>8.3317315658657822</v>
+        <v>8.263270336894001</v>
       </c>
       <c r="C25" s="2">
         <f t="shared" ref="C25" si="61">D24/D25</f>
-        <v>1.0301574150787076</v>
+        <v>1.0216926869350864</v>
       </c>
       <c r="D25" s="6">
         <f t="shared" ref="D25" si="62">SUM(F25:H25)</f>
-        <v>60.35</v>
+        <v>60.849999999999994</v>
       </c>
       <c r="E25" s="9">
-        <v>246.52</v>
+        <v>244.44</v>
       </c>
       <c r="F25" s="9">
-        <v>30.96</v>
+        <v>31.2</v>
       </c>
       <c r="G25" s="13">
-        <v>27.91</v>
+        <v>28.18</v>
       </c>
       <c r="H25" s="9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I25" s="14">
-        <v>18.809999999999999</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="2">
         <f t="shared" ref="K25:K27" si="63">M$2/M25</f>
-        <v>15.79924242424242</v>
+        <v>15.85931558935361</v>
       </c>
       <c r="L25" s="2">
         <f t="shared" ref="L25:L27" si="64">M24/M25</f>
-        <v>1.071969696969697</v>
+        <v>1.0760456273764258</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" ref="M25:M27" si="65">SUM(O25:Q25)</f>
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="N25" s="9">
-        <v>11.72</v>
+        <v>11.87</v>
       </c>
       <c r="O25" s="9">
-        <v>1.1200000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P25" s="13">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R25" s="14">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="S25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="T25" s="2">
         <f t="shared" ref="T25" si="66">ROUND(B25/K25,3)</f>
-        <v>0.52700000000000002</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" ref="U25" si="67">ROUND(C25/L25,3)</f>
-        <v>0.96099999999999997</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="V25" s="6">
         <f t="shared" ref="V25" si="68">ROUND(D25/M25,3)</f>
-        <v>22.86</v>
+        <v>23.137</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" ref="W25" si="69">ROUND(E25/N25,3)</f>
-        <v>21.033999999999999</v>
+        <v>20.593</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" ref="X25" si="70">ROUND(F25/O25,3)</f>
-        <v>27.643000000000001</v>
+        <v>28.108000000000001</v>
       </c>
       <c r="Y25" s="13">
         <f t="shared" ref="Y25" si="71">ROUND(G25/P25,3)</f>
-        <v>22.690999999999999</v>
+        <v>22.725999999999999</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" ref="Z25" si="72">ROUND(H25/Q25,3)</f>
-        <v>5.1029999999999998</v>
+        <v>5.25</v>
       </c>
       <c r="AA25" s="14">
         <f t="shared" ref="AA25" si="73">ROUND(I25/R25,3)</f>
-        <v>20.9</v>
+        <v>21.696999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3096,95 +3100,95 @@
       </c>
       <c r="B26" s="2">
         <f t="shared" ref="B26" si="74">D$2/D26</f>
-        <v>9.3097574523236428</v>
+        <v>9.1923217550274217</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" si="75">D25/D26</f>
-        <v>1.1173856693204962</v>
+        <v>1.1124314442413163</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" ref="D26" si="76">SUM(F26:H26)</f>
-        <v>54.01</v>
+        <v>54.699999999999996</v>
       </c>
       <c r="E26" s="9">
-        <v>244.97</v>
+        <v>249.17</v>
       </c>
       <c r="F26" s="9">
-        <v>31.1</v>
+        <v>31.37</v>
       </c>
       <c r="G26" s="13">
-        <v>21.48</v>
+        <v>21.93</v>
       </c>
       <c r="H26" s="9">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="I26" s="14">
-        <v>17.510000000000002</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>34</v>
       </c>
       <c r="K26" s="2">
         <f t="shared" si="63"/>
-        <v>16.751004016064254</v>
+        <v>17.024489795918363</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="64"/>
-        <v>1.0602409638554215</v>
+        <v>1.0734693877551018</v>
       </c>
       <c r="M26" s="6">
         <f t="shared" si="65"/>
-        <v>2.4900000000000002</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="N26" s="9">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="O26" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P26" s="13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q26" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R26" s="14">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="S26" s="17" t="s">
         <v>34</v>
       </c>
       <c r="T26" s="2">
         <f t="shared" ref="T26" si="77">ROUND(B26/K26,3)</f>
-        <v>0.55600000000000005</v>
+        <v>0.54</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" ref="U26" si="78">ROUND(C26/L26,3)</f>
-        <v>1.054</v>
+        <v>1.036</v>
       </c>
       <c r="V26" s="6">
         <f t="shared" ref="V26" si="79">ROUND(D26/M26,3)</f>
-        <v>21.690999999999999</v>
+        <v>22.327000000000002</v>
       </c>
       <c r="W26" s="9">
         <f t="shared" ref="W26" si="80">ROUND(E26/N26,3)</f>
-        <v>21.155000000000001</v>
+        <v>21.648</v>
       </c>
       <c r="X26" s="9">
         <f t="shared" ref="X26" si="81">ROUND(F26/O26,3)</f>
-        <v>26.81</v>
+        <v>27.760999999999999</v>
       </c>
       <c r="Y26" s="13">
         <f t="shared" ref="Y26" si="82">ROUND(G26/P26,3)</f>
-        <v>20.457000000000001</v>
+        <v>21.087</v>
       </c>
       <c r="Z26" s="9">
         <f t="shared" ref="Z26" si="83">ROUND(H26/Q26,3)</f>
-        <v>5.1070000000000002</v>
+        <v>5</v>
       </c>
       <c r="AA26" s="14">
         <f t="shared" ref="AA26" si="84">ROUND(I26/R26,3)</f>
-        <v>19.898</v>
+        <v>20.701000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3193,27 +3197,27 @@
       </c>
       <c r="B27" s="2">
         <f t="shared" ref="B27" si="85">D$2/D27</f>
-        <v>10.536881810561606</v>
+        <v>10.453638253638253</v>
       </c>
       <c r="C27" s="2">
         <f t="shared" ref="C27" si="86">D26/D27</f>
-        <v>1.1318105616093879</v>
+        <v>1.1372141372141373</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27" si="87">SUM(F27:H27)</f>
-        <v>47.720000000000006</v>
+        <v>48.099999999999994</v>
       </c>
       <c r="E27" s="9">
-        <v>244.09</v>
+        <v>244.7</v>
       </c>
       <c r="F27" s="13">
-        <v>25.17</v>
+        <v>25.5</v>
       </c>
       <c r="G27" s="9">
-        <v>21.09</v>
+        <v>21.16</v>
       </c>
       <c r="H27" s="9">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I27" s="10">
         <v>17.38</v>
@@ -3223,27 +3227,27 @@
       </c>
       <c r="K27" s="2">
         <f t="shared" si="63"/>
-        <v>18.455752212389381</v>
+        <v>17.978448275862064</v>
       </c>
       <c r="L27" s="2">
         <f t="shared" si="64"/>
-        <v>1.101769911504425</v>
+        <v>1.0560344827586206</v>
       </c>
       <c r="M27" s="6">
         <f t="shared" si="65"/>
-        <v>2.2599999999999998</v>
+        <v>2.3200000000000003</v>
       </c>
       <c r="N27" s="9">
-        <v>11.76</v>
+        <v>11.65</v>
       </c>
       <c r="O27" s="13">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="P27" s="9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Q27" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R27" s="10">
         <v>0.88</v>
@@ -3253,35 +3257,132 @@
       </c>
       <c r="T27" s="2">
         <f t="shared" ref="T27" si="88">ROUND(B27/K27,3)</f>
-        <v>0.57099999999999995</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="U27" s="2">
         <f t="shared" ref="U27" si="89">ROUND(C27/L27,3)</f>
-        <v>1.0269999999999999</v>
+        <v>1.077</v>
       </c>
       <c r="V27" s="6">
         <f t="shared" ref="V27" si="90">ROUND(D27/M27,3)</f>
-        <v>21.114999999999998</v>
+        <v>20.733000000000001</v>
       </c>
       <c r="W27" s="9">
         <f t="shared" ref="W27" si="91">ROUND(E27/N27,3)</f>
-        <v>20.756</v>
+        <v>21.004000000000001</v>
       </c>
       <c r="X27" s="13">
         <f t="shared" ref="X27" si="92">ROUND(F27/O27,3)</f>
-        <v>26.777000000000001</v>
+        <v>26.02</v>
       </c>
       <c r="Y27" s="9">
         <f t="shared" ref="Y27" si="93">ROUND(G27/P27,3)</f>
-        <v>20.279</v>
+        <v>20.152000000000001</v>
       </c>
       <c r="Z27" s="9">
         <f t="shared" ref="Z27" si="94">ROUND(H27/Q27,3)</f>
-        <v>5.2140000000000004</v>
+        <v>4.9660000000000002</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" ref="AA27" si="95">ROUND(I27/R27,3)</f>
         <v>19.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="2">
+        <f t="shared" ref="B28" si="96">D$2/D28</f>
+        <v>11.007443082311733</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" ref="C28" si="97">D27/D28</f>
+        <v>1.0529772329246934</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" ref="D28" si="98">SUM(F28:H28)</f>
+        <v>45.68</v>
+      </c>
+      <c r="E28" s="9">
+        <v>247.43</v>
+      </c>
+      <c r="F28" s="9">
+        <v>24.9</v>
+      </c>
+      <c r="G28" s="13">
+        <v>19.32</v>
+      </c>
+      <c r="H28" s="9">
+        <v>1.46</v>
+      </c>
+      <c r="I28" s="14">
+        <v>15.61</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K28" s="2">
+        <f t="shared" ref="K28" si="99">M$2/M28</f>
+        <v>19.221198156682025</v>
+      </c>
+      <c r="L28" s="2">
+        <f t="shared" ref="L28" si="100">M27/M28</f>
+        <v>1.0691244239631339</v>
+      </c>
+      <c r="M28" s="6">
+        <f t="shared" ref="M28" si="101">SUM(O28:Q28)</f>
+        <v>2.17</v>
+      </c>
+      <c r="N28" s="9">
+        <v>11.56</v>
+      </c>
+      <c r="O28" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="P28" s="13">
+        <v>0.95</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>0.27</v>
+      </c>
+      <c r="R28" s="14">
+        <v>0.76</v>
+      </c>
+      <c r="S28" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" s="2">
+        <f t="shared" ref="T28" si="102">ROUND(B28/K28,3)</f>
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="U28" s="2">
+        <f t="shared" ref="U28" si="103">ROUND(C28/L28,3)</f>
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="V28" s="6">
+        <f t="shared" ref="V28" si="104">ROUND(D28/M28,3)</f>
+        <v>21.050999999999998</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" ref="W28" si="105">ROUND(E28/N28,3)</f>
+        <v>21.404</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" ref="X28" si="106">ROUND(F28/O28,3)</f>
+        <v>26.210999999999999</v>
+      </c>
+      <c r="Y28" s="13">
+        <f t="shared" ref="Y28" si="107">ROUND(G28/P28,3)</f>
+        <v>20.337</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" ref="Z28" si="108">ROUND(H28/Q28,3)</f>
+        <v>5.407</v>
+      </c>
+      <c r="AA28" s="14">
+        <f t="shared" ref="AA28" si="109">ROUND(I28/R28,3)</f>
+        <v>20.539000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48904AFF-8CE2-42FA-9197-31B2939FD50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277B0380-0923-4DCB-9A6D-949AFCAF5517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
   <si>
     <t>H23</t>
   </si>
@@ -155,6 +155,10 @@
   </si>
   <si>
     <t>H48</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H49</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -299,7 +303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -355,6 +359,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -671,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3294,51 +3301,51 @@
       </c>
       <c r="B28" s="2">
         <f t="shared" ref="B28" si="96">D$2/D28</f>
-        <v>11.007443082311733</v>
+        <v>11.070453544693967</v>
       </c>
       <c r="C28" s="2">
         <f t="shared" ref="C28" si="97">D27/D28</f>
-        <v>1.0529772329246934</v>
+        <v>1.0590048436811976</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" ref="D28" si="98">SUM(F28:H28)</f>
-        <v>45.68</v>
+        <v>45.419999999999995</v>
       </c>
       <c r="E28" s="9">
-        <v>247.43</v>
+        <v>244.39</v>
       </c>
       <c r="F28" s="9">
-        <v>24.9</v>
+        <v>24.83</v>
       </c>
       <c r="G28" s="13">
-        <v>19.32</v>
+        <v>19.13</v>
       </c>
       <c r="H28" s="9">
         <v>1.46</v>
       </c>
       <c r="I28" s="14">
-        <v>15.61</v>
+        <v>14.94</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>36</v>
       </c>
       <c r="K28" s="2">
         <f t="shared" ref="K28" si="99">M$2/M28</f>
-        <v>19.221198156682025</v>
+        <v>19.861904761904757</v>
       </c>
       <c r="L28" s="2">
         <f t="shared" ref="L28" si="100">M27/M28</f>
-        <v>1.0691244239631339</v>
+        <v>1.1047619047619048</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" ref="M28" si="101">SUM(O28:Q28)</f>
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="N28" s="9">
-        <v>11.56</v>
+        <v>11.6</v>
       </c>
       <c r="O28" s="9">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="P28" s="13">
         <v>0.95</v>
@@ -3354,27 +3361,27 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" ref="T28" si="102">ROUND(B28/K28,3)</f>
-        <v>0.57299999999999995</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" ref="U28" si="103">ROUND(C28/L28,3)</f>
-        <v>0.98499999999999999</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="V28" s="6">
         <f t="shared" ref="V28" si="104">ROUND(D28/M28,3)</f>
-        <v>21.050999999999998</v>
+        <v>21.629000000000001</v>
       </c>
       <c r="W28" s="9">
         <f t="shared" ref="W28" si="105">ROUND(E28/N28,3)</f>
-        <v>21.404</v>
+        <v>21.068000000000001</v>
       </c>
       <c r="X28" s="9">
         <f t="shared" ref="X28" si="106">ROUND(F28/O28,3)</f>
-        <v>26.210999999999999</v>
+        <v>28.216000000000001</v>
       </c>
       <c r="Y28" s="13">
         <f t="shared" ref="Y28" si="107">ROUND(G28/P28,3)</f>
-        <v>20.337</v>
+        <v>20.137</v>
       </c>
       <c r="Z28" s="9">
         <f t="shared" ref="Z28" si="108">ROUND(H28/Q28,3)</f>
@@ -3382,7 +3389,104 @@
       </c>
       <c r="AA28" s="14">
         <f t="shared" ref="AA28" si="109">ROUND(I28/R28,3)</f>
-        <v>20.539000000000001</v>
+        <v>19.658000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="2">
+        <f t="shared" ref="B29" si="110">D$2/D29</f>
+        <v>12.932613168724279</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" ref="C29" si="111">D28/D29</f>
+        <v>1.1682098765432098</v>
+      </c>
+      <c r="D29" s="6">
+        <f t="shared" ref="D29" si="112">SUM(F29:H29)</f>
+        <v>38.879999999999995</v>
+      </c>
+      <c r="E29" s="9">
+        <v>244.31</v>
+      </c>
+      <c r="F29" s="9">
+        <v>25.12</v>
+      </c>
+      <c r="G29" s="13">
+        <v>12.29</v>
+      </c>
+      <c r="H29" s="9">
+        <v>1.47</v>
+      </c>
+      <c r="I29" s="19">
+        <v>14.97</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="2">
+        <f t="shared" ref="K29" si="113">M$2/M29</f>
+        <v>23.04419889502762</v>
+      </c>
+      <c r="L29" s="2">
+        <f t="shared" ref="L29" si="114">M28/M29</f>
+        <v>1.160220994475138</v>
+      </c>
+      <c r="M29" s="6">
+        <f t="shared" ref="M29" si="115">SUM(O29:Q29)</f>
+        <v>1.81</v>
+      </c>
+      <c r="N29" s="9">
+        <v>11.71</v>
+      </c>
+      <c r="O29" s="9">
+        <v>0.88</v>
+      </c>
+      <c r="P29" s="13">
+        <v>0.65</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R29" s="19">
+        <v>0.78</v>
+      </c>
+      <c r="S29" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="T29" s="2">
+        <f t="shared" ref="T29" si="116">ROUND(B29/K29,3)</f>
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="U29" s="2">
+        <f t="shared" ref="U29" si="117">ROUND(C29/L29,3)</f>
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="V29" s="6">
+        <f t="shared" ref="V29" si="118">ROUND(D29/M29,3)</f>
+        <v>21.481000000000002</v>
+      </c>
+      <c r="W29" s="9">
+        <f t="shared" ref="W29" si="119">ROUND(E29/N29,3)</f>
+        <v>20.863</v>
+      </c>
+      <c r="X29" s="9">
+        <f t="shared" ref="X29" si="120">ROUND(F29/O29,3)</f>
+        <v>28.545000000000002</v>
+      </c>
+      <c r="Y29" s="13">
+        <f t="shared" ref="Y29" si="121">ROUND(G29/P29,3)</f>
+        <v>18.908000000000001</v>
+      </c>
+      <c r="Z29" s="9">
+        <f t="shared" ref="Z29" si="122">ROUND(H29/Q29,3)</f>
+        <v>5.25</v>
+      </c>
+      <c r="AA29" s="19">
+        <f t="shared" ref="AA29" si="123">ROUND(I29/R29,3)</f>
+        <v>19.192</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277B0380-0923-4DCB-9A6D-949AFCAF5517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CD199F-B606-4B90-879D-52919ED688E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="39">
   <si>
     <t>H23</t>
   </si>
@@ -159,6 +159,10 @@
   </si>
   <si>
     <t>H49</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -678,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3301,51 +3305,51 @@
       </c>
       <c r="B28" s="2">
         <f t="shared" ref="B28" si="96">D$2/D28</f>
-        <v>11.070453544693967</v>
+        <v>11.06071271447426</v>
       </c>
       <c r="C28" s="2">
         <f t="shared" ref="C28" si="97">D27/D28</f>
-        <v>1.0590048436811976</v>
+        <v>1.0580730312362514</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" ref="D28" si="98">SUM(F28:H28)</f>
-        <v>45.419999999999995</v>
+        <v>45.460000000000008</v>
       </c>
       <c r="E28" s="9">
-        <v>244.39</v>
+        <v>245.41</v>
       </c>
       <c r="F28" s="9">
-        <v>24.83</v>
+        <v>24.98</v>
       </c>
       <c r="G28" s="13">
-        <v>19.13</v>
+        <v>19.03</v>
       </c>
       <c r="H28" s="9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I28" s="14">
-        <v>14.94</v>
+        <v>14.98</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>36</v>
       </c>
       <c r="K28" s="2">
         <f t="shared" ref="K28" si="99">M$2/M28</f>
-        <v>19.861904761904757</v>
+        <v>19.31018518518518</v>
       </c>
       <c r="L28" s="2">
         <f t="shared" ref="L28" si="100">M27/M28</f>
-        <v>1.1047619047619048</v>
+        <v>1.0740740740740742</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" ref="M28" si="101">SUM(O28:Q28)</f>
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="N28" s="9">
-        <v>11.6</v>
+        <v>11.83</v>
       </c>
       <c r="O28" s="9">
-        <v>0.88</v>
+        <v>0.94</v>
       </c>
       <c r="P28" s="13">
         <v>0.95</v>
@@ -3361,35 +3365,35 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" ref="T28" si="102">ROUND(B28/K28,3)</f>
-        <v>0.55700000000000005</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" ref="U28" si="103">ROUND(C28/L28,3)</f>
-        <v>0.95899999999999996</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="V28" s="6">
         <f t="shared" ref="V28" si="104">ROUND(D28/M28,3)</f>
-        <v>21.629000000000001</v>
+        <v>21.045999999999999</v>
       </c>
       <c r="W28" s="9">
         <f t="shared" ref="W28" si="105">ROUND(E28/N28,3)</f>
-        <v>21.068000000000001</v>
+        <v>20.745000000000001</v>
       </c>
       <c r="X28" s="9">
         <f t="shared" ref="X28" si="106">ROUND(F28/O28,3)</f>
-        <v>28.216000000000001</v>
+        <v>26.574000000000002</v>
       </c>
       <c r="Y28" s="13">
         <f t="shared" ref="Y28" si="107">ROUND(G28/P28,3)</f>
-        <v>20.137</v>
+        <v>20.032</v>
       </c>
       <c r="Z28" s="9">
         <f t="shared" ref="Z28" si="108">ROUND(H28/Q28,3)</f>
-        <v>5.407</v>
+        <v>5.37</v>
       </c>
       <c r="AA28" s="14">
         <f t="shared" ref="AA28" si="109">ROUND(I28/R28,3)</f>
-        <v>19.658000000000001</v>
+        <v>19.710999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3398,95 +3402,192 @@
       </c>
       <c r="B29" s="2">
         <f t="shared" ref="B29" si="110">D$2/D29</f>
-        <v>12.932613168724279</v>
+        <v>13.029800466442083</v>
       </c>
       <c r="C29" s="2">
         <f t="shared" ref="C29" si="111">D28/D29</f>
-        <v>1.1682098765432098</v>
+        <v>1.1780253951800987</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" ref="D29" si="112">SUM(F29:H29)</f>
-        <v>38.879999999999995</v>
+        <v>38.589999999999996</v>
       </c>
       <c r="E29" s="9">
-        <v>244.31</v>
+        <v>244.04</v>
       </c>
       <c r="F29" s="9">
-        <v>25.12</v>
+        <v>24.98</v>
       </c>
       <c r="G29" s="13">
-        <v>12.29</v>
+        <v>12.2</v>
       </c>
       <c r="H29" s="9">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="I29" s="19">
-        <v>14.97</v>
+        <v>15.03</v>
       </c>
       <c r="J29" s="17" t="s">
         <v>37</v>
       </c>
       <c r="K29" s="2">
-        <f t="shared" ref="K29" si="113">M$2/M29</f>
-        <v>23.04419889502762</v>
+        <f t="shared" ref="K29:K30" si="113">M$2/M29</f>
+        <v>22.668478260869559</v>
       </c>
       <c r="L29" s="2">
-        <f t="shared" ref="L29" si="114">M28/M29</f>
-        <v>1.160220994475138</v>
+        <f t="shared" ref="L29:L30" si="114">M28/M29</f>
+        <v>1.173913043478261</v>
       </c>
       <c r="M29" s="6">
-        <f t="shared" ref="M29" si="115">SUM(O29:Q29)</f>
-        <v>1.81</v>
+        <f t="shared" ref="M29:M30" si="115">SUM(O29:Q29)</f>
+        <v>1.84</v>
       </c>
       <c r="N29" s="9">
-        <v>11.71</v>
+        <v>11.37</v>
       </c>
       <c r="O29" s="9">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="P29" s="13">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="Q29" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="R29" s="19">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="S29" s="17" t="s">
         <v>37</v>
       </c>
       <c r="T29" s="2">
         <f t="shared" ref="T29" si="116">ROUND(B29/K29,3)</f>
-        <v>0.56100000000000005</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="U29" s="2">
         <f t="shared" ref="U29" si="117">ROUND(C29/L29,3)</f>
-        <v>1.0069999999999999</v>
+        <v>1.004</v>
       </c>
       <c r="V29" s="6">
         <f t="shared" ref="V29" si="118">ROUND(D29/M29,3)</f>
-        <v>21.481000000000002</v>
+        <v>20.972999999999999</v>
       </c>
       <c r="W29" s="9">
         <f t="shared" ref="W29" si="119">ROUND(E29/N29,3)</f>
-        <v>20.863</v>
+        <v>21.463999999999999</v>
       </c>
       <c r="X29" s="9">
         <f t="shared" ref="X29" si="120">ROUND(F29/O29,3)</f>
-        <v>28.545000000000002</v>
+        <v>26.86</v>
       </c>
       <c r="Y29" s="13">
         <f t="shared" ref="Y29" si="121">ROUND(G29/P29,3)</f>
-        <v>18.908000000000001</v>
+        <v>19.062999999999999</v>
       </c>
       <c r="Z29" s="9">
         <f t="shared" ref="Z29" si="122">ROUND(H29/Q29,3)</f>
-        <v>5.25</v>
+        <v>5.2220000000000004</v>
       </c>
       <c r="AA29" s="19">
         <f t="shared" ref="AA29" si="123">ROUND(I29/R29,3)</f>
-        <v>19.192</v>
+        <v>19.518999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="5">
+        <f t="shared" ref="B30" si="124">D$2/D30</f>
+        <v>12.827040816326528</v>
+      </c>
+      <c r="C30" s="5">
+        <f t="shared" ref="C30" si="125">D29/D30</f>
+        <v>0.98443877551020387</v>
+      </c>
+      <c r="D30" s="4">
+        <f t="shared" ref="D30" si="126">SUM(F30:H30)</f>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E30" s="13">
+        <v>206.15</v>
+      </c>
+      <c r="F30" s="9">
+        <v>24.88</v>
+      </c>
+      <c r="G30" s="9">
+        <v>12.68</v>
+      </c>
+      <c r="H30" s="9">
+        <v>1.64</v>
+      </c>
+      <c r="I30" s="10">
+        <v>15.83</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="5">
+        <f t="shared" si="113"/>
+        <v>22.668478260869559</v>
+      </c>
+      <c r="L30" s="5">
+        <f t="shared" si="114"/>
+        <v>1</v>
+      </c>
+      <c r="M30" s="4">
+        <f t="shared" si="115"/>
+        <v>1.84</v>
+      </c>
+      <c r="N30" s="13">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="O30" s="9">
+        <v>0.94</v>
+      </c>
+      <c r="P30" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="R30" s="10">
+        <v>0.76</v>
+      </c>
+      <c r="S30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T30" s="5">
+        <f t="shared" ref="T30" si="127">ROUND(B30/K30,3)</f>
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="U30" s="5">
+        <f t="shared" ref="U30" si="128">ROUND(C30/L30,3)</f>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="V30" s="4">
+        <f t="shared" ref="V30" si="129">ROUND(D30/M30,3)</f>
+        <v>21.303999999999998</v>
+      </c>
+      <c r="W30" s="13">
+        <f t="shared" ref="W30" si="130">ROUND(E30/N30,3)</f>
+        <v>21.978000000000002</v>
+      </c>
+      <c r="X30" s="9">
+        <f t="shared" ref="X30" si="131">ROUND(F30/O30,3)</f>
+        <v>26.468</v>
+      </c>
+      <c r="Y30" s="9">
+        <f t="shared" ref="Y30" si="132">ROUND(G30/P30,3)</f>
+        <v>19.812999999999999</v>
+      </c>
+      <c r="Z30" s="9">
+        <f t="shared" ref="Z30" si="133">ROUND(H30/Q30,3)</f>
+        <v>6.3079999999999998</v>
+      </c>
+      <c r="AA30" s="10">
+        <f t="shared" ref="AA30" si="134">ROUND(I30/R30,3)</f>
+        <v>20.829000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CD199F-B606-4B90-879D-52919ED688E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28AFD8-101B-4335-AE33-EFFC17A0F8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="40">
   <si>
     <t>H23</t>
   </si>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>H50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H51</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3305,51 +3309,51 @@
       </c>
       <c r="B28" s="2">
         <f t="shared" ref="B28" si="96">D$2/D28</f>
-        <v>11.06071271447426</v>
+        <v>11.085097001763668</v>
       </c>
       <c r="C28" s="2">
         <f t="shared" ref="C28" si="97">D27/D28</f>
-        <v>1.0580730312362514</v>
+        <v>1.0604056437389771</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" ref="D28" si="98">SUM(F28:H28)</f>
-        <v>45.460000000000008</v>
+        <v>45.36</v>
       </c>
       <c r="E28" s="9">
-        <v>245.41</v>
+        <v>244.24</v>
       </c>
       <c r="F28" s="9">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="G28" s="13">
-        <v>19.03</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="H28" s="9">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="I28" s="14">
-        <v>14.98</v>
+        <v>14.95</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>36</v>
       </c>
       <c r="K28" s="2">
         <f t="shared" ref="K28" si="99">M$2/M28</f>
-        <v>19.31018518518518</v>
+        <v>19.490654205607473</v>
       </c>
       <c r="L28" s="2">
         <f t="shared" ref="L28" si="100">M27/M28</f>
-        <v>1.0740740740740742</v>
+        <v>1.0841121495327104</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" ref="M28" si="101">SUM(O28:Q28)</f>
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="N28" s="9">
-        <v>11.83</v>
+        <v>11.59</v>
       </c>
       <c r="O28" s="9">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="P28" s="13">
         <v>0.95</v>
@@ -3358,42 +3362,42 @@
         <v>0.27</v>
       </c>
       <c r="R28" s="14">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="S28" s="17" t="s">
         <v>36</v>
       </c>
       <c r="T28" s="2">
         <f t="shared" ref="T28" si="102">ROUND(B28/K28,3)</f>
-        <v>0.57299999999999995</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" ref="U28" si="103">ROUND(C28/L28,3)</f>
-        <v>0.98499999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="V28" s="6">
         <f t="shared" ref="V28" si="104">ROUND(D28/M28,3)</f>
-        <v>21.045999999999999</v>
+        <v>21.196000000000002</v>
       </c>
       <c r="W28" s="9">
         <f t="shared" ref="W28" si="105">ROUND(E28/N28,3)</f>
-        <v>20.745000000000001</v>
+        <v>21.073</v>
       </c>
       <c r="X28" s="9">
         <f t="shared" ref="X28" si="106">ROUND(F28/O28,3)</f>
-        <v>26.574000000000002</v>
+        <v>27.13</v>
       </c>
       <c r="Y28" s="13">
         <f t="shared" ref="Y28" si="107">ROUND(G28/P28,3)</f>
-        <v>20.032</v>
+        <v>20.010999999999999</v>
       </c>
       <c r="Z28" s="9">
         <f t="shared" ref="Z28" si="108">ROUND(H28/Q28,3)</f>
-        <v>5.37</v>
+        <v>5.1479999999999997</v>
       </c>
       <c r="AA28" s="14">
         <f t="shared" ref="AA28" si="109">ROUND(I28/R28,3)</f>
-        <v>19.710999999999999</v>
+        <v>19.416</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3402,57 +3406,57 @@
       </c>
       <c r="B29" s="2">
         <f t="shared" ref="B29" si="110">D$2/D29</f>
-        <v>13.029800466442083</v>
+        <v>13.023051023051021</v>
       </c>
       <c r="C29" s="2">
         <f t="shared" ref="C29" si="111">D28/D29</f>
-        <v>1.1780253951800987</v>
+        <v>1.1748251748251748</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" ref="D29" si="112">SUM(F29:H29)</f>
-        <v>38.589999999999996</v>
+        <v>38.61</v>
       </c>
       <c r="E29" s="9">
-        <v>244.04</v>
+        <v>248.57</v>
       </c>
       <c r="F29" s="9">
-        <v>24.98</v>
+        <v>25.06</v>
       </c>
       <c r="G29" s="13">
-        <v>12.2</v>
+        <v>12.11</v>
       </c>
       <c r="H29" s="9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="I29" s="19">
-        <v>15.03</v>
+        <v>14.92</v>
       </c>
       <c r="J29" s="17" t="s">
         <v>37</v>
       </c>
       <c r="K29" s="2">
         <f t="shared" ref="K29:K30" si="113">M$2/M29</f>
-        <v>22.668478260869559</v>
+        <v>21.952631578947365</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" ref="L29:L30" si="114">M28/M29</f>
-        <v>1.173913043478261</v>
+        <v>1.1263157894736842</v>
       </c>
       <c r="M29" s="6">
         <f t="shared" ref="M29:M30" si="115">SUM(O29:Q29)</f>
-        <v>1.84</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="N29" s="9">
-        <v>11.37</v>
+        <v>11.49</v>
       </c>
       <c r="O29" s="9">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="P29" s="13">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="Q29" s="9">
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="R29" s="19">
         <v>0.77</v>
@@ -3462,35 +3466,35 @@
       </c>
       <c r="T29" s="2">
         <f t="shared" ref="T29" si="116">ROUND(B29/K29,3)</f>
-        <v>0.57499999999999996</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="U29" s="2">
         <f t="shared" ref="U29" si="117">ROUND(C29/L29,3)</f>
-        <v>1.004</v>
+        <v>1.0429999999999999</v>
       </c>
       <c r="V29" s="6">
         <f t="shared" ref="V29" si="118">ROUND(D29/M29,3)</f>
-        <v>20.972999999999999</v>
+        <v>20.321000000000002</v>
       </c>
       <c r="W29" s="9">
         <f t="shared" ref="W29" si="119">ROUND(E29/N29,3)</f>
-        <v>21.463999999999999</v>
+        <v>21.634</v>
       </c>
       <c r="X29" s="9">
         <f t="shared" ref="X29" si="120">ROUND(F29/O29,3)</f>
-        <v>26.86</v>
+        <v>25.835000000000001</v>
       </c>
       <c r="Y29" s="13">
         <f t="shared" ref="Y29" si="121">ROUND(G29/P29,3)</f>
-        <v>19.062999999999999</v>
+        <v>18.631</v>
       </c>
       <c r="Z29" s="9">
         <f t="shared" ref="Z29" si="122">ROUND(H29/Q29,3)</f>
-        <v>5.2220000000000004</v>
+        <v>5.1429999999999998</v>
       </c>
       <c r="AA29" s="19">
         <f t="shared" ref="AA29" si="123">ROUND(I29/R29,3)</f>
-        <v>19.518999999999998</v>
+        <v>19.376999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3499,95 +3503,192 @@
       </c>
       <c r="B30" s="5">
         <f t="shared" ref="B30" si="124">D$2/D30</f>
-        <v>12.827040816326528</v>
+        <v>13.019678922837906</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" ref="C30" si="125">D29/D30</f>
-        <v>0.98443877551020387</v>
+        <v>0.99974106680476438</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" ref="D30" si="126">SUM(F30:H30)</f>
-        <v>39.200000000000003</v>
+        <v>38.619999999999997</v>
       </c>
       <c r="E30" s="13">
-        <v>206.15</v>
+        <v>206.11</v>
       </c>
       <c r="F30" s="9">
-        <v>24.88</v>
+        <v>24.64</v>
       </c>
       <c r="G30" s="9">
-        <v>12.68</v>
+        <v>12.36</v>
       </c>
       <c r="H30" s="9">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="I30" s="10">
-        <v>15.83</v>
+        <v>15.35</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="113"/>
-        <v>22.668478260869559</v>
+        <v>22.545945945945945</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="114"/>
-        <v>1</v>
+        <v>1.0270270270270272</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" si="115"/>
-        <v>1.84</v>
+        <v>1.8499999999999999</v>
       </c>
       <c r="N30" s="13">
-        <v>9.3800000000000008</v>
+        <v>9.57</v>
       </c>
       <c r="O30" s="9">
         <v>0.94</v>
       </c>
       <c r="P30" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="Q30" s="9">
         <v>0.26</v>
       </c>
       <c r="R30" s="10">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="S30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T30" s="5">
         <f t="shared" ref="T30" si="127">ROUND(B30/K30,3)</f>
-        <v>0.56599999999999995</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" ref="U30" si="128">ROUND(C30/L30,3)</f>
-        <v>0.98399999999999999</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" ref="V30" si="129">ROUND(D30/M30,3)</f>
-        <v>21.303999999999998</v>
+        <v>20.876000000000001</v>
       </c>
       <c r="W30" s="13">
         <f t="shared" ref="W30" si="130">ROUND(E30/N30,3)</f>
-        <v>21.978000000000002</v>
+        <v>21.536999999999999</v>
       </c>
       <c r="X30" s="9">
         <f t="shared" ref="X30" si="131">ROUND(F30/O30,3)</f>
-        <v>26.468</v>
+        <v>26.213000000000001</v>
       </c>
       <c r="Y30" s="9">
         <f t="shared" ref="Y30" si="132">ROUND(G30/P30,3)</f>
-        <v>19.812999999999999</v>
+        <v>19.015000000000001</v>
       </c>
       <c r="Z30" s="9">
         <f t="shared" ref="Z30" si="133">ROUND(H30/Q30,3)</f>
-        <v>6.3079999999999998</v>
+        <v>6.2309999999999999</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" ref="AA30" si="134">ROUND(I30/R30,3)</f>
-        <v>20.829000000000001</v>
+        <v>19.678999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="2">
+        <f t="shared" ref="B31" si="135">D$2/D31</f>
+        <v>13.1387509798798</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" ref="C31" si="136">D30/D31</f>
+        <v>1.0091455448131696</v>
+      </c>
+      <c r="D31" s="6">
+        <f t="shared" ref="D31" si="137">SUM(F31:H31)</f>
+        <v>38.269999999999996</v>
+      </c>
+      <c r="E31" s="9">
+        <v>202.28</v>
+      </c>
+      <c r="F31" s="9">
+        <v>24.82</v>
+      </c>
+      <c r="G31" s="9">
+        <v>12.29</v>
+      </c>
+      <c r="H31" s="13">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I31" s="10">
+        <v>15.53</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="2">
+        <f t="shared" ref="K31" si="138">M$2/M31</f>
+        <v>26.566878980891715</v>
+      </c>
+      <c r="L31" s="2">
+        <f t="shared" ref="L31" si="139">M30/M31</f>
+        <v>1.1783439490445859</v>
+      </c>
+      <c r="M31" s="6">
+        <f t="shared" ref="M31" si="140">SUM(O31:Q31)</f>
+        <v>1.57</v>
+      </c>
+      <c r="N31" s="9">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="O31" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="P31" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="R31" s="10">
+        <v>0.77</v>
+      </c>
+      <c r="S31" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="T31" s="2">
+        <f t="shared" ref="T31" si="141">ROUND(B31/K31,3)</f>
+        <v>0.495</v>
+      </c>
+      <c r="U31" s="2">
+        <f t="shared" ref="U31" si="142">ROUND(C31/L31,3)</f>
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="V31" s="6">
+        <f t="shared" ref="V31" si="143">ROUND(D31/M31,3)</f>
+        <v>24.376000000000001</v>
+      </c>
+      <c r="W31" s="9">
+        <f t="shared" ref="W31" si="144">ROUND(E31/N31,3)</f>
+        <v>21.181000000000001</v>
+      </c>
+      <c r="X31" s="9">
+        <f t="shared" ref="X31" si="145">ROUND(F31/O31,3)</f>
+        <v>27.577999999999999</v>
+      </c>
+      <c r="Y31" s="9">
+        <f t="shared" ref="Y31" si="146">ROUND(G31/P31,3)</f>
+        <v>19.202999999999999</v>
+      </c>
+      <c r="Z31" s="13">
+        <f t="shared" ref="Z31" si="147">ROUND(H31/Q31,3)</f>
+        <v>38.667000000000002</v>
+      </c>
+      <c r="AA31" s="10">
+        <f t="shared" ref="AA31" si="148">ROUND(I31/R31,3)</f>
+        <v>20.169</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28AFD8-101B-4335-AE33-EFFC17A0F8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18443230-68BD-4421-BE97-5AC668035BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="42">
   <si>
     <t>H23</t>
   </si>
@@ -167,6 +167,14 @@
   </si>
   <si>
     <t>H51</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H52</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H53</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -686,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3503,51 +3511,51 @@
       </c>
       <c r="B30" s="5">
         <f t="shared" ref="B30" si="124">D$2/D30</f>
-        <v>13.019678922837906</v>
+        <v>13.036556909515166</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" ref="C30" si="125">D29/D30</f>
-        <v>0.99974106680476438</v>
+        <v>1.0010370754472389</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" ref="D30" si="126">SUM(F30:H30)</f>
-        <v>38.619999999999997</v>
+        <v>38.57</v>
       </c>
       <c r="E30" s="13">
-        <v>206.11</v>
+        <v>205.43</v>
       </c>
       <c r="F30" s="9">
-        <v>24.64</v>
+        <v>24.6</v>
       </c>
       <c r="G30" s="9">
-        <v>12.36</v>
+        <v>12.37</v>
       </c>
       <c r="H30" s="9">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="I30" s="10">
-        <v>15.35</v>
+        <v>15.39</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="113"/>
-        <v>22.545945945945945</v>
+        <v>22.792349726775953</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="114"/>
-        <v>1.0270270270270272</v>
+        <v>1.0382513661202186</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" si="115"/>
-        <v>1.8499999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="N30" s="13">
-        <v>9.57</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="O30" s="9">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="P30" s="9">
         <v>0.65</v>
@@ -3556,42 +3564,42 @@
         <v>0.26</v>
       </c>
       <c r="R30" s="10">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="S30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T30" s="5">
         <f t="shared" ref="T30" si="127">ROUND(B30/K30,3)</f>
-        <v>0.57699999999999996</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" ref="U30" si="128">ROUND(C30/L30,3)</f>
-        <v>0.97299999999999998</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" ref="V30" si="129">ROUND(D30/M30,3)</f>
-        <v>20.876000000000001</v>
+        <v>21.077000000000002</v>
       </c>
       <c r="W30" s="13">
         <f t="shared" ref="W30" si="130">ROUND(E30/N30,3)</f>
-        <v>21.536999999999999</v>
+        <v>21.510999999999999</v>
       </c>
       <c r="X30" s="9">
         <f t="shared" ref="X30" si="131">ROUND(F30/O30,3)</f>
-        <v>26.213000000000001</v>
+        <v>26.739000000000001</v>
       </c>
       <c r="Y30" s="9">
         <f t="shared" ref="Y30" si="132">ROUND(G30/P30,3)</f>
-        <v>19.015000000000001</v>
+        <v>19.030999999999999</v>
       </c>
       <c r="Z30" s="9">
         <f t="shared" ref="Z30" si="133">ROUND(H30/Q30,3)</f>
-        <v>6.2309999999999999</v>
+        <v>6.1539999999999999</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" ref="AA30" si="134">ROUND(I30/R30,3)</f>
-        <v>19.678999999999998</v>
+        <v>19.986999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3600,87 +3608,87 @@
       </c>
       <c r="B31" s="2">
         <f t="shared" ref="B31" si="135">D$2/D31</f>
-        <v>13.1387509798798</v>
+        <v>12.925964010282778</v>
       </c>
       <c r="C31" s="2">
         <f t="shared" ref="C31" si="136">D30/D31</f>
-        <v>1.0091455448131696</v>
+        <v>0.99151670951156834</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="137">SUM(F31:H31)</f>
-        <v>38.269999999999996</v>
+        <v>38.899999999999991</v>
       </c>
       <c r="E31" s="9">
-        <v>202.28</v>
+        <v>206.67</v>
       </c>
       <c r="F31" s="9">
-        <v>24.82</v>
+        <v>25.22</v>
       </c>
       <c r="G31" s="9">
-        <v>12.29</v>
+        <v>12.52</v>
       </c>
       <c r="H31" s="13">
         <v>1.1599999999999999</v>
       </c>
       <c r="I31" s="10">
-        <v>15.53</v>
+        <v>15.47</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" ref="K31" si="138">M$2/M31</f>
+        <f t="shared" ref="K31:K33" si="138">M$2/M31</f>
         <v>26.566878980891715</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" ref="L31" si="139">M30/M31</f>
-        <v>1.1783439490445859</v>
+        <f t="shared" ref="L31:L33" si="139">M30/M31</f>
+        <v>1.1656050955414012</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" ref="M31" si="140">SUM(O31:Q31)</f>
+        <f t="shared" ref="M31:M33" si="140">SUM(O31:Q31)</f>
         <v>1.57</v>
       </c>
       <c r="N31" s="9">
-        <v>9.5500000000000007</v>
+        <v>9.44</v>
       </c>
       <c r="O31" s="9">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="P31" s="9">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="Q31" s="13">
         <v>0.03</v>
       </c>
       <c r="R31" s="10">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="S31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="T31" s="2">
         <f t="shared" ref="T31" si="141">ROUND(B31/K31,3)</f>
-        <v>0.495</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="U31" s="2">
         <f t="shared" ref="U31" si="142">ROUND(C31/L31,3)</f>
-        <v>0.85599999999999998</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="V31" s="6">
         <f t="shared" ref="V31" si="143">ROUND(D31/M31,3)</f>
-        <v>24.376000000000001</v>
+        <v>24.777000000000001</v>
       </c>
       <c r="W31" s="9">
         <f t="shared" ref="W31" si="144">ROUND(E31/N31,3)</f>
-        <v>21.181000000000001</v>
+        <v>21.893000000000001</v>
       </c>
       <c r="X31" s="9">
         <f t="shared" ref="X31" si="145">ROUND(F31/O31,3)</f>
-        <v>27.577999999999999</v>
+        <v>27.713999999999999</v>
       </c>
       <c r="Y31" s="9">
         <f t="shared" ref="Y31" si="146">ROUND(G31/P31,3)</f>
-        <v>19.202999999999999</v>
+        <v>19.873000000000001</v>
       </c>
       <c r="Z31" s="13">
         <f t="shared" ref="Z31" si="147">ROUND(H31/Q31,3)</f>
@@ -3688,7 +3696,201 @@
       </c>
       <c r="AA31" s="10">
         <f t="shared" ref="AA31" si="148">ROUND(I31/R31,3)</f>
-        <v>20.169</v>
+        <v>20.355</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5">
+        <f t="shared" ref="B32" si="149">D$2/D32</f>
+        <v>13.22514466070489</v>
+      </c>
+      <c r="C32" s="5">
+        <f t="shared" ref="C32" si="150">D31/D32</f>
+        <v>1.0231457127827457</v>
+      </c>
+      <c r="D32" s="4">
+        <f t="shared" ref="D32" si="151">SUM(F32:H32)</f>
+        <v>38.020000000000003</v>
+      </c>
+      <c r="E32" s="9">
+        <v>209.98</v>
+      </c>
+      <c r="F32" s="13">
+        <v>24.45</v>
+      </c>
+      <c r="G32" s="9">
+        <v>12.4</v>
+      </c>
+      <c r="H32" s="9">
+        <v>1.17</v>
+      </c>
+      <c r="I32" s="10">
+        <v>14.83</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K32" s="5">
+        <f t="shared" si="138"/>
+        <v>28.182432432432424</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="139"/>
+        <v>1.0608108108108107</v>
+      </c>
+      <c r="M32" s="4">
+        <f t="shared" si="140"/>
+        <v>1.4800000000000002</v>
+      </c>
+      <c r="N32" s="9">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="O32" s="13">
+        <v>0.81</v>
+      </c>
+      <c r="P32" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="Q32" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R32" s="10">
+        <v>0.76</v>
+      </c>
+      <c r="S32" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="T32" s="2">
+        <f t="shared" ref="T32:T33" si="152">ROUND(B32/K32,3)</f>
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="U32" s="2">
+        <f t="shared" ref="U32:U33" si="153">ROUND(C32/L32,3)</f>
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="V32" s="6">
+        <f t="shared" ref="V32:V33" si="154">ROUND(D32/M32,3)</f>
+        <v>25.689</v>
+      </c>
+      <c r="W32" s="9">
+        <f t="shared" ref="W32:W33" si="155">ROUND(E32/N32,3)</f>
+        <v>22.172999999999998</v>
+      </c>
+      <c r="X32" s="9">
+        <f t="shared" ref="X32:X33" si="156">ROUND(F32/O32,3)</f>
+        <v>30.184999999999999</v>
+      </c>
+      <c r="Y32" s="9">
+        <f t="shared" ref="Y32:Y33" si="157">ROUND(G32/P32,3)</f>
+        <v>19.375</v>
+      </c>
+      <c r="Z32" s="13">
+        <f t="shared" ref="Z32:Z33" si="158">ROUND(H32/Q32,3)</f>
+        <v>39</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" ref="AA32:AA33" si="159">ROUND(I32/R32,3)</f>
+        <v>19.513000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="5">
+        <f t="shared" ref="B33" si="160">D$2/D33</f>
+        <v>13.498523489932884</v>
+      </c>
+      <c r="C33" s="5">
+        <f t="shared" ref="C33" si="161">D32/D33</f>
+        <v>1.0206711409395974</v>
+      </c>
+      <c r="D33" s="4">
+        <f t="shared" ref="D33" si="162">SUM(F33:H33)</f>
+        <v>37.25</v>
+      </c>
+      <c r="E33" s="9">
+        <v>202.68</v>
+      </c>
+      <c r="F33" s="9">
+        <v>24.36</v>
+      </c>
+      <c r="G33" s="13">
+        <v>11.73</v>
+      </c>
+      <c r="H33" s="9">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I33" s="14">
+        <v>14.62</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="5">
+        <f t="shared" si="138"/>
+        <v>29.581560283687942</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="139"/>
+        <v>1.0496453900709222</v>
+      </c>
+      <c r="M33" s="4">
+        <f t="shared" si="140"/>
+        <v>1.41</v>
+      </c>
+      <c r="N33" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="O33" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="P33" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R33" s="14">
+        <v>0.71</v>
+      </c>
+      <c r="S33" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T33" s="5">
+        <f t="shared" si="152"/>
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="U33" s="5">
+        <f t="shared" si="153"/>
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="V33" s="4">
+        <f t="shared" si="154"/>
+        <v>26.417999999999999</v>
+      </c>
+      <c r="W33" s="9">
+        <f t="shared" si="155"/>
+        <v>21.335000000000001</v>
+      </c>
+      <c r="X33" s="9">
+        <f t="shared" si="156"/>
+        <v>31.231000000000002</v>
+      </c>
+      <c r="Y33" s="13">
+        <f t="shared" si="157"/>
+        <v>19.55</v>
+      </c>
+      <c r="Z33" s="9">
+        <f t="shared" si="158"/>
+        <v>38.667000000000002</v>
+      </c>
+      <c r="AA33" s="14">
+        <f t="shared" si="159"/>
+        <v>20.591999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18443230-68BD-4421-BE97-5AC668035BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F6F3EA-DE08-4D46-95BE-43C5BE9C3B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="43">
   <si>
     <t>H23</t>
   </si>
@@ -175,6 +175,10 @@
   </si>
   <si>
     <t>H53</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H54</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB33"/>
+  <dimension ref="A1:AB34"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3511,51 +3515,51 @@
       </c>
       <c r="B30" s="5">
         <f t="shared" ref="B30" si="124">D$2/D30</f>
-        <v>13.036556909515166</v>
+        <v>12.774898373983739</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" ref="C30" si="125">D29/D30</f>
-        <v>1.0010370754472389</v>
+        <v>0.98094512195121952</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" ref="D30" si="126">SUM(F30:H30)</f>
-        <v>38.57</v>
+        <v>39.36</v>
       </c>
       <c r="E30" s="13">
-        <v>205.43</v>
+        <v>206.44</v>
       </c>
       <c r="F30" s="9">
-        <v>24.6</v>
+        <v>25.32</v>
       </c>
       <c r="G30" s="9">
-        <v>12.37</v>
+        <v>12.45</v>
       </c>
       <c r="H30" s="9">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I30" s="10">
-        <v>15.39</v>
+        <v>15.46</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="113"/>
-        <v>22.792349726775953</v>
+        <v>22.917582417582413</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="114"/>
-        <v>1.0382513661202186</v>
+        <v>1.043956043956044</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" si="115"/>
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N30" s="13">
-        <v>9.5500000000000007</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="O30" s="9">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="P30" s="9">
         <v>0.65</v>
@@ -3571,35 +3575,35 @@
       </c>
       <c r="T30" s="5">
         <f t="shared" ref="T30" si="127">ROUND(B30/K30,3)</f>
-        <v>0.57199999999999995</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" ref="U30" si="128">ROUND(C30/L30,3)</f>
-        <v>0.96399999999999997</v>
+        <v>0.94</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" ref="V30" si="129">ROUND(D30/M30,3)</f>
-        <v>21.077000000000002</v>
+        <v>21.626000000000001</v>
       </c>
       <c r="W30" s="13">
         <f t="shared" ref="W30" si="130">ROUND(E30/N30,3)</f>
-        <v>21.510999999999999</v>
+        <v>21.065000000000001</v>
       </c>
       <c r="X30" s="9">
         <f t="shared" ref="X30" si="131">ROUND(F30/O30,3)</f>
-        <v>26.739000000000001</v>
+        <v>27.824000000000002</v>
       </c>
       <c r="Y30" s="9">
         <f t="shared" ref="Y30" si="132">ROUND(G30/P30,3)</f>
-        <v>19.030999999999999</v>
+        <v>19.154</v>
       </c>
       <c r="Z30" s="9">
         <f t="shared" ref="Z30" si="133">ROUND(H30/Q30,3)</f>
-        <v>6.1539999999999999</v>
+        <v>6.1150000000000002</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" ref="AA30" si="134">ROUND(I30/R30,3)</f>
-        <v>19.986999999999998</v>
+        <v>20.077999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3608,51 +3612,51 @@
       </c>
       <c r="B31" s="2">
         <f t="shared" ref="B31" si="135">D$2/D31</f>
-        <v>12.925964010282778</v>
+        <v>12.979349509550849</v>
       </c>
       <c r="C31" s="2">
         <f t="shared" ref="C31" si="136">D30/D31</f>
-        <v>0.99151670951156834</v>
+        <v>1.0160041300980898</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="137">SUM(F31:H31)</f>
-        <v>38.899999999999991</v>
+        <v>38.74</v>
       </c>
       <c r="E31" s="9">
-        <v>206.67</v>
+        <v>204.69</v>
       </c>
       <c r="F31" s="9">
-        <v>25.22</v>
+        <v>25.05</v>
       </c>
       <c r="G31" s="9">
         <v>12.52</v>
       </c>
       <c r="H31" s="13">
-        <v>1.1599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="I31" s="10">
-        <v>15.47</v>
+        <v>15.61</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" ref="K31:K33" si="138">M$2/M31</f>
-        <v>26.566878980891715</v>
+        <f t="shared" ref="K31:K34" si="138">M$2/M31</f>
+        <v>25.746913580246911</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" ref="L31:L33" si="139">M30/M31</f>
-        <v>1.1656050955414012</v>
+        <f t="shared" ref="L31:L34" si="139">M30/M31</f>
+        <v>1.1234567901234569</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" ref="M31:M33" si="140">SUM(O31:Q31)</f>
-        <v>1.57</v>
+        <f t="shared" ref="M31:M34" si="140">SUM(O31:Q31)</f>
+        <v>1.6199999999999999</v>
       </c>
       <c r="N31" s="9">
-        <v>9.44</v>
+        <v>9.51</v>
       </c>
       <c r="O31" s="9">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="P31" s="9">
         <v>0.63</v>
@@ -3661,30 +3665,30 @@
         <v>0.03</v>
       </c>
       <c r="R31" s="10">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="S31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="T31" s="2">
         <f t="shared" ref="T31" si="141">ROUND(B31/K31,3)</f>
-        <v>0.48699999999999999</v>
+        <v>0.504</v>
       </c>
       <c r="U31" s="2">
         <f t="shared" ref="U31" si="142">ROUND(C31/L31,3)</f>
-        <v>0.85099999999999998</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="V31" s="6">
         <f t="shared" ref="V31" si="143">ROUND(D31/M31,3)</f>
-        <v>24.777000000000001</v>
+        <v>23.914000000000001</v>
       </c>
       <c r="W31" s="9">
         <f t="shared" ref="W31" si="144">ROUND(E31/N31,3)</f>
-        <v>21.893000000000001</v>
+        <v>21.524000000000001</v>
       </c>
       <c r="X31" s="9">
         <f t="shared" ref="X31" si="145">ROUND(F31/O31,3)</f>
-        <v>27.713999999999999</v>
+        <v>26.094000000000001</v>
       </c>
       <c r="Y31" s="9">
         <f t="shared" ref="Y31" si="146">ROUND(G31/P31,3)</f>
@@ -3692,11 +3696,11 @@
       </c>
       <c r="Z31" s="13">
         <f t="shared" ref="Z31" si="147">ROUND(H31/Q31,3)</f>
-        <v>38.667000000000002</v>
+        <v>39</v>
       </c>
       <c r="AA31" s="10">
         <f t="shared" ref="AA31" si="148">ROUND(I31/R31,3)</f>
-        <v>20.355</v>
+        <v>20.812999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3705,54 +3709,54 @@
       </c>
       <c r="B32" s="5">
         <f t="shared" ref="B32" si="149">D$2/D32</f>
-        <v>13.22514466070489</v>
+        <v>13.152498038189901</v>
       </c>
       <c r="C32" s="5">
         <f t="shared" ref="C32" si="150">D31/D32</f>
-        <v>1.0231457127827457</v>
+        <v>1.0133403086581219</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" ref="D32" si="151">SUM(F32:H32)</f>
-        <v>38.020000000000003</v>
+        <v>38.230000000000004</v>
       </c>
       <c r="E32" s="9">
-        <v>209.98</v>
+        <v>206.61</v>
       </c>
       <c r="F32" s="13">
-        <v>24.45</v>
+        <v>24.56</v>
       </c>
       <c r="G32" s="9">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="H32" s="9">
         <v>1.17</v>
       </c>
       <c r="I32" s="10">
-        <v>14.83</v>
+        <v>14.96</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>40</v>
       </c>
       <c r="K32" s="5">
         <f t="shared" si="138"/>
-        <v>28.182432432432424</v>
+        <v>28.965277777777771</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="139"/>
-        <v>1.0608108108108107</v>
+        <v>1.1249999999999998</v>
       </c>
       <c r="M32" s="4">
         <f t="shared" si="140"/>
-        <v>1.4800000000000002</v>
+        <v>1.4400000000000002</v>
       </c>
       <c r="N32" s="9">
-        <v>9.4700000000000006</v>
+        <v>9.49</v>
       </c>
       <c r="O32" s="13">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="P32" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="Q32" s="9">
         <v>0.03</v>
@@ -3765,27 +3769,27 @@
       </c>
       <c r="T32" s="2">
         <f t="shared" ref="T32:T33" si="152">ROUND(B32/K32,3)</f>
-        <v>0.46899999999999997</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="U32" s="2">
         <f t="shared" ref="U32:U33" si="153">ROUND(C32/L32,3)</f>
-        <v>0.96399999999999997</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="V32" s="6">
         <f t="shared" ref="V32:V33" si="154">ROUND(D32/M32,3)</f>
-        <v>25.689</v>
+        <v>26.548999999999999</v>
       </c>
       <c r="W32" s="9">
         <f t="shared" ref="W32:W33" si="155">ROUND(E32/N32,3)</f>
-        <v>22.172999999999998</v>
+        <v>21.771000000000001</v>
       </c>
       <c r="X32" s="9">
         <f t="shared" ref="X32:X33" si="156">ROUND(F32/O32,3)</f>
-        <v>30.184999999999999</v>
+        <v>32.316000000000003</v>
       </c>
       <c r="Y32" s="9">
         <f t="shared" ref="Y32:Y33" si="157">ROUND(G32/P32,3)</f>
-        <v>19.375</v>
+        <v>19.231000000000002</v>
       </c>
       <c r="Z32" s="13">
         <f t="shared" ref="Z32:Z33" si="158">ROUND(H32/Q32,3)</f>
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AA32" s="10">
         <f t="shared" ref="AA32:AA33" si="159">ROUND(I32/R32,3)</f>
-        <v>19.513000000000002</v>
+        <v>19.684000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3802,51 +3806,51 @@
       </c>
       <c r="B33" s="5">
         <f t="shared" ref="B33" si="160">D$2/D33</f>
-        <v>13.498523489932884</v>
+        <v>13.630252100840337</v>
       </c>
       <c r="C33" s="5">
         <f t="shared" ref="C33" si="161">D32/D33</f>
-        <v>1.0206711409395974</v>
+        <v>1.0363242071021961</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" ref="D33" si="162">SUM(F33:H33)</f>
-        <v>37.25</v>
+        <v>36.889999999999993</v>
       </c>
       <c r="E33" s="9">
-        <v>202.68</v>
+        <v>203.57</v>
       </c>
       <c r="F33" s="9">
-        <v>24.36</v>
+        <v>24.06</v>
       </c>
       <c r="G33" s="13">
-        <v>11.73</v>
+        <v>11.67</v>
       </c>
       <c r="H33" s="9">
         <v>1.1599999999999999</v>
       </c>
       <c r="I33" s="14">
-        <v>14.62</v>
+        <v>14.69</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>41</v>
       </c>
       <c r="K33" s="5">
         <f t="shared" si="138"/>
-        <v>29.581560283687942</v>
+        <v>28.765517241379307</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="139"/>
-        <v>1.0496453900709222</v>
+        <v>0.99310344827586217</v>
       </c>
       <c r="M33" s="4">
         <f t="shared" si="140"/>
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="N33" s="9">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="O33" s="9">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="P33" s="13">
         <v>0.6</v>
@@ -3862,27 +3866,27 @@
       </c>
       <c r="T33" s="5">
         <f t="shared" si="152"/>
-        <v>0.45600000000000002</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="U33" s="5">
         <f t="shared" si="153"/>
-        <v>0.97199999999999998</v>
+        <v>1.044</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="154"/>
-        <v>26.417999999999999</v>
+        <v>25.440999999999999</v>
       </c>
       <c r="W33" s="9">
         <f t="shared" si="155"/>
-        <v>21.335000000000001</v>
+        <v>21.587</v>
       </c>
       <c r="X33" s="9">
         <f t="shared" si="156"/>
-        <v>31.231000000000002</v>
+        <v>29.341000000000001</v>
       </c>
       <c r="Y33" s="13">
         <f t="shared" si="157"/>
-        <v>19.55</v>
+        <v>19.45</v>
       </c>
       <c r="Z33" s="9">
         <f t="shared" si="158"/>
@@ -3890,7 +3894,104 @@
       </c>
       <c r="AA33" s="14">
         <f t="shared" si="159"/>
-        <v>20.591999999999999</v>
+        <v>20.69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="5">
+        <f t="shared" ref="B34" si="163">D$2/D34</f>
+        <v>13.505774912704807</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" ref="C34" si="164">D33/D34</f>
+        <v>0.99086757990867569</v>
+      </c>
+      <c r="D34" s="6">
+        <f t="shared" ref="D34" si="165">SUM(F34:H34)</f>
+        <v>37.229999999999997</v>
+      </c>
+      <c r="E34" s="13">
+        <v>208.35</v>
+      </c>
+      <c r="F34" s="9">
+        <v>24.24</v>
+      </c>
+      <c r="G34" s="13">
+        <v>11.8</v>
+      </c>
+      <c r="H34" s="9">
+        <v>1.19</v>
+      </c>
+      <c r="I34" s="14">
+        <v>14.75</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" s="2">
+        <f t="shared" si="138"/>
+        <v>32.333333333333329</v>
+      </c>
+      <c r="L34" s="2">
+        <f t="shared" si="139"/>
+        <v>1.124031007751938</v>
+      </c>
+      <c r="M34" s="6">
+        <f t="shared" si="140"/>
+        <v>1.29</v>
+      </c>
+      <c r="N34" s="9">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="O34" s="9">
+        <v>0.83</v>
+      </c>
+      <c r="P34" s="13">
+        <v>0.43</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R34" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="S34" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="T34" s="2">
+        <f t="shared" ref="T34" si="166">ROUND(B34/K34,3)</f>
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="U34" s="2">
+        <f t="shared" ref="U34" si="167">ROUND(C34/L34,3)</f>
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="V34" s="6">
+        <f t="shared" ref="V34" si="168">ROUND(D34/M34,3)</f>
+        <v>28.86</v>
+      </c>
+      <c r="W34" s="9">
+        <f t="shared" ref="W34" si="169">ROUND(E34/N34,3)</f>
+        <v>21.817</v>
+      </c>
+      <c r="X34" s="9">
+        <f t="shared" ref="X34" si="170">ROUND(F34/O34,3)</f>
+        <v>29.204999999999998</v>
+      </c>
+      <c r="Y34" s="13">
+        <f t="shared" ref="Y34" si="171">ROUND(G34/P34,3)</f>
+        <v>27.442</v>
+      </c>
+      <c r="Z34" s="9">
+        <f t="shared" ref="Z34" si="172">ROUND(H34/Q34,3)</f>
+        <v>39.667000000000002</v>
+      </c>
+      <c r="AA34" s="14">
+        <f t="shared" ref="AA34" si="173">ROUND(I34/R34,3)</f>
+        <v>23.047000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F6F3EA-DE08-4D46-95BE-43C5BE9C3B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9EE873-4CD5-48DC-A681-F440ED455ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="44">
   <si>
     <t>H23</t>
   </si>
@@ -179,6 +179,10 @@
   </si>
   <si>
     <t>H54</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H55</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AB35"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3767,15 +3771,15 @@
       <c r="S32" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="T32" s="2">
+      <c r="T32" s="5">
         <f t="shared" ref="T32:T33" si="152">ROUND(B32/K32,3)</f>
         <v>0.45400000000000001</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="5">
         <f t="shared" ref="U32:U33" si="153">ROUND(C32/L32,3)</f>
         <v>0.90100000000000002</v>
       </c>
-      <c r="V32" s="6">
+      <c r="V32" s="4">
         <f t="shared" ref="V32:V33" si="154">ROUND(D32/M32,3)</f>
         <v>26.548999999999999</v>
       </c>
@@ -3783,7 +3787,7 @@
         <f t="shared" ref="W32:W33" si="155">ROUND(E32/N32,3)</f>
         <v>21.771000000000001</v>
       </c>
-      <c r="X32" s="9">
+      <c r="X32" s="13">
         <f t="shared" ref="X32:X33" si="156">ROUND(F32/O32,3)</f>
         <v>32.316000000000003</v>
       </c>
@@ -3791,7 +3795,7 @@
         <f t="shared" ref="Y32:Y33" si="157">ROUND(G32/P32,3)</f>
         <v>19.231000000000002</v>
       </c>
-      <c r="Z32" s="13">
+      <c r="Z32" s="9">
         <f t="shared" ref="Z32:Z33" si="158">ROUND(H32/Q32,3)</f>
         <v>39</v>
       </c>
@@ -3901,97 +3905,194 @@
       <c r="A34" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="2">
         <f t="shared" ref="B34" si="163">D$2/D34</f>
-        <v>13.505774912704807</v>
+        <v>13.71950886766712</v>
       </c>
       <c r="C34" s="2">
         <f t="shared" ref="C34" si="164">D33/D34</f>
-        <v>0.99086757990867569</v>
+        <v>1.0065484311050477</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" ref="D34" si="165">SUM(F34:H34)</f>
-        <v>37.229999999999997</v>
-      </c>
-      <c r="E34" s="13">
-        <v>208.35</v>
+        <v>36.65</v>
+      </c>
+      <c r="E34" s="18">
+        <v>203.32</v>
       </c>
       <c r="F34" s="9">
-        <v>24.24</v>
+        <v>23.96</v>
       </c>
       <c r="G34" s="13">
-        <v>11.8</v>
+        <v>11.53</v>
       </c>
       <c r="H34" s="9">
-        <v>1.19</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I34" s="14">
-        <v>14.75</v>
+        <v>14.62</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="K34" s="2">
         <f t="shared" si="138"/>
-        <v>32.333333333333329</v>
+        <v>31.36090225563909</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="139"/>
-        <v>1.124031007751938</v>
+        <v>1.0902255639097744</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="140"/>
-        <v>1.29</v>
-      </c>
-      <c r="N34" s="9">
-        <v>9.5500000000000007</v>
+        <v>1.33</v>
+      </c>
+      <c r="N34" s="18">
+        <v>9.86</v>
       </c>
       <c r="O34" s="9">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="P34" s="13">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="Q34" s="9">
         <v>0.03</v>
       </c>
       <c r="R34" s="14">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="S34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="T34" s="2">
         <f t="shared" ref="T34" si="166">ROUND(B34/K34,3)</f>
-        <v>0.41799999999999998</v>
+        <v>0.437</v>
       </c>
       <c r="U34" s="2">
         <f t="shared" ref="U34" si="167">ROUND(C34/L34,3)</f>
-        <v>0.88200000000000001</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="V34" s="6">
         <f t="shared" ref="V34" si="168">ROUND(D34/M34,3)</f>
-        <v>28.86</v>
-      </c>
-      <c r="W34" s="9">
+        <v>27.556000000000001</v>
+      </c>
+      <c r="W34" s="18">
         <f t="shared" ref="W34" si="169">ROUND(E34/N34,3)</f>
-        <v>21.817</v>
+        <v>20.620999999999999</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" ref="X34" si="170">ROUND(F34/O34,3)</f>
-        <v>29.204999999999998</v>
+        <v>27.86</v>
       </c>
       <c r="Y34" s="13">
         <f t="shared" ref="Y34" si="171">ROUND(G34/P34,3)</f>
-        <v>27.442</v>
+        <v>26.204999999999998</v>
       </c>
       <c r="Z34" s="9">
         <f t="shared" ref="Z34" si="172">ROUND(H34/Q34,3)</f>
-        <v>39.667000000000002</v>
+        <v>38.667000000000002</v>
       </c>
       <c r="AA34" s="14">
         <f t="shared" ref="AA34" si="173">ROUND(I34/R34,3)</f>
-        <v>23.047000000000001</v>
+        <v>22.492000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="2">
+        <f t="shared" ref="B35" si="174">D$2/D35</f>
+        <v>19.549766718506998</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" ref="C35" si="175">D34/D35</f>
+        <v>1.4249611197511665</v>
+      </c>
+      <c r="D35" s="6">
+        <f t="shared" ref="D35" si="176">SUM(F35:H35)</f>
+        <v>25.72</v>
+      </c>
+      <c r="E35" s="9">
+        <v>203.83</v>
+      </c>
+      <c r="F35" s="13">
+        <v>13.19</v>
+      </c>
+      <c r="G35" s="9">
+        <v>11.37</v>
+      </c>
+      <c r="H35" s="9">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I35" s="10">
+        <v>14.68</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K35" s="2">
+        <f t="shared" ref="K35" si="177">M$2/M35</f>
+        <v>35.050420168067227</v>
+      </c>
+      <c r="L35" s="2">
+        <f t="shared" ref="L35" si="178">M34/M35</f>
+        <v>1.1176470588235294</v>
+      </c>
+      <c r="M35" s="6">
+        <f t="shared" ref="M35" si="179">SUM(O35:Q35)</f>
+        <v>1.19</v>
+      </c>
+      <c r="N35" s="9">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="O35" s="13">
+        <v>0.73</v>
+      </c>
+      <c r="P35" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R35" s="10">
+        <v>0.64</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="T35" s="2">
+        <f t="shared" ref="T35" si="180">ROUND(B35/K35,3)</f>
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="U35" s="2">
+        <f t="shared" ref="U35" si="181">ROUND(C35/L35,3)</f>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="V35" s="6">
+        <f t="shared" ref="V35" si="182">ROUND(D35/M35,3)</f>
+        <v>21.613</v>
+      </c>
+      <c r="W35" s="9">
+        <f t="shared" ref="W35" si="183">ROUND(E35/N35,3)</f>
+        <v>21.343</v>
+      </c>
+      <c r="X35" s="13">
+        <f t="shared" ref="X35" si="184">ROUND(F35/O35,3)</f>
+        <v>18.068000000000001</v>
+      </c>
+      <c r="Y35" s="9">
+        <f t="shared" ref="Y35" si="185">ROUND(G35/P35,3)</f>
+        <v>26.442</v>
+      </c>
+      <c r="Z35" s="9">
+        <f t="shared" ref="Z35" si="186">ROUND(H35/Q35,3)</f>
+        <v>38.667000000000002</v>
+      </c>
+      <c r="AA35" s="10">
+        <f t="shared" ref="AA35" si="187">ROUND(I35/R35,3)</f>
+        <v>22.937999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9EE873-4CD5-48DC-A681-F440ED455ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67195B1B-B5DE-45D3-A727-CF348C589155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="45">
   <si>
     <t>H23</t>
   </si>
@@ -183,6 +183,10 @@
   </si>
   <si>
     <t>H55</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H56</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -327,7 +331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -386,6 +390,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -702,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB35"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3907,95 +3914,95 @@
       </c>
       <c r="B34" s="2">
         <f t="shared" ref="B34" si="163">D$2/D34</f>
-        <v>13.71950886766712</v>
+        <v>13.726999726999727</v>
       </c>
       <c r="C34" s="2">
         <f t="shared" ref="C34" si="164">D33/D34</f>
-        <v>1.0065484311050477</v>
+        <v>1.0070980070980071</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" ref="D34" si="165">SUM(F34:H34)</f>
-        <v>36.65</v>
+        <v>36.629999999999995</v>
       </c>
       <c r="E34" s="18">
-        <v>203.32</v>
+        <v>207.16</v>
       </c>
       <c r="F34" s="9">
-        <v>23.96</v>
+        <v>23.86</v>
       </c>
       <c r="G34" s="13">
-        <v>11.53</v>
+        <v>11.62</v>
       </c>
       <c r="H34" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I34" s="14">
-        <v>14.62</v>
+        <v>14.55</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="K34" s="2">
         <f t="shared" si="138"/>
-        <v>31.36090225563909</v>
+        <v>34.188524590163929</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="139"/>
-        <v>1.0902255639097744</v>
+        <v>1.1885245901639345</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="140"/>
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="N34" s="18">
-        <v>9.86</v>
+        <v>9.59</v>
       </c>
       <c r="O34" s="9">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="P34" s="13">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="Q34" s="9">
         <v>0.03</v>
       </c>
       <c r="R34" s="14">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="S34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="T34" s="2">
         <f t="shared" ref="T34" si="166">ROUND(B34/K34,3)</f>
-        <v>0.437</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="U34" s="2">
         <f t="shared" ref="U34" si="167">ROUND(C34/L34,3)</f>
-        <v>0.92300000000000004</v>
+        <v>0.84699999999999998</v>
       </c>
       <c r="V34" s="6">
         <f t="shared" ref="V34" si="168">ROUND(D34/M34,3)</f>
-        <v>27.556000000000001</v>
+        <v>30.024999999999999</v>
       </c>
       <c r="W34" s="18">
         <f t="shared" ref="W34" si="169">ROUND(E34/N34,3)</f>
-        <v>20.620999999999999</v>
+        <v>21.602</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" ref="X34" si="170">ROUND(F34/O34,3)</f>
-        <v>27.86</v>
+        <v>31.395</v>
       </c>
       <c r="Y34" s="13">
         <f t="shared" ref="Y34" si="171">ROUND(G34/P34,3)</f>
-        <v>26.204999999999998</v>
+        <v>27.023</v>
       </c>
       <c r="Z34" s="9">
         <f t="shared" ref="Z34" si="172">ROUND(H34/Q34,3)</f>
-        <v>38.667000000000002</v>
+        <v>38.332999999999998</v>
       </c>
       <c r="AA34" s="14">
         <f t="shared" ref="AA34" si="173">ROUND(I34/R34,3)</f>
-        <v>22.492000000000001</v>
+        <v>22.734000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4003,52 +4010,52 @@
         <v>43</v>
       </c>
       <c r="B35" s="2">
-        <f t="shared" ref="B35" si="174">D$2/D35</f>
-        <v>19.549766718506998</v>
+        <f t="shared" ref="B35:B36" si="174">D$2/D35</f>
+        <v>19.287303413885688</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" ref="C35" si="175">D34/D35</f>
-        <v>1.4249611197511665</v>
+        <f t="shared" ref="C35:C36" si="175">D34/D35</f>
+        <v>1.4050632911392402</v>
       </c>
       <c r="D35" s="6">
-        <f t="shared" ref="D35" si="176">SUM(F35:H35)</f>
-        <v>25.72</v>
+        <f t="shared" ref="D35:D36" si="176">SUM(F35:H35)</f>
+        <v>26.07</v>
       </c>
       <c r="E35" s="9">
-        <v>203.83</v>
+        <v>206.87</v>
       </c>
       <c r="F35" s="13">
-        <v>13.19</v>
+        <v>13.32</v>
       </c>
       <c r="G35" s="9">
-        <v>11.37</v>
+        <v>11.58</v>
       </c>
       <c r="H35" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="I35" s="10">
-        <v>14.68</v>
+        <v>14.8</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>43</v>
       </c>
       <c r="K35" s="2">
         <f t="shared" ref="K35" si="177">M$2/M35</f>
-        <v>35.050420168067227</v>
+        <v>32.333333333333329</v>
       </c>
       <c r="L35" s="2">
         <f t="shared" ref="L35" si="178">M34/M35</f>
-        <v>1.1176470588235294</v>
+        <v>0.94573643410852704</v>
       </c>
       <c r="M35" s="6">
         <f t="shared" ref="M35" si="179">SUM(O35:Q35)</f>
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="N35" s="9">
-        <v>9.5500000000000007</v>
+        <v>9.44</v>
       </c>
       <c r="O35" s="13">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="P35" s="9">
         <v>0.43</v>
@@ -4064,35 +4071,132 @@
       </c>
       <c r="T35" s="2">
         <f t="shared" ref="T35" si="180">ROUND(B35/K35,3)</f>
-        <v>0.55800000000000005</v>
+        <v>0.59699999999999998</v>
       </c>
       <c r="U35" s="2">
         <f t="shared" ref="U35" si="181">ROUND(C35/L35,3)</f>
-        <v>1.2749999999999999</v>
+        <v>1.486</v>
       </c>
       <c r="V35" s="6">
         <f t="shared" ref="V35" si="182">ROUND(D35/M35,3)</f>
-        <v>21.613</v>
+        <v>20.209</v>
       </c>
       <c r="W35" s="9">
         <f t="shared" ref="W35" si="183">ROUND(E35/N35,3)</f>
-        <v>21.343</v>
+        <v>21.914000000000001</v>
       </c>
       <c r="X35" s="13">
         <f t="shared" ref="X35" si="184">ROUND(F35/O35,3)</f>
-        <v>18.068000000000001</v>
+        <v>16.047999999999998</v>
       </c>
       <c r="Y35" s="9">
         <f t="shared" ref="Y35" si="185">ROUND(G35/P35,3)</f>
-        <v>26.442</v>
+        <v>26.93</v>
       </c>
       <c r="Z35" s="9">
         <f t="shared" ref="Z35" si="186">ROUND(H35/Q35,3)</f>
-        <v>38.667000000000002</v>
+        <v>39</v>
       </c>
       <c r="AA35" s="10">
         <f t="shared" ref="AA35" si="187">ROUND(I35/R35,3)</f>
-        <v>22.937999999999999</v>
+        <v>23.125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="5">
+        <f t="shared" si="174"/>
+        <v>19.913663366336632</v>
+      </c>
+      <c r="C36" s="5">
+        <f t="shared" si="175"/>
+        <v>1.0324752475247525</v>
+      </c>
+      <c r="D36" s="4">
+        <f t="shared" si="176"/>
+        <v>25.25</v>
+      </c>
+      <c r="E36" s="9">
+        <v>204.9</v>
+      </c>
+      <c r="F36" s="13">
+        <v>12.43</v>
+      </c>
+      <c r="G36" s="9">
+        <v>11.67</v>
+      </c>
+      <c r="H36" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I36" s="10">
+        <v>15.06</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="K36" s="5">
+        <f t="shared" ref="K36" si="188">M$2/M36</f>
+        <v>38.981308411214947</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" ref="L36" si="189">M35/M36</f>
+        <v>1.205607476635514</v>
+      </c>
+      <c r="M36" s="4">
+        <f t="shared" ref="M36" si="190">SUM(O36:Q36)</f>
+        <v>1.07</v>
+      </c>
+      <c r="N36" s="9">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="O36" s="13">
+        <v>0.61</v>
+      </c>
+      <c r="P36" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="Q36" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R36" s="10">
+        <v>0.64</v>
+      </c>
+      <c r="S36" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="T36" s="5">
+        <f t="shared" ref="T36" si="191">ROUND(B36/K36,3)</f>
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="U36" s="5">
+        <f t="shared" ref="U36" si="192">ROUND(C36/L36,3)</f>
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="V36" s="4">
+        <f t="shared" ref="V36" si="193">ROUND(D36/M36,3)</f>
+        <v>23.597999999999999</v>
+      </c>
+      <c r="W36" s="9">
+        <f t="shared" ref="W36" si="194">ROUND(E36/N36,3)</f>
+        <v>21.454999999999998</v>
+      </c>
+      <c r="X36" s="13">
+        <f t="shared" ref="X36" si="195">ROUND(F36/O36,3)</f>
+        <v>20.376999999999999</v>
+      </c>
+      <c r="Y36" s="9">
+        <f t="shared" ref="Y36" si="196">ROUND(G36/P36,3)</f>
+        <v>27.14</v>
+      </c>
+      <c r="Z36" s="9">
+        <f t="shared" ref="Z36" si="197">ROUND(H36/Q36,3)</f>
+        <v>38.332999999999998</v>
+      </c>
+      <c r="AA36" s="10">
+        <f t="shared" ref="AA36" si="198">ROUND(I36/R36,3)</f>
+        <v>23.530999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67195B1B-B5DE-45D3-A727-CF348C589155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7F0FC3-3B2A-4281-B3EF-3C45D489741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="49">
   <si>
     <t>H23</t>
   </si>
@@ -188,6 +188,18 @@
   <si>
     <t>H56</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H57</t>
+  </si>
+  <si>
+    <t>H58</t>
+  </si>
+  <si>
+    <t>H59</t>
+  </si>
+  <si>
+    <t>H60</t>
   </si>
 </sst>
 </file>
@@ -709,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3652,15 +3664,15 @@
         <v>39</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" ref="K31:K34" si="138">M$2/M31</f>
+        <f t="shared" ref="K31:K39" si="138">M$2/M31</f>
         <v>25.746913580246911</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" ref="L31:L34" si="139">M30/M31</f>
+        <f t="shared" ref="L31:L39" si="139">M30/M31</f>
         <v>1.1234567901234569</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" ref="M31:M34" si="140">SUM(O31:Q31)</f>
+        <f t="shared" ref="M31:M39" si="140">SUM(O31:Q31)</f>
         <v>1.6199999999999999</v>
       </c>
       <c r="N31" s="9">
@@ -3914,95 +3926,95 @@
       </c>
       <c r="B34" s="2">
         <f t="shared" ref="B34" si="163">D$2/D34</f>
-        <v>13.726999726999727</v>
+        <v>13.667300896982876</v>
       </c>
       <c r="C34" s="2">
         <f t="shared" ref="C34" si="164">D33/D34</f>
-        <v>1.0070980070980071</v>
+        <v>1.0027181299266106</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" ref="D34" si="165">SUM(F34:H34)</f>
-        <v>36.629999999999995</v>
+        <v>36.789999999999992</v>
       </c>
       <c r="E34" s="18">
-        <v>207.16</v>
+        <v>203.58</v>
       </c>
       <c r="F34" s="9">
-        <v>23.86</v>
+        <v>24.02</v>
       </c>
       <c r="G34" s="13">
-        <v>11.62</v>
+        <v>11.61</v>
       </c>
       <c r="H34" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I34" s="14">
-        <v>14.55</v>
+        <v>14.81</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="K34" s="2">
         <f t="shared" si="138"/>
-        <v>34.188524590163929</v>
+        <v>31.36090225563909</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="139"/>
-        <v>1.1885245901639345</v>
+        <v>1.0902255639097744</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="140"/>
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="N34" s="18">
-        <v>9.59</v>
+        <v>9.52</v>
       </c>
       <c r="O34" s="9">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="P34" s="13">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="Q34" s="9">
         <v>0.03</v>
       </c>
       <c r="R34" s="14">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="S34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="T34" s="2">
         <f t="shared" ref="T34" si="166">ROUND(B34/K34,3)</f>
-        <v>0.40200000000000002</v>
+        <v>0.436</v>
       </c>
       <c r="U34" s="2">
         <f t="shared" ref="U34" si="167">ROUND(C34/L34,3)</f>
-        <v>0.84699999999999998</v>
+        <v>0.92</v>
       </c>
       <c r="V34" s="6">
         <f t="shared" ref="V34" si="168">ROUND(D34/M34,3)</f>
-        <v>30.024999999999999</v>
+        <v>27.661999999999999</v>
       </c>
       <c r="W34" s="18">
         <f t="shared" ref="W34" si="169">ROUND(E34/N34,3)</f>
-        <v>21.602</v>
+        <v>21.384</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" ref="X34" si="170">ROUND(F34/O34,3)</f>
-        <v>31.395</v>
+        <v>27.93</v>
       </c>
       <c r="Y34" s="13">
         <f t="shared" ref="Y34" si="171">ROUND(G34/P34,3)</f>
-        <v>27.023</v>
+        <v>26.385999999999999</v>
       </c>
       <c r="Z34" s="9">
         <f t="shared" ref="Z34" si="172">ROUND(H34/Q34,3)</f>
-        <v>38.332999999999998</v>
+        <v>38.667000000000002</v>
       </c>
       <c r="AA34" s="14">
         <f t="shared" ref="AA34" si="173">ROUND(I34/R34,3)</f>
-        <v>22.734000000000002</v>
+        <v>22.439</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4011,51 +4023,51 @@
       </c>
       <c r="B35" s="2">
         <f t="shared" ref="B35:B36" si="174">D$2/D35</f>
-        <v>19.287303413885688</v>
+        <v>19.20626432391138</v>
       </c>
       <c r="C35" s="2">
         <f t="shared" ref="C35:C36" si="175">D34/D35</f>
-        <v>1.4050632911392402</v>
+        <v>1.4052711993888463</v>
       </c>
       <c r="D35" s="6">
         <f t="shared" ref="D35:D36" si="176">SUM(F35:H35)</f>
-        <v>26.07</v>
+        <v>26.18</v>
       </c>
       <c r="E35" s="9">
-        <v>206.87</v>
+        <v>203.73</v>
       </c>
       <c r="F35" s="13">
-        <v>13.32</v>
+        <v>13.5</v>
       </c>
       <c r="G35" s="9">
-        <v>11.58</v>
+        <v>11.5</v>
       </c>
       <c r="H35" s="9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="I35" s="10">
-        <v>14.8</v>
+        <v>14.86</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>43</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" ref="K35" si="177">M$2/M35</f>
-        <v>32.333333333333329</v>
+        <f t="shared" si="138"/>
+        <v>34.758333333333333</v>
       </c>
       <c r="L35" s="2">
-        <f t="shared" ref="L35" si="178">M34/M35</f>
-        <v>0.94573643410852704</v>
+        <f t="shared" si="139"/>
+        <v>1.1083333333333334</v>
       </c>
       <c r="M35" s="6">
-        <f t="shared" ref="M35" si="179">SUM(O35:Q35)</f>
-        <v>1.29</v>
+        <f t="shared" si="140"/>
+        <v>1.2</v>
       </c>
       <c r="N35" s="9">
-        <v>9.44</v>
+        <v>9.52</v>
       </c>
       <c r="O35" s="13">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="P35" s="9">
         <v>0.43</v>
@@ -4070,89 +4082,89 @@
         <v>43</v>
       </c>
       <c r="T35" s="2">
-        <f t="shared" ref="T35" si="180">ROUND(B35/K35,3)</f>
-        <v>0.59699999999999998</v>
+        <f t="shared" ref="T35" si="177">ROUND(B35/K35,3)</f>
+        <v>0.55300000000000005</v>
       </c>
       <c r="U35" s="2">
-        <f t="shared" ref="U35" si="181">ROUND(C35/L35,3)</f>
-        <v>1.486</v>
+        <f t="shared" ref="U35" si="178">ROUND(C35/L35,3)</f>
+        <v>1.268</v>
       </c>
       <c r="V35" s="6">
-        <f t="shared" ref="V35" si="182">ROUND(D35/M35,3)</f>
-        <v>20.209</v>
+        <f t="shared" ref="V35" si="179">ROUND(D35/M35,3)</f>
+        <v>21.817</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" ref="W35" si="183">ROUND(E35/N35,3)</f>
-        <v>21.914000000000001</v>
+        <f t="shared" ref="W35" si="180">ROUND(E35/N35,3)</f>
+        <v>21.4</v>
       </c>
       <c r="X35" s="13">
-        <f t="shared" ref="X35" si="184">ROUND(F35/O35,3)</f>
-        <v>16.047999999999998</v>
+        <f t="shared" ref="X35" si="181">ROUND(F35/O35,3)</f>
+        <v>18.242999999999999</v>
       </c>
       <c r="Y35" s="9">
-        <f t="shared" ref="Y35" si="185">ROUND(G35/P35,3)</f>
-        <v>26.93</v>
+        <f t="shared" ref="Y35" si="182">ROUND(G35/P35,3)</f>
+        <v>26.744</v>
       </c>
       <c r="Z35" s="9">
-        <f t="shared" ref="Z35" si="186">ROUND(H35/Q35,3)</f>
-        <v>39</v>
+        <f t="shared" ref="Z35" si="183">ROUND(H35/Q35,3)</f>
+        <v>39.332999999999998</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" ref="AA35" si="187">ROUND(I35/R35,3)</f>
-        <v>23.125</v>
+        <f t="shared" ref="AA35" si="184">ROUND(I35/R35,3)</f>
+        <v>23.219000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="2">
         <f t="shared" si="174"/>
-        <v>19.913663366336632</v>
-      </c>
-      <c r="C36" s="5">
+        <v>20.064644852354345</v>
+      </c>
+      <c r="C36" s="2">
         <f t="shared" si="175"/>
-        <v>1.0324752475247525</v>
-      </c>
-      <c r="D36" s="4">
+        <v>1.0446927374301676</v>
+      </c>
+      <c r="D36" s="6">
         <f t="shared" si="176"/>
-        <v>25.25</v>
+        <v>25.060000000000002</v>
       </c>
       <c r="E36" s="9">
-        <v>204.9</v>
+        <v>207.64</v>
       </c>
       <c r="F36" s="13">
-        <v>12.43</v>
+        <v>12.22</v>
       </c>
       <c r="G36" s="9">
-        <v>11.67</v>
+        <v>11.66</v>
       </c>
       <c r="H36" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="I36" s="10">
-        <v>15.06</v>
+        <v>14.99</v>
       </c>
       <c r="J36" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="K36" s="5">
-        <f t="shared" ref="K36" si="188">M$2/M36</f>
-        <v>38.981308411214947</v>
-      </c>
-      <c r="L36" s="5">
-        <f t="shared" ref="L36" si="189">M35/M36</f>
-        <v>1.205607476635514</v>
-      </c>
-      <c r="M36" s="4">
-        <f t="shared" ref="M36" si="190">SUM(O36:Q36)</f>
-        <v>1.07</v>
+      <c r="K36" s="2">
+        <f t="shared" si="138"/>
+        <v>37.576576576576571</v>
+      </c>
+      <c r="L36" s="2">
+        <f t="shared" si="139"/>
+        <v>1.0810810810810809</v>
+      </c>
+      <c r="M36" s="6">
+        <f t="shared" si="140"/>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N36" s="9">
-        <v>9.5500000000000007</v>
+        <v>9.52</v>
       </c>
       <c r="O36" s="13">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="P36" s="9">
         <v>0.43</v>
@@ -4166,37 +4178,365 @@
       <c r="S36" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="T36" s="5">
-        <f t="shared" ref="T36" si="191">ROUND(B36/K36,3)</f>
-        <v>0.51100000000000001</v>
-      </c>
-      <c r="U36" s="5">
-        <f t="shared" ref="U36" si="192">ROUND(C36/L36,3)</f>
-        <v>0.85599999999999998</v>
-      </c>
-      <c r="V36" s="4">
-        <f t="shared" ref="V36" si="193">ROUND(D36/M36,3)</f>
-        <v>23.597999999999999</v>
+      <c r="T36" s="2">
+        <f t="shared" ref="T36:T37" si="185">ROUND(B36/K36,3)</f>
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="U36" s="2">
+        <f t="shared" ref="U36:U37" si="186">ROUND(C36/L36,3)</f>
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="V36" s="6">
+        <f t="shared" ref="V36:V37" si="187">ROUND(D36/M36,3)</f>
+        <v>22.577000000000002</v>
       </c>
       <c r="W36" s="9">
-        <f t="shared" ref="W36" si="194">ROUND(E36/N36,3)</f>
-        <v>21.454999999999998</v>
+        <f t="shared" ref="W36:W37" si="188">ROUND(E36/N36,3)</f>
+        <v>21.811</v>
       </c>
       <c r="X36" s="13">
-        <f t="shared" ref="X36" si="195">ROUND(F36/O36,3)</f>
-        <v>20.376999999999999</v>
+        <f t="shared" ref="X36:X37" si="189">ROUND(F36/O36,3)</f>
+        <v>18.8</v>
       </c>
       <c r="Y36" s="9">
-        <f t="shared" ref="Y36" si="196">ROUND(G36/P36,3)</f>
-        <v>27.14</v>
+        <f t="shared" ref="Y36:Y37" si="190">ROUND(G36/P36,3)</f>
+        <v>27.116</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" ref="Z36" si="197">ROUND(H36/Q36,3)</f>
-        <v>38.332999999999998</v>
+        <f t="shared" ref="Z36:Z37" si="191">ROUND(H36/Q36,3)</f>
+        <v>39.332999999999998</v>
       </c>
       <c r="AA36" s="10">
-        <f t="shared" ref="AA36" si="198">ROUND(I36/R36,3)</f>
-        <v>23.530999999999999</v>
+        <f t="shared" ref="AA36:AA37" si="192">ROUND(I36/R36,3)</f>
+        <v>23.422000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="5">
+        <f t="shared" ref="B37:B40" si="193">D$2/D37</f>
+        <v>20.250503423278293</v>
+      </c>
+      <c r="C37" s="5">
+        <f t="shared" ref="C37:C40" si="194">D36/D37</f>
+        <v>1.0092629883205801</v>
+      </c>
+      <c r="D37" s="4">
+        <f t="shared" ref="D37:D40" si="195">SUM(F37:H37)</f>
+        <v>24.83</v>
+      </c>
+      <c r="E37" s="18">
+        <v>204.03</v>
+      </c>
+      <c r="F37" s="18">
+        <v>12.23</v>
+      </c>
+      <c r="G37" s="13">
+        <v>11.43</v>
+      </c>
+      <c r="H37" s="18">
+        <v>1.17</v>
+      </c>
+      <c r="I37" s="14">
+        <v>13.37</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" s="5">
+        <f t="shared" si="138"/>
+        <v>38.266055045871553</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="139"/>
+        <v>1.0183486238532111</v>
+      </c>
+      <c r="M37" s="4">
+        <f t="shared" si="140"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N37" s="18">
+        <v>9.48</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0.63</v>
+      </c>
+      <c r="P37" s="13">
+        <v>0.43</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="R37" s="14">
+        <v>0.62</v>
+      </c>
+      <c r="S37" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="T37" s="5">
+        <f t="shared" si="185"/>
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="U37" s="5">
+        <f t="shared" si="186"/>
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="V37" s="4">
+        <f t="shared" si="187"/>
+        <v>22.78</v>
+      </c>
+      <c r="W37" s="18">
+        <f t="shared" si="188"/>
+        <v>21.521999999999998</v>
+      </c>
+      <c r="X37" s="18">
+        <f t="shared" si="189"/>
+        <v>19.413</v>
+      </c>
+      <c r="Y37" s="13">
+        <f t="shared" si="190"/>
+        <v>26.581</v>
+      </c>
+      <c r="Z37" s="18">
+        <f t="shared" si="191"/>
+        <v>39</v>
+      </c>
+      <c r="AA37" s="14">
+        <f t="shared" si="192"/>
+        <v>21.565000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="5" t="e">
+        <f t="shared" si="193"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C38" s="5" t="e">
+        <f t="shared" si="194"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D38" s="4">
+        <f t="shared" si="195"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K38" s="5" t="e">
+        <f t="shared" si="138"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L38" s="5" t="e">
+        <f t="shared" si="139"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M38" s="4">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="T38" s="5" t="e">
+        <f t="shared" ref="T38:T40" si="196">ROUND(B38/K38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U38" s="5" t="e">
+        <f t="shared" ref="U38:U40" si="197">ROUND(C38/L38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V38" s="4" t="e">
+        <f t="shared" ref="V38:V40" si="198">ROUND(D38/M38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W38" s="18" t="e">
+        <f t="shared" ref="W38:W40" si="199">ROUND(E38/N38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X38" s="18" t="e">
+        <f t="shared" ref="X38:X40" si="200">ROUND(F38/O38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y38" s="18" t="e">
+        <f t="shared" ref="Y38:Y40" si="201">ROUND(G38/P38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z38" s="18" t="e">
+        <f t="shared" ref="Z38:Z40" si="202">ROUND(H38/Q38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA38" s="19" t="e">
+        <f t="shared" ref="AA38:AA40" si="203">ROUND(I38/R38,3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="5" t="e">
+        <f t="shared" si="193"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C39" s="5" t="e">
+        <f t="shared" si="194"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D39" s="4">
+        <f t="shared" si="195"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" s="5" t="e">
+        <f t="shared" si="138"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L39" s="5" t="e">
+        <f t="shared" si="139"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M39" s="4">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="T39" s="5" t="e">
+        <f t="shared" si="196"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U39" s="5" t="e">
+        <f t="shared" si="197"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V39" s="4" t="e">
+        <f t="shared" si="198"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W39" s="18" t="e">
+        <f t="shared" si="199"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X39" s="18" t="e">
+        <f t="shared" si="200"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y39" s="18" t="e">
+        <f t="shared" si="201"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z39" s="18" t="e">
+        <f t="shared" si="202"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA39" s="19" t="e">
+        <f t="shared" si="203"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="5" t="e">
+        <f t="shared" si="193"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C40" s="5" t="e">
+        <f t="shared" si="194"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D40" s="4">
+        <f t="shared" si="195"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K40" s="5" t="e">
+        <f t="shared" ref="K40" si="204">M$2/M40</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L40" s="5" t="e">
+        <f t="shared" ref="L40" si="205">M39/M40</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M40" s="4">
+        <f t="shared" ref="M40" si="206">SUM(O40:Q40)</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="T40" s="5" t="e">
+        <f t="shared" si="196"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U40" s="5" t="e">
+        <f t="shared" si="197"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V40" s="4" t="e">
+        <f t="shared" si="198"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W40" s="18" t="e">
+        <f t="shared" si="199"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X40" s="18" t="e">
+        <f t="shared" si="200"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y40" s="18" t="e">
+        <f t="shared" si="201"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z40" s="18" t="e">
+        <f t="shared" si="202"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA40" s="19" t="e">
+        <f t="shared" si="203"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7F0FC3-3B2A-4281-B3EF-3C45D489741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289E4BE9-4B19-4173-B253-A3CDC9609417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -3926,95 +3926,95 @@
       </c>
       <c r="B34" s="2">
         <f t="shared" ref="B34" si="163">D$2/D34</f>
-        <v>13.667300896982876</v>
+        <v>13.600757370841221</v>
       </c>
       <c r="C34" s="2">
         <f t="shared" ref="C34" si="164">D33/D34</f>
-        <v>1.0027181299266106</v>
+        <v>0.99783608331079243</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" ref="D34" si="165">SUM(F34:H34)</f>
-        <v>36.789999999999992</v>
+        <v>36.97</v>
       </c>
       <c r="E34" s="18">
-        <v>203.58</v>
+        <v>203.2</v>
       </c>
       <c r="F34" s="9">
-        <v>24.02</v>
+        <v>24.08</v>
       </c>
       <c r="G34" s="13">
-        <v>11.61</v>
+        <v>11.72</v>
       </c>
       <c r="H34" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="I34" s="14">
-        <v>14.81</v>
+        <v>14.62</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="K34" s="2">
         <f t="shared" si="138"/>
-        <v>31.36090225563909</v>
+        <v>32.842519685039363</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="139"/>
-        <v>1.0902255639097744</v>
+        <v>1.1417322834645669</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="140"/>
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="N34" s="18">
-        <v>9.52</v>
+        <v>9.5</v>
       </c>
       <c r="O34" s="9">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="P34" s="13">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="Q34" s="9">
         <v>0.03</v>
       </c>
       <c r="R34" s="14">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="S34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="T34" s="2">
         <f t="shared" ref="T34" si="166">ROUND(B34/K34,3)</f>
-        <v>0.436</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="U34" s="2">
         <f t="shared" ref="U34" si="167">ROUND(C34/L34,3)</f>
-        <v>0.92</v>
+        <v>0.874</v>
       </c>
       <c r="V34" s="6">
         <f t="shared" ref="V34" si="168">ROUND(D34/M34,3)</f>
-        <v>27.661999999999999</v>
+        <v>29.11</v>
       </c>
       <c r="W34" s="18">
         <f t="shared" ref="W34" si="169">ROUND(E34/N34,3)</f>
-        <v>21.384</v>
+        <v>21.388999999999999</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" ref="X34" si="170">ROUND(F34/O34,3)</f>
-        <v>27.93</v>
+        <v>29.728000000000002</v>
       </c>
       <c r="Y34" s="13">
         <f t="shared" ref="Y34" si="171">ROUND(G34/P34,3)</f>
-        <v>26.385999999999999</v>
+        <v>27.256</v>
       </c>
       <c r="Z34" s="9">
         <f t="shared" ref="Z34" si="172">ROUND(H34/Q34,3)</f>
-        <v>38.667000000000002</v>
+        <v>39</v>
       </c>
       <c r="AA34" s="14">
         <f t="shared" ref="AA34" si="173">ROUND(I34/R34,3)</f>
-        <v>22.439</v>
+        <v>23.206</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4023,51 +4023,51 @@
       </c>
       <c r="B35" s="2">
         <f t="shared" ref="B35:B36" si="174">D$2/D35</f>
-        <v>19.20626432391138</v>
+        <v>19.294704528012275</v>
       </c>
       <c r="C35" s="2">
         <f t="shared" ref="C35:C36" si="175">D34/D35</f>
-        <v>1.4052711993888463</v>
+        <v>1.418649270913277</v>
       </c>
       <c r="D35" s="6">
         <f t="shared" ref="D35:D36" si="176">SUM(F35:H35)</f>
-        <v>26.18</v>
+        <v>26.060000000000002</v>
       </c>
       <c r="E35" s="9">
-        <v>203.73</v>
+        <v>207.16</v>
       </c>
       <c r="F35" s="13">
-        <v>13.5</v>
+        <v>13.35</v>
       </c>
       <c r="G35" s="9">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="H35" s="9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I35" s="10">
-        <v>14.86</v>
+        <v>14.89</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>43</v>
       </c>
       <c r="K35" s="2">
         <f t="shared" si="138"/>
-        <v>34.758333333333333</v>
+        <v>33.910569105691053</v>
       </c>
       <c r="L35" s="2">
         <f t="shared" si="139"/>
-        <v>1.1083333333333334</v>
+        <v>1.032520325203252</v>
       </c>
       <c r="M35" s="6">
         <f t="shared" si="140"/>
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="N35" s="9">
-        <v>9.52</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="O35" s="13">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="P35" s="9">
         <v>0.43</v>
@@ -4076,42 +4076,42 @@
         <v>0.03</v>
       </c>
       <c r="R35" s="10">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>43</v>
       </c>
       <c r="T35" s="2">
         <f t="shared" ref="T35" si="177">ROUND(B35/K35,3)</f>
-        <v>0.55300000000000005</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="U35" s="2">
         <f t="shared" ref="U35" si="178">ROUND(C35/L35,3)</f>
-        <v>1.268</v>
+        <v>1.3740000000000001</v>
       </c>
       <c r="V35" s="6">
         <f t="shared" ref="V35" si="179">ROUND(D35/M35,3)</f>
-        <v>21.817</v>
+        <v>21.187000000000001</v>
       </c>
       <c r="W35" s="9">
         <f t="shared" ref="W35" si="180">ROUND(E35/N35,3)</f>
-        <v>21.4</v>
+        <v>22.085000000000001</v>
       </c>
       <c r="X35" s="13">
         <f t="shared" ref="X35" si="181">ROUND(F35/O35,3)</f>
-        <v>18.242999999999999</v>
+        <v>17.338000000000001</v>
       </c>
       <c r="Y35" s="9">
         <f t="shared" ref="Y35" si="182">ROUND(G35/P35,3)</f>
-        <v>26.744</v>
+        <v>26.837</v>
       </c>
       <c r="Z35" s="9">
         <f t="shared" ref="Z35" si="183">ROUND(H35/Q35,3)</f>
-        <v>39.332999999999998</v>
+        <v>39</v>
       </c>
       <c r="AA35" s="10">
         <f t="shared" ref="AA35" si="184">ROUND(I35/R35,3)</f>
-        <v>23.219000000000001</v>
+        <v>23.635000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4120,51 +4120,51 @@
       </c>
       <c r="B36" s="2">
         <f t="shared" si="174"/>
-        <v>20.064644852354345</v>
+        <v>20.08067092651757</v>
       </c>
       <c r="C36" s="2">
         <f t="shared" si="175"/>
-        <v>1.0446927374301676</v>
+        <v>1.0407348242811503</v>
       </c>
       <c r="D36" s="6">
         <f t="shared" si="176"/>
-        <v>25.060000000000002</v>
+        <v>25.04</v>
       </c>
       <c r="E36" s="9">
-        <v>207.64</v>
+        <v>203.79</v>
       </c>
       <c r="F36" s="13">
-        <v>12.22</v>
+        <v>12.19</v>
       </c>
       <c r="G36" s="9">
-        <v>11.66</v>
+        <v>11.69</v>
       </c>
       <c r="H36" s="9">
-        <v>1.18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I36" s="10">
-        <v>14.99</v>
+        <v>14.62</v>
       </c>
       <c r="J36" s="20" t="s">
         <v>44</v>
       </c>
       <c r="K36" s="2">
         <f t="shared" si="138"/>
-        <v>37.576576576576571</v>
+        <v>38.981308411214947</v>
       </c>
       <c r="L36" s="2">
         <f t="shared" si="139"/>
-        <v>1.0810810810810809</v>
+        <v>1.1495327102803738</v>
       </c>
       <c r="M36" s="6">
         <f t="shared" si="140"/>
-        <v>1.1100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="N36" s="9">
-        <v>9.52</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="O36" s="13">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="P36" s="9">
         <v>0.43</v>
@@ -4173,42 +4173,42 @@
         <v>0.03</v>
       </c>
       <c r="R36" s="10">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="S36" s="20" t="s">
         <v>44</v>
       </c>
       <c r="T36" s="2">
         <f t="shared" ref="T36:T37" si="185">ROUND(B36/K36,3)</f>
-        <v>0.53400000000000003</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="U36" s="2">
         <f t="shared" ref="U36:U37" si="186">ROUND(C36/L36,3)</f>
-        <v>0.96599999999999997</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="V36" s="6">
         <f t="shared" ref="V36:V37" si="187">ROUND(D36/M36,3)</f>
-        <v>22.577000000000002</v>
+        <v>23.402000000000001</v>
       </c>
       <c r="W36" s="9">
         <f t="shared" ref="W36:W37" si="188">ROUND(E36/N36,3)</f>
-        <v>21.811</v>
+        <v>21.52</v>
       </c>
       <c r="X36" s="13">
         <f t="shared" ref="X36:X37" si="189">ROUND(F36/O36,3)</f>
-        <v>18.8</v>
+        <v>19.984000000000002</v>
       </c>
       <c r="Y36" s="9">
         <f t="shared" ref="Y36:Y37" si="190">ROUND(G36/P36,3)</f>
-        <v>27.116</v>
+        <v>27.186</v>
       </c>
       <c r="Z36" s="9">
         <f t="shared" ref="Z36:Z37" si="191">ROUND(H36/Q36,3)</f>
-        <v>39.332999999999998</v>
+        <v>38.667000000000002</v>
       </c>
       <c r="AA36" s="10">
         <f t="shared" ref="AA36:AA37" si="192">ROUND(I36/R36,3)</f>
-        <v>23.422000000000001</v>
+        <v>23.206</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4217,54 +4217,54 @@
       </c>
       <c r="B37" s="5">
         <f t="shared" ref="B37:B40" si="193">D$2/D37</f>
-        <v>20.250503423278293</v>
+        <v>20.291364003228409</v>
       </c>
       <c r="C37" s="5">
         <f t="shared" ref="C37:C40" si="194">D36/D37</f>
-        <v>1.0092629883205801</v>
+        <v>1.0104923325262309</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" ref="D37:D40" si="195">SUM(F37:H37)</f>
-        <v>24.83</v>
+        <v>24.779999999999998</v>
       </c>
       <c r="E37" s="18">
-        <v>204.03</v>
+        <v>203.12</v>
       </c>
       <c r="F37" s="18">
-        <v>12.23</v>
+        <v>12.26</v>
       </c>
       <c r="G37" s="13">
-        <v>11.43</v>
+        <v>11.36</v>
       </c>
       <c r="H37" s="18">
-        <v>1.17</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I37" s="14">
-        <v>13.37</v>
+        <v>13.09</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>45</v>
       </c>
       <c r="K37" s="5">
         <f t="shared" si="138"/>
-        <v>38.266055045871553</v>
+        <v>40.105769230769226</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="139"/>
-        <v>1.0183486238532111</v>
+        <v>1.028846153846154</v>
       </c>
       <c r="M37" s="4">
         <f t="shared" si="140"/>
-        <v>1.0900000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="N37" s="18">
-        <v>9.48</v>
+        <v>9.4</v>
       </c>
       <c r="O37" s="18">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="P37" s="13">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="Q37" s="18">
         <v>0.03</v>
@@ -4277,112 +4277,132 @@
       </c>
       <c r="T37" s="5">
         <f t="shared" si="185"/>
-        <v>0.52900000000000003</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="U37" s="5">
         <f t="shared" si="186"/>
-        <v>0.99099999999999999</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="187"/>
-        <v>22.78</v>
+        <v>23.827000000000002</v>
       </c>
       <c r="W37" s="18">
         <f t="shared" si="188"/>
-        <v>21.521999999999998</v>
+        <v>21.609000000000002</v>
       </c>
       <c r="X37" s="18">
         <f t="shared" si="189"/>
-        <v>19.413</v>
+        <v>20.78</v>
       </c>
       <c r="Y37" s="13">
         <f t="shared" si="190"/>
-        <v>26.581</v>
+        <v>27.047999999999998</v>
       </c>
       <c r="Z37" s="18">
         <f t="shared" si="191"/>
-        <v>39</v>
+        <v>38.667000000000002</v>
       </c>
       <c r="AA37" s="14">
         <f t="shared" si="192"/>
-        <v>21.565000000000001</v>
+        <v>21.113</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="5" t="e">
+      <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C38" s="5" t="e">
+        <v>19.913663366336632</v>
+      </c>
+      <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>#DIV/0!</v>
+        <v>0.98138613861386126</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>0</v>
-      </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="19"/>
+        <v>25.25</v>
+      </c>
+      <c r="E38" s="13">
+        <v>153.47999999999999</v>
+      </c>
+      <c r="F38" s="18">
+        <v>12.48</v>
+      </c>
+      <c r="G38" s="18">
+        <v>11.6</v>
+      </c>
+      <c r="H38" s="18">
+        <v>1.17</v>
+      </c>
+      <c r="I38" s="19">
+        <v>13.38</v>
+      </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="5" t="e">
+      <c r="K38" s="5">
         <f t="shared" si="138"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L38" s="5" t="e">
+        <v>37.918181818181807</v>
+      </c>
+      <c r="L38" s="5">
         <f t="shared" si="139"/>
-        <v>#DIV/0!</v>
+        <v>0.94545454545454544</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="140"/>
-        <v>0</v>
-      </c>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="19"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N38" s="13">
+        <v>8.02</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0.42</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="R38" s="19">
+        <v>0.62</v>
+      </c>
       <c r="S38" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="T38" s="5" t="e">
+      <c r="T38" s="5">
         <f t="shared" ref="T38:T40" si="196">ROUND(B38/K38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U38" s="5" t="e">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="U38" s="5">
         <f t="shared" ref="U38:U40" si="197">ROUND(C38/L38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V38" s="4" t="e">
+        <v>1.038</v>
+      </c>
+      <c r="V38" s="4">
         <f t="shared" ref="V38:V40" si="198">ROUND(D38/M38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W38" s="18" t="e">
+        <v>22.954999999999998</v>
+      </c>
+      <c r="W38" s="18">
         <f t="shared" ref="W38:W40" si="199">ROUND(E38/N38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X38" s="18" t="e">
+        <v>19.137</v>
+      </c>
+      <c r="X38" s="18">
         <f t="shared" ref="X38:X40" si="200">ROUND(F38/O38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y38" s="18" t="e">
+        <v>19.2</v>
+      </c>
+      <c r="Y38" s="18">
         <f t="shared" ref="Y38:Y40" si="201">ROUND(G38/P38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z38" s="18" t="e">
+        <v>27.619</v>
+      </c>
+      <c r="Z38" s="18">
         <f t="shared" ref="Z38:Z40" si="202">ROUND(H38/Q38,3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA38" s="19" t="e">
+        <v>39</v>
+      </c>
+      <c r="AA38" s="19">
         <f t="shared" ref="AA38:AA40" si="203">ROUND(I38/R38,3)</f>
-        <v>#DIV/0!</v>
+        <v>21.581</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289E4BE9-4B19-4173-B253-A3CDC9609417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE2E92-143B-4049-8203-94D43AA9C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="47">
   <si>
     <t>H23</t>
   </si>
@@ -194,12 +194,6 @@
   </si>
   <si>
     <t>H58</t>
-  </si>
-  <si>
-    <t>H59</t>
-  </si>
-  <si>
-    <t>H60</t>
   </si>
 </sst>
 </file>
@@ -721,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AB38"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2762,95 +2756,95 @@
       </c>
       <c r="B22" s="2">
         <f t="shared" ref="B22" si="24">D$2/D22</f>
-        <v>7.137260468417316</v>
+        <v>7.111016829302784</v>
       </c>
       <c r="C22" s="2">
         <f t="shared" ref="C22" si="25">D21/D22</f>
-        <v>1.2681334279630945</v>
+        <v>1.2634705133644462</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" ref="D22" si="26">SUM(F22:H22)</f>
-        <v>70.45</v>
+        <v>70.710000000000008</v>
       </c>
       <c r="E22" s="9">
-        <v>296.97000000000003</v>
+        <v>294.77</v>
       </c>
       <c r="F22" s="9">
-        <v>30.4</v>
+        <v>30.51</v>
       </c>
       <c r="G22" s="13">
-        <v>38.47</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="H22" s="9">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="I22" s="14">
-        <v>27.24</v>
+        <v>27.42</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="2">
         <f t="shared" ref="K22:K24" si="27">M$2/M22</f>
-        <v>12.677811550151974</v>
+        <v>12.913312693498451</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" ref="L22:L24" si="28">M21/M22</f>
-        <v>1.1519756838905775</v>
+        <v>1.173374613003096</v>
       </c>
       <c r="M22" s="6">
         <f t="shared" ref="M22:M24" si="29">SUM(O22:Q22)</f>
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="N22" s="9">
-        <v>14.05</v>
+        <v>13.94</v>
       </c>
       <c r="O22" s="9">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P22" s="13">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="R22" s="14">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S22" s="17" t="s">
         <v>30</v>
       </c>
       <c r="T22" s="2">
         <f t="shared" ref="T22" si="30">ROUND(B22/K22,3)</f>
-        <v>0.56299999999999994</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="U22" s="2">
         <f t="shared" ref="U22" si="31">ROUND(C22/L22,3)</f>
-        <v>1.101</v>
+        <v>1.077</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" ref="V22" si="32">ROUND(D22/M22,3)</f>
-        <v>21.413</v>
+        <v>21.891999999999999</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" ref="W22" si="33">ROUND(E22/N22,3)</f>
-        <v>21.137</v>
+        <v>21.146000000000001</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" ref="X22" si="34">ROUND(F22/O22,3)</f>
-        <v>24.715</v>
+        <v>25.425000000000001</v>
       </c>
       <c r="Y22" s="13">
         <f t="shared" ref="Y22" si="35">ROUND(G22/P22,3)</f>
-        <v>21.611999999999998</v>
+        <v>21.966000000000001</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" ref="Z22" si="36">ROUND(H22/Q22,3)</f>
-        <v>5.6429999999999998</v>
+        <v>5.7039999999999997</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" ref="AA22" si="37">ROUND(I22/R22,3)</f>
-        <v>19.597000000000001</v>
+        <v>20.463000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2859,30 +2853,30 @@
       </c>
       <c r="B23" s="5">
         <f t="shared" ref="B23" si="38">D$2/D23</f>
-        <v>6.9392768423958042</v>
+        <v>6.9392768423958033</v>
       </c>
       <c r="C23" s="5">
         <f t="shared" ref="C23" si="39">D22/D23</f>
-        <v>0.97226055754899265</v>
+        <v>0.97584874413469502</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" ref="D23" si="40">SUM(F23:H23)</f>
-        <v>72.459999999999994</v>
+        <v>72.460000000000008</v>
       </c>
       <c r="E23" s="13">
-        <v>244.74</v>
+        <v>245.07</v>
       </c>
       <c r="F23" s="9">
-        <v>30.53</v>
+        <v>31.89</v>
       </c>
       <c r="G23" s="9">
-        <v>40.36</v>
+        <v>39.07</v>
       </c>
       <c r="H23" s="9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="I23" s="10">
-        <v>28.45</v>
+        <v>27.8</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>31</v>
@@ -2893,20 +2887,20 @@
       </c>
       <c r="L23" s="5">
         <f t="shared" si="28"/>
-        <v>1.0444444444444443</v>
+        <v>1.0253968253968253</v>
       </c>
       <c r="M23" s="6">
         <f t="shared" si="29"/>
         <v>3.1500000000000004</v>
       </c>
       <c r="N23" s="13">
-        <v>12.88</v>
+        <v>11.42</v>
       </c>
       <c r="O23" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P23" s="9">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" s="9">
         <v>0.28000000000000003</v>
@@ -2923,7 +2917,7 @@
       </c>
       <c r="U23" s="5">
         <f t="shared" ref="U23" si="42">ROUND(C23/L23,3)</f>
-        <v>0.93100000000000005</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="V23" s="6">
         <f t="shared" ref="V23" si="43">ROUND(D23/M23,3)</f>
@@ -2931,23 +2925,23 @@
       </c>
       <c r="W23" s="13">
         <f t="shared" ref="W23" si="44">ROUND(E23/N23,3)</f>
-        <v>19.001999999999999</v>
+        <v>21.46</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" ref="X23" si="45">ROUND(F23/O23,3)</f>
-        <v>26.547999999999998</v>
+        <v>27.974</v>
       </c>
       <c r="Y23" s="9">
         <f t="shared" ref="Y23" si="46">ROUND(G23/P23,3)</f>
-        <v>23.465</v>
+        <v>22.584</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" ref="Z23" si="47">ROUND(H23/Q23,3)</f>
-        <v>5.6070000000000002</v>
+        <v>5.3570000000000002</v>
       </c>
       <c r="AA23" s="10">
         <f t="shared" ref="AA23" si="48">ROUND(I23/R23,3)</f>
-        <v>21.718</v>
+        <v>21.221</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2956,95 +2950,95 @@
       </c>
       <c r="B24" s="2">
         <f t="shared" ref="B24" si="49">D$2/D24</f>
-        <v>8.0878237091844927</v>
+        <v>7.9800031740993482</v>
       </c>
       <c r="C24" s="2">
         <f t="shared" ref="C24" si="50">D23/D24</f>
-        <v>1.165513913463085</v>
+        <v>1.1499761942548803</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" ref="D24" si="51">SUM(F24:H24)</f>
-        <v>62.17</v>
+        <v>63.01</v>
       </c>
       <c r="E24" s="9">
-        <v>250.47</v>
+        <v>263.2</v>
       </c>
       <c r="F24" s="9">
-        <v>30.59</v>
+        <v>32.31</v>
       </c>
       <c r="G24" s="13">
-        <v>30.11</v>
+        <v>29.29</v>
       </c>
       <c r="H24" s="9">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="I24" s="14">
-        <v>21.64</v>
+        <v>21</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="K24" s="2">
         <f t="shared" si="27"/>
-        <v>14.738515901060069</v>
+        <v>14.949820788530463</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="28"/>
-        <v>1.1130742049469966</v>
+        <v>1.1290322580645162</v>
       </c>
       <c r="M24" s="6">
         <f t="shared" si="29"/>
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="N24" s="9">
-        <v>11.47</v>
+        <v>11.46</v>
       </c>
       <c r="O24" s="9">
-        <v>1.1499999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P24" s="13">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q24" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R24" s="14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="S24" s="17" t="s">
         <v>32</v>
       </c>
       <c r="T24" s="2">
         <f t="shared" ref="T24" si="52">ROUND(B24/K24,3)</f>
-        <v>0.54900000000000004</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="U24" s="2">
         <f t="shared" ref="U24" si="53">ROUND(C24/L24,3)</f>
-        <v>1.0469999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="V24" s="6">
         <f t="shared" ref="V24" si="54">ROUND(D24/M24,3)</f>
-        <v>21.968</v>
+        <v>22.584</v>
       </c>
       <c r="W24" s="9">
         <f t="shared" ref="W24" si="55">ROUND(E24/N24,3)</f>
-        <v>21.837</v>
+        <v>22.966999999999999</v>
       </c>
       <c r="X24" s="9">
         <f t="shared" ref="X24" si="56">ROUND(F24/O24,3)</f>
-        <v>26.6</v>
+        <v>28.593</v>
       </c>
       <c r="Y24" s="13">
         <f t="shared" ref="Y24" si="57">ROUND(G24/P24,3)</f>
-        <v>21.507000000000001</v>
+        <v>21.225000000000001</v>
       </c>
       <c r="Z24" s="9">
         <f t="shared" ref="Z24" si="58">ROUND(H24/Q24,3)</f>
-        <v>5.25</v>
+        <v>5.0359999999999996</v>
       </c>
       <c r="AA24" s="14">
         <f t="shared" ref="AA24" si="59">ROUND(I24/R24,3)</f>
-        <v>20.808</v>
+        <v>20.792000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3053,95 +3047,95 @@
       </c>
       <c r="B25" s="2">
         <f t="shared" ref="B25" si="60">D$2/D25</f>
-        <v>8.263270336894001</v>
+        <v>8.3636061210911503</v>
       </c>
       <c r="C25" s="2">
         <f t="shared" ref="C25" si="61">D24/D25</f>
-        <v>1.0216926869350864</v>
+        <v>1.0480705256154359</v>
       </c>
       <c r="D25" s="6">
         <f t="shared" ref="D25" si="62">SUM(F25:H25)</f>
-        <v>60.849999999999994</v>
+        <v>60.12</v>
       </c>
       <c r="E25" s="9">
         <v>244.44</v>
       </c>
       <c r="F25" s="9">
-        <v>31.2</v>
+        <v>31.77</v>
       </c>
       <c r="G25" s="13">
-        <v>28.18</v>
+        <v>26.74</v>
       </c>
       <c r="H25" s="9">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="I25" s="14">
-        <v>19.309999999999999</v>
+        <v>18.14</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="2">
         <f t="shared" ref="K25:K27" si="63">M$2/M25</f>
-        <v>15.85931558935361</v>
+        <v>15.919847328244272</v>
       </c>
       <c r="L25" s="2">
         <f t="shared" ref="L25:L27" si="64">M24/M25</f>
-        <v>1.0760456273764258</v>
+        <v>1.0648854961832062</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" ref="M25:M27" si="65">SUM(O25:Q25)</f>
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="N25" s="9">
-        <v>11.87</v>
+        <v>11.44</v>
       </c>
       <c r="O25" s="9">
         <v>1.1100000000000001</v>
       </c>
       <c r="P25" s="13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q25" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="R25" s="14">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="S25" s="17" t="s">
         <v>33</v>
       </c>
       <c r="T25" s="2">
         <f t="shared" ref="T25" si="66">ROUND(B25/K25,3)</f>
-        <v>0.52100000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" ref="U25" si="67">ROUND(C25/L25,3)</f>
-        <v>0.94899999999999995</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="V25" s="6">
         <f t="shared" ref="V25" si="68">ROUND(D25/M25,3)</f>
-        <v>23.137</v>
+        <v>22.946999999999999</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" ref="W25" si="69">ROUND(E25/N25,3)</f>
-        <v>20.593</v>
+        <v>21.367000000000001</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" ref="X25" si="70">ROUND(F25/O25,3)</f>
-        <v>28.108000000000001</v>
+        <v>28.622</v>
       </c>
       <c r="Y25" s="13">
         <f t="shared" ref="Y25" si="71">ROUND(G25/P25,3)</f>
-        <v>22.725999999999999</v>
+        <v>21.74</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" ref="Z25" si="72">ROUND(H25/Q25,3)</f>
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA25" s="14">
         <f t="shared" ref="AA25" si="73">ROUND(I25/R25,3)</f>
-        <v>21.696999999999999</v>
+        <v>20.155999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3150,57 +3144,57 @@
       </c>
       <c r="B26" s="2">
         <f t="shared" ref="B26" si="74">D$2/D26</f>
-        <v>9.1923217550274217</v>
+        <v>9.3132061492869038</v>
       </c>
       <c r="C26" s="2">
         <f t="shared" ref="C26" si="75">D25/D26</f>
-        <v>1.1124314442413163</v>
+        <v>1.1135395443600666</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" ref="D26" si="76">SUM(F26:H26)</f>
-        <v>54.699999999999996</v>
+        <v>53.99</v>
       </c>
       <c r="E26" s="9">
-        <v>249.17</v>
+        <v>243.14</v>
       </c>
       <c r="F26" s="9">
-        <v>31.37</v>
+        <v>31.66</v>
       </c>
       <c r="G26" s="13">
-        <v>21.93</v>
+        <v>20.87</v>
       </c>
       <c r="H26" s="9">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="I26" s="14">
-        <v>18.010000000000002</v>
+        <v>16.89</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>34</v>
       </c>
       <c r="K26" s="2">
         <f t="shared" si="63"/>
-        <v>17.024489795918363</v>
+        <v>17.379166666666666</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="64"/>
-        <v>1.0734693877551018</v>
+        <v>1.0916666666666668</v>
       </c>
       <c r="M26" s="6">
         <f t="shared" si="65"/>
-        <v>2.4500000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="N26" s="9">
-        <v>11.51</v>
+        <v>11.49</v>
       </c>
       <c r="O26" s="9">
-        <v>1.1299999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P26" s="13">
         <v>1.04</v>
       </c>
       <c r="Q26" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="R26" s="14">
         <v>0.87</v>
@@ -3210,35 +3204,35 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" ref="T26" si="77">ROUND(B26/K26,3)</f>
-        <v>0.54</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" ref="U26" si="78">ROUND(C26/L26,3)</f>
-        <v>1.036</v>
+        <v>1.02</v>
       </c>
       <c r="V26" s="6">
         <f t="shared" ref="V26" si="79">ROUND(D26/M26,3)</f>
-        <v>22.327000000000002</v>
+        <v>22.495999999999999</v>
       </c>
       <c r="W26" s="9">
         <f t="shared" ref="W26" si="80">ROUND(E26/N26,3)</f>
-        <v>21.648</v>
+        <v>21.161000000000001</v>
       </c>
       <c r="X26" s="9">
         <f t="shared" ref="X26" si="81">ROUND(F26/O26,3)</f>
-        <v>27.760999999999999</v>
+        <v>29.045999999999999</v>
       </c>
       <c r="Y26" s="13">
         <f t="shared" ref="Y26" si="82">ROUND(G26/P26,3)</f>
-        <v>21.087</v>
+        <v>20.067</v>
       </c>
       <c r="Z26" s="9">
         <f t="shared" ref="Z26" si="83">ROUND(H26/Q26,3)</f>
-        <v>5</v>
+        <v>5.407</v>
       </c>
       <c r="AA26" s="14">
         <f t="shared" ref="AA26" si="84">ROUND(I26/R26,3)</f>
-        <v>20.701000000000001</v>
+        <v>19.414000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3247,48 +3241,48 @@
       </c>
       <c r="B27" s="2">
         <f t="shared" ref="B27" si="85">D$2/D27</f>
-        <v>10.453638253638253</v>
+        <v>10.481967896602042</v>
       </c>
       <c r="C27" s="2">
         <f t="shared" ref="C27" si="86">D26/D27</f>
-        <v>1.1372141372141373</v>
+        <v>1.1254951011048573</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" ref="D27" si="87">SUM(F27:H27)</f>
-        <v>48.099999999999994</v>
+        <v>47.97</v>
       </c>
       <c r="E27" s="9">
-        <v>244.7</v>
+        <v>244.45</v>
       </c>
       <c r="F27" s="13">
-        <v>25.5</v>
+        <v>25.66</v>
       </c>
       <c r="G27" s="9">
-        <v>21.16</v>
+        <v>20.75</v>
       </c>
       <c r="H27" s="9">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="I27" s="10">
-        <v>17.38</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K27" s="2">
         <f t="shared" si="63"/>
-        <v>17.978448275862064</v>
+        <v>18.134782608695648</v>
       </c>
       <c r="L27" s="2">
         <f t="shared" si="64"/>
-        <v>1.0560344827586206</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="M27" s="6">
         <f t="shared" si="65"/>
-        <v>2.3200000000000003</v>
+        <v>2.3000000000000003</v>
       </c>
       <c r="N27" s="9">
-        <v>11.65</v>
+        <v>11.49</v>
       </c>
       <c r="O27" s="13">
         <v>0.98</v>
@@ -3297,45 +3291,45 @@
         <v>1.05</v>
       </c>
       <c r="Q27" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.27</v>
       </c>
       <c r="R27" s="10">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="S27" s="17" t="s">
         <v>35</v>
       </c>
       <c r="T27" s="2">
         <f t="shared" ref="T27" si="88">ROUND(B27/K27,3)</f>
-        <v>0.58099999999999996</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="U27" s="2">
         <f t="shared" ref="U27" si="89">ROUND(C27/L27,3)</f>
-        <v>1.077</v>
+        <v>1.079</v>
       </c>
       <c r="V27" s="6">
         <f t="shared" ref="V27" si="90">ROUND(D27/M27,3)</f>
-        <v>20.733000000000001</v>
+        <v>20.856999999999999</v>
       </c>
       <c r="W27" s="9">
         <f t="shared" ref="W27" si="91">ROUND(E27/N27,3)</f>
-        <v>21.004000000000001</v>
+        <v>21.274999999999999</v>
       </c>
       <c r="X27" s="13">
         <f t="shared" ref="X27" si="92">ROUND(F27/O27,3)</f>
-        <v>26.02</v>
+        <v>26.184000000000001</v>
       </c>
       <c r="Y27" s="9">
         <f t="shared" ref="Y27" si="93">ROUND(G27/P27,3)</f>
-        <v>20.152000000000001</v>
+        <v>19.762</v>
       </c>
       <c r="Z27" s="9">
         <f t="shared" ref="Z27" si="94">ROUND(H27/Q27,3)</f>
-        <v>4.9660000000000002</v>
+        <v>5.7779999999999996</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" ref="AA27" si="95">ROUND(I27/R27,3)</f>
-        <v>19.75</v>
+        <v>19.321999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3344,30 +3338,30 @@
       </c>
       <c r="B28" s="2">
         <f t="shared" ref="B28" si="96">D$2/D28</f>
-        <v>11.085097001763668</v>
+        <v>10.947528848247332</v>
       </c>
       <c r="C28" s="2">
         <f t="shared" ref="C28" si="97">D27/D28</f>
-        <v>1.0604056437389771</v>
+        <v>1.0444154147615936</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" ref="D28" si="98">SUM(F28:H28)</f>
-        <v>45.36</v>
+        <v>45.93</v>
       </c>
       <c r="E28" s="9">
-        <v>244.24</v>
+        <v>245.89</v>
       </c>
       <c r="F28" s="9">
-        <v>24.96</v>
+        <v>25.38</v>
       </c>
       <c r="G28" s="13">
-        <v>19.010000000000002</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="H28" s="9">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="I28" s="14">
-        <v>14.95</v>
+        <v>14.59</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>36</v>
@@ -3378,61 +3372,61 @@
       </c>
       <c r="L28" s="2">
         <f t="shared" ref="L28" si="100">M27/M28</f>
-        <v>1.0841121495327104</v>
+        <v>1.0747663551401869</v>
       </c>
       <c r="M28" s="6">
         <f t="shared" ref="M28" si="101">SUM(O28:Q28)</f>
         <v>2.14</v>
       </c>
       <c r="N28" s="9">
-        <v>11.59</v>
+        <v>11.39</v>
       </c>
       <c r="O28" s="9">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="P28" s="13">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="Q28" s="9">
         <v>0.27</v>
       </c>
       <c r="R28" s="14">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="S28" s="17" t="s">
         <v>36</v>
       </c>
       <c r="T28" s="2">
         <f t="shared" ref="T28" si="102">ROUND(B28/K28,3)</f>
-        <v>0.56899999999999995</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" ref="U28" si="103">ROUND(C28/L28,3)</f>
-        <v>0.97799999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="V28" s="6">
         <f t="shared" ref="V28" si="104">ROUND(D28/M28,3)</f>
-        <v>21.196000000000002</v>
+        <v>21.463000000000001</v>
       </c>
       <c r="W28" s="9">
         <f t="shared" ref="W28" si="105">ROUND(E28/N28,3)</f>
-        <v>21.073</v>
+        <v>21.588000000000001</v>
       </c>
       <c r="X28" s="9">
         <f t="shared" ref="X28" si="106">ROUND(F28/O28,3)</f>
-        <v>27.13</v>
+        <v>27.89</v>
       </c>
       <c r="Y28" s="13">
         <f t="shared" ref="Y28" si="107">ROUND(G28/P28,3)</f>
-        <v>20.010999999999999</v>
+        <v>19.853999999999999</v>
       </c>
       <c r="Z28" s="9">
         <f t="shared" ref="Z28" si="108">ROUND(H28/Q28,3)</f>
-        <v>5.1479999999999997</v>
+        <v>5.5190000000000001</v>
       </c>
       <c r="AA28" s="14">
         <f t="shared" ref="AA28" si="109">ROUND(I28/R28,3)</f>
-        <v>19.416</v>
+        <v>19.196999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3441,95 +3435,95 @@
       </c>
       <c r="B29" s="2">
         <f t="shared" ref="B29" si="110">D$2/D29</f>
-        <v>13.023051023051021</v>
+        <v>13.033177812337998</v>
       </c>
       <c r="C29" s="2">
         <f t="shared" ref="C29" si="111">D28/D29</f>
-        <v>1.1748251748251748</v>
+        <v>1.1905132192846035</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" ref="D29" si="112">SUM(F29:H29)</f>
-        <v>38.61</v>
+        <v>38.58</v>
       </c>
       <c r="E29" s="9">
-        <v>248.57</v>
+        <v>243.45</v>
       </c>
       <c r="F29" s="9">
-        <v>25.06</v>
+        <v>24.9</v>
       </c>
       <c r="G29" s="13">
         <v>12.11</v>
       </c>
       <c r="H29" s="9">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="I29" s="19">
-        <v>14.92</v>
+        <v>15.35</v>
       </c>
       <c r="J29" s="17" t="s">
         <v>37</v>
       </c>
       <c r="K29" s="2">
         <f t="shared" ref="K29:K30" si="113">M$2/M29</f>
-        <v>21.952631578947365</v>
+        <v>22.792349726775953</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" ref="L29:L30" si="114">M28/M29</f>
-        <v>1.1263157894736842</v>
+        <v>1.1693989071038251</v>
       </c>
       <c r="M29" s="6">
         <f t="shared" ref="M29:M30" si="115">SUM(O29:Q29)</f>
-        <v>1.9000000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="N29" s="9">
-        <v>11.49</v>
+        <v>11.6</v>
       </c>
       <c r="O29" s="9">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="P29" s="13">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="Q29" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="R29" s="19">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="S29" s="17" t="s">
         <v>37</v>
       </c>
       <c r="T29" s="2">
         <f t="shared" ref="T29" si="116">ROUND(B29/K29,3)</f>
-        <v>0.59299999999999997</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="U29" s="2">
         <f t="shared" ref="U29" si="117">ROUND(C29/L29,3)</f>
-        <v>1.0429999999999999</v>
+        <v>1.018</v>
       </c>
       <c r="V29" s="6">
         <f t="shared" ref="V29" si="118">ROUND(D29/M29,3)</f>
-        <v>20.321000000000002</v>
+        <v>21.082000000000001</v>
       </c>
       <c r="W29" s="9">
         <f t="shared" ref="W29" si="119">ROUND(E29/N29,3)</f>
-        <v>21.634</v>
+        <v>20.986999999999998</v>
       </c>
       <c r="X29" s="9">
         <f t="shared" ref="X29" si="120">ROUND(F29/O29,3)</f>
-        <v>25.835000000000001</v>
+        <v>27.065000000000001</v>
       </c>
       <c r="Y29" s="13">
         <f t="shared" ref="Y29" si="121">ROUND(G29/P29,3)</f>
-        <v>18.631</v>
+        <v>18.922000000000001</v>
       </c>
       <c r="Z29" s="9">
         <f t="shared" ref="Z29" si="122">ROUND(H29/Q29,3)</f>
-        <v>5.1429999999999998</v>
+        <v>5.8150000000000004</v>
       </c>
       <c r="AA29" s="19">
         <f t="shared" ref="AA29" si="123">ROUND(I29/R29,3)</f>
-        <v>19.376999999999999</v>
+        <v>20.196999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3538,51 +3532,51 @@
       </c>
       <c r="B30" s="5">
         <f t="shared" ref="B30" si="124">D$2/D30</f>
-        <v>12.774898373983739</v>
+        <v>13.090861754751366</v>
       </c>
       <c r="C30" s="5">
         <f t="shared" ref="C30" si="125">D29/D30</f>
-        <v>0.98094512195121952</v>
+        <v>1.0044259307472012</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" ref="D30" si="126">SUM(F30:H30)</f>
-        <v>39.36</v>
+        <v>38.409999999999997</v>
       </c>
       <c r="E30" s="13">
-        <v>206.44</v>
+        <v>203.17</v>
       </c>
       <c r="F30" s="9">
-        <v>25.32</v>
+        <v>25.03</v>
       </c>
       <c r="G30" s="9">
-        <v>12.45</v>
+        <v>11.97</v>
       </c>
       <c r="H30" s="9">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="I30" s="10">
-        <v>15.46</v>
+        <v>14.57</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="113"/>
-        <v>22.917582417582413</v>
+        <v>22.424731182795693</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="114"/>
-        <v>1.043956043956044</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" si="115"/>
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="N30" s="13">
-        <v>9.8000000000000007</v>
+        <v>9.52</v>
       </c>
       <c r="O30" s="9">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="P30" s="9">
         <v>0.65</v>
@@ -3598,35 +3592,35 @@
       </c>
       <c r="T30" s="5">
         <f t="shared" ref="T30" si="127">ROUND(B30/K30,3)</f>
-        <v>0.55700000000000005</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" ref="U30" si="128">ROUND(C30/L30,3)</f>
-        <v>0.94</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" ref="V30" si="129">ROUND(D30/M30,3)</f>
-        <v>21.626000000000001</v>
+        <v>20.651</v>
       </c>
       <c r="W30" s="13">
         <f t="shared" ref="W30" si="130">ROUND(E30/N30,3)</f>
-        <v>21.065000000000001</v>
+        <v>21.341000000000001</v>
       </c>
       <c r="X30" s="9">
         <f t="shared" ref="X30" si="131">ROUND(F30/O30,3)</f>
-        <v>27.824000000000002</v>
+        <v>26.347000000000001</v>
       </c>
       <c r="Y30" s="9">
         <f t="shared" ref="Y30" si="132">ROUND(G30/P30,3)</f>
-        <v>19.154</v>
+        <v>18.414999999999999</v>
       </c>
       <c r="Z30" s="9">
         <f t="shared" ref="Z30" si="133">ROUND(H30/Q30,3)</f>
-        <v>6.1150000000000002</v>
+        <v>5.423</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" ref="AA30" si="134">ROUND(I30/R30,3)</f>
-        <v>20.077999999999999</v>
+        <v>18.922000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3635,54 +3629,54 @@
       </c>
       <c r="B31" s="2">
         <f t="shared" ref="B31" si="135">D$2/D31</f>
-        <v>12.979349509550849</v>
+        <v>13.176624737945492</v>
       </c>
       <c r="C31" s="2">
         <f t="shared" ref="C31" si="136">D30/D31</f>
-        <v>1.0160041300980898</v>
+        <v>1.0065513626834381</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" ref="D31" si="137">SUM(F31:H31)</f>
-        <v>38.74</v>
+        <v>38.159999999999997</v>
       </c>
       <c r="E31" s="9">
-        <v>204.69</v>
+        <v>202.69</v>
       </c>
       <c r="F31" s="9">
-        <v>25.05</v>
+        <v>24.9</v>
       </c>
       <c r="G31" s="9">
-        <v>12.52</v>
+        <v>12.18</v>
       </c>
       <c r="H31" s="13">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="I31" s="10">
-        <v>15.61</v>
+        <v>14.71</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" ref="K31:K39" si="138">M$2/M31</f>
-        <v>25.746913580246911</v>
+        <f t="shared" ref="K31:K38" si="138">M$2/M31</f>
+        <v>25.588957055214717</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" ref="L31:L39" si="139">M30/M31</f>
-        <v>1.1234567901234569</v>
+        <f t="shared" ref="L31:L38" si="139">M30/M31</f>
+        <v>1.1411042944785277</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" ref="M31:M39" si="140">SUM(O31:Q31)</f>
-        <v>1.6199999999999999</v>
+        <f t="shared" ref="M31:M38" si="140">SUM(O31:Q31)</f>
+        <v>1.6300000000000001</v>
       </c>
       <c r="N31" s="9">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="O31" s="9">
         <v>0.96</v>
       </c>
       <c r="P31" s="9">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="Q31" s="13">
         <v>0.03</v>
@@ -3695,35 +3689,35 @@
       </c>
       <c r="T31" s="2">
         <f t="shared" ref="T31" si="141">ROUND(B31/K31,3)</f>
-        <v>0.504</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="U31" s="2">
         <f t="shared" ref="U31" si="142">ROUND(C31/L31,3)</f>
-        <v>0.90400000000000003</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="V31" s="6">
         <f t="shared" ref="V31" si="143">ROUND(D31/M31,3)</f>
-        <v>23.914000000000001</v>
+        <v>23.411000000000001</v>
       </c>
       <c r="W31" s="9">
         <f t="shared" ref="W31" si="144">ROUND(E31/N31,3)</f>
-        <v>21.524000000000001</v>
+        <v>21.335999999999999</v>
       </c>
       <c r="X31" s="9">
         <f t="shared" ref="X31" si="145">ROUND(F31/O31,3)</f>
-        <v>26.094000000000001</v>
+        <v>25.937999999999999</v>
       </c>
       <c r="Y31" s="9">
         <f t="shared" ref="Y31" si="146">ROUND(G31/P31,3)</f>
-        <v>19.873000000000001</v>
+        <v>19.030999999999999</v>
       </c>
       <c r="Z31" s="13">
         <f t="shared" ref="Z31" si="147">ROUND(H31/Q31,3)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA31" s="10">
         <f t="shared" ref="AA31" si="148">ROUND(I31/R31,3)</f>
-        <v>20.812999999999999</v>
+        <v>19.613</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3732,54 +3726,54 @@
       </c>
       <c r="B32" s="5">
         <f t="shared" ref="B32" si="149">D$2/D32</f>
-        <v>13.152498038189901</v>
+        <v>13.560409924487594</v>
       </c>
       <c r="C32" s="5">
         <f t="shared" ref="C32" si="150">D31/D32</f>
-        <v>1.0133403086581219</v>
+        <v>1.029126213592233</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" ref="D32" si="151">SUM(F32:H32)</f>
-        <v>38.230000000000004</v>
+        <v>37.08</v>
       </c>
       <c r="E32" s="9">
-        <v>206.61</v>
+        <v>203.18</v>
       </c>
       <c r="F32" s="13">
-        <v>24.56</v>
+        <v>23.97</v>
       </c>
       <c r="G32" s="9">
-        <v>12.5</v>
+        <v>12.04</v>
       </c>
       <c r="H32" s="9">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="I32" s="10">
-        <v>14.96</v>
+        <v>14.73</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>40</v>
       </c>
       <c r="K32" s="5">
         <f t="shared" si="138"/>
-        <v>28.965277777777771</v>
+        <v>27.622516556291387</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="139"/>
-        <v>1.1249999999999998</v>
+        <v>1.0794701986754967</v>
       </c>
       <c r="M32" s="4">
         <f t="shared" si="140"/>
-        <v>1.4400000000000002</v>
+        <v>1.51</v>
       </c>
       <c r="N32" s="9">
-        <v>9.49</v>
+        <v>9.61</v>
       </c>
       <c r="O32" s="13">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="P32" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="Q32" s="9">
         <v>0.03</v>
@@ -3792,35 +3786,35 @@
       </c>
       <c r="T32" s="5">
         <f t="shared" ref="T32:T33" si="152">ROUND(B32/K32,3)</f>
-        <v>0.45400000000000001</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="U32" s="5">
         <f t="shared" ref="U32:U33" si="153">ROUND(C32/L32,3)</f>
-        <v>0.90100000000000002</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" ref="V32:V33" si="154">ROUND(D32/M32,3)</f>
-        <v>26.548999999999999</v>
+        <v>24.556000000000001</v>
       </c>
       <c r="W32" s="9">
         <f t="shared" ref="W32:W33" si="155">ROUND(E32/N32,3)</f>
-        <v>21.771000000000001</v>
+        <v>21.143000000000001</v>
       </c>
       <c r="X32" s="13">
         <f t="shared" ref="X32:X33" si="156">ROUND(F32/O32,3)</f>
-        <v>32.316000000000003</v>
+        <v>28.536000000000001</v>
       </c>
       <c r="Y32" s="9">
         <f t="shared" ref="Y32:Y33" si="157">ROUND(G32/P32,3)</f>
-        <v>19.231000000000002</v>
+        <v>18.812999999999999</v>
       </c>
       <c r="Z32" s="9">
         <f t="shared" ref="Z32:Z33" si="158">ROUND(H32/Q32,3)</f>
-        <v>39</v>
+        <v>35.667000000000002</v>
       </c>
       <c r="AA32" s="10">
         <f t="shared" ref="AA32:AA33" si="159">ROUND(I32/R32,3)</f>
-        <v>19.684000000000001</v>
+        <v>19.382000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3829,51 +3823,51 @@
       </c>
       <c r="B33" s="5">
         <f t="shared" ref="B33" si="160">D$2/D33</f>
-        <v>13.630252100840337</v>
+        <v>13.791003839824461</v>
       </c>
       <c r="C33" s="5">
         <f t="shared" ref="C33" si="161">D32/D33</f>
-        <v>1.0363242071021961</v>
+        <v>1.0170049369171692</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" ref="D33" si="162">SUM(F33:H33)</f>
-        <v>36.889999999999993</v>
+        <v>36.460000000000008</v>
       </c>
       <c r="E33" s="9">
-        <v>203.57</v>
+        <v>202.94</v>
       </c>
       <c r="F33" s="9">
-        <v>24.06</v>
+        <v>24.03</v>
       </c>
       <c r="G33" s="13">
-        <v>11.67</v>
+        <v>11.34</v>
       </c>
       <c r="H33" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I33" s="14">
-        <v>14.69</v>
+        <v>14.5</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>41</v>
       </c>
       <c r="K33" s="5">
         <f t="shared" si="138"/>
-        <v>28.765517241379307</v>
+        <v>29.581560283687942</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="139"/>
-        <v>0.99310344827586217</v>
+        <v>1.0709219858156029</v>
       </c>
       <c r="M33" s="4">
         <f t="shared" si="140"/>
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="N33" s="9">
-        <v>9.43</v>
+        <v>9.83</v>
       </c>
       <c r="O33" s="9">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="P33" s="13">
         <v>0.6</v>
@@ -3882,42 +3876,42 @@
         <v>0.03</v>
       </c>
       <c r="R33" s="14">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>41</v>
       </c>
       <c r="T33" s="5">
         <f t="shared" si="152"/>
-        <v>0.47399999999999998</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="U33" s="5">
         <f t="shared" si="153"/>
-        <v>1.044</v>
+        <v>0.95</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="154"/>
-        <v>25.440999999999999</v>
+        <v>25.858000000000001</v>
       </c>
       <c r="W33" s="9">
         <f t="shared" si="155"/>
-        <v>21.587</v>
+        <v>20.645</v>
       </c>
       <c r="X33" s="9">
         <f t="shared" si="156"/>
-        <v>29.341000000000001</v>
+        <v>30.808</v>
       </c>
       <c r="Y33" s="13">
         <f t="shared" si="157"/>
-        <v>19.45</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="Z33" s="9">
         <f t="shared" si="158"/>
-        <v>38.667000000000002</v>
+        <v>36.332999999999998</v>
       </c>
       <c r="AA33" s="14">
         <f t="shared" si="159"/>
-        <v>20.69</v>
+        <v>20.138999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3926,51 +3920,51 @@
       </c>
       <c r="B34" s="2">
         <f t="shared" ref="B34" si="163">D$2/D34</f>
-        <v>13.600757370841221</v>
+        <v>13.760810071154898</v>
       </c>
       <c r="C34" s="2">
         <f t="shared" ref="C34" si="164">D33/D34</f>
-        <v>0.99783608331079243</v>
+        <v>0.99781061850027386</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" ref="D34" si="165">SUM(F34:H34)</f>
-        <v>36.97</v>
+        <v>36.54</v>
       </c>
       <c r="E34" s="18">
-        <v>203.2</v>
+        <v>203.04</v>
       </c>
       <c r="F34" s="9">
         <v>24.08</v>
       </c>
       <c r="G34" s="13">
-        <v>11.72</v>
+        <v>11.36</v>
       </c>
       <c r="H34" s="9">
-        <v>1.17</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I34" s="14">
-        <v>14.62</v>
+        <v>14.52</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="K34" s="2">
         <f t="shared" si="138"/>
-        <v>32.842519685039363</v>
+        <v>32.585937499999993</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="139"/>
-        <v>1.1417322834645669</v>
+        <v>1.1015625</v>
       </c>
       <c r="M34" s="6">
         <f t="shared" si="140"/>
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="N34" s="18">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="O34" s="9">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="P34" s="13">
         <v>0.43</v>
@@ -3986,35 +3980,35 @@
       </c>
       <c r="T34" s="2">
         <f t="shared" ref="T34" si="166">ROUND(B34/K34,3)</f>
-        <v>0.41399999999999998</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="U34" s="2">
         <f t="shared" ref="U34" si="167">ROUND(C34/L34,3)</f>
-        <v>0.874</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="V34" s="6">
         <f t="shared" ref="V34" si="168">ROUND(D34/M34,3)</f>
-        <v>29.11</v>
+        <v>28.547000000000001</v>
       </c>
       <c r="W34" s="18">
         <f t="shared" ref="W34" si="169">ROUND(E34/N34,3)</f>
-        <v>21.388999999999999</v>
+        <v>21.15</v>
       </c>
       <c r="X34" s="9">
         <f t="shared" ref="X34" si="170">ROUND(F34/O34,3)</f>
-        <v>29.728000000000002</v>
+        <v>29.366</v>
       </c>
       <c r="Y34" s="13">
         <f t="shared" ref="Y34" si="171">ROUND(G34/P34,3)</f>
-        <v>27.256</v>
+        <v>26.419</v>
       </c>
       <c r="Z34" s="9">
         <f t="shared" ref="Z34" si="172">ROUND(H34/Q34,3)</f>
-        <v>39</v>
+        <v>36.667000000000002</v>
       </c>
       <c r="AA34" s="14">
         <f t="shared" ref="AA34" si="173">ROUND(I34/R34,3)</f>
-        <v>23.206</v>
+        <v>23.047999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4023,51 +4017,51 @@
       </c>
       <c r="B35" s="2">
         <f t="shared" ref="B35:B36" si="174">D$2/D35</f>
-        <v>19.294704528012275</v>
+        <v>19.587845734320215</v>
       </c>
       <c r="C35" s="2">
         <f t="shared" ref="C35:C36" si="175">D34/D35</f>
-        <v>1.418649270913277</v>
+        <v>1.4234514998052199</v>
       </c>
       <c r="D35" s="6">
         <f t="shared" ref="D35:D36" si="176">SUM(F35:H35)</f>
-        <v>26.060000000000002</v>
+        <v>25.67</v>
       </c>
       <c r="E35" s="9">
-        <v>207.16</v>
+        <v>204.76</v>
       </c>
       <c r="F35" s="13">
-        <v>13.35</v>
+        <v>13.17</v>
       </c>
       <c r="G35" s="9">
-        <v>11.54</v>
+        <v>11.4</v>
       </c>
       <c r="H35" s="9">
-        <v>1.17</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I35" s="10">
-        <v>14.89</v>
+        <v>14.39</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>43</v>
       </c>
       <c r="K35" s="2">
         <f t="shared" si="138"/>
-        <v>33.910569105691053</v>
+        <v>33.367999999999995</v>
       </c>
       <c r="L35" s="2">
         <f t="shared" si="139"/>
-        <v>1.032520325203252</v>
+        <v>1.024</v>
       </c>
       <c r="M35" s="6">
         <f t="shared" si="140"/>
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="N35" s="9">
-        <v>9.3800000000000008</v>
+        <v>9.39</v>
       </c>
       <c r="O35" s="13">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="P35" s="9">
         <v>0.43</v>
@@ -4083,35 +4077,35 @@
       </c>
       <c r="T35" s="2">
         <f t="shared" ref="T35" si="177">ROUND(B35/K35,3)</f>
-        <v>0.56899999999999995</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="U35" s="2">
         <f t="shared" ref="U35" si="178">ROUND(C35/L35,3)</f>
-        <v>1.3740000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="V35" s="6">
         <f t="shared" ref="V35" si="179">ROUND(D35/M35,3)</f>
-        <v>21.187000000000001</v>
+        <v>20.536000000000001</v>
       </c>
       <c r="W35" s="9">
         <f t="shared" ref="W35" si="180">ROUND(E35/N35,3)</f>
-        <v>22.085000000000001</v>
+        <v>21.806000000000001</v>
       </c>
       <c r="X35" s="13">
         <f t="shared" ref="X35" si="181">ROUND(F35/O35,3)</f>
-        <v>17.338000000000001</v>
+        <v>16.670999999999999</v>
       </c>
       <c r="Y35" s="9">
         <f t="shared" ref="Y35" si="182">ROUND(G35/P35,3)</f>
-        <v>26.837</v>
+        <v>26.512</v>
       </c>
       <c r="Z35" s="9">
         <f t="shared" ref="Z35" si="183">ROUND(H35/Q35,3)</f>
-        <v>39</v>
+        <v>36.667000000000002</v>
       </c>
       <c r="AA35" s="10">
         <f t="shared" ref="AA35" si="184">ROUND(I35/R35,3)</f>
-        <v>23.635000000000002</v>
+        <v>22.841000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4120,51 +4114,51 @@
       </c>
       <c r="B36" s="2">
         <f t="shared" si="174"/>
-        <v>20.08067092651757</v>
+        <v>20.357085020242913</v>
       </c>
       <c r="C36" s="2">
         <f t="shared" si="175"/>
-        <v>1.0407348242811503</v>
+        <v>1.0392712550607288</v>
       </c>
       <c r="D36" s="6">
         <f t="shared" si="176"/>
-        <v>25.04</v>
+        <v>24.7</v>
       </c>
       <c r="E36" s="9">
-        <v>203.79</v>
+        <v>202.61</v>
       </c>
       <c r="F36" s="13">
-        <v>12.19</v>
+        <v>12.39</v>
       </c>
       <c r="G36" s="9">
-        <v>11.69</v>
+        <v>11.22</v>
       </c>
       <c r="H36" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I36" s="10">
-        <v>14.62</v>
+        <v>14.26</v>
       </c>
       <c r="J36" s="20" t="s">
         <v>44</v>
       </c>
       <c r="K36" s="2">
         <f t="shared" si="138"/>
-        <v>38.981308411214947</v>
+        <v>37.918181818181807</v>
       </c>
       <c r="L36" s="2">
         <f t="shared" si="139"/>
-        <v>1.1495327102803738</v>
+        <v>1.1363636363636362</v>
       </c>
       <c r="M36" s="6">
         <f t="shared" si="140"/>
-        <v>1.07</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N36" s="9">
-        <v>9.4700000000000006</v>
+        <v>9.51</v>
       </c>
       <c r="O36" s="13">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="P36" s="9">
         <v>0.43</v>
@@ -4173,42 +4167,42 @@
         <v>0.03</v>
       </c>
       <c r="R36" s="10">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="S36" s="20" t="s">
         <v>44</v>
       </c>
       <c r="T36" s="2">
         <f t="shared" ref="T36:T37" si="185">ROUND(B36/K36,3)</f>
-        <v>0.51500000000000001</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="U36" s="2">
         <f t="shared" ref="U36:U37" si="186">ROUND(C36/L36,3)</f>
-        <v>0.90500000000000003</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="V36" s="6">
         <f t="shared" ref="V36:V37" si="187">ROUND(D36/M36,3)</f>
-        <v>23.402000000000001</v>
+        <v>22.454999999999998</v>
       </c>
       <c r="W36" s="9">
         <f t="shared" ref="W36:W37" si="188">ROUND(E36/N36,3)</f>
-        <v>21.52</v>
+        <v>21.305</v>
       </c>
       <c r="X36" s="13">
         <f t="shared" ref="X36:X37" si="189">ROUND(F36/O36,3)</f>
-        <v>19.984000000000002</v>
+        <v>19.359000000000002</v>
       </c>
       <c r="Y36" s="9">
         <f t="shared" ref="Y36:Y37" si="190">ROUND(G36/P36,3)</f>
-        <v>27.186</v>
+        <v>26.093</v>
       </c>
       <c r="Z36" s="9">
         <f t="shared" ref="Z36:Z37" si="191">ROUND(H36/Q36,3)</f>
-        <v>38.667000000000002</v>
+        <v>36.332999999999998</v>
       </c>
       <c r="AA36" s="10">
         <f t="shared" ref="AA36:AA37" si="192">ROUND(I36/R36,3)</f>
-        <v>23.206</v>
+        <v>22.280999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4216,55 +4210,55 @@
         <v>45</v>
       </c>
       <c r="B37" s="5">
-        <f t="shared" ref="B37:B40" si="193">D$2/D37</f>
-        <v>20.291364003228409</v>
+        <f t="shared" ref="B37:B38" si="193">D$2/D37</f>
+        <v>20.598934862761162</v>
       </c>
       <c r="C37" s="5">
-        <f t="shared" ref="C37:C40" si="194">D36/D37</f>
-        <v>1.0104923325262309</v>
+        <f t="shared" ref="C37:C38" si="194">D36/D37</f>
+        <v>1.0118803768947153</v>
       </c>
       <c r="D37" s="4">
-        <f t="shared" ref="D37:D40" si="195">SUM(F37:H37)</f>
-        <v>24.779999999999998</v>
+        <f t="shared" ref="D37:D38" si="195">SUM(F37:H37)</f>
+        <v>24.41</v>
       </c>
       <c r="E37" s="18">
-        <v>203.12</v>
+        <v>202.53</v>
       </c>
       <c r="F37" s="18">
-        <v>12.26</v>
+        <v>12.29</v>
       </c>
       <c r="G37" s="13">
-        <v>11.36</v>
+        <v>11.05</v>
       </c>
       <c r="H37" s="18">
-        <v>1.1599999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="I37" s="14">
-        <v>13.09</v>
+        <v>12.67</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>45</v>
       </c>
       <c r="K37" s="5">
         <f t="shared" si="138"/>
-        <v>40.105769230769226</v>
+        <v>37.576576576576571</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="139"/>
-        <v>1.028846153846154</v>
+        <v>0.99099099099099097</v>
       </c>
       <c r="M37" s="4">
         <f t="shared" si="140"/>
-        <v>1.04</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N37" s="18">
-        <v>9.4</v>
+        <v>9.51</v>
       </c>
       <c r="O37" s="18">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="P37" s="13">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="Q37" s="18">
         <v>0.03</v>
@@ -4277,35 +4271,35 @@
       </c>
       <c r="T37" s="5">
         <f t="shared" si="185"/>
-        <v>0.50600000000000001</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="U37" s="5">
         <f t="shared" si="186"/>
-        <v>0.98199999999999998</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="187"/>
-        <v>23.827000000000002</v>
+        <v>21.991</v>
       </c>
       <c r="W37" s="18">
         <f t="shared" si="188"/>
-        <v>21.609000000000002</v>
+        <v>21.297000000000001</v>
       </c>
       <c r="X37" s="18">
         <f t="shared" si="189"/>
-        <v>20.78</v>
+        <v>18.908000000000001</v>
       </c>
       <c r="Y37" s="13">
         <f t="shared" si="190"/>
-        <v>27.047999999999998</v>
+        <v>25.698</v>
       </c>
       <c r="Z37" s="18">
         <f t="shared" si="191"/>
-        <v>38.667000000000002</v>
+        <v>35.667000000000002</v>
       </c>
       <c r="AA37" s="14">
         <f t="shared" si="192"/>
-        <v>21.113</v>
+        <v>20.434999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4314,30 +4308,30 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>19.913663366336632</v>
+        <v>20.072654690618759</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.98138613861386126</v>
+        <v>0.97445109780439121</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>25.25</v>
+        <v>25.05</v>
       </c>
       <c r="E38" s="13">
-        <v>153.47999999999999</v>
+        <v>151.44</v>
       </c>
       <c r="F38" s="18">
-        <v>12.48</v>
+        <v>12.61</v>
       </c>
       <c r="G38" s="18">
-        <v>11.6</v>
+        <v>11.34</v>
       </c>
       <c r="H38" s="18">
-        <v>1.17</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I38" s="19">
-        <v>13.38</v>
+        <v>13.29</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
@@ -4348,14 +4342,14 @@
       </c>
       <c r="L38" s="5">
         <f t="shared" si="139"/>
-        <v>0.94545454545454544</v>
+        <v>1.009090909090909</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="140"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="N38" s="13">
-        <v>8.02</v>
+        <v>8.11</v>
       </c>
       <c r="O38" s="18">
         <v>0.65</v>
@@ -4373,190 +4367,36 @@
         <v>46</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" ref="T38:T40" si="196">ROUND(B38/K38,3)</f>
-        <v>0.52500000000000002</v>
+        <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
+        <v>0.52900000000000003</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" ref="U38:U40" si="197">ROUND(C38/L38,3)</f>
-        <v>1.038</v>
+        <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
+        <v>0.96599999999999997</v>
       </c>
       <c r="V38" s="4">
-        <f t="shared" ref="V38:V40" si="198">ROUND(D38/M38,3)</f>
-        <v>22.954999999999998</v>
+        <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
+        <v>22.773</v>
       </c>
       <c r="W38" s="18">
-        <f t="shared" ref="W38:W40" si="199">ROUND(E38/N38,3)</f>
-        <v>19.137</v>
+        <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
+        <v>18.672999999999998</v>
       </c>
       <c r="X38" s="18">
-        <f t="shared" ref="X38:X40" si="200">ROUND(F38/O38,3)</f>
-        <v>19.2</v>
+        <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
+        <v>19.399999999999999</v>
       </c>
       <c r="Y38" s="18">
-        <f t="shared" ref="Y38:Y40" si="201">ROUND(G38/P38,3)</f>
-        <v>27.619</v>
+        <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
+        <v>27</v>
       </c>
       <c r="Z38" s="18">
-        <f t="shared" ref="Z38:Z40" si="202">ROUND(H38/Q38,3)</f>
-        <v>39</v>
+        <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
+        <v>36.667000000000002</v>
       </c>
       <c r="AA38" s="19">
-        <f t="shared" ref="AA38:AA40" si="203">ROUND(I38/R38,3)</f>
-        <v>21.581</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="5" t="e">
-        <f t="shared" si="193"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C39" s="5" t="e">
-        <f t="shared" si="194"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D39" s="4">
-        <f t="shared" si="195"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="K39" s="5" t="e">
-        <f t="shared" si="138"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L39" s="5" t="e">
-        <f t="shared" si="139"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M39" s="4">
-        <f t="shared" si="140"/>
-        <v>0</v>
-      </c>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="T39" s="5" t="e">
-        <f t="shared" si="196"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U39" s="5" t="e">
-        <f t="shared" si="197"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V39" s="4" t="e">
-        <f t="shared" si="198"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W39" s="18" t="e">
-        <f t="shared" si="199"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X39" s="18" t="e">
-        <f t="shared" si="200"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y39" s="18" t="e">
-        <f t="shared" si="201"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z39" s="18" t="e">
-        <f t="shared" si="202"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA39" s="19" t="e">
-        <f t="shared" si="203"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="5" t="e">
-        <f t="shared" si="193"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C40" s="5" t="e">
-        <f t="shared" si="194"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D40" s="4">
-        <f t="shared" si="195"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="K40" s="5" t="e">
-        <f t="shared" ref="K40" si="204">M$2/M40</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L40" s="5" t="e">
-        <f t="shared" ref="L40" si="205">M39/M40</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M40" s="4">
-        <f t="shared" ref="M40" si="206">SUM(O40:Q40)</f>
-        <v>0</v>
-      </c>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="T40" s="5" t="e">
-        <f t="shared" si="196"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U40" s="5" t="e">
-        <f t="shared" si="197"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V40" s="4" t="e">
-        <f t="shared" si="198"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W40" s="18" t="e">
-        <f t="shared" si="199"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X40" s="18" t="e">
-        <f t="shared" si="200"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y40" s="18" t="e">
-        <f t="shared" si="201"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z40" s="18" t="e">
-        <f t="shared" si="202"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA40" s="19" t="e">
-        <f t="shared" si="203"/>
-        <v>#DIV/0!</v>
+        <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
+        <v>21.434999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE2E92-143B-4049-8203-94D43AA9C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C95D972-4E42-446D-B480-FD323B5C417C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="48">
   <si>
     <t>H23</t>
   </si>
@@ -194,6 +194,10 @@
   </si>
   <si>
     <t>H58</t>
+  </si>
+  <si>
+    <t>H59</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -715,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AB39"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -2293,7 +2297,7 @@
       <c r="H17" s="18">
         <v>1.46</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="13">
         <v>64.06</v>
       </c>
       <c r="J17" s="17" t="s">
@@ -2323,7 +2327,7 @@
       <c r="Q17" s="18">
         <v>0.27</v>
       </c>
-      <c r="R17" s="18">
+      <c r="R17" s="13">
         <v>4.26</v>
       </c>
       <c r="S17" s="17" t="s">
@@ -2357,7 +2361,7 @@
         <f t="shared" si="6"/>
         <v>5.407</v>
       </c>
-      <c r="AA17" s="18">
+      <c r="AA17" s="13">
         <f t="shared" si="7"/>
         <v>15.038</v>
       </c>
@@ -3658,15 +3662,15 @@
         <v>39</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" ref="K31:K38" si="138">M$2/M31</f>
+        <f t="shared" ref="K31:K39" si="138">M$2/M31</f>
         <v>25.588957055214717</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" ref="L31:L38" si="139">M30/M31</f>
+        <f t="shared" ref="L31:L39" si="139">M30/M31</f>
         <v>1.1411042944785277</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" ref="M31:M38" si="140">SUM(O31:Q31)</f>
+        <f t="shared" ref="M31:M39" si="140">SUM(O31:Q31)</f>
         <v>1.6300000000000001</v>
       </c>
       <c r="N31" s="9">
@@ -4308,30 +4312,30 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>20.072654690618759</v>
+        <v>20.23420523138833</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.97445109780439121</v>
+        <v>0.98229376257545276</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>25.05</v>
+        <v>24.849999999999998</v>
       </c>
       <c r="E38" s="13">
-        <v>151.44</v>
+        <v>159.16</v>
       </c>
       <c r="F38" s="18">
-        <v>12.61</v>
+        <v>12.47</v>
       </c>
       <c r="G38" s="18">
-        <v>11.34</v>
+        <v>11.29</v>
       </c>
       <c r="H38" s="18">
-        <v>1.1000000000000001</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I38" s="19">
-        <v>13.29</v>
+        <v>13.23</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
@@ -4349,54 +4353,151 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="N38" s="13">
-        <v>8.11</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="O38" s="18">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="P38" s="18">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="Q38" s="18">
         <v>0.03</v>
       </c>
       <c r="R38" s="19">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="S38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.52900000000000003</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.96599999999999997</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>22.773</v>
-      </c>
-      <c r="W38" s="18">
+        <v>22.591000000000001</v>
+      </c>
+      <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>18.672999999999998</v>
+        <v>18.658999999999999</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>19.399999999999999</v>
+        <v>19.484000000000002</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>27</v>
+        <v>26.256</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
-        <v>36.667000000000002</v>
+        <v>36.332999999999998</v>
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>21.434999999999999</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="5">
+        <f t="shared" ref="B39" si="204">D$2/D39</f>
+        <v>20.498165511618424</v>
+      </c>
+      <c r="C39" s="5">
+        <f t="shared" ref="C39" si="205">D38/D39</f>
+        <v>1.013045250713412</v>
+      </c>
+      <c r="D39" s="4">
+        <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
+        <v>24.53</v>
+      </c>
+      <c r="E39" s="13">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="F39" s="9">
+        <v>12.42</v>
+      </c>
+      <c r="G39" s="9">
+        <v>11.03</v>
+      </c>
+      <c r="H39" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="I39" s="10">
+        <v>12.64</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" s="5">
+        <f t="shared" si="138"/>
+        <v>39.349056603773576</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="139"/>
+        <v>1.0377358490566038</v>
+      </c>
+      <c r="M39" s="4">
+        <f t="shared" si="140"/>
+        <v>1.06</v>
+      </c>
+      <c r="N39" s="13">
+        <v>1.62</v>
+      </c>
+      <c r="O39" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="P39" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R39" s="10">
+        <v>0.62</v>
+      </c>
+      <c r="S39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="T39" s="5">
+        <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="U39" s="5">
+        <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="V39" s="4">
+        <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
+        <v>23.141999999999999</v>
+      </c>
+      <c r="W39" s="13">
+        <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
+        <v>5.2160000000000002</v>
+      </c>
+      <c r="X39" s="18">
+        <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
+        <v>20.7</v>
+      </c>
+      <c r="Y39" s="18">
+        <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
+        <v>25.651</v>
+      </c>
+      <c r="Z39" s="18">
+        <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
+        <v>36</v>
+      </c>
+      <c r="AA39" s="19">
+        <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
+        <v>20.387</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C95D972-4E42-446D-B480-FD323B5C417C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A151B3FE-CA61-4F94-A7DB-68DD59251CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="49">
   <si>
     <t>H23</t>
   </si>
@@ -197,6 +197,10 @@
   </si>
   <si>
     <t>H59</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H60</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -719,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB39"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -3821,7 +3825,7 @@
         <v>19.382000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>41</v>
       </c>
@@ -3918,7 +3922,7 @@
         <v>20.138999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>42</v>
       </c>
@@ -4015,7 +4019,7 @@
         <v>23.047999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>43</v>
       </c>
@@ -4112,7 +4116,7 @@
         <v>22.841000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>44</v>
       </c>
@@ -4209,7 +4213,7 @@
         <v>22.280999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
         <v>45</v>
       </c>
@@ -4306,199 +4310,297 @@
         <v>20.434999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>20.23420523138833</v>
+        <v>20.398377281947262</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.98229376257545276</v>
+        <v>0.99026369168357009</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>24.849999999999998</v>
+        <v>24.65</v>
       </c>
       <c r="E38" s="13">
-        <v>159.16</v>
+        <v>144.94</v>
       </c>
       <c r="F38" s="18">
-        <v>12.47</v>
+        <v>12.43</v>
       </c>
       <c r="G38" s="18">
-        <v>11.29</v>
+        <v>11.09</v>
       </c>
       <c r="H38" s="18">
-        <v>1.0900000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I38" s="19">
-        <v>13.23</v>
+        <v>13.08</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="K38" s="5">
         <f t="shared" si="138"/>
-        <v>37.918181818181807</v>
+        <v>39.723809523809514</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="139"/>
-        <v>1.009090909090909</v>
+        <v>1.0571428571428572</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="140"/>
-        <v>1.1000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="N38" s="13">
-        <v>8.5299999999999994</v>
+        <v>7.69</v>
       </c>
       <c r="O38" s="18">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="P38" s="18">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="Q38" s="18">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R38" s="19">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="S38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.53400000000000003</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.97299999999999998</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>22.591000000000001</v>
+        <v>23.475999999999999</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>18.658999999999999</v>
+        <v>18.847999999999999</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>19.484000000000002</v>
+        <v>20.376999999999999</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>26.256</v>
+        <v>26.405000000000001</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
-        <v>36.332999999999998</v>
+        <v>56.5</v>
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>21</v>
+        <v>21.097000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="B39" s="5">
         <f t="shared" ref="B39" si="204">D$2/D39</f>
-        <v>20.498165511618424</v>
+        <v>20.531645569620252</v>
       </c>
       <c r="C39" s="5">
         <f t="shared" ref="C39" si="205">D38/D39</f>
-        <v>1.013045250713412</v>
+        <v>1.0065332788893426</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
-        <v>24.53</v>
+        <v>24.49</v>
       </c>
       <c r="E39" s="13">
-        <v>8.4499999999999993</v>
+        <v>1.47</v>
       </c>
       <c r="F39" s="9">
         <v>12.42</v>
       </c>
       <c r="G39" s="9">
-        <v>11.03</v>
+        <v>11.01</v>
       </c>
       <c r="H39" s="9">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="I39" s="10">
-        <v>12.64</v>
+        <v>12.8</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="K39" s="5">
         <f t="shared" si="138"/>
-        <v>39.349056603773576</v>
+        <v>40.495145631067956</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="139"/>
-        <v>1.0377358490566038</v>
+        <v>1.0194174757281553</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" si="140"/>
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N39" s="13">
-        <v>1.62</v>
+        <v>0.35</v>
       </c>
       <c r="O39" s="9">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="P39" s="9">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="Q39" s="9">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R39" s="10">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="S39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="T39" s="5">
         <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
-        <v>0.52100000000000002</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
-        <v>0.97599999999999998</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
-        <v>23.141999999999999</v>
+        <v>23.777000000000001</v>
       </c>
       <c r="W39" s="13">
         <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
-        <v>5.2160000000000002</v>
+        <v>4.2</v>
       </c>
       <c r="X39" s="18">
         <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
-        <v>20.7</v>
+        <v>21.050999999999998</v>
       </c>
       <c r="Y39" s="18">
         <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
-        <v>25.651</v>
+        <v>26.213999999999999</v>
       </c>
       <c r="Z39" s="18">
         <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="AA39" s="19">
         <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
-        <v>20.387</v>
-      </c>
+        <v>20.984000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="5">
+        <f t="shared" ref="B40" si="215">D$2/D40</f>
+        <v>20.514891880864951</v>
+      </c>
+      <c r="C40" s="5">
+        <f t="shared" ref="C40" si="216">D39/D40</f>
+        <v>0.99918400652794781</v>
+      </c>
+      <c r="D40" s="4">
+        <f t="shared" ref="D40" si="217">SUM(F40:H40)</f>
+        <v>24.509999999999998</v>
+      </c>
+      <c r="E40" s="18">
+        <v>1.49</v>
+      </c>
+      <c r="F40" s="18">
+        <v>12.29</v>
+      </c>
+      <c r="G40" s="18">
+        <v>11.14</v>
+      </c>
+      <c r="H40" s="18">
+        <v>1.08</v>
+      </c>
+      <c r="I40" s="19">
+        <v>12.72</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K40" s="5">
+        <f t="shared" ref="K40" si="218">M$2/M40</f>
+        <v>40.495145631067956</v>
+      </c>
+      <c r="L40" s="5">
+        <f t="shared" ref="L40" si="219">M39/M40</f>
+        <v>1</v>
+      </c>
+      <c r="M40" s="4">
+        <f t="shared" ref="M40" si="220">SUM(O40:Q40)</f>
+        <v>1.03</v>
+      </c>
+      <c r="N40" s="18">
+        <v>0.36</v>
+      </c>
+      <c r="O40" s="18">
+        <v>0.59</v>
+      </c>
+      <c r="P40" s="18">
+        <v>0.42</v>
+      </c>
+      <c r="Q40" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R40" s="19">
+        <v>0.62</v>
+      </c>
+      <c r="S40" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="T40" s="5">
+        <f t="shared" ref="T40" si="221">ROUND(B40/K40,3)</f>
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="U40" s="5">
+        <f t="shared" ref="U40" si="222">ROUND(C40/L40,3)</f>
+        <v>0.999</v>
+      </c>
+      <c r="V40" s="4">
+        <f t="shared" ref="V40" si="223">ROUND(D40/M40,3)</f>
+        <v>23.795999999999999</v>
+      </c>
+      <c r="W40" s="18">
+        <f t="shared" ref="W40" si="224">ROUND(E40/N40,3)</f>
+        <v>4.1390000000000002</v>
+      </c>
+      <c r="X40" s="18">
+        <f t="shared" ref="X40" si="225">ROUND(F40/O40,3)</f>
+        <v>20.831</v>
+      </c>
+      <c r="Y40" s="18">
+        <f t="shared" ref="Y40" si="226">ROUND(G40/P40,3)</f>
+        <v>26.524000000000001</v>
+      </c>
+      <c r="Z40" s="18">
+        <f t="shared" ref="Z40" si="227">ROUND(H40/Q40,3)</f>
+        <v>54</v>
+      </c>
+      <c r="AA40" s="19">
+        <f t="shared" ref="AA40" si="228">ROUND(I40/R40,3)</f>
+        <v>20.515999999999998</v>
+      </c>
+      <c r="AB40" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A151B3FE-CA61-4F94-A7DB-68DD59251CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59450E2-5248-4696-9EB8-FDF0FE9CA591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -4316,30 +4316,30 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>20.398377281947262</v>
+        <v>19.976956694477551</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.99026369168357009</v>
+        <v>0.96980532379817252</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>24.65</v>
+        <v>25.169999999999998</v>
       </c>
       <c r="E38" s="13">
-        <v>144.94</v>
+        <v>153.79</v>
       </c>
       <c r="F38" s="18">
-        <v>12.43</v>
+        <v>12.78</v>
       </c>
       <c r="G38" s="18">
-        <v>11.09</v>
+        <v>11.26</v>
       </c>
       <c r="H38" s="18">
         <v>1.1299999999999999</v>
       </c>
       <c r="I38" s="19">
-        <v>13.08</v>
+        <v>13.16</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
@@ -4357,7 +4357,7 @@
         <v>1.05</v>
       </c>
       <c r="N38" s="13">
-        <v>7.69</v>
+        <v>7.07</v>
       </c>
       <c r="O38" s="18">
         <v>0.61</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.51400000000000001</v>
+        <v>0.503</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.93700000000000006</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>23.475999999999999</v>
+        <v>23.971</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>18.847999999999999</v>
+        <v>21.751999999999999</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>20.376999999999999</v>
+        <v>20.951000000000001</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>26.405000000000001</v>
+        <v>26.81</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>21.097000000000001</v>
+        <v>21.225999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4413,51 +4413,51 @@
       </c>
       <c r="B39" s="5">
         <f t="shared" ref="B39" si="204">D$2/D39</f>
-        <v>20.531645569620252</v>
+        <v>20.582071223905032</v>
       </c>
       <c r="C39" s="5">
         <f t="shared" ref="C39" si="205">D38/D39</f>
-        <v>1.0065332788893426</v>
+        <v>1.0302906262791649</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
-        <v>24.49</v>
+        <v>24.43</v>
       </c>
       <c r="E39" s="13">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="F39" s="9">
-        <v>12.42</v>
+        <v>12.35</v>
       </c>
       <c r="G39" s="9">
         <v>11.01</v>
       </c>
       <c r="H39" s="9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I39" s="10">
-        <v>12.8</v>
+        <v>12.63</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="K39" s="5">
         <f t="shared" si="138"/>
-        <v>40.495145631067956</v>
+        <v>40.105769230769226</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="139"/>
-        <v>1.0194174757281553</v>
+        <v>1.0096153846153846</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" si="140"/>
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N39" s="13">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="O39" s="9">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="P39" s="9">
         <v>0.42</v>
@@ -4473,23 +4473,23 @@
       </c>
       <c r="T39" s="5">
         <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
-        <v>0.50700000000000001</v>
+        <v>0.51300000000000001</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
-        <v>0.98699999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
-        <v>23.777000000000001</v>
+        <v>23.49</v>
       </c>
       <c r="W39" s="13">
         <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
-        <v>4.2</v>
+        <v>4.2060000000000004</v>
       </c>
       <c r="X39" s="18">
         <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
-        <v>21.050999999999998</v>
+        <v>20.582999999999998</v>
       </c>
       <c r="Y39" s="18">
         <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="Z39" s="18">
         <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="AA39" s="19">
         <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
-        <v>20.984000000000002</v>
+        <v>20.704999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4510,27 +4510,27 @@
       </c>
       <c r="B40" s="5">
         <f t="shared" ref="B40" si="215">D$2/D40</f>
-        <v>20.514891880864951</v>
+        <v>20.565235173824124</v>
       </c>
       <c r="C40" s="5">
         <f t="shared" ref="C40" si="216">D39/D40</f>
-        <v>0.99918400652794781</v>
+        <v>0.99918200408997937</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" ref="D40" si="217">SUM(F40:H40)</f>
-        <v>24.509999999999998</v>
-      </c>
-      <c r="E40" s="18">
-        <v>1.49</v>
+        <v>24.450000000000003</v>
+      </c>
+      <c r="E40" s="13">
+        <v>1.4</v>
       </c>
       <c r="F40" s="18">
-        <v>12.29</v>
+        <v>12.21</v>
       </c>
       <c r="G40" s="18">
-        <v>11.14</v>
+        <v>11.17</v>
       </c>
       <c r="H40" s="18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I40" s="19">
         <v>12.72</v>
@@ -4540,24 +4540,24 @@
       </c>
       <c r="K40" s="5">
         <f t="shared" ref="K40" si="218">M$2/M40</f>
-        <v>40.495145631067956</v>
+        <v>39.349056603773576</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" ref="L40" si="219">M39/M40</f>
-        <v>1</v>
+        <v>0.98113207547169812</v>
       </c>
       <c r="M40" s="4">
         <f t="shared" ref="M40" si="220">SUM(O40:Q40)</f>
-        <v>1.03</v>
-      </c>
-      <c r="N40" s="18">
-        <v>0.36</v>
+        <v>1.06</v>
+      </c>
+      <c r="N40" s="13">
+        <v>0.2</v>
       </c>
       <c r="O40" s="18">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="P40" s="18">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="Q40" s="18">
         <v>0.02</v>
@@ -4570,31 +4570,31 @@
       </c>
       <c r="T40" s="5">
         <f t="shared" ref="T40" si="221">ROUND(B40/K40,3)</f>
-        <v>0.50700000000000001</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" ref="U40" si="222">ROUND(C40/L40,3)</f>
-        <v>0.999</v>
+        <v>1.018</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" ref="V40" si="223">ROUND(D40/M40,3)</f>
-        <v>23.795999999999999</v>
-      </c>
-      <c r="W40" s="18">
+        <v>23.065999999999999</v>
+      </c>
+      <c r="W40" s="13">
         <f t="shared" ref="W40" si="224">ROUND(E40/N40,3)</f>
-        <v>4.1390000000000002</v>
+        <v>7</v>
       </c>
       <c r="X40" s="18">
         <f t="shared" ref="X40" si="225">ROUND(F40/O40,3)</f>
-        <v>20.831</v>
+        <v>20.015999999999998</v>
       </c>
       <c r="Y40" s="18">
         <f t="shared" ref="Y40" si="226">ROUND(G40/P40,3)</f>
-        <v>26.524000000000001</v>
+        <v>25.977</v>
       </c>
       <c r="Z40" s="18">
         <f t="shared" ref="Z40" si="227">ROUND(H40/Q40,3)</f>
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="AA40" s="19">
         <f t="shared" ref="AA40" si="228">ROUND(I40/R40,3)</f>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59450E2-5248-4696-9EB8-FDF0FE9CA591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E471D7-223C-4BB6-B56E-FCDDB4A02ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="50">
   <si>
     <t>H23</t>
   </si>
@@ -201,6 +201,10 @@
   </si>
   <si>
     <t>H60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H61</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -723,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4316,51 +4320,51 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>19.976956694477551</v>
+        <v>20.193574297188754</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.96980532379817252</v>
+        <v>0.98032128514056227</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>25.169999999999998</v>
+        <v>24.9</v>
       </c>
       <c r="E38" s="13">
-        <v>153.79</v>
+        <v>145.12</v>
       </c>
       <c r="F38" s="18">
-        <v>12.78</v>
+        <v>12.68</v>
       </c>
       <c r="G38" s="18">
-        <v>11.26</v>
+        <v>11.12</v>
       </c>
       <c r="H38" s="18">
-        <v>1.1299999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I38" s="19">
-        <v>13.16</v>
+        <v>13.13</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="K38" s="5">
         <f t="shared" si="138"/>
-        <v>39.723809523809514</v>
+        <v>40.105769230769226</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="139"/>
-        <v>1.0571428571428572</v>
+        <v>1.0673076923076923</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="140"/>
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N38" s="13">
-        <v>7.07</v>
+        <v>7.03</v>
       </c>
       <c r="O38" s="18">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="P38" s="18">
         <v>0.42</v>
@@ -4369,42 +4373,42 @@
         <v>0.02</v>
       </c>
       <c r="R38" s="19">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="S38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.503</v>
+        <v>0.504</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.91700000000000004</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>23.971</v>
+        <v>23.942</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>21.751999999999999</v>
+        <v>20.643000000000001</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>20.951000000000001</v>
+        <v>21.132999999999999</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>26.81</v>
+        <v>26.475999999999999</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
-        <v>56.5</v>
+        <v>55</v>
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>21.225999999999999</v>
+        <v>21.524999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4413,24 +4417,24 @@
       </c>
       <c r="B39" s="5">
         <f t="shared" ref="B39" si="204">D$2/D39</f>
-        <v>20.582071223905032</v>
+        <v>20.666666666666664</v>
       </c>
       <c r="C39" s="5">
         <f t="shared" ref="C39" si="205">D38/D39</f>
-        <v>1.0302906262791649</v>
+        <v>1.0234278668310728</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
-        <v>24.43</v>
+        <v>24.33</v>
       </c>
       <c r="E39" s="13">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="F39" s="9">
-        <v>12.35</v>
+        <v>12.31</v>
       </c>
       <c r="G39" s="9">
-        <v>11.01</v>
+        <v>10.95</v>
       </c>
       <c r="H39" s="9">
         <v>1.07</v>
@@ -4443,21 +4447,21 @@
       </c>
       <c r="K39" s="5">
         <f t="shared" si="138"/>
-        <v>40.105769230769226</v>
+        <v>40.495145631067956</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="139"/>
-        <v>1.0096153846153846</v>
+        <v>1.0097087378640777</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" si="140"/>
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N39" s="13">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="O39" s="9">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="P39" s="9">
         <v>0.42</v>
@@ -4473,33 +4477,33 @@
       </c>
       <c r="T39" s="5">
         <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
-        <v>0.51300000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
-        <v>1.02</v>
+        <v>1.014</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
-        <v>23.49</v>
+        <v>23.620999999999999</v>
       </c>
       <c r="W39" s="13">
         <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
-        <v>4.2060000000000004</v>
-      </c>
-      <c r="X39" s="18">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="X39" s="9">
         <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
-        <v>20.582999999999998</v>
-      </c>
-      <c r="Y39" s="18">
+        <v>20.864000000000001</v>
+      </c>
+      <c r="Y39" s="9">
         <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
-        <v>26.213999999999999</v>
-      </c>
-      <c r="Z39" s="18">
+        <v>26.071000000000002</v>
+      </c>
+      <c r="Z39" s="9">
         <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
         <v>53.5</v>
       </c>
-      <c r="AA39" s="19">
+      <c r="AA39" s="10">
         <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
         <v>20.704999999999998</v>
       </c>
@@ -4509,88 +4513,88 @@
         <v>48</v>
       </c>
       <c r="B40" s="5">
-        <f t="shared" ref="B40" si="215">D$2/D40</f>
-        <v>20.565235173824124</v>
+        <f t="shared" ref="B40:B41" si="215">D$2/D40</f>
+        <v>20.473127035830615</v>
       </c>
       <c r="C40" s="5">
-        <f t="shared" ref="C40" si="216">D39/D40</f>
-        <v>0.99918200408997937</v>
+        <f t="shared" ref="C40:C41" si="216">D39/D40</f>
+        <v>0.99063517915309429</v>
       </c>
       <c r="D40" s="4">
-        <f t="shared" ref="D40" si="217">SUM(F40:H40)</f>
-        <v>24.450000000000003</v>
+        <f t="shared" ref="D40:D41" si="217">SUM(F40:H40)</f>
+        <v>24.560000000000002</v>
       </c>
       <c r="E40" s="13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="F40" s="18">
-        <v>12.21</v>
+        <v>12.33</v>
       </c>
       <c r="G40" s="18">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
       <c r="H40" s="18">
         <v>1.07</v>
       </c>
       <c r="I40" s="19">
-        <v>12.72</v>
+        <v>12.78</v>
       </c>
       <c r="J40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="K40" s="5">
         <f t="shared" ref="K40" si="218">M$2/M40</f>
-        <v>39.349056603773576</v>
+        <v>40.105769230769226</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" ref="L40" si="219">M39/M40</f>
-        <v>0.98113207547169812</v>
+        <v>0.99038461538461542</v>
       </c>
       <c r="M40" s="4">
         <f t="shared" ref="M40" si="220">SUM(O40:Q40)</f>
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N40" s="13">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O40" s="18">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="P40" s="18">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="Q40" s="18">
         <v>0.02</v>
       </c>
       <c r="R40" s="19">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="S40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="T40" s="5">
         <f t="shared" ref="T40" si="221">ROUND(B40/K40,3)</f>
-        <v>0.52300000000000002</v>
+        <v>0.51</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" ref="U40" si="222">ROUND(C40/L40,3)</f>
-        <v>1.018</v>
+        <v>1</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" ref="V40" si="223">ROUND(D40/M40,3)</f>
-        <v>23.065999999999999</v>
+        <v>23.614999999999998</v>
       </c>
       <c r="W40" s="13">
         <f t="shared" ref="W40" si="224">ROUND(E40/N40,3)</f>
-        <v>7</v>
+        <v>6.13</v>
       </c>
       <c r="X40" s="18">
         <f t="shared" ref="X40" si="225">ROUND(F40/O40,3)</f>
-        <v>20.015999999999998</v>
+        <v>20.55</v>
       </c>
       <c r="Y40" s="18">
         <f t="shared" ref="Y40" si="226">ROUND(G40/P40,3)</f>
-        <v>25.977</v>
+        <v>26.571000000000002</v>
       </c>
       <c r="Z40" s="18">
         <f t="shared" ref="Z40" si="227">ROUND(H40/Q40,3)</f>
@@ -4598,9 +4602,106 @@
       </c>
       <c r="AA40" s="19">
         <f t="shared" ref="AA40" si="228">ROUND(I40/R40,3)</f>
-        <v>20.515999999999998</v>
+        <v>20.951000000000001</v>
       </c>
       <c r="AB40" s="20"/>
+    </row>
+    <row r="41" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="5">
+        <f t="shared" si="215"/>
+        <v>20.531645569620249</v>
+      </c>
+      <c r="C41" s="5">
+        <f t="shared" si="216"/>
+        <v>1.0028583095140875</v>
+      </c>
+      <c r="D41" s="4">
+        <f t="shared" si="217"/>
+        <v>24.490000000000002</v>
+      </c>
+      <c r="E41" s="13">
+        <v>1.28</v>
+      </c>
+      <c r="F41" s="9">
+        <v>12.3</v>
+      </c>
+      <c r="G41" s="9">
+        <v>11.12</v>
+      </c>
+      <c r="H41" s="9">
+        <v>1.07</v>
+      </c>
+      <c r="I41" s="10">
+        <v>12.98</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="K41" s="5">
+        <f t="shared" ref="K41" si="229">M$2/M41</f>
+        <v>42.131313131313128</v>
+      </c>
+      <c r="L41" s="5">
+        <f t="shared" ref="L41" si="230">M40/M41</f>
+        <v>1.0505050505050506</v>
+      </c>
+      <c r="M41" s="4">
+        <f t="shared" ref="M41" si="231">SUM(O41:Q41)</f>
+        <v>0.99</v>
+      </c>
+      <c r="N41" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="O41" s="9">
+        <v>0.61</v>
+      </c>
+      <c r="P41" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R41" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S41" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="T41" s="5">
+        <f t="shared" ref="T41" si="232">ROUND(B41/K41,3)</f>
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="U41" s="5">
+        <f t="shared" ref="U41" si="233">ROUND(C41/L41,3)</f>
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="V41" s="4">
+        <f t="shared" ref="V41" si="234">ROUND(D41/M41,3)</f>
+        <v>24.736999999999998</v>
+      </c>
+      <c r="W41" s="13">
+        <f t="shared" ref="W41" si="235">ROUND(E41/N41,3)</f>
+        <v>8.5329999999999995</v>
+      </c>
+      <c r="X41" s="9">
+        <f t="shared" ref="X41" si="236">ROUND(F41/O41,3)</f>
+        <v>20.164000000000001</v>
+      </c>
+      <c r="Y41" s="9">
+        <f t="shared" ref="Y41" si="237">ROUND(G41/P41,3)</f>
+        <v>30.888999999999999</v>
+      </c>
+      <c r="Z41" s="9">
+        <f t="shared" ref="Z41" si="238">ROUND(H41/Q41,3)</f>
+        <v>53.5</v>
+      </c>
+      <c r="AA41" s="10">
+        <f t="shared" ref="AA41" si="239">ROUND(I41/R41,3)</f>
+        <v>22.379000000000001</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E471D7-223C-4BB6-B56E-FCDDB4A02ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836F6765-BB40-421B-BFF6-9844544DA4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="51">
   <si>
     <t>H23</t>
   </si>
@@ -205,6 +205,10 @@
   </si>
   <si>
     <t>H61</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H62</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -727,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4320,30 +4324,30 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>20.193574297188754</v>
+        <v>20.266827891979037</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.98032128514056227</v>
+        <v>0.98387746876259563</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>24.9</v>
+        <v>24.810000000000002</v>
       </c>
       <c r="E38" s="13">
-        <v>145.12</v>
+        <v>145.78</v>
       </c>
       <c r="F38" s="18">
-        <v>12.68</v>
+        <v>12.52</v>
       </c>
       <c r="G38" s="18">
-        <v>11.12</v>
+        <v>11.19</v>
       </c>
       <c r="H38" s="18">
         <v>1.1000000000000001</v>
       </c>
       <c r="I38" s="19">
-        <v>13.13</v>
+        <v>12.8</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
@@ -4361,7 +4365,7 @@
         <v>1.04</v>
       </c>
       <c r="N38" s="13">
-        <v>7.03</v>
+        <v>6.85</v>
       </c>
       <c r="O38" s="18">
         <v>0.6</v>
@@ -4380,27 +4384,27 @@
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.504</v>
+        <v>0.505</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.91800000000000004</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>23.942</v>
+        <v>23.856000000000002</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>20.643000000000001</v>
+        <v>21.282</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>21.132999999999999</v>
+        <v>20.867000000000001</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>26.475999999999999</v>
+        <v>26.643000000000001</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
@@ -4408,7 +4412,7 @@
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>21.524999999999999</v>
+        <v>20.984000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4417,51 +4421,51 @@
       </c>
       <c r="B39" s="5">
         <f t="shared" ref="B39" si="204">D$2/D39</f>
-        <v>20.666666666666664</v>
+        <v>20.582071223905032</v>
       </c>
       <c r="C39" s="5">
         <f t="shared" ref="C39" si="205">D38/D39</f>
-        <v>1.0234278668310728</v>
+        <v>1.015554645927139</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
-        <v>24.33</v>
+        <v>24.43</v>
       </c>
       <c r="E39" s="13">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="F39" s="9">
-        <v>12.31</v>
+        <v>12.39</v>
       </c>
       <c r="G39" s="9">
-        <v>10.95</v>
+        <v>10.98</v>
       </c>
       <c r="H39" s="9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I39" s="10">
-        <v>12.63</v>
+        <v>12.65</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="K39" s="5">
         <f t="shared" si="138"/>
-        <v>40.495145631067956</v>
+        <v>40.105769230769226</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="139"/>
-        <v>1.0097087378640777</v>
+        <v>1</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" si="140"/>
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N39" s="13">
         <v>0.36</v>
       </c>
       <c r="O39" s="9">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="P39" s="9">
         <v>0.42</v>
@@ -4477,35 +4481,35 @@
       </c>
       <c r="T39" s="5">
         <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
-        <v>0.51</v>
+        <v>0.51300000000000001</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
-        <v>1.014</v>
+        <v>1.016</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
-        <v>23.620999999999999</v>
+        <v>23.49</v>
       </c>
       <c r="W39" s="13">
         <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
-        <v>4.1669999999999998</v>
+        <v>3.8610000000000002</v>
       </c>
       <c r="X39" s="9">
         <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
-        <v>20.864000000000001</v>
+        <v>20.65</v>
       </c>
       <c r="Y39" s="9">
         <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
-        <v>26.071000000000002</v>
+        <v>26.143000000000001</v>
       </c>
       <c r="Z39" s="9">
         <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
-        <v>53.5</v>
+        <v>53</v>
       </c>
       <c r="AA39" s="10">
         <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
-        <v>20.704999999999998</v>
+        <v>20.738</v>
       </c>
     </row>
     <row r="40" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4514,51 +4518,51 @@
       </c>
       <c r="B40" s="5">
         <f t="shared" ref="B40:B41" si="215">D$2/D40</f>
-        <v>20.473127035830615</v>
+        <v>20.54842664487127</v>
       </c>
       <c r="C40" s="5">
         <f t="shared" ref="C40:C41" si="216">D39/D40</f>
-        <v>0.99063517915309429</v>
+        <v>0.99836534532080101</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" ref="D40:D41" si="217">SUM(F40:H40)</f>
-        <v>24.560000000000002</v>
+        <v>24.47</v>
       </c>
       <c r="E40" s="13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="F40" s="18">
-        <v>12.33</v>
+        <v>12.27</v>
       </c>
       <c r="G40" s="18">
-        <v>11.16</v>
+        <v>11.12</v>
       </c>
       <c r="H40" s="18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I40" s="19">
-        <v>12.78</v>
+        <v>12.69</v>
       </c>
       <c r="J40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="K40" s="5">
         <f t="shared" ref="K40" si="218">M$2/M40</f>
-        <v>40.105769230769226</v>
+        <v>39.723809523809514</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" ref="L40" si="219">M39/M40</f>
-        <v>0.99038461538461542</v>
+        <v>0.99047619047619051</v>
       </c>
       <c r="M40" s="4">
         <f t="shared" ref="M40" si="220">SUM(O40:Q40)</f>
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N40" s="13">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="O40" s="18">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="P40" s="18">
         <v>0.42</v>
@@ -4574,35 +4578,35 @@
       </c>
       <c r="T40" s="5">
         <f t="shared" ref="T40" si="221">ROUND(B40/K40,3)</f>
-        <v>0.51</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" ref="U40" si="222">ROUND(C40/L40,3)</f>
-        <v>1</v>
+        <v>1.008</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" ref="V40" si="223">ROUND(D40/M40,3)</f>
-        <v>23.614999999999998</v>
+        <v>23.305</v>
       </c>
       <c r="W40" s="13">
         <f t="shared" ref="W40" si="224">ROUND(E40/N40,3)</f>
-        <v>6.13</v>
+        <v>6.7619999999999996</v>
       </c>
       <c r="X40" s="18">
         <f t="shared" ref="X40" si="225">ROUND(F40/O40,3)</f>
-        <v>20.55</v>
+        <v>20.114999999999998</v>
       </c>
       <c r="Y40" s="18">
         <f t="shared" ref="Y40" si="226">ROUND(G40/P40,3)</f>
-        <v>26.571000000000002</v>
+        <v>26.475999999999999</v>
       </c>
       <c r="Z40" s="18">
         <f t="shared" ref="Z40" si="227">ROUND(H40/Q40,3)</f>
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="AA40" s="19">
         <f t="shared" ref="AA40" si="228">ROUND(I40/R40,3)</f>
-        <v>20.951000000000001</v>
+        <v>20.803000000000001</v>
       </c>
       <c r="AB40" s="20"/>
     </row>
@@ -4612,51 +4616,51 @@
       </c>
       <c r="B41" s="5">
         <f t="shared" si="215"/>
-        <v>20.531645569620249</v>
+        <v>20.61582615826158</v>
       </c>
       <c r="C41" s="5">
         <f t="shared" si="216"/>
-        <v>1.0028583095140875</v>
+        <v>1.003280032800328</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="217"/>
-        <v>24.490000000000002</v>
+        <v>24.39</v>
       </c>
       <c r="E41" s="13">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="F41" s="9">
-        <v>12.3</v>
+        <v>12.27</v>
       </c>
       <c r="G41" s="9">
-        <v>11.12</v>
+        <v>11.05</v>
       </c>
       <c r="H41" s="9">
         <v>1.07</v>
       </c>
       <c r="I41" s="10">
-        <v>12.98</v>
+        <v>12.66</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>49</v>
       </c>
       <c r="K41" s="5">
         <f t="shared" ref="K41" si="229">M$2/M41</f>
-        <v>42.131313131313128</v>
+        <v>42.561224489795912</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" ref="L41" si="230">M40/M41</f>
-        <v>1.0505050505050506</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="M41" s="4">
         <f t="shared" ref="M41" si="231">SUM(O41:Q41)</f>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="N41" s="13">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O41" s="9">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="P41" s="9">
         <v>0.36</v>
@@ -4665,34 +4669,34 @@
         <v>0.02</v>
       </c>
       <c r="R41" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="S41" s="20" t="s">
         <v>49</v>
       </c>
       <c r="T41" s="5">
         <f t="shared" ref="T41" si="232">ROUND(B41/K41,3)</f>
-        <v>0.48699999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" ref="U41" si="233">ROUND(C41/L41,3)</f>
-        <v>0.95499999999999996</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" ref="V41" si="234">ROUND(D41/M41,3)</f>
-        <v>24.736999999999998</v>
+        <v>24.888000000000002</v>
       </c>
       <c r="W41" s="13">
         <f t="shared" ref="W41" si="235">ROUND(E41/N41,3)</f>
-        <v>8.5329999999999995</v>
+        <v>8.9290000000000003</v>
       </c>
       <c r="X41" s="9">
         <f t="shared" ref="X41" si="236">ROUND(F41/O41,3)</f>
-        <v>20.164000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="Y41" s="9">
         <f t="shared" ref="Y41" si="237">ROUND(G41/P41,3)</f>
-        <v>30.888999999999999</v>
+        <v>30.693999999999999</v>
       </c>
       <c r="Z41" s="9">
         <f t="shared" ref="Z41" si="238">ROUND(H41/Q41,3)</f>
@@ -4700,7 +4704,104 @@
       </c>
       <c r="AA41" s="10">
         <f t="shared" ref="AA41" si="239">ROUND(I41/R41,3)</f>
-        <v>22.379000000000001</v>
+        <v>21.457999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="5">
+        <f t="shared" ref="B42" si="240">D$2/D42</f>
+        <v>20.726298433635613</v>
+      </c>
+      <c r="C42" s="5">
+        <f t="shared" ref="C42" si="241">D41/D42</f>
+        <v>1.005358615004122</v>
+      </c>
+      <c r="D42" s="4">
+        <f t="shared" ref="D42" si="242">SUM(F42:H42)</f>
+        <v>24.259999999999998</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.26</v>
+      </c>
+      <c r="F42" s="13">
+        <v>12.11</v>
+      </c>
+      <c r="G42" s="9">
+        <v>11.09</v>
+      </c>
+      <c r="H42" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="I42" s="10">
+        <v>12.6</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="5">
+        <f t="shared" ref="K42" si="243">M$2/M42</f>
+        <v>42.999999999999993</v>
+      </c>
+      <c r="L42" s="5">
+        <f t="shared" ref="L42" si="244">M41/M42</f>
+        <v>1.0103092783505154</v>
+      </c>
+      <c r="M42" s="4">
+        <f t="shared" ref="M42" si="245">SUM(O42:Q42)</f>
+        <v>0.97</v>
+      </c>
+      <c r="N42" s="9">
+        <v>0.13</v>
+      </c>
+      <c r="O42" s="13">
+        <v>0.59</v>
+      </c>
+      <c r="P42" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R42" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S42" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="T42" s="5">
+        <f t="shared" ref="T42" si="246">ROUND(B42/K42,3)</f>
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="U42" s="5">
+        <f t="shared" ref="U42" si="247">ROUND(C42/L42,3)</f>
+        <v>0.995</v>
+      </c>
+      <c r="V42" s="4">
+        <f t="shared" ref="V42" si="248">ROUND(D42/M42,3)</f>
+        <v>25.01</v>
+      </c>
+      <c r="W42" s="18">
+        <f t="shared" ref="W42" si="249">ROUND(E42/N42,3)</f>
+        <v>9.6920000000000002</v>
+      </c>
+      <c r="X42" s="13">
+        <f t="shared" ref="X42" si="250">ROUND(F42/O42,3)</f>
+        <v>20.524999999999999</v>
+      </c>
+      <c r="Y42" s="9">
+        <f t="shared" ref="Y42" si="251">ROUND(G42/P42,3)</f>
+        <v>30.806000000000001</v>
+      </c>
+      <c r="Z42" s="9">
+        <f t="shared" ref="Z42" si="252">ROUND(H42/Q42,3)</f>
+        <v>53</v>
+      </c>
+      <c r="AA42" s="10">
+        <f t="shared" ref="AA42" si="253">ROUND(I42/R42,3)</f>
+        <v>21.724</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836F6765-BB40-421B-BFF6-9844544DA4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49700552-7753-41A0-8CFE-23143EDEDC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="52">
   <si>
     <t>H23</t>
   </si>
@@ -209,6 +209,10 @@
   </si>
   <si>
     <t>H62</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H63</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -731,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AB43"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4324,30 +4328,30 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>20.266827891979037</v>
+        <v>20.291364003228406</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.98387746876259563</v>
+        <v>0.98506860371267146</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>24.810000000000002</v>
+        <v>24.78</v>
       </c>
       <c r="E38" s="13">
-        <v>145.78</v>
+        <v>144.26</v>
       </c>
       <c r="F38" s="18">
-        <v>12.52</v>
+        <v>12.58</v>
       </c>
       <c r="G38" s="18">
-        <v>11.19</v>
+        <v>11.13</v>
       </c>
       <c r="H38" s="18">
-        <v>1.1000000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="I38" s="19">
-        <v>12.8</v>
+        <v>13.04</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
@@ -4365,7 +4369,7 @@
         <v>1.04</v>
       </c>
       <c r="N38" s="13">
-        <v>6.85</v>
+        <v>6.81</v>
       </c>
       <c r="O38" s="18">
         <v>0.6</v>
@@ -4377,42 +4381,42 @@
         <v>0.02</v>
       </c>
       <c r="R38" s="19">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="S38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.505</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.92200000000000004</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>23.856000000000002</v>
+        <v>23.827000000000002</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>21.282</v>
+        <v>21.184000000000001</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>20.867000000000001</v>
+        <v>20.966999999999999</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>26.643000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>20.984000000000002</v>
+        <v>21.032</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4421,30 +4425,30 @@
       </c>
       <c r="B39" s="5">
         <f t="shared" ref="B39" si="204">D$2/D39</f>
-        <v>20.582071223905032</v>
+        <v>20.531645569620252</v>
       </c>
       <c r="C39" s="5">
         <f t="shared" ref="C39" si="205">D38/D39</f>
-        <v>1.015554645927139</v>
+        <v>1.0118415679869335</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
-        <v>24.43</v>
+        <v>24.49</v>
       </c>
       <c r="E39" s="13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="F39" s="9">
-        <v>12.39</v>
+        <v>12.5</v>
       </c>
       <c r="G39" s="9">
-        <v>10.98</v>
+        <v>10.94</v>
       </c>
       <c r="H39" s="9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I39" s="10">
-        <v>12.65</v>
+        <v>12.59</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>47</v>
@@ -4462,7 +4466,7 @@
         <v>1.04</v>
       </c>
       <c r="N39" s="13">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="O39" s="9">
         <v>0.6</v>
@@ -4474,42 +4478,42 @@
         <v>0.02</v>
       </c>
       <c r="R39" s="10">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="S39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="T39" s="5">
         <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
-        <v>0.51300000000000001</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
-        <v>1.016</v>
+        <v>1.012</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
-        <v>23.49</v>
+        <v>23.547999999999998</v>
       </c>
       <c r="W39" s="13">
         <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
-        <v>3.8610000000000002</v>
+        <v>3.7839999999999998</v>
       </c>
       <c r="X39" s="9">
         <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
-        <v>20.65</v>
+        <v>20.832999999999998</v>
       </c>
       <c r="Y39" s="9">
         <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
-        <v>26.143000000000001</v>
+        <v>26.047999999999998</v>
       </c>
       <c r="Z39" s="9">
         <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="AA39" s="10">
         <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
-        <v>20.738</v>
+        <v>20.306000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4518,51 +4522,51 @@
       </c>
       <c r="B40" s="5">
         <f t="shared" ref="B40:B41" si="215">D$2/D40</f>
-        <v>20.54842664487127</v>
+        <v>20.193574297188754</v>
       </c>
       <c r="C40" s="5">
         <f t="shared" ref="C40:C41" si="216">D39/D40</f>
-        <v>0.99836534532080101</v>
+        <v>0.98353413654618471</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" ref="D40:D41" si="217">SUM(F40:H40)</f>
-        <v>24.47</v>
+        <v>24.9</v>
       </c>
       <c r="E40" s="13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="F40" s="18">
-        <v>12.27</v>
+        <v>12.68</v>
       </c>
       <c r="G40" s="18">
-        <v>11.12</v>
+        <v>11.15</v>
       </c>
       <c r="H40" s="18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I40" s="19">
-        <v>12.69</v>
+        <v>12.62</v>
       </c>
       <c r="J40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="K40" s="5">
         <f t="shared" ref="K40" si="218">M$2/M40</f>
-        <v>39.723809523809514</v>
+        <v>40.105769230769226</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" ref="L40" si="219">M39/M40</f>
-        <v>0.99047619047619051</v>
+        <v>1</v>
       </c>
       <c r="M40" s="4">
         <f t="shared" ref="M40" si="220">SUM(O40:Q40)</f>
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N40" s="13">
         <v>0.21</v>
       </c>
       <c r="O40" s="18">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="P40" s="18">
         <v>0.42</v>
@@ -4578,35 +4582,35 @@
       </c>
       <c r="T40" s="5">
         <f t="shared" ref="T40" si="221">ROUND(B40/K40,3)</f>
-        <v>0.51700000000000002</v>
+        <v>0.504</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" ref="U40" si="222">ROUND(C40/L40,3)</f>
-        <v>1.008</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" ref="V40" si="223">ROUND(D40/M40,3)</f>
-        <v>23.305</v>
+        <v>23.942</v>
       </c>
       <c r="W40" s="13">
         <f t="shared" ref="W40" si="224">ROUND(E40/N40,3)</f>
-        <v>6.7619999999999996</v>
+        <v>6.7140000000000004</v>
       </c>
       <c r="X40" s="18">
         <f t="shared" ref="X40" si="225">ROUND(F40/O40,3)</f>
-        <v>20.114999999999998</v>
+        <v>21.132999999999999</v>
       </c>
       <c r="Y40" s="18">
         <f t="shared" ref="Y40" si="226">ROUND(G40/P40,3)</f>
-        <v>26.475999999999999</v>
+        <v>26.547999999999998</v>
       </c>
       <c r="Z40" s="18">
         <f t="shared" ref="Z40" si="227">ROUND(H40/Q40,3)</f>
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="AA40" s="19">
         <f t="shared" ref="AA40" si="228">ROUND(I40/R40,3)</f>
-        <v>20.803000000000001</v>
+        <v>20.689</v>
       </c>
       <c r="AB40" s="20"/>
     </row>
@@ -4616,30 +4620,30 @@
       </c>
       <c r="B41" s="5">
         <f t="shared" si="215"/>
-        <v>20.61582615826158</v>
+        <v>20.473127035830618</v>
       </c>
       <c r="C41" s="5">
         <f t="shared" si="216"/>
-        <v>1.003280032800328</v>
+        <v>1.013843648208469</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="217"/>
-        <v>24.39</v>
+        <v>24.56</v>
       </c>
       <c r="E41" s="13">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="F41" s="9">
-        <v>12.27</v>
+        <v>12.26</v>
       </c>
       <c r="G41" s="9">
-        <v>11.05</v>
+        <v>11.17</v>
       </c>
       <c r="H41" s="9">
-        <v>1.07</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I41" s="10">
-        <v>12.66</v>
+        <v>12.94</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>49</v>
@@ -4650,14 +4654,14 @@
       </c>
       <c r="L41" s="5">
         <f t="shared" ref="L41" si="230">M40/M41</f>
-        <v>1.0714285714285714</v>
+        <v>1.0612244897959184</v>
       </c>
       <c r="M41" s="4">
         <f t="shared" ref="M41" si="231">SUM(O41:Q41)</f>
         <v>0.98</v>
       </c>
       <c r="N41" s="13">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="O41" s="9">
         <v>0.6</v>
@@ -4676,35 +4680,35 @@
       </c>
       <c r="T41" s="5">
         <f t="shared" ref="T41" si="232">ROUND(B41/K41,3)</f>
-        <v>0.48399999999999999</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" ref="U41" si="233">ROUND(C41/L41,3)</f>
-        <v>0.93600000000000005</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" ref="V41" si="234">ROUND(D41/M41,3)</f>
-        <v>24.888000000000002</v>
+        <v>25.061</v>
       </c>
       <c r="W41" s="13">
         <f t="shared" ref="W41" si="235">ROUND(E41/N41,3)</f>
-        <v>8.9290000000000003</v>
+        <v>9.8460000000000001</v>
       </c>
       <c r="X41" s="9">
         <f t="shared" ref="X41" si="236">ROUND(F41/O41,3)</f>
-        <v>20.45</v>
+        <v>20.433</v>
       </c>
       <c r="Y41" s="9">
         <f t="shared" ref="Y41" si="237">ROUND(G41/P41,3)</f>
-        <v>30.693999999999999</v>
+        <v>31.027999999999999</v>
       </c>
       <c r="Z41" s="9">
         <f t="shared" ref="Z41" si="238">ROUND(H41/Q41,3)</f>
-        <v>53.5</v>
+        <v>56.5</v>
       </c>
       <c r="AA41" s="10">
         <f t="shared" ref="AA41" si="239">ROUND(I41/R41,3)</f>
-        <v>21.457999999999998</v>
+        <v>21.931999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4713,51 +4717,51 @@
       </c>
       <c r="B42" s="5">
         <f t="shared" ref="B42" si="240">D$2/D42</f>
-        <v>20.726298433635613</v>
+        <v>20.683669271904563</v>
       </c>
       <c r="C42" s="5">
         <f t="shared" ref="C42" si="241">D41/D42</f>
-        <v>1.005358615004122</v>
+        <v>1.0102838338132454</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" ref="D42" si="242">SUM(F42:H42)</f>
-        <v>24.259999999999998</v>
+        <v>24.310000000000002</v>
       </c>
       <c r="E42" s="9">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="F42" s="13">
-        <v>12.11</v>
+        <v>12.15</v>
       </c>
       <c r="G42" s="9">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
       <c r="H42" s="9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I42" s="10">
-        <v>12.6</v>
+        <v>12.69</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>50</v>
       </c>
       <c r="K42" s="5">
         <f t="shared" ref="K42" si="243">M$2/M42</f>
-        <v>42.999999999999993</v>
+        <v>42.561224489795912</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" ref="L42" si="244">M41/M42</f>
-        <v>1.0103092783505154</v>
+        <v>1</v>
       </c>
       <c r="M42" s="4">
         <f t="shared" ref="M42" si="245">SUM(O42:Q42)</f>
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="N42" s="9">
         <v>0.13</v>
       </c>
       <c r="O42" s="13">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="P42" s="9">
         <v>0.36</v>
@@ -4773,35 +4777,132 @@
       </c>
       <c r="T42" s="5">
         <f t="shared" ref="T42" si="246">ROUND(B42/K42,3)</f>
-        <v>0.48199999999999998</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="U42" s="5">
         <f t="shared" ref="U42" si="247">ROUND(C42/L42,3)</f>
-        <v>0.995</v>
+        <v>1.01</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" ref="V42" si="248">ROUND(D42/M42,3)</f>
-        <v>25.01</v>
+        <v>24.806000000000001</v>
       </c>
       <c r="W42" s="18">
         <f t="shared" ref="W42" si="249">ROUND(E42/N42,3)</f>
-        <v>9.6920000000000002</v>
+        <v>9.8460000000000001</v>
       </c>
       <c r="X42" s="13">
         <f t="shared" ref="X42" si="250">ROUND(F42/O42,3)</f>
-        <v>20.524999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="Y42" s="9">
         <f t="shared" ref="Y42" si="251">ROUND(G42/P42,3)</f>
-        <v>30.806000000000001</v>
+        <v>30.777999999999999</v>
       </c>
       <c r="Z42" s="9">
         <f t="shared" ref="Z42" si="252">ROUND(H42/Q42,3)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA42" s="10">
         <f t="shared" ref="AA42" si="253">ROUND(I42/R42,3)</f>
-        <v>21.724</v>
+        <v>21.879000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="5">
+        <f t="shared" ref="B43" si="254">D$2/D43</f>
+        <v>21.543273350471292</v>
+      </c>
+      <c r="C43" s="5">
+        <f t="shared" ref="C43" si="255">D42/D43</f>
+        <v>1.0415595544130249</v>
+      </c>
+      <c r="D43" s="4">
+        <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
+        <v>23.34</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.33</v>
+      </c>
+      <c r="F43" s="13">
+        <v>11</v>
+      </c>
+      <c r="G43" s="9">
+        <v>11.25</v>
+      </c>
+      <c r="H43" s="9">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I43" s="10">
+        <v>12.87</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K43" s="5">
+        <f t="shared" ref="K43" si="257">M$2/M43</f>
+        <v>42.561224489795912</v>
+      </c>
+      <c r="L43" s="5">
+        <f t="shared" ref="L43" si="258">M42/M43</f>
+        <v>1</v>
+      </c>
+      <c r="M43" s="4">
+        <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
+        <v>0.98</v>
+      </c>
+      <c r="N43" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O43" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="P43" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R43" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S43" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="T43" s="5">
+        <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="U43" s="5">
+        <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
+        <v>1.042</v>
+      </c>
+      <c r="V43" s="4">
+        <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
+        <v>23.815999999999999</v>
+      </c>
+      <c r="W43" s="18">
+        <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
+        <v>9.5</v>
+      </c>
+      <c r="X43" s="13">
+        <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
+        <v>18.332999999999998</v>
+      </c>
+      <c r="Y43" s="9">
+        <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
+        <v>31.25</v>
+      </c>
+      <c r="Z43" s="9">
+        <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
+        <v>54.5</v>
+      </c>
+      <c r="AA43" s="10">
+        <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
+        <v>22.19</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49700552-7753-41A0-8CFE-23143EDEDC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A408EA-158E-48BB-8AD4-AA6C7F929FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
   <si>
     <t>H23</t>
   </si>
@@ -213,6 +213,10 @@
   </si>
   <si>
     <t>H63</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H64</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -735,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4328,30 +4332,30 @@
       </c>
       <c r="B38" s="5">
         <f t="shared" si="193"/>
-        <v>20.291364003228406</v>
+        <v>20.217933252915159</v>
       </c>
       <c r="C38" s="5">
         <f t="shared" si="194"/>
-        <v>0.98506860371267146</v>
+        <v>0.98150381986328916</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="195"/>
-        <v>24.78</v>
+        <v>24.869999999999997</v>
       </c>
       <c r="E38" s="13">
-        <v>144.26</v>
+        <v>144.19999999999999</v>
       </c>
       <c r="F38" s="18">
-        <v>12.58</v>
+        <v>12.67</v>
       </c>
       <c r="G38" s="18">
-        <v>11.13</v>
+        <v>11.12</v>
       </c>
       <c r="H38" s="18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I38" s="19">
-        <v>13.04</v>
+        <v>13</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>46</v>
@@ -4369,7 +4373,7 @@
         <v>1.04</v>
       </c>
       <c r="N38" s="13">
-        <v>6.81</v>
+        <v>7.02</v>
       </c>
       <c r="O38" s="18">
         <v>0.6</v>
@@ -4381,42 +4385,42 @@
         <v>0.02</v>
       </c>
       <c r="R38" s="19">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="S38" s="20" t="s">
         <v>46</v>
       </c>
       <c r="T38" s="5">
         <f t="shared" ref="T38" si="196">ROUND(B38/K38,3)</f>
-        <v>0.50600000000000001</v>
+        <v>0.504</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" ref="U38" si="197">ROUND(C38/L38,3)</f>
-        <v>0.92300000000000004</v>
+        <v>0.92</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" ref="V38" si="198">ROUND(D38/M38,3)</f>
-        <v>23.827000000000002</v>
+        <v>23.913</v>
       </c>
       <c r="W38" s="13">
         <f t="shared" ref="W38" si="199">ROUND(E38/N38,3)</f>
-        <v>21.184000000000001</v>
+        <v>20.541</v>
       </c>
       <c r="X38" s="18">
         <f t="shared" ref="X38" si="200">ROUND(F38/O38,3)</f>
-        <v>20.966999999999999</v>
+        <v>21.117000000000001</v>
       </c>
       <c r="Y38" s="18">
         <f t="shared" ref="Y38" si="201">ROUND(G38/P38,3)</f>
-        <v>26.5</v>
+        <v>26.475999999999999</v>
       </c>
       <c r="Z38" s="18">
         <f t="shared" ref="Z38" si="202">ROUND(H38/Q38,3)</f>
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="AA38" s="19">
         <f t="shared" ref="AA38" si="203">ROUND(I38/R38,3)</f>
-        <v>21.032</v>
+        <v>21.311</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4425,30 +4429,30 @@
       </c>
       <c r="B39" s="5">
         <f t="shared" ref="B39" si="204">D$2/D39</f>
-        <v>20.531645569620252</v>
+        <v>20.777685950413222</v>
       </c>
       <c r="C39" s="5">
         <f t="shared" ref="C39" si="205">D38/D39</f>
-        <v>1.0118415679869335</v>
+        <v>1.027685950413223</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" ref="D39" si="206">SUM(F39:H39)</f>
-        <v>24.49</v>
+        <v>24.2</v>
       </c>
       <c r="E39" s="13">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="F39" s="9">
-        <v>12.5</v>
+        <v>12.11</v>
       </c>
       <c r="G39" s="9">
-        <v>10.94</v>
+        <v>11.02</v>
       </c>
       <c r="H39" s="9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I39" s="10">
-        <v>12.59</v>
+        <v>12.65</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>47</v>
@@ -4478,42 +4482,42 @@
         <v>0.02</v>
       </c>
       <c r="R39" s="10">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="S39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="T39" s="5">
         <f t="shared" ref="T39" si="207">ROUND(B39/K39,3)</f>
-        <v>0.51200000000000001</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" ref="U39" si="208">ROUND(C39/L39,3)</f>
-        <v>1.012</v>
+        <v>1.028</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" ref="V39" si="209">ROUND(D39/M39,3)</f>
-        <v>23.547999999999998</v>
+        <v>23.268999999999998</v>
       </c>
       <c r="W39" s="13">
         <f t="shared" ref="W39" si="210">ROUND(E39/N39,3)</f>
-        <v>3.7839999999999998</v>
+        <v>4.1890000000000001</v>
       </c>
       <c r="X39" s="9">
         <f t="shared" ref="X39" si="211">ROUND(F39/O39,3)</f>
-        <v>20.832999999999998</v>
+        <v>20.183</v>
       </c>
       <c r="Y39" s="9">
         <f t="shared" ref="Y39" si="212">ROUND(G39/P39,3)</f>
-        <v>26.047999999999998</v>
+        <v>26.238</v>
       </c>
       <c r="Z39" s="9">
         <f t="shared" ref="Z39" si="213">ROUND(H39/Q39,3)</f>
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="AA39" s="10">
         <f t="shared" ref="AA39" si="214">ROUND(I39/R39,3)</f>
-        <v>20.306000000000001</v>
+        <v>20.738</v>
       </c>
     </row>
     <row r="40" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4522,51 +4526,51 @@
       </c>
       <c r="B40" s="5">
         <f t="shared" ref="B40:B41" si="215">D$2/D40</f>
-        <v>20.193574297188754</v>
+        <v>20.64121510673235</v>
       </c>
       <c r="C40" s="5">
         <f t="shared" ref="C40:C41" si="216">D39/D40</f>
-        <v>0.98353413654618471</v>
+        <v>0.99343185550082114</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" ref="D40:D41" si="217">SUM(F40:H40)</f>
-        <v>24.9</v>
+        <v>24.359999999999996</v>
       </c>
       <c r="E40" s="13">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="F40" s="18">
-        <v>12.68</v>
+        <v>12.2</v>
       </c>
       <c r="G40" s="18">
-        <v>11.15</v>
+        <v>11.1</v>
       </c>
       <c r="H40" s="18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I40" s="19">
-        <v>12.62</v>
+        <v>12.74</v>
       </c>
       <c r="J40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="K40" s="5">
         <f t="shared" ref="K40" si="218">M$2/M40</f>
-        <v>40.105769230769226</v>
+        <v>39.723809523809514</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" ref="L40" si="219">M39/M40</f>
-        <v>1</v>
+        <v>0.99047619047619051</v>
       </c>
       <c r="M40" s="4">
         <f t="shared" ref="M40" si="220">SUM(O40:Q40)</f>
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N40" s="13">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="O40" s="18">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="P40" s="18">
         <v>0.42</v>
@@ -4575,42 +4579,42 @@
         <v>0.02</v>
       </c>
       <c r="R40" s="19">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="S40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="T40" s="5">
         <f t="shared" ref="T40" si="221">ROUND(B40/K40,3)</f>
-        <v>0.504</v>
+        <v>0.52</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" ref="U40" si="222">ROUND(C40/L40,3)</f>
-        <v>0.98399999999999999</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" ref="V40" si="223">ROUND(D40/M40,3)</f>
-        <v>23.942</v>
+        <v>23.2</v>
       </c>
       <c r="W40" s="13">
         <f t="shared" ref="W40" si="224">ROUND(E40/N40,3)</f>
-        <v>6.7140000000000004</v>
+        <v>6.8</v>
       </c>
       <c r="X40" s="18">
         <f t="shared" ref="X40" si="225">ROUND(F40/O40,3)</f>
-        <v>21.132999999999999</v>
+        <v>20</v>
       </c>
       <c r="Y40" s="18">
         <f t="shared" ref="Y40" si="226">ROUND(G40/P40,3)</f>
-        <v>26.547999999999998</v>
+        <v>26.428999999999998</v>
       </c>
       <c r="Z40" s="18">
         <f t="shared" ref="Z40" si="227">ROUND(H40/Q40,3)</f>
-        <v>53.5</v>
+        <v>53</v>
       </c>
       <c r="AA40" s="19">
         <f t="shared" ref="AA40" si="228">ROUND(I40/R40,3)</f>
-        <v>20.689</v>
+        <v>20.547999999999998</v>
       </c>
       <c r="AB40" s="20"/>
     </row>
@@ -4620,51 +4624,51 @@
       </c>
       <c r="B41" s="5">
         <f t="shared" si="215"/>
-        <v>20.473127035830618</v>
+        <v>20.489812550937245</v>
       </c>
       <c r="C41" s="5">
         <f t="shared" si="216"/>
-        <v>1.013843648208469</v>
+        <v>0.99266503667481654</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="217"/>
-        <v>24.56</v>
+        <v>24.54</v>
       </c>
       <c r="E41" s="13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="F41" s="9">
-        <v>12.26</v>
+        <v>12.24</v>
       </c>
       <c r="G41" s="9">
-        <v>11.17</v>
+        <v>11.19</v>
       </c>
       <c r="H41" s="9">
-        <v>1.1299999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="I41" s="10">
-        <v>12.94</v>
+        <v>12.92</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>49</v>
       </c>
       <c r="K41" s="5">
         <f t="shared" ref="K41" si="229">M$2/M41</f>
-        <v>42.561224489795912</v>
+        <v>42.131313131313128</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" ref="L41" si="230">M40/M41</f>
-        <v>1.0612244897959184</v>
+        <v>1.0606060606060606</v>
       </c>
       <c r="M41" s="4">
         <f t="shared" ref="M41" si="231">SUM(O41:Q41)</f>
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="N41" s="13">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O41" s="9">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="P41" s="9">
         <v>0.36</v>
@@ -4673,42 +4677,42 @@
         <v>0.02</v>
       </c>
       <c r="R41" s="10">
-        <v>0.59</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="S41" s="20" t="s">
         <v>49</v>
       </c>
       <c r="T41" s="5">
         <f t="shared" ref="T41" si="232">ROUND(B41/K41,3)</f>
-        <v>0.48099999999999998</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" ref="U41" si="233">ROUND(C41/L41,3)</f>
-        <v>0.95499999999999996</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" ref="V41" si="234">ROUND(D41/M41,3)</f>
-        <v>25.061</v>
+        <v>24.788</v>
       </c>
       <c r="W41" s="13">
         <f t="shared" ref="W41" si="235">ROUND(E41/N41,3)</f>
-        <v>9.8460000000000001</v>
+        <v>9.0709999999999997</v>
       </c>
       <c r="X41" s="9">
         <f t="shared" ref="X41" si="236">ROUND(F41/O41,3)</f>
-        <v>20.433</v>
+        <v>20.065999999999999</v>
       </c>
       <c r="Y41" s="9">
         <f t="shared" ref="Y41" si="237">ROUND(G41/P41,3)</f>
-        <v>31.027999999999999</v>
+        <v>31.082999999999998</v>
       </c>
       <c r="Z41" s="9">
         <f t="shared" ref="Z41" si="238">ROUND(H41/Q41,3)</f>
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="AA41" s="10">
         <f t="shared" ref="AA41" si="239">ROUND(I41/R41,3)</f>
-        <v>21.931999999999999</v>
+        <v>22.667000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4717,37 +4721,37 @@
       </c>
       <c r="B42" s="5">
         <f t="shared" ref="B42" si="240">D$2/D42</f>
-        <v>20.683669271904563</v>
+        <v>20.23420523138833</v>
       </c>
       <c r="C42" s="5">
         <f t="shared" ref="C42" si="241">D41/D42</f>
-        <v>1.0102838338132454</v>
+        <v>0.98752515090543269</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" ref="D42" si="242">SUM(F42:H42)</f>
-        <v>24.310000000000002</v>
+        <v>24.849999999999998</v>
       </c>
       <c r="E42" s="9">
         <v>1.28</v>
       </c>
       <c r="F42" s="13">
-        <v>12.15</v>
+        <v>12.59</v>
       </c>
       <c r="G42" s="9">
-        <v>11.08</v>
+        <v>11.17</v>
       </c>
       <c r="H42" s="9">
-        <v>1.08</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I42" s="10">
-        <v>12.69</v>
+        <v>12.91</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>50</v>
       </c>
       <c r="K42" s="5">
         <f t="shared" ref="K42" si="243">M$2/M42</f>
-        <v>42.561224489795912</v>
+        <v>42.131313131313128</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" ref="L42" si="244">M41/M42</f>
@@ -4755,13 +4759,13 @@
       </c>
       <c r="M42" s="4">
         <f t="shared" ref="M42" si="245">SUM(O42:Q42)</f>
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="N42" s="9">
         <v>0.13</v>
       </c>
       <c r="O42" s="13">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="P42" s="9">
         <v>0.36</v>
@@ -4770,22 +4774,22 @@
         <v>0.02</v>
       </c>
       <c r="R42" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="S42" s="12" t="s">
         <v>50</v>
       </c>
       <c r="T42" s="5">
         <f t="shared" ref="T42" si="246">ROUND(B42/K42,3)</f>
-        <v>0.48599999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="U42" s="5">
         <f t="shared" ref="U42" si="247">ROUND(C42/L42,3)</f>
-        <v>1.01</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" ref="V42" si="248">ROUND(D42/M42,3)</f>
-        <v>24.806000000000001</v>
+        <v>25.100999999999999</v>
       </c>
       <c r="W42" s="18">
         <f t="shared" ref="W42" si="249">ROUND(E42/N42,3)</f>
@@ -4793,19 +4797,19 @@
       </c>
       <c r="X42" s="13">
         <f t="shared" ref="X42" si="250">ROUND(F42/O42,3)</f>
-        <v>20.25</v>
+        <v>20.638999999999999</v>
       </c>
       <c r="Y42" s="9">
         <f t="shared" ref="Y42" si="251">ROUND(G42/P42,3)</f>
-        <v>30.777999999999999</v>
+        <v>31.027999999999999</v>
       </c>
       <c r="Z42" s="9">
         <f t="shared" ref="Z42" si="252">ROUND(H42/Q42,3)</f>
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="AA42" s="10">
         <f t="shared" ref="AA42" si="253">ROUND(I42/R42,3)</f>
-        <v>21.879000000000001</v>
+        <v>22.649000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4814,51 +4818,51 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.543273350471292</v>
+        <v>21.890291684806268</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0415595544130249</v>
+        <v>1.0818458859381801</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>23.34</v>
+        <v>22.97</v>
       </c>
       <c r="E43" s="9">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="F43" s="13">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="G43" s="9">
-        <v>11.25</v>
+        <v>11.06</v>
       </c>
       <c r="H43" s="9">
-        <v>1.0900000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="I43" s="10">
-        <v>12.87</v>
+        <v>12.62</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
-        <v>42.561224489795912</v>
+        <v>42.999999999999993</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" ref="L43" si="258">M42/M43</f>
-        <v>1</v>
+        <v>1.0206185567010309</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N43" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="O43" s="13">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="P43" s="9">
         <v>0.36</v>
@@ -4867,42 +4871,139 @@
         <v>0.02</v>
       </c>
       <c r="R43" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.50600000000000001</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.042</v>
+        <v>1.06</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.815999999999999</v>
+        <v>23.68</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>9.5</v>
+        <v>8.4670000000000005</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.332999999999998</v>
+        <v>18.356000000000002</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>31.25</v>
+        <v>30.722000000000001</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>22.19</v>
+        <v>22.14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="2">
+        <f t="shared" ref="B44" si="268">D$2/D44</f>
+        <v>22.337627721012879</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" ref="C44" si="269">D43/D44</f>
+        <v>1.020435362061306</v>
+      </c>
+      <c r="D44" s="6">
+        <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
+        <v>22.51</v>
+      </c>
+      <c r="E44" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="F44" s="9">
+        <v>10.8</v>
+      </c>
+      <c r="G44" s="9">
+        <v>11.05</v>
+      </c>
+      <c r="H44" s="13">
+        <v>0.66</v>
+      </c>
+      <c r="I44" s="10">
+        <v>12.62</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K44" s="2">
+        <f t="shared" ref="K44" si="271">M$2/M44</f>
+        <v>42.131313131313128</v>
+      </c>
+      <c r="L44" s="2">
+        <f t="shared" ref="L44" si="272">M43/M44</f>
+        <v>0.97979797979797978</v>
+      </c>
+      <c r="M44" s="6">
+        <f t="shared" ref="M44" si="273">SUM(O44:Q44)</f>
+        <v>0.99</v>
+      </c>
+      <c r="N44" s="9">
+        <v>0.11</v>
+      </c>
+      <c r="O44" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="P44" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="Q44" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="R44" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S44" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="T44" s="2">
+        <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
+        <v>0.53</v>
+      </c>
+      <c r="U44" s="2">
+        <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
+        <v>1.0409999999999999</v>
+      </c>
+      <c r="V44" s="6">
+        <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
+        <v>22.736999999999998</v>
+      </c>
+      <c r="W44" s="9">
+        <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
+        <v>9.5449999999999999</v>
+      </c>
+      <c r="X44" s="9">
+        <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
+        <v>18</v>
+      </c>
+      <c r="Y44" s="9">
+        <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
+        <v>30.693999999999999</v>
+      </c>
+      <c r="Z44" s="13">
+        <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
+        <v>22</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
+        <v>21.759</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A408EA-158E-48BB-8AD4-AA6C7F929FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461B4999-E0C8-4451-8630-81ECE0536D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="54">
   <si>
     <t>H23</t>
   </si>
@@ -217,6 +217,10 @@
   </si>
   <si>
     <t>H64</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H65</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4818,51 +4822,51 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.890291684806268</v>
+        <v>21.617368873602747</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0818458859381801</v>
+        <v>1.0683576956147891</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>22.97</v>
+        <v>23.26</v>
       </c>
       <c r="E43" s="9">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="F43" s="13">
-        <v>10.83</v>
+        <v>10.97</v>
       </c>
       <c r="G43" s="9">
-        <v>11.06</v>
+        <v>11.15</v>
       </c>
       <c r="H43" s="9">
-        <v>1.08</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="I43" s="10">
-        <v>12.62</v>
+        <v>12.81</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
-        <v>42.999999999999993</v>
+        <v>42.561224489795912</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" ref="L43" si="258">M42/M43</f>
-        <v>1.0206185567010309</v>
+        <v>1.010204081632653</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="N43" s="9">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="O43" s="13">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="P43" s="9">
         <v>0.36</v>
@@ -4871,42 +4875,42 @@
         <v>0.02</v>
       </c>
       <c r="R43" s="10">
-        <v>0.56999999999999995</v>
+        <v>0.59</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.50900000000000001</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.06</v>
+        <v>1.0580000000000001</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.68</v>
+        <v>23.734999999999999</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>8.4670000000000005</v>
+        <v>8.4090000000000007</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.356000000000002</v>
+        <v>18.283000000000001</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>30.722000000000001</v>
+        <v>30.972000000000001</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>22.14</v>
+        <v>21.712</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4915,48 +4919,48 @@
       </c>
       <c r="B44" s="2">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>22.337627721012879</v>
+        <v>21.986007870572802</v>
       </c>
       <c r="C44" s="2">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.020435362061306</v>
+        <v>1.0170529077393968</v>
       </c>
       <c r="D44" s="6">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.51</v>
+        <v>22.869999999999997</v>
       </c>
       <c r="E44" s="9">
         <v>1.05</v>
       </c>
       <c r="F44" s="9">
-        <v>10.8</v>
+        <v>11.04</v>
       </c>
       <c r="G44" s="9">
-        <v>11.05</v>
+        <v>11.18</v>
       </c>
       <c r="H44" s="13">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I44" s="10">
-        <v>12.62</v>
+        <v>12.77</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="K44" s="2">
-        <f t="shared" ref="K44" si="271">M$2/M44</f>
-        <v>42.131313131313128</v>
+        <f t="shared" ref="K44:K45" si="271">M$2/M44</f>
+        <v>41.709999999999994</v>
       </c>
       <c r="L44" s="2">
-        <f t="shared" ref="L44" si="272">M43/M44</f>
-        <v>0.97979797979797978</v>
+        <f t="shared" ref="L44:L45" si="272">M43/M44</f>
+        <v>0.98</v>
       </c>
       <c r="M44" s="6">
-        <f t="shared" ref="M44" si="273">SUM(O44:Q44)</f>
-        <v>0.99</v>
+        <f t="shared" ref="M44:M45" si="273">SUM(O44:Q44)</f>
+        <v>1</v>
       </c>
       <c r="N44" s="9">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="O44" s="9">
         <v>0.6</v>
@@ -4965,45 +4969,142 @@
         <v>0.36</v>
       </c>
       <c r="Q44" s="13">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="R44" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="T44" s="2">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.53</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="U44" s="2">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.0409999999999999</v>
+        <v>1.038</v>
       </c>
       <c r="V44" s="6">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>22.736999999999998</v>
+        <v>22.87</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>9.5449999999999999</v>
+        <v>4.5650000000000004</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>18</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
-        <v>30.693999999999999</v>
+        <v>31.056000000000001</v>
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>22</v>
+        <v>16.25</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>21.759</v>
+        <v>21.643999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="2">
+        <f t="shared" ref="B45" si="282">D$2/D45</f>
+        <v>23.662117647058821</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" ref="C45" si="283">D44/D45</f>
+        <v>1.076235294117647</v>
+      </c>
+      <c r="D45" s="6">
+        <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
+        <v>21.25</v>
+      </c>
+      <c r="E45" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F45" s="13">
+        <v>9.35</v>
+      </c>
+      <c r="G45" s="9">
+        <v>11.26</v>
+      </c>
+      <c r="H45" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="I45" s="10">
+        <v>13.55</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K45" s="2">
+        <f t="shared" si="271"/>
+        <v>46.344444444444434</v>
+      </c>
+      <c r="L45" s="2">
+        <f t="shared" si="272"/>
+        <v>1.1111111111111112</v>
+      </c>
+      <c r="M45" s="6">
+        <f t="shared" si="273"/>
+        <v>0.9</v>
+      </c>
+      <c r="N45" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="O45" s="13">
+        <v>0.51</v>
+      </c>
+      <c r="P45" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R45" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S45" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="T45" s="2">
+        <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="U45" s="2">
+        <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="V45" s="6">
+        <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
+        <v>23.611000000000001</v>
+      </c>
+      <c r="W45" s="9">
+        <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
+        <v>7.3330000000000002</v>
+      </c>
+      <c r="X45" s="13">
+        <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
+        <v>18.332999999999998</v>
+      </c>
+      <c r="Y45" s="9">
+        <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
+        <v>31.277999999999999</v>
+      </c>
+      <c r="Z45" s="9">
+        <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
+        <v>21.332999999999998</v>
+      </c>
+      <c r="AA45" s="10">
+        <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
+        <v>23.361999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461B4999-E0C8-4451-8630-81ECE0536D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23595F6D-2F55-4B7F-9839-B7EEE936EA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="55">
   <si>
     <t>H23</t>
   </si>
@@ -221,6 +221,10 @@
   </si>
   <si>
     <t>H65</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H66</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4822,51 +4826,51 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.617368873602747</v>
+        <v>21.909368191721128</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0683576956147891</v>
+        <v>1.0827886710239649</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>23.26</v>
+        <v>22.950000000000003</v>
       </c>
       <c r="E43" s="9">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="F43" s="13">
-        <v>10.97</v>
+        <v>10.8</v>
       </c>
       <c r="G43" s="9">
-        <v>11.15</v>
+        <v>11.07</v>
       </c>
       <c r="H43" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I43" s="10">
-        <v>12.81</v>
+        <v>12.62</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
-        <v>42.561224489795912</v>
+        <v>43.447916666666664</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" ref="L43" si="258">M42/M43</f>
-        <v>1.010204081632653</v>
+        <v>1.03125</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="N43" s="9">
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O43" s="13">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P43" s="9">
         <v>0.36</v>
@@ -4875,42 +4879,42 @@
         <v>0.02</v>
       </c>
       <c r="R43" s="10">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.50800000000000001</v>
+        <v>0.504</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.0580000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.734999999999999</v>
+        <v>23.905999999999999</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>8.4090000000000007</v>
+        <v>9.4290000000000003</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.283000000000001</v>
+        <v>18.620999999999999</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>30.972000000000001</v>
+        <v>30.75</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>21.712</v>
+        <v>21.759</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4919,48 +4923,48 @@
       </c>
       <c r="B44" s="2">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>21.986007870572802</v>
+        <v>22.337627721012879</v>
       </c>
       <c r="C44" s="2">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.0170529077393968</v>
+        <v>1.0195468680586406</v>
       </c>
       <c r="D44" s="6">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.869999999999997</v>
+        <v>22.51</v>
       </c>
       <c r="E44" s="9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="F44" s="9">
-        <v>11.04</v>
+        <v>10.78</v>
       </c>
       <c r="G44" s="9">
-        <v>11.18</v>
+        <v>11.07</v>
       </c>
       <c r="H44" s="13">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I44" s="10">
-        <v>12.77</v>
+        <v>12.8</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="K44" s="2">
-        <f t="shared" ref="K44:K45" si="271">M$2/M44</f>
-        <v>41.709999999999994</v>
+        <f t="shared" ref="K44:K46" si="271">M$2/M44</f>
+        <v>42.131313131313128</v>
       </c>
       <c r="L44" s="2">
-        <f t="shared" ref="L44:L45" si="272">M43/M44</f>
-        <v>0.98</v>
+        <f t="shared" ref="L44:L46" si="272">M43/M44</f>
+        <v>0.96969696969696972</v>
       </c>
       <c r="M44" s="6">
-        <f t="shared" ref="M44:M45" si="273">SUM(O44:Q44)</f>
-        <v>1</v>
+        <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
+        <v>0.99</v>
       </c>
       <c r="N44" s="9">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="O44" s="9">
         <v>0.6</v>
@@ -4969,45 +4973,45 @@
         <v>0.36</v>
       </c>
       <c r="Q44" s="13">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R44" s="10">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="T44" s="2">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.52700000000000002</v>
+        <v>0.53</v>
       </c>
       <c r="U44" s="2">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.038</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="V44" s="6">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>22.87</v>
+        <v>22.736999999999998</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>4.5650000000000004</v>
+        <v>9.3640000000000008</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>18.399999999999999</v>
+        <v>17.966999999999999</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
-        <v>31.056000000000001</v>
+        <v>30.75</v>
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>16.25</v>
+        <v>22</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>21.643999999999998</v>
+        <v>22.068999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5016,51 +5020,51 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45" si="282">D$2/D45</f>
-        <v>23.662117647058821</v>
+        <v>24.5517578125</v>
       </c>
       <c r="C45" s="2">
         <f t="shared" ref="C45" si="283">D44/D45</f>
-        <v>1.076235294117647</v>
+        <v>1.0991210937500002</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
-        <v>21.25</v>
+        <v>20.479999999999997</v>
       </c>
       <c r="E45" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="F45" s="13">
-        <v>9.35</v>
+        <v>8.74</v>
       </c>
       <c r="G45" s="9">
-        <v>11.26</v>
+        <v>11.09</v>
       </c>
       <c r="H45" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I45" s="10">
-        <v>13.55</v>
+        <v>12.56</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="2">
         <f t="shared" si="271"/>
-        <v>46.344444444444434</v>
+        <v>45.336956521739118</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="272"/>
-        <v>1.1111111111111112</v>
+        <v>1.076086956521739</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="273"/>
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="N45" s="9">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="O45" s="13">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="P45" s="9">
         <v>0.36</v>
@@ -5076,35 +5080,132 @@
       </c>
       <c r="T45" s="2">
         <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
-        <v>0.51100000000000001</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="U45" s="2">
         <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
-        <v>0.96899999999999997</v>
+        <v>1.0209999999999999</v>
       </c>
       <c r="V45" s="6">
         <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
-        <v>23.611000000000001</v>
+        <v>22.260999999999999</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
-        <v>7.3330000000000002</v>
+        <v>9.6359999999999992</v>
       </c>
       <c r="X45" s="13">
         <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
-        <v>18.332999999999998</v>
+        <v>16.491</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
-        <v>31.277999999999999</v>
+        <v>30.806000000000001</v>
       </c>
       <c r="Z45" s="9">
         <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
-        <v>23.361999999999998</v>
+        <v>21.655000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="5">
+        <f t="shared" ref="B46" si="293">D$2/D46</f>
+        <v>24.255668113844667</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="shared" ref="C46" si="294">D45/D46</f>
+        <v>0.98794018330921352</v>
+      </c>
+      <c r="D46" s="4">
+        <f t="shared" ref="D46" si="295">SUM(F46:H46)</f>
+        <v>20.73</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="F46" s="9">
+        <v>8.86</v>
+      </c>
+      <c r="G46" s="9">
+        <v>11.18</v>
+      </c>
+      <c r="H46" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="I46" s="14">
+        <v>9.92</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K46" s="5">
+        <f t="shared" si="271"/>
+        <v>45.835164835164825</v>
+      </c>
+      <c r="L46" s="5">
+        <f t="shared" si="272"/>
+        <v>1.0109890109890109</v>
+      </c>
+      <c r="M46" s="4">
+        <f t="shared" si="273"/>
+        <v>0.91</v>
+      </c>
+      <c r="N46" s="9">
+        <v>0.11</v>
+      </c>
+      <c r="O46" s="9">
+        <v>0.52</v>
+      </c>
+      <c r="P46" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R46" s="14">
+        <v>0.34</v>
+      </c>
+      <c r="S46" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="T46" s="5">
+        <f t="shared" ref="T46" si="296">ROUND(B46/K46,3)</f>
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="U46" s="5">
+        <f t="shared" ref="U46" si="297">ROUND(C46/L46,3)</f>
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="V46" s="4">
+        <f t="shared" ref="V46" si="298">ROUND(D46/M46,3)</f>
+        <v>22.78</v>
+      </c>
+      <c r="W46" s="9">
+        <f t="shared" ref="W46" si="299">ROUND(E46/N46,3)</f>
+        <v>9.1820000000000004</v>
+      </c>
+      <c r="X46" s="9">
+        <f t="shared" ref="X46" si="300">ROUND(F46/O46,3)</f>
+        <v>17.038</v>
+      </c>
+      <c r="Y46" s="9">
+        <f t="shared" ref="Y46" si="301">ROUND(G46/P46,3)</f>
+        <v>31.056000000000001</v>
+      </c>
+      <c r="Z46" s="9">
+        <f t="shared" ref="Z46" si="302">ROUND(H46/Q46,3)</f>
+        <v>23</v>
+      </c>
+      <c r="AA46" s="14">
+        <f t="shared" ref="AA46" si="303">ROUND(I46/R46,3)</f>
+        <v>29.175999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23595F6D-2F55-4B7F-9839-B7EEE936EA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5660C37-40F7-4449-8A1E-12BED4730EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="57">
   <si>
     <t>H23</t>
   </si>
@@ -225,6 +225,14 @@
   </si>
   <si>
     <t>H66</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H67</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H67</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -747,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB46"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4826,51 +4834,51 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.909368191721128</v>
+        <v>21.497221034630179</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0827886710239649</v>
+        <v>1.062419837537409</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>22.950000000000003</v>
+        <v>23.39</v>
       </c>
       <c r="E43" s="9">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="F43" s="13">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G43" s="9">
-        <v>11.07</v>
+        <v>11.3</v>
       </c>
       <c r="H43" s="9">
-        <v>1.08</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I43" s="10">
-        <v>12.62</v>
+        <v>12.89</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
-        <v>43.447916666666664</v>
+        <v>42.131313131313128</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" ref="L43" si="258">M42/M43</f>
-        <v>1.03125</v>
+        <v>1</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="N43" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="O43" s="13">
-        <v>0.57999999999999996</v>
+        <v>0.61</v>
       </c>
       <c r="P43" s="9">
         <v>0.36</v>
@@ -4879,42 +4887,42 @@
         <v>0.02</v>
       </c>
       <c r="R43" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.504</v>
+        <v>0.51</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.05</v>
+        <v>1.0620000000000001</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.905999999999999</v>
+        <v>23.626000000000001</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>9.4290000000000003</v>
+        <v>9.0670000000000002</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.620999999999999</v>
+        <v>18.033000000000001</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>30.75</v>
+        <v>31.388999999999999</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>21.759</v>
+        <v>21.847000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4923,30 +4931,30 @@
       </c>
       <c r="B44" s="2">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>22.337627721012879</v>
+        <v>22.229000884173299</v>
       </c>
       <c r="C44" s="2">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.0195468680586406</v>
+        <v>1.0340406719717066</v>
       </c>
       <c r="D44" s="6">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.51</v>
+        <v>22.619999999999997</v>
       </c>
       <c r="E44" s="9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="F44" s="9">
-        <v>10.78</v>
+        <v>10.82</v>
       </c>
       <c r="G44" s="9">
-        <v>11.07</v>
+        <v>11.15</v>
       </c>
       <c r="H44" s="13">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I44" s="10">
-        <v>12.8</v>
+        <v>12.65</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
@@ -4957,14 +4965,14 @@
       </c>
       <c r="L44" s="2">
         <f t="shared" ref="L44:L46" si="272">M43/M44</f>
-        <v>0.96969696969696972</v>
+        <v>1</v>
       </c>
       <c r="M44" s="6">
         <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
         <v>0.99</v>
       </c>
       <c r="N44" s="9">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O44" s="9">
         <v>0.6</v>
@@ -4983,35 +4991,35 @@
       </c>
       <c r="T44" s="2">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.53</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="U44" s="2">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.0509999999999999</v>
+        <v>1.034</v>
       </c>
       <c r="V44" s="6">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>22.736999999999998</v>
+        <v>22.847999999999999</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>9.3640000000000008</v>
+        <v>10.6</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>17.966999999999999</v>
+        <v>18.033000000000001</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
-        <v>30.75</v>
+        <v>30.972000000000001</v>
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>22</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>22.068999999999999</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5020,45 +5028,45 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45" si="282">D$2/D45</f>
-        <v>24.5517578125</v>
+        <v>24.527804878048777</v>
       </c>
       <c r="C45" s="2">
         <f t="shared" ref="C45" si="283">D44/D45</f>
-        <v>1.0991210937500002</v>
+        <v>1.1034146341463413</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
-        <v>20.479999999999997</v>
+        <v>20.5</v>
       </c>
       <c r="E45" s="9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="F45" s="13">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="G45" s="9">
         <v>11.09</v>
       </c>
       <c r="H45" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I45" s="10">
-        <v>12.56</v>
+        <v>12.65</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="2">
         <f t="shared" si="271"/>
-        <v>45.336956521739118</v>
+        <v>44.849462365591386</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="272"/>
-        <v>1.076086956521739</v>
+        <v>1.064516129032258</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="273"/>
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="N45" s="9">
         <v>0.11</v>
@@ -5067,48 +5075,48 @@
         <v>0.53</v>
       </c>
       <c r="P45" s="9">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="Q45" s="9">
         <v>0.03</v>
       </c>
       <c r="R45" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="T45" s="2">
         <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
-        <v>0.54200000000000004</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="U45" s="2">
         <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
-        <v>1.0209999999999999</v>
+        <v>1.0369999999999999</v>
       </c>
       <c r="V45" s="6">
         <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
-        <v>22.260999999999999</v>
+        <v>22.042999999999999</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
-        <v>9.6359999999999992</v>
+        <v>9.4550000000000001</v>
       </c>
       <c r="X45" s="13">
         <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
-        <v>16.491</v>
+        <v>16.547000000000001</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
-        <v>30.806000000000001</v>
+        <v>29.972999999999999</v>
       </c>
       <c r="Z45" s="9">
         <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
-        <v>21.655000000000001</v>
+        <v>21.440999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5117,51 +5125,51 @@
       </c>
       <c r="B46" s="5">
         <f t="shared" ref="B46" si="293">D$2/D46</f>
-        <v>24.255668113844667</v>
+        <v>24.587775061124688</v>
       </c>
       <c r="C46" s="5">
         <f t="shared" ref="C46" si="294">D45/D46</f>
-        <v>0.98794018330921352</v>
+        <v>1.002444987775061</v>
       </c>
       <c r="D46" s="4">
         <f t="shared" ref="D46" si="295">SUM(F46:H46)</f>
-        <v>20.73</v>
+        <v>20.450000000000003</v>
       </c>
       <c r="E46" s="9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="F46" s="9">
-        <v>8.86</v>
+        <v>8.73</v>
       </c>
       <c r="G46" s="9">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="H46" s="9">
-        <v>0.69</v>
+        <v>0.64</v>
       </c>
       <c r="I46" s="14">
-        <v>9.92</v>
+        <v>9.68</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="271"/>
-        <v>45.835164835164825</v>
+        <v>46.344444444444434</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="272"/>
-        <v>1.0109890109890109</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="M46" s="4">
         <f t="shared" si="273"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N46" s="9">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O46" s="9">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P46" s="9">
         <v>0.36</v>
@@ -5176,36 +5184,133 @@
         <v>54</v>
       </c>
       <c r="T46" s="5">
-        <f t="shared" ref="T46" si="296">ROUND(B46/K46,3)</f>
-        <v>0.52900000000000003</v>
+        <f t="shared" ref="T46:T47" si="296">ROUND(B46/K46,3)</f>
+        <v>0.53100000000000003</v>
       </c>
       <c r="U46" s="5">
-        <f t="shared" ref="U46" si="297">ROUND(C46/L46,3)</f>
-        <v>0.97699999999999998</v>
+        <f t="shared" ref="U46:U47" si="297">ROUND(C46/L46,3)</f>
+        <v>0.97</v>
       </c>
       <c r="V46" s="4">
-        <f t="shared" ref="V46" si="298">ROUND(D46/M46,3)</f>
-        <v>22.78</v>
+        <f t="shared" ref="V46:V47" si="298">ROUND(D46/M46,3)</f>
+        <v>22.722000000000001</v>
       </c>
       <c r="W46" s="9">
-        <f t="shared" ref="W46" si="299">ROUND(E46/N46,3)</f>
-        <v>9.1820000000000004</v>
+        <f t="shared" ref="W46:W47" si="299">ROUND(E46/N46,3)</f>
+        <v>10.3</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" ref="X46" si="300">ROUND(F46/O46,3)</f>
-        <v>17.038</v>
+        <f t="shared" ref="X46:X47" si="300">ROUND(F46/O46,3)</f>
+        <v>17.117999999999999</v>
       </c>
       <c r="Y46" s="9">
-        <f t="shared" ref="Y46" si="301">ROUND(G46/P46,3)</f>
-        <v>31.056000000000001</v>
+        <f t="shared" ref="Y46:Y47" si="301">ROUND(G46/P46,3)</f>
+        <v>30.777999999999999</v>
       </c>
       <c r="Z46" s="9">
-        <f t="shared" ref="Z46" si="302">ROUND(H46/Q46,3)</f>
-        <v>23</v>
+        <f t="shared" ref="Z46:Z47" si="302">ROUND(H46/Q46,3)</f>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA46" s="14">
         <f t="shared" ref="AA46" si="303">ROUND(I46/R46,3)</f>
-        <v>29.175999999999998</v>
+        <v>28.471</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="5">
+        <f t="shared" ref="B47" si="304">D$2/D47</f>
+        <v>25.040836653386453</v>
+      </c>
+      <c r="C47" s="5">
+        <f t="shared" ref="C47" si="305">D46/D47</f>
+        <v>1.0184262948207174</v>
+      </c>
+      <c r="D47" s="4">
+        <f t="shared" ref="D47" si="306">SUM(F47:H47)</f>
+        <v>20.079999999999998</v>
+      </c>
+      <c r="E47" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="F47" s="9">
+        <v>8.76</v>
+      </c>
+      <c r="G47" s="13">
+        <v>10.69</v>
+      </c>
+      <c r="H47" s="9">
+        <v>0.63</v>
+      </c>
+      <c r="I47" s="14">
+        <v>9.39</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K47" s="5">
+        <f t="shared" ref="K47" si="307">M$2/M47</f>
+        <v>47.397727272727266</v>
+      </c>
+      <c r="L47" s="5">
+        <f t="shared" ref="L47" si="308">M46/M47</f>
+        <v>1.0227272727272727</v>
+      </c>
+      <c r="M47" s="4">
+        <f t="shared" ref="M47" si="309">SUM(O47:Q47)</f>
+        <v>0.88</v>
+      </c>
+      <c r="N47" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="O47" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="P47" s="13">
+        <v>0.35</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R47" s="14">
+        <v>0.33</v>
+      </c>
+      <c r="S47" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="T47" s="5">
+        <f t="shared" ref="T47" si="310">ROUND(B47/K47,3)</f>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="U47" s="5">
+        <f t="shared" ref="U47" si="311">ROUND(C47/L47,3)</f>
+        <v>0.996</v>
+      </c>
+      <c r="V47" s="4">
+        <f t="shared" ref="V47" si="312">ROUND(D47/M47,3)</f>
+        <v>22.818000000000001</v>
+      </c>
+      <c r="W47" s="9">
+        <f t="shared" ref="W47" si="313">ROUND(E47/N47,3)</f>
+        <v>10.3</v>
+      </c>
+      <c r="X47" s="9">
+        <f t="shared" ref="X47" si="314">ROUND(F47/O47,3)</f>
+        <v>17.52</v>
+      </c>
+      <c r="Y47" s="13">
+        <f t="shared" ref="Y47" si="315">ROUND(G47/P47,3)</f>
+        <v>30.542999999999999</v>
+      </c>
+      <c r="Z47" s="9">
+        <f t="shared" ref="Z47" si="316">ROUND(H47/Q47,3)</f>
+        <v>21</v>
+      </c>
+      <c r="AA47" s="14">
+        <f t="shared" ref="AA47" si="317">ROUND(I47/R47,3)</f>
+        <v>28.454999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5660C37-40F7-4449-8A1E-12BED4730EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E063CBA1-EEA8-46EE-B07A-C9060EE07EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="58">
   <si>
     <t>H23</t>
   </si>
@@ -233,6 +233,10 @@
   </si>
   <si>
     <t>H67</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H68</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -755,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB47"/>
+  <dimension ref="A1:AB48"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4834,51 +4838,51 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.497221034630179</v>
+        <v>21.928477976450065</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.062419837537409</v>
+        <v>1.0837331007413868</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>23.39</v>
+        <v>22.929999999999996</v>
       </c>
       <c r="E43" s="9">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="F43" s="13">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="G43" s="9">
-        <v>11.3</v>
+        <v>11.04</v>
       </c>
       <c r="H43" s="9">
-        <v>1.0900000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I43" s="10">
-        <v>12.89</v>
+        <v>12.65</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
-        <v>42.131313131313128</v>
+        <v>43.447916666666664</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" ref="L43" si="258">M42/M43</f>
-        <v>1</v>
+        <v>1.03125</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="N43" s="9">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O43" s="13">
-        <v>0.61</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P43" s="9">
         <v>0.36</v>
@@ -4894,85 +4898,85 @@
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.0620000000000001</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.626000000000001</v>
+        <v>23.885000000000002</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>9.0670000000000002</v>
+        <v>9.5709999999999997</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.033000000000001</v>
+        <v>18.672000000000001</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>31.388999999999999</v>
+        <v>30.667000000000002</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>21.847000000000001</v>
+        <v>21.440999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="5">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>22.229000884173299</v>
-      </c>
-      <c r="C44" s="2">
+        <v>22.298004434589796</v>
+      </c>
+      <c r="C44" s="5">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.0340406719717066</v>
-      </c>
-      <c r="D44" s="6">
+        <v>1.0168514412416849</v>
+      </c>
+      <c r="D44" s="4">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.619999999999997</v>
+        <v>22.55</v>
       </c>
       <c r="E44" s="9">
         <v>1.06</v>
       </c>
       <c r="F44" s="9">
-        <v>10.82</v>
+        <v>10.86</v>
       </c>
       <c r="G44" s="9">
-        <v>11.15</v>
+        <v>11.06</v>
       </c>
       <c r="H44" s="13">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="I44" s="10">
-        <v>12.65</v>
+        <v>12.73</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="5">
         <f t="shared" ref="K44:K46" si="271">M$2/M44</f>
-        <v>42.131313131313128</v>
-      </c>
-      <c r="L44" s="2">
+        <v>41.709999999999994</v>
+      </c>
+      <c r="L44" s="5">
         <f t="shared" ref="L44:L46" si="272">M43/M44</f>
+        <v>0.96</v>
+      </c>
+      <c r="M44" s="4">
+        <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
         <v>1</v>
       </c>
-      <c r="M44" s="6">
-        <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
-        <v>0.99</v>
-      </c>
       <c r="N44" s="9">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="O44" s="9">
         <v>0.6</v>
@@ -4981,45 +4985,45 @@
         <v>0.36</v>
       </c>
       <c r="Q44" s="13">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="R44" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="T44" s="2">
+      <c r="T44" s="5">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.52800000000000002</v>
-      </c>
-      <c r="U44" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="U44" s="5">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.034</v>
-      </c>
-      <c r="V44" s="6">
+        <v>1.0589999999999999</v>
+      </c>
+      <c r="V44" s="4">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>22.847999999999999</v>
+        <v>22.55</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>10.6</v>
+        <v>9.6359999999999992</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>18.033000000000001</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
-        <v>30.972000000000001</v>
+        <v>30.722000000000001</v>
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>21.667000000000002</v>
+        <v>15.75</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>21.81</v>
+        <v>21.576000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5028,51 +5032,51 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45" si="282">D$2/D45</f>
-        <v>24.527804878048777</v>
+        <v>24.337850919651494</v>
       </c>
       <c r="C45" s="2">
         <f t="shared" ref="C45" si="283">D44/D45</f>
-        <v>1.1034146341463413</v>
+        <v>1.0914811229428847</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
-        <v>20.5</v>
+        <v>20.660000000000004</v>
       </c>
       <c r="E45" s="9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="F45" s="13">
-        <v>8.77</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="G45" s="9">
-        <v>11.09</v>
+        <v>11.14</v>
       </c>
       <c r="H45" s="9">
         <v>0.64</v>
       </c>
       <c r="I45" s="10">
-        <v>12.65</v>
+        <v>12.73</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="2">
         <f t="shared" si="271"/>
-        <v>44.849462365591386</v>
+        <v>45.336956521739118</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="272"/>
-        <v>1.064516129032258</v>
+        <v>1.0869565217391304</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="273"/>
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="N45" s="9">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O45" s="13">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="P45" s="9">
         <v>0.37</v>
@@ -5088,27 +5092,27 @@
       </c>
       <c r="T45" s="2">
         <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
-        <v>0.54700000000000004</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="U45" s="2">
         <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
-        <v>1.0369999999999999</v>
+        <v>1.004</v>
       </c>
       <c r="V45" s="6">
         <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
-        <v>22.042999999999999</v>
+        <v>22.457000000000001</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
-        <v>9.4550000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="X45" s="13">
         <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
-        <v>16.547000000000001</v>
+        <v>17.077000000000002</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
-        <v>29.972999999999999</v>
+        <v>30.108000000000001</v>
       </c>
       <c r="Z45" s="9">
         <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
@@ -5116,7 +5120,7 @@
       </c>
       <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
-        <v>21.440999999999999</v>
+        <v>21.576000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5125,51 +5129,51 @@
       </c>
       <c r="B46" s="5">
         <f t="shared" ref="B46" si="293">D$2/D46</f>
-        <v>24.587775061124688</v>
+        <v>24.503898635477576</v>
       </c>
       <c r="C46" s="5">
         <f t="shared" ref="C46" si="294">D45/D46</f>
-        <v>1.002444987775061</v>
+        <v>1.00682261208577</v>
       </c>
       <c r="D46" s="4">
         <f t="shared" ref="D46" si="295">SUM(F46:H46)</f>
-        <v>20.450000000000003</v>
+        <v>20.520000000000003</v>
       </c>
       <c r="E46" s="9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="F46" s="9">
-        <v>8.73</v>
+        <v>8.69</v>
       </c>
       <c r="G46" s="9">
-        <v>11.08</v>
+        <v>11.16</v>
       </c>
       <c r="H46" s="9">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="I46" s="14">
-        <v>9.68</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="271"/>
-        <v>46.344444444444434</v>
+        <v>45.835164835164825</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="272"/>
-        <v>1.0333333333333334</v>
+        <v>1.0109890109890109</v>
       </c>
       <c r="M46" s="4">
         <f t="shared" si="273"/>
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N46" s="9">
         <v>0.1</v>
       </c>
       <c r="O46" s="9">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="P46" s="9">
         <v>0.36</v>
@@ -5184,36 +5188,36 @@
         <v>54</v>
       </c>
       <c r="T46" s="5">
-        <f t="shared" ref="T46:T47" si="296">ROUND(B46/K46,3)</f>
-        <v>0.53100000000000003</v>
+        <f t="shared" ref="T46" si="296">ROUND(B46/K46,3)</f>
+        <v>0.53500000000000003</v>
       </c>
       <c r="U46" s="5">
-        <f t="shared" ref="U46:U47" si="297">ROUND(C46/L46,3)</f>
-        <v>0.97</v>
+        <f t="shared" ref="U46" si="297">ROUND(C46/L46,3)</f>
+        <v>0.996</v>
       </c>
       <c r="V46" s="4">
-        <f t="shared" ref="V46:V47" si="298">ROUND(D46/M46,3)</f>
-        <v>22.722000000000001</v>
+        <f t="shared" ref="V46" si="298">ROUND(D46/M46,3)</f>
+        <v>22.548999999999999</v>
       </c>
       <c r="W46" s="9">
-        <f t="shared" ref="W46:W47" si="299">ROUND(E46/N46,3)</f>
-        <v>10.3</v>
+        <f t="shared" ref="W46" si="299">ROUND(E46/N46,3)</f>
+        <v>10.5</v>
       </c>
       <c r="X46" s="9">
-        <f t="shared" ref="X46:X47" si="300">ROUND(F46/O46,3)</f>
-        <v>17.117999999999999</v>
+        <f t="shared" ref="X46" si="300">ROUND(F46/O46,3)</f>
+        <v>16.712</v>
       </c>
       <c r="Y46" s="9">
-        <f t="shared" ref="Y46:Y47" si="301">ROUND(G46/P46,3)</f>
-        <v>30.777999999999999</v>
+        <f t="shared" ref="Y46" si="301">ROUND(G46/P46,3)</f>
+        <v>31</v>
       </c>
       <c r="Z46" s="9">
-        <f t="shared" ref="Z46:Z47" si="302">ROUND(H46/Q46,3)</f>
-        <v>21.332999999999998</v>
+        <f t="shared" ref="Z46" si="302">ROUND(H46/Q46,3)</f>
+        <v>22.332999999999998</v>
       </c>
       <c r="AA46" s="14">
         <f t="shared" ref="AA46" si="303">ROUND(I46/R46,3)</f>
-        <v>28.471</v>
+        <v>29.059000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5222,54 +5226,54 @@
       </c>
       <c r="B47" s="5">
         <f t="shared" ref="B47" si="304">D$2/D47</f>
-        <v>25.040836653386453</v>
+        <v>24.929102627664843</v>
       </c>
       <c r="C47" s="5">
         <f t="shared" ref="C47" si="305">D46/D47</f>
-        <v>1.0184262948207174</v>
+        <v>1.0173525037183937</v>
       </c>
       <c r="D47" s="4">
         <f t="shared" ref="D47" si="306">SUM(F47:H47)</f>
-        <v>20.079999999999998</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="E47" s="9">
         <v>1.03</v>
       </c>
       <c r="F47" s="9">
-        <v>8.76</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G47" s="13">
-        <v>10.69</v>
+        <v>10.73</v>
       </c>
       <c r="H47" s="9">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I47" s="14">
-        <v>9.39</v>
+        <v>9.42</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>56</v>
       </c>
       <c r="K47" s="5">
         <f t="shared" ref="K47" si="307">M$2/M47</f>
-        <v>47.397727272727266</v>
+        <v>46.344444444444434</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" ref="L47" si="308">M46/M47</f>
-        <v>1.0227272727272727</v>
+        <v>1.0111111111111111</v>
       </c>
       <c r="M47" s="4">
         <f t="shared" ref="M47" si="309">SUM(O47:Q47)</f>
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="N47" s="9">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="O47" s="9">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="P47" s="13">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="Q47" s="9">
         <v>0.03</v>
@@ -5282,35 +5286,132 @@
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47" si="310">ROUND(B47/K47,3)</f>
-        <v>0.52800000000000002</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" ref="U47" si="311">ROUND(C47/L47,3)</f>
-        <v>0.996</v>
+        <v>1.006</v>
       </c>
       <c r="V47" s="4">
         <f t="shared" ref="V47" si="312">ROUND(D47/M47,3)</f>
-        <v>22.818000000000001</v>
+        <v>22.411000000000001</v>
       </c>
       <c r="W47" s="9">
         <f t="shared" ref="W47" si="313">ROUND(E47/N47,3)</f>
-        <v>10.3</v>
+        <v>9.3640000000000008</v>
       </c>
       <c r="X47" s="9">
         <f t="shared" ref="X47" si="314">ROUND(F47/O47,3)</f>
-        <v>17.52</v>
+        <v>17.254999999999999</v>
       </c>
       <c r="Y47" s="13">
         <f t="shared" ref="Y47" si="315">ROUND(G47/P47,3)</f>
-        <v>30.542999999999999</v>
+        <v>29.806000000000001</v>
       </c>
       <c r="Z47" s="9">
         <f t="shared" ref="Z47" si="316">ROUND(H47/Q47,3)</f>
-        <v>21</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA47" s="14">
         <f t="shared" ref="AA47" si="317">ROUND(I47/R47,3)</f>
-        <v>28.454999999999998</v>
+        <v>28.545000000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="2">
+        <f t="shared" ref="B48" si="318">D$2/D48</f>
+        <v>26.688959660297243</v>
+      </c>
+      <c r="C48" s="2">
+        <f t="shared" ref="C48" si="319">D47/D48</f>
+        <v>1.070594479830149</v>
+      </c>
+      <c r="D48" s="6">
+        <f t="shared" ref="D48" si="320">SUM(F48:H48)</f>
+        <v>18.839999999999996</v>
+      </c>
+      <c r="E48" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="F48" s="18">
+        <v>8.82</v>
+      </c>
+      <c r="G48" s="13">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="I48" s="14">
+        <v>7</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K48" s="2">
+        <f t="shared" ref="K48" si="321">M$2/M48</f>
+        <v>54.168831168831161</v>
+      </c>
+      <c r="L48" s="2">
+        <f t="shared" ref="L48" si="322">M47/M48</f>
+        <v>1.1688311688311688</v>
+      </c>
+      <c r="M48" s="6">
+        <f t="shared" ref="M48" si="323">SUM(O48:Q48)</f>
+        <v>0.77</v>
+      </c>
+      <c r="N48" s="9">
+        <v>0.11</v>
+      </c>
+      <c r="O48" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="P48" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="Q48" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R48" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="S48" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="T48" s="2">
+        <f t="shared" ref="T48" si="324">ROUND(B48/K48,3)</f>
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="U48" s="2">
+        <f t="shared" ref="U48" si="325">ROUND(C48/L48,3)</f>
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="V48" s="6">
+        <f t="shared" ref="V48" si="326">ROUND(D48/M48,3)</f>
+        <v>24.468</v>
+      </c>
+      <c r="W48" s="9">
+        <f t="shared" ref="W48" si="327">ROUND(E48/N48,3)</f>
+        <v>9.2729999999999997</v>
+      </c>
+      <c r="X48" s="9">
+        <f t="shared" ref="X48" si="328">ROUND(F48/O48,3)</f>
+        <v>17.64</v>
+      </c>
+      <c r="Y48" s="13">
+        <f t="shared" ref="Y48" si="329">ROUND(G48/P48,3)</f>
+        <v>37.479999999999997</v>
+      </c>
+      <c r="Z48" s="9">
+        <f t="shared" ref="Z48" si="330">ROUND(H48/Q48,3)</f>
+        <v>32.5</v>
+      </c>
+      <c r="AA48" s="14">
+        <f t="shared" ref="AA48" si="331">ROUND(I48/R48,3)</f>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E063CBA1-EEA8-46EE-B07A-C9060EE07EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA33BBB8-693C-41B3-990F-35F63AC3FEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="59">
   <si>
     <t>H23</t>
   </si>
@@ -237,6 +237,10 @@
   </si>
   <si>
     <t>H68</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H69</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -759,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AB49"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4838,30 +4842,30 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.928477976450065</v>
+        <v>21.947621126145783</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0837331007413868</v>
+        <v>1.0846791793976429</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>22.929999999999996</v>
+        <v>22.91</v>
       </c>
       <c r="E43" s="9">
-        <v>1.34</v>
+        <v>0.95</v>
       </c>
       <c r="F43" s="13">
-        <v>10.83</v>
+        <v>10.79</v>
       </c>
       <c r="G43" s="9">
-        <v>11.04</v>
+        <v>11.06</v>
       </c>
       <c r="H43" s="9">
         <v>1.06</v>
       </c>
       <c r="I43" s="10">
-        <v>12.65</v>
+        <v>12.7</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
@@ -4879,7 +4883,7 @@
         <v>0.96</v>
       </c>
       <c r="N43" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O43" s="13">
         <v>0.57999999999999996</v>
@@ -4891,7 +4895,7 @@
         <v>0.02</v>
       </c>
       <c r="R43" s="10">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>51</v>
@@ -4902,23 +4906,23 @@
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.0509999999999999</v>
+        <v>1.052</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.885000000000002</v>
+        <v>23.864999999999998</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>9.5709999999999997</v>
+        <v>9.5</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.672000000000001</v>
+        <v>18.603000000000002</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>30.667000000000002</v>
+        <v>30.722000000000001</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
@@ -4926,7 +4930,7 @@
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>21.440999999999999</v>
+        <v>21.896999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4935,95 +4939,95 @@
       </c>
       <c r="B44" s="5">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>22.298004434589796</v>
+        <v>22.278245458573327</v>
       </c>
       <c r="C44" s="5">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.0168514412416849</v>
+        <v>1.0150642445724414</v>
       </c>
       <c r="D44" s="4">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.55</v>
+        <v>22.569999999999997</v>
       </c>
       <c r="E44" s="9">
-        <v>1.06</v>
+        <v>0.8</v>
       </c>
       <c r="F44" s="9">
-        <v>10.86</v>
+        <v>10.83</v>
       </c>
       <c r="G44" s="9">
-        <v>11.06</v>
+        <v>11.04</v>
       </c>
       <c r="H44" s="13">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="I44" s="10">
-        <v>12.73</v>
+        <v>12.95</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="K44" s="5">
         <f t="shared" ref="K44:K46" si="271">M$2/M44</f>
-        <v>41.709999999999994</v>
+        <v>42.561224489795912</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" ref="L44:L46" si="272">M43/M44</f>
-        <v>0.96</v>
+        <v>0.97959183673469385</v>
       </c>
       <c r="M44" s="4">
         <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="N44" s="9">
-        <v>0.11</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O44" s="9">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="P44" s="9">
         <v>0.36</v>
       </c>
       <c r="Q44" s="13">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R44" s="10">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="T44" s="5">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.53500000000000003</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.0589999999999999</v>
+        <v>1.036</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>22.55</v>
+        <v>23.030999999999999</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>9.6359999999999992</v>
+        <v>11.429</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>18.100000000000001</v>
+        <v>18.356000000000002</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
-        <v>30.722000000000001</v>
+        <v>30.667000000000002</v>
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>15.75</v>
+        <v>23.332999999999998</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>21.576000000000001</v>
+        <v>22.327999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5032,87 +5036,87 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45" si="282">D$2/D45</f>
-        <v>24.337850919651494</v>
+        <v>24.672227674190378</v>
       </c>
       <c r="C45" s="2">
         <f t="shared" ref="C45" si="283">D44/D45</f>
-        <v>1.0914811229428847</v>
+        <v>1.1074582924435719</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
-        <v>20.660000000000004</v>
+        <v>20.380000000000003</v>
       </c>
       <c r="E45" s="9">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="F45" s="13">
-        <v>8.8800000000000008</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="G45" s="9">
-        <v>11.14</v>
+        <v>11.03</v>
       </c>
       <c r="H45" s="9">
         <v>0.64</v>
       </c>
       <c r="I45" s="10">
-        <v>12.73</v>
+        <v>12.66</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="2">
         <f t="shared" si="271"/>
-        <v>45.336956521739118</v>
+        <v>46.344444444444434</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="272"/>
-        <v>1.0869565217391304</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="273"/>
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="N45" s="9">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="O45" s="13">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P45" s="9">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="Q45" s="9">
         <v>0.03</v>
       </c>
       <c r="R45" s="10">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="T45" s="2">
         <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
-        <v>0.53700000000000003</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="U45" s="2">
         <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
-        <v>1.004</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="V45" s="6">
         <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
-        <v>22.457000000000001</v>
+        <v>22.643999999999998</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="X45" s="13">
         <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
-        <v>17.077000000000002</v>
+        <v>17.077999999999999</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
-        <v>30.108000000000001</v>
+        <v>30.638999999999999</v>
       </c>
       <c r="Z45" s="9">
         <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
@@ -5120,7 +5124,7 @@
       </c>
       <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
-        <v>21.576000000000001</v>
+        <v>21.827999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5129,51 +5133,51 @@
       </c>
       <c r="B46" s="5">
         <f t="shared" ref="B46" si="293">D$2/D46</f>
-        <v>24.503898635477576</v>
+        <v>24.696463654223965</v>
       </c>
       <c r="C46" s="5">
         <f t="shared" ref="C46" si="294">D45/D46</f>
-        <v>1.00682261208577</v>
+        <v>1.0009823182711199</v>
       </c>
       <c r="D46" s="4">
         <f t="shared" ref="D46" si="295">SUM(F46:H46)</f>
-        <v>20.520000000000003</v>
+        <v>20.36</v>
       </c>
       <c r="E46" s="9">
-        <v>1.05</v>
+        <v>0.78</v>
       </c>
       <c r="F46" s="9">
-        <v>8.69</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="G46" s="9">
-        <v>11.16</v>
+        <v>11.02</v>
       </c>
       <c r="H46" s="9">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="I46" s="14">
-        <v>9.8800000000000008</v>
+        <v>9.77</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="271"/>
-        <v>45.835164835164825</v>
+        <v>46.344444444444434</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="272"/>
-        <v>1.0109890109890109</v>
+        <v>1</v>
       </c>
       <c r="M46" s="4">
         <f t="shared" si="273"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N46" s="9">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="O46" s="9">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P46" s="9">
         <v>0.36</v>
@@ -5189,35 +5193,35 @@
       </c>
       <c r="T46" s="5">
         <f t="shared" ref="T46" si="296">ROUND(B46/K46,3)</f>
-        <v>0.53500000000000003</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" ref="U46" si="297">ROUND(C46/L46,3)</f>
-        <v>0.996</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" ref="V46" si="298">ROUND(D46/M46,3)</f>
-        <v>22.548999999999999</v>
+        <v>22.622</v>
       </c>
       <c r="W46" s="9">
         <f t="shared" ref="W46" si="299">ROUND(E46/N46,3)</f>
-        <v>10.5</v>
+        <v>9.75</v>
       </c>
       <c r="X46" s="9">
         <f t="shared" ref="X46" si="300">ROUND(F46/O46,3)</f>
-        <v>16.712</v>
+        <v>17.077999999999999</v>
       </c>
       <c r="Y46" s="9">
         <f t="shared" ref="Y46" si="301">ROUND(G46/P46,3)</f>
-        <v>31</v>
+        <v>30.611000000000001</v>
       </c>
       <c r="Z46" s="9">
         <f t="shared" ref="Z46" si="302">ROUND(H46/Q46,3)</f>
-        <v>22.332999999999998</v>
+        <v>21</v>
       </c>
       <c r="AA46" s="14">
         <f t="shared" ref="AA46" si="303">ROUND(I46/R46,3)</f>
-        <v>29.059000000000001</v>
+        <v>28.734999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5226,54 +5230,54 @@
       </c>
       <c r="B47" s="5">
         <f t="shared" ref="B47" si="304">D$2/D47</f>
-        <v>24.929102627664843</v>
+        <v>25.166166166166168</v>
       </c>
       <c r="C47" s="5">
         <f t="shared" ref="C47" si="305">D46/D47</f>
-        <v>1.0173525037183937</v>
+        <v>1.0190190190190191</v>
       </c>
       <c r="D47" s="4">
         <f t="shared" ref="D47" si="306">SUM(F47:H47)</f>
-        <v>20.170000000000002</v>
+        <v>19.979999999999997</v>
       </c>
       <c r="E47" s="9">
-        <v>1.03</v>
+        <v>0.81</v>
       </c>
       <c r="F47" s="9">
-        <v>8.8000000000000007</v>
+        <v>8.67</v>
       </c>
       <c r="G47" s="13">
-        <v>10.73</v>
+        <v>10.66</v>
       </c>
       <c r="H47" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I47" s="14">
-        <v>9.42</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>56</v>
       </c>
       <c r="K47" s="5">
         <f t="shared" ref="K47" si="307">M$2/M47</f>
-        <v>46.344444444444434</v>
+        <v>47.397727272727266</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" ref="L47" si="308">M46/M47</f>
-        <v>1.0111111111111111</v>
+        <v>1.0227272727272727</v>
       </c>
       <c r="M47" s="4">
         <f t="shared" ref="M47" si="309">SUM(O47:Q47)</f>
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="N47" s="9">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="O47" s="9">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="P47" s="13">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="Q47" s="9">
         <v>0.03</v>
@@ -5286,35 +5290,35 @@
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47" si="310">ROUND(B47/K47,3)</f>
-        <v>0.53800000000000003</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" ref="U47" si="311">ROUND(C47/L47,3)</f>
-        <v>1.006</v>
+        <v>0.996</v>
       </c>
       <c r="V47" s="4">
         <f t="shared" ref="V47" si="312">ROUND(D47/M47,3)</f>
-        <v>22.411000000000001</v>
+        <v>22.704999999999998</v>
       </c>
       <c r="W47" s="9">
         <f t="shared" ref="W47" si="313">ROUND(E47/N47,3)</f>
-        <v>9.3640000000000008</v>
+        <v>10.125</v>
       </c>
       <c r="X47" s="9">
         <f t="shared" ref="X47" si="314">ROUND(F47/O47,3)</f>
-        <v>17.254999999999999</v>
+        <v>17.34</v>
       </c>
       <c r="Y47" s="13">
         <f t="shared" ref="Y47" si="315">ROUND(G47/P47,3)</f>
-        <v>29.806000000000001</v>
+        <v>30.457000000000001</v>
       </c>
       <c r="Z47" s="9">
         <f t="shared" ref="Z47" si="316">ROUND(H47/Q47,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA47" s="14">
         <f t="shared" ref="AA47" si="317">ROUND(I47/R47,3)</f>
-        <v>28.545000000000002</v>
+        <v>28.667000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5323,48 +5327,48 @@
       </c>
       <c r="B48" s="2">
         <f t="shared" ref="B48" si="318">D$2/D48</f>
-        <v>26.688959660297243</v>
+        <v>27.004296455424271</v>
       </c>
       <c r="C48" s="2">
         <f t="shared" ref="C48" si="319">D47/D48</f>
-        <v>1.070594479830149</v>
+        <v>1.0730397422126743</v>
       </c>
       <c r="D48" s="6">
         <f t="shared" ref="D48" si="320">SUM(F48:H48)</f>
-        <v>18.839999999999996</v>
+        <v>18.62</v>
       </c>
       <c r="E48" s="9">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="F48" s="18">
-        <v>8.82</v>
+        <v>8.65</v>
       </c>
       <c r="G48" s="13">
-        <v>9.3699999999999992</v>
+        <v>9.31</v>
       </c>
       <c r="H48" s="9">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I48" s="14">
-        <v>7</v>
+        <v>7.15</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>57</v>
       </c>
       <c r="K48" s="2">
         <f t="shared" ref="K48" si="321">M$2/M48</f>
-        <v>54.168831168831161</v>
+        <v>53.474358974358964</v>
       </c>
       <c r="L48" s="2">
         <f t="shared" ref="L48" si="322">M47/M48</f>
-        <v>1.1688311688311688</v>
+        <v>1.1282051282051282</v>
       </c>
       <c r="M48" s="6">
         <f t="shared" ref="M48" si="323">SUM(O48:Q48)</f>
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="N48" s="9">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="O48" s="9">
         <v>0.5</v>
@@ -5373,7 +5377,7 @@
         <v>0.25</v>
       </c>
       <c r="Q48" s="9">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R48" s="14">
         <v>0.25</v>
@@ -5383,35 +5387,132 @@
       </c>
       <c r="T48" s="2">
         <f t="shared" ref="T48" si="324">ROUND(B48/K48,3)</f>
-        <v>0.49299999999999999</v>
+        <v>0.505</v>
       </c>
       <c r="U48" s="2">
         <f t="shared" ref="U48" si="325">ROUND(C48/L48,3)</f>
-        <v>0.91600000000000004</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" ref="V48" si="326">ROUND(D48/M48,3)</f>
-        <v>24.468</v>
+        <v>23.872</v>
       </c>
       <c r="W48" s="9">
         <f t="shared" ref="W48" si="327">ROUND(E48/N48,3)</f>
-        <v>9.2729999999999997</v>
+        <v>9.75</v>
       </c>
       <c r="X48" s="9">
         <f t="shared" ref="X48" si="328">ROUND(F48/O48,3)</f>
-        <v>17.64</v>
+        <v>17.3</v>
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="329">ROUND(G48/P48,3)</f>
-        <v>37.479999999999997</v>
+        <v>37.24</v>
       </c>
       <c r="Z48" s="9">
         <f t="shared" ref="Z48" si="330">ROUND(H48/Q48,3)</f>
-        <v>32.5</v>
+        <v>22</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="331">ROUND(I48/R48,3)</f>
-        <v>28</v>
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="5">
+        <f t="shared" ref="B49" si="332">D$2/D49</f>
+        <v>26.975321888412012</v>
+      </c>
+      <c r="C49" s="5">
+        <f t="shared" ref="C49" si="333">D48/D49</f>
+        <v>0.99892703862660948</v>
+      </c>
+      <c r="D49" s="4">
+        <f t="shared" ref="D49" si="334">SUM(F49:H49)</f>
+        <v>18.64</v>
+      </c>
+      <c r="E49" s="13">
+        <v>0.67</v>
+      </c>
+      <c r="F49" s="9">
+        <v>8.66</v>
+      </c>
+      <c r="G49" s="9">
+        <v>9.33</v>
+      </c>
+      <c r="H49" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="I49" s="14">
+        <v>6.93</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="K49" s="5">
+        <f t="shared" ref="K49" si="335">M$2/M49</f>
+        <v>54.168831168831161</v>
+      </c>
+      <c r="L49" s="5">
+        <f t="shared" ref="L49" si="336">M48/M49</f>
+        <v>1.0129870129870131</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" ref="M49" si="337">SUM(O49:Q49)</f>
+        <v>0.77</v>
+      </c>
+      <c r="N49" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="O49" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="P49" s="9">
+        <v>0.24</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R49" s="14">
+        <v>0.24</v>
+      </c>
+      <c r="S49" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="T49" s="5">
+        <f t="shared" ref="T49" si="338">ROUND(B49/K49,3)</f>
+        <v>0.498</v>
+      </c>
+      <c r="U49" s="5">
+        <f t="shared" ref="U49" si="339">ROUND(C49/L49,3)</f>
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="V49" s="4">
+        <f t="shared" ref="V49" si="340">ROUND(D49/M49,3)</f>
+        <v>24.207999999999998</v>
+      </c>
+      <c r="W49" s="13">
+        <f t="shared" ref="W49" si="341">ROUND(E49/N49,3)</f>
+        <v>8.375</v>
+      </c>
+      <c r="X49" s="18">
+        <f t="shared" ref="X49" si="342">ROUND(F49/O49,3)</f>
+        <v>17.32</v>
+      </c>
+      <c r="Y49" s="18">
+        <f t="shared" ref="Y49" si="343">ROUND(G49/P49,3)</f>
+        <v>38.875</v>
+      </c>
+      <c r="Z49" s="18">
+        <f t="shared" ref="Z49" si="344">ROUND(H49/Q49,3)</f>
+        <v>21.667000000000002</v>
+      </c>
+      <c r="AA49" s="14">
+        <f t="shared" ref="AA49" si="345">ROUND(I49/R49,3)</f>
+        <v>28.875</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA33BBB8-693C-41B3-990F-35F63AC3FEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09E4A42-FC77-405E-8B13-3D9131EBBDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="60">
   <si>
     <t>H23</t>
   </si>
@@ -241,6 +241,10 @@
   </si>
   <si>
     <t>H69</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H70</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -763,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB50"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4842,51 +4846,51 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.947621126145783</v>
+        <v>21.976398601398596</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0846791793976429</v>
+        <v>1.0861013986013983</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>22.91</v>
+        <v>22.880000000000003</v>
       </c>
       <c r="E43" s="9">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="F43" s="13">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="G43" s="9">
         <v>11.06</v>
       </c>
       <c r="H43" s="9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I43" s="10">
-        <v>12.7</v>
+        <v>12.65</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="K43" s="5">
         <f t="shared" ref="K43" si="257">M$2/M43</f>
-        <v>43.447916666666664</v>
+        <v>42.999999999999993</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" ref="L43" si="258">M42/M43</f>
-        <v>1.03125</v>
+        <v>1.0206185567010309</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ref="M43" si="259">SUM(O43:Q43)</f>
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="N43" s="9">
         <v>0.1</v>
       </c>
       <c r="O43" s="13">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="P43" s="9">
         <v>0.36</v>
@@ -4902,23 +4906,23 @@
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.505</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.052</v>
+        <v>1.0640000000000001</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.864999999999998</v>
+        <v>23.588000000000001</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>9.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.603000000000002</v>
+        <v>18.22</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
@@ -4926,11 +4930,11 @@
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>21.896999999999998</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4939,51 +4943,51 @@
       </c>
       <c r="B44" s="5">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>22.278245458573327</v>
+        <v>22.307897071872226</v>
       </c>
       <c r="C44" s="5">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.0150642445724414</v>
+        <v>1.0150842945874003</v>
       </c>
       <c r="D44" s="4">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.569999999999997</v>
+        <v>22.54</v>
       </c>
       <c r="E44" s="9">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="F44" s="9">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="G44" s="9">
         <v>11.04</v>
       </c>
       <c r="H44" s="13">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="I44" s="10">
-        <v>12.95</v>
+        <v>12.73</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="K44" s="5">
         <f t="shared" ref="K44:K46" si="271">M$2/M44</f>
-        <v>42.561224489795912</v>
+        <v>42.999999999999993</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" ref="L44:L46" si="272">M43/M44</f>
-        <v>0.97959183673469385</v>
+        <v>1</v>
       </c>
       <c r="M44" s="4">
         <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N44" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O44" s="9">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P44" s="9">
         <v>0.36</v>
@@ -4999,23 +5003,23 @@
       </c>
       <c r="T44" s="5">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.52300000000000002</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.036</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>23.030999999999999</v>
+        <v>23.236999999999998</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>11.429</v>
+        <v>9.75</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>18.356000000000002</v>
+        <v>18.690000000000001</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
@@ -5023,11 +5027,11 @@
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>23.332999999999998</v>
+        <v>22</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>22.327999999999999</v>
+        <v>21.948</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5036,51 +5040,51 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45" si="282">D$2/D45</f>
-        <v>24.672227674190378</v>
+        <v>24.635962763351294</v>
       </c>
       <c r="C45" s="2">
         <f t="shared" ref="C45" si="283">D44/D45</f>
-        <v>1.1074582924435719</v>
+        <v>1.1043606075453209</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
-        <v>20.380000000000003</v>
+        <v>20.41</v>
       </c>
       <c r="E45" s="9">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="F45" s="13">
-        <v>8.7100000000000009</v>
+        <v>8.75</v>
       </c>
       <c r="G45" s="9">
-        <v>11.03</v>
+        <v>11.02</v>
       </c>
       <c r="H45" s="9">
         <v>0.64</v>
       </c>
       <c r="I45" s="10">
-        <v>12.66</v>
+        <v>12.67</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="2">
         <f t="shared" si="271"/>
-        <v>46.344444444444434</v>
+        <v>45.835164835164825</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="272"/>
-        <v>1.0888888888888888</v>
+        <v>1.0659340659340659</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="273"/>
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N45" s="9">
         <v>0.08</v>
       </c>
       <c r="O45" s="13">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="P45" s="9">
         <v>0.36</v>
@@ -5096,27 +5100,27 @@
       </c>
       <c r="T45" s="2">
         <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
-        <v>0.53200000000000003</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="U45" s="2">
         <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
-        <v>1.0169999999999999</v>
+        <v>1.036</v>
       </c>
       <c r="V45" s="6">
         <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
-        <v>22.643999999999998</v>
+        <v>22.428999999999998</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
-        <v>10.75</v>
+        <v>9.875</v>
       </c>
       <c r="X45" s="13">
         <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
-        <v>17.077999999999999</v>
+        <v>16.827000000000002</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
-        <v>30.638999999999999</v>
+        <v>30.611000000000001</v>
       </c>
       <c r="Z45" s="9">
         <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
@@ -5124,7 +5128,7 @@
       </c>
       <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
-        <v>21.827999999999999</v>
+        <v>21.844999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5133,37 +5137,37 @@
       </c>
       <c r="B46" s="5">
         <f t="shared" ref="B46" si="293">D$2/D46</f>
-        <v>24.696463654223965</v>
+        <v>24.611845325501712</v>
       </c>
       <c r="C46" s="5">
         <f t="shared" ref="C46" si="294">D45/D46</f>
-        <v>1.0009823182711199</v>
+        <v>0.99902104747919729</v>
       </c>
       <c r="D46" s="4">
         <f t="shared" ref="D46" si="295">SUM(F46:H46)</f>
-        <v>20.36</v>
+        <v>20.43</v>
       </c>
       <c r="E46" s="9">
         <v>0.78</v>
       </c>
       <c r="F46" s="9">
-        <v>8.7100000000000009</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="G46" s="9">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
       <c r="H46" s="9">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I46" s="14">
-        <v>9.77</v>
+        <v>9.81</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="271"/>
-        <v>46.344444444444434</v>
+        <v>45.835164835164825</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="272"/>
@@ -5171,13 +5175,13 @@
       </c>
       <c r="M46" s="4">
         <f t="shared" si="273"/>
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N46" s="9">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="O46" s="9">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="P46" s="9">
         <v>0.36</v>
@@ -5193,35 +5197,35 @@
       </c>
       <c r="T46" s="5">
         <f t="shared" ref="T46" si="296">ROUND(B46/K46,3)</f>
-        <v>0.53300000000000003</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" ref="U46" si="297">ROUND(C46/L46,3)</f>
-        <v>1.0009999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" ref="V46" si="298">ROUND(D46/M46,3)</f>
-        <v>22.622</v>
+        <v>22.451000000000001</v>
       </c>
       <c r="W46" s="9">
         <f t="shared" ref="W46" si="299">ROUND(E46/N46,3)</f>
-        <v>9.75</v>
+        <v>8.6669999999999998</v>
       </c>
       <c r="X46" s="9">
         <f t="shared" ref="X46" si="300">ROUND(F46/O46,3)</f>
-        <v>17.077999999999999</v>
+        <v>16.885000000000002</v>
       </c>
       <c r="Y46" s="9">
         <f t="shared" ref="Y46" si="301">ROUND(G46/P46,3)</f>
-        <v>30.611000000000001</v>
+        <v>30.582999999999998</v>
       </c>
       <c r="Z46" s="9">
         <f t="shared" ref="Z46" si="302">ROUND(H46/Q46,3)</f>
-        <v>21</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA46" s="14">
         <f t="shared" ref="AA46" si="303">ROUND(I46/R46,3)</f>
-        <v>28.734999999999999</v>
+        <v>28.853000000000002</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5230,30 +5234,30 @@
       </c>
       <c r="B47" s="5">
         <f t="shared" ref="B47" si="304">D$2/D47</f>
-        <v>25.166166166166168</v>
+        <v>25.128435782108944</v>
       </c>
       <c r="C47" s="5">
         <f t="shared" ref="C47" si="305">D46/D47</f>
-        <v>1.0190190190190191</v>
+        <v>1.0209895052473763</v>
       </c>
       <c r="D47" s="4">
         <f t="shared" ref="D47" si="306">SUM(F47:H47)</f>
-        <v>19.979999999999997</v>
+        <v>20.009999999999998</v>
       </c>
       <c r="E47" s="9">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="F47" s="9">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="G47" s="13">
-        <v>10.66</v>
+        <v>10.68</v>
       </c>
       <c r="H47" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I47" s="14">
-        <v>9.4600000000000009</v>
+        <v>9.42</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>56</v>
@@ -5264,7 +5268,7 @@
       </c>
       <c r="L47" s="5">
         <f t="shared" ref="L47" si="308">M46/M47</f>
-        <v>1.0227272727272727</v>
+        <v>1.0340909090909092</v>
       </c>
       <c r="M47" s="4">
         <f t="shared" ref="M47" si="309">SUM(O47:Q47)</f>
@@ -5274,10 +5278,10 @@
         <v>0.08</v>
       </c>
       <c r="O47" s="9">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="P47" s="13">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="Q47" s="9">
         <v>0.03</v>
@@ -5290,35 +5294,35 @@
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47" si="310">ROUND(B47/K47,3)</f>
-        <v>0.53100000000000003</v>
+        <v>0.53</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" ref="U47" si="311">ROUND(C47/L47,3)</f>
-        <v>0.996</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="V47" s="4">
         <f t="shared" ref="V47" si="312">ROUND(D47/M47,3)</f>
-        <v>22.704999999999998</v>
+        <v>22.739000000000001</v>
       </c>
       <c r="W47" s="9">
         <f t="shared" ref="W47" si="313">ROUND(E47/N47,3)</f>
-        <v>10.125</v>
+        <v>10</v>
       </c>
       <c r="X47" s="9">
         <f t="shared" ref="X47" si="314">ROUND(F47/O47,3)</f>
-        <v>17.34</v>
+        <v>17.734999999999999</v>
       </c>
       <c r="Y47" s="13">
         <f t="shared" ref="Y47" si="315">ROUND(G47/P47,3)</f>
-        <v>30.457000000000001</v>
+        <v>29.667000000000002</v>
       </c>
       <c r="Z47" s="9">
         <f t="shared" ref="Z47" si="316">ROUND(H47/Q47,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA47" s="14">
         <f t="shared" ref="AA47" si="317">ROUND(I47/R47,3)</f>
-        <v>28.667000000000002</v>
+        <v>28.545000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5327,30 +5331,30 @@
       </c>
       <c r="B48" s="2">
         <f t="shared" ref="B48" si="318">D$2/D48</f>
-        <v>27.004296455424271</v>
+        <v>27.062432723358448</v>
       </c>
       <c r="C48" s="2">
         <f t="shared" ref="C48" si="319">D47/D48</f>
-        <v>1.0730397422126743</v>
+        <v>1.0769644779332617</v>
       </c>
       <c r="D48" s="6">
         <f t="shared" ref="D48" si="320">SUM(F48:H48)</f>
-        <v>18.62</v>
+        <v>18.579999999999998</v>
       </c>
       <c r="E48" s="9">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="F48" s="18">
-        <v>8.65</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="G48" s="13">
-        <v>9.31</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="H48" s="9">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I48" s="14">
-        <v>7.15</v>
+        <v>7.11</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>57</v>
@@ -5387,35 +5391,35 @@
       </c>
       <c r="T48" s="2">
         <f t="shared" ref="T48" si="324">ROUND(B48/K48,3)</f>
-        <v>0.505</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="U48" s="2">
         <f t="shared" ref="U48" si="325">ROUND(C48/L48,3)</f>
-        <v>0.95099999999999996</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" ref="V48" si="326">ROUND(D48/M48,3)</f>
-        <v>23.872</v>
+        <v>23.821000000000002</v>
       </c>
       <c r="W48" s="9">
         <f t="shared" ref="W48" si="327">ROUND(E48/N48,3)</f>
-        <v>9.75</v>
+        <v>11.375</v>
       </c>
       <c r="X48" s="9">
         <f t="shared" ref="X48" si="328">ROUND(F48/O48,3)</f>
-        <v>17.3</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="329">ROUND(G48/P48,3)</f>
-        <v>37.24</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="Z48" s="9">
         <f t="shared" ref="Z48" si="330">ROUND(H48/Q48,3)</f>
-        <v>22</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="331">ROUND(I48/R48,3)</f>
-        <v>28.6</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="49" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5424,30 +5428,30 @@
       </c>
       <c r="B49" s="5">
         <f t="shared" ref="B49" si="332">D$2/D49</f>
-        <v>26.975321888412012</v>
+        <v>27.312330255296033</v>
       </c>
       <c r="C49" s="5">
         <f t="shared" ref="C49" si="333">D48/D49</f>
-        <v>0.99892703862660948</v>
+        <v>1.0092341118957087</v>
       </c>
       <c r="D49" s="4">
         <f t="shared" ref="D49" si="334">SUM(F49:H49)</f>
-        <v>18.64</v>
+        <v>18.41</v>
       </c>
       <c r="E49" s="13">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="F49" s="9">
-        <v>8.66</v>
+        <v>8.69</v>
       </c>
       <c r="G49" s="9">
-        <v>9.33</v>
+        <v>9.08</v>
       </c>
       <c r="H49" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I49" s="14">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="J49" s="12" t="s">
         <v>58</v>
@@ -5465,7 +5469,7 @@
         <v>0.77</v>
       </c>
       <c r="N49" s="13">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O49" s="9">
         <v>0.5</v>
@@ -5484,35 +5488,132 @@
       </c>
       <c r="T49" s="5">
         <f t="shared" ref="T49" si="338">ROUND(B49/K49,3)</f>
-        <v>0.498</v>
+        <v>0.504</v>
       </c>
       <c r="U49" s="5">
         <f t="shared" ref="U49" si="339">ROUND(C49/L49,3)</f>
-        <v>0.98599999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="V49" s="4">
         <f t="shared" ref="V49" si="340">ROUND(D49/M49,3)</f>
-        <v>24.207999999999998</v>
+        <v>23.908999999999999</v>
       </c>
       <c r="W49" s="13">
         <f t="shared" ref="W49" si="341">ROUND(E49/N49,3)</f>
-        <v>8.375</v>
+        <v>8.5709999999999997</v>
       </c>
       <c r="X49" s="18">
         <f t="shared" ref="X49" si="342">ROUND(F49/O49,3)</f>
-        <v>17.32</v>
+        <v>17.38</v>
       </c>
       <c r="Y49" s="18">
         <f t="shared" ref="Y49" si="343">ROUND(G49/P49,3)</f>
-        <v>38.875</v>
+        <v>37.832999999999998</v>
       </c>
       <c r="Z49" s="18">
         <f t="shared" ref="Z49" si="344">ROUND(H49/Q49,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA49" s="14">
         <f t="shared" ref="AA49" si="345">ROUND(I49/R49,3)</f>
-        <v>28.875</v>
+        <v>28.917000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="2">
+        <f t="shared" ref="B50" si="346">D$2/D50</f>
+        <v>28.699771689497712</v>
+      </c>
+      <c r="C50" s="2">
+        <f t="shared" ref="C50" si="347">D49/D50</f>
+        <v>1.0507990867579908</v>
+      </c>
+      <c r="D50" s="6">
+        <f t="shared" ref="D50" si="348">SUM(F50:H50)</f>
+        <v>17.52</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="F50" s="13">
+        <v>7.78</v>
+      </c>
+      <c r="G50" s="9">
+        <v>9.09</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="I50" s="10">
+        <v>6.91</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="K50" s="2">
+        <f t="shared" ref="K50" si="349">M$2/M50</f>
+        <v>56.364864864864856</v>
+      </c>
+      <c r="L50" s="2">
+        <f t="shared" ref="L50" si="350">M49/M50</f>
+        <v>1.0405405405405406</v>
+      </c>
+      <c r="M50" s="6">
+        <f t="shared" ref="M50" si="351">SUM(O50:Q50)</f>
+        <v>0.74</v>
+      </c>
+      <c r="N50" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O50" s="13">
+        <v>0.47</v>
+      </c>
+      <c r="P50" s="9">
+        <v>0.24</v>
+      </c>
+      <c r="Q50" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R50" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="S50" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="T50" s="2">
+        <f t="shared" ref="T50" si="352">ROUND(B50/K50,3)</f>
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="U50" s="2">
+        <f t="shared" ref="U50" si="353">ROUND(C50/L50,3)</f>
+        <v>1.01</v>
+      </c>
+      <c r="V50" s="6">
+        <f t="shared" ref="V50" si="354">ROUND(D50/M50,3)</f>
+        <v>23.675999999999998</v>
+      </c>
+      <c r="W50" s="18">
+        <f t="shared" ref="W50" si="355">ROUND(E50/N50,3)</f>
+        <v>9.8569999999999993</v>
+      </c>
+      <c r="X50" s="13">
+        <f t="shared" ref="X50" si="356">ROUND(F50/O50,3)</f>
+        <v>16.553000000000001</v>
+      </c>
+      <c r="Y50" s="18">
+        <f t="shared" ref="Y50" si="357">ROUND(G50/P50,3)</f>
+        <v>37.875</v>
+      </c>
+      <c r="Z50" s="18">
+        <f t="shared" ref="Z50" si="358">ROUND(H50/Q50,3)</f>
+        <v>21.667000000000002</v>
+      </c>
+      <c r="AA50" s="19">
+        <f t="shared" ref="AA50" si="359">ROUND(I50/R50,3)</f>
+        <v>28.792000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09E4A42-FC77-405E-8B13-3D9131EBBDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F1F8E4-B6B9-42C8-887A-E398519E3391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="9600" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
   <si>
     <t>H23</t>
   </si>
@@ -245,6 +245,10 @@
   </si>
   <si>
     <t>H70</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H71</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -767,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB50"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -4846,30 +4850,30 @@
       </c>
       <c r="B43" s="5">
         <f t="shared" ref="B43" si="254">D$2/D43</f>
-        <v>21.976398601398596</v>
+        <v>21.880765883376846</v>
       </c>
       <c r="C43" s="5">
         <f t="shared" ref="C43" si="255">D42/D43</f>
-        <v>1.0861013986013983</v>
+        <v>1.0813751087902523</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" ref="D43" si="256">SUM(F43:H43)</f>
-        <v>22.880000000000003</v>
+        <v>22.98</v>
       </c>
       <c r="E43" s="9">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="F43" s="13">
-        <v>10.75</v>
+        <v>10.82</v>
       </c>
       <c r="G43" s="9">
-        <v>11.06</v>
+        <v>11.09</v>
       </c>
       <c r="H43" s="9">
         <v>1.07</v>
       </c>
       <c r="I43" s="10">
-        <v>12.65</v>
+        <v>12.7</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>51</v>
@@ -4887,7 +4891,7 @@
         <v>0.97</v>
       </c>
       <c r="N43" s="9">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O43" s="13">
         <v>0.59</v>
@@ -4899,34 +4903,34 @@
         <v>0.02</v>
       </c>
       <c r="R43" s="10">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>51</v>
       </c>
       <c r="T43" s="5">
         <f t="shared" ref="T43" si="260">ROUND(B43/K43,3)</f>
-        <v>0.51100000000000001</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" ref="U43" si="261">ROUND(C43/L43,3)</f>
-        <v>1.0640000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" ref="V43" si="262">ROUND(D43/M43,3)</f>
-        <v>23.588000000000001</v>
+        <v>23.690999999999999</v>
       </c>
       <c r="W43" s="18">
         <f t="shared" ref="W43" si="263">ROUND(E43/N43,3)</f>
-        <v>9.8000000000000007</v>
+        <v>11.111000000000001</v>
       </c>
       <c r="X43" s="13">
         <f t="shared" ref="X43" si="264">ROUND(F43/O43,3)</f>
-        <v>18.22</v>
+        <v>18.338999999999999</v>
       </c>
       <c r="Y43" s="9">
         <f t="shared" ref="Y43" si="265">ROUND(G43/P43,3)</f>
-        <v>30.722000000000001</v>
+        <v>30.806000000000001</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" ref="Z43" si="266">ROUND(H43/Q43,3)</f>
@@ -4934,7 +4938,7 @@
       </c>
       <c r="AA43" s="10">
         <f t="shared" ref="AA43" si="267">ROUND(I43/R43,3)</f>
-        <v>21.81</v>
+        <v>21.524999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4943,51 +4947,51 @@
       </c>
       <c r="B44" s="5">
         <f t="shared" ref="B44" si="268">D$2/D44</f>
-        <v>22.307897071872226</v>
+        <v>22.427297056199816</v>
       </c>
       <c r="C44" s="5">
         <f t="shared" ref="C44" si="269">D43/D44</f>
-        <v>1.0150842945874003</v>
+        <v>1.0249776984834968</v>
       </c>
       <c r="D44" s="4">
         <f t="shared" ref="D44" si="270">SUM(F44:H44)</f>
-        <v>22.54</v>
+        <v>22.42</v>
       </c>
       <c r="E44" s="9">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="F44" s="9">
-        <v>10.84</v>
+        <v>10.78</v>
       </c>
       <c r="G44" s="9">
-        <v>11.04</v>
+        <v>11</v>
       </c>
       <c r="H44" s="13">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="I44" s="10">
-        <v>12.73</v>
+        <v>12.71</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>52</v>
       </c>
       <c r="K44" s="5">
         <f t="shared" ref="K44:K46" si="271">M$2/M44</f>
-        <v>42.999999999999993</v>
+        <v>42.561224489795912</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" ref="L44:L46" si="272">M43/M44</f>
-        <v>1</v>
+        <v>0.98979591836734693</v>
       </c>
       <c r="M44" s="4">
         <f t="shared" ref="M44:M46" si="273">SUM(O44:Q44)</f>
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="N44" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O44" s="9">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="P44" s="9">
         <v>0.36</v>
@@ -5003,35 +5007,35 @@
       </c>
       <c r="T44" s="5">
         <f t="shared" ref="T44" si="274">ROUND(B44/K44,3)</f>
-        <v>0.51900000000000002</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" ref="U44" si="275">ROUND(C44/L44,3)</f>
-        <v>1.0149999999999999</v>
+        <v>1.036</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" ref="V44" si="276">ROUND(D44/M44,3)</f>
-        <v>23.236999999999998</v>
+        <v>22.878</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" ref="W44" si="277">ROUND(E44/N44,3)</f>
-        <v>9.75</v>
+        <v>11.429</v>
       </c>
       <c r="X44" s="9">
         <f t="shared" ref="X44" si="278">ROUND(F44/O44,3)</f>
-        <v>18.690000000000001</v>
+        <v>18.271000000000001</v>
       </c>
       <c r="Y44" s="9">
         <f t="shared" ref="Y44" si="279">ROUND(G44/P44,3)</f>
-        <v>30.667000000000002</v>
+        <v>30.556000000000001</v>
       </c>
       <c r="Z44" s="13">
         <f t="shared" ref="Z44" si="280">ROUND(H44/Q44,3)</f>
-        <v>22</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" ref="AA44" si="281">ROUND(I44/R44,3)</f>
-        <v>21.948</v>
+        <v>21.914000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5040,51 +5044,51 @@
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45" si="282">D$2/D45</f>
-        <v>24.635962763351294</v>
+        <v>24.720747295968536</v>
       </c>
       <c r="C45" s="2">
         <f t="shared" ref="C45" si="283">D44/D45</f>
-        <v>1.1043606075453209</v>
+        <v>1.1022615535889875</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" ref="D45" si="284">SUM(F45:H45)</f>
-        <v>20.41</v>
+        <v>20.339999999999996</v>
       </c>
       <c r="E45" s="9">
         <v>0.79</v>
       </c>
       <c r="F45" s="13">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="G45" s="9">
-        <v>11.02</v>
+        <v>11</v>
       </c>
       <c r="H45" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I45" s="10">
-        <v>12.67</v>
+        <v>12.58</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>53</v>
       </c>
       <c r="K45" s="2">
         <f t="shared" si="271"/>
-        <v>45.835164835164825</v>
+        <v>46.344444444444434</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="272"/>
-        <v>1.0659340659340659</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="M45" s="6">
         <f t="shared" si="273"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N45" s="9">
         <v>0.08</v>
       </c>
       <c r="O45" s="13">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P45" s="9">
         <v>0.36</v>
@@ -5100,15 +5104,15 @@
       </c>
       <c r="T45" s="2">
         <f t="shared" ref="T45" si="285">ROUND(B45/K45,3)</f>
-        <v>0.53700000000000003</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="U45" s="2">
         <f t="shared" ref="U45" si="286">ROUND(C45/L45,3)</f>
-        <v>1.036</v>
+        <v>1.012</v>
       </c>
       <c r="V45" s="6">
         <f t="shared" ref="V45" si="287">ROUND(D45/M45,3)</f>
-        <v>22.428999999999998</v>
+        <v>22.6</v>
       </c>
       <c r="W45" s="9">
         <f t="shared" ref="W45" si="288">ROUND(E45/N45,3)</f>
@@ -5116,19 +5120,19 @@
       </c>
       <c r="X45" s="13">
         <f t="shared" ref="X45" si="289">ROUND(F45/O45,3)</f>
-        <v>16.827000000000002</v>
+        <v>17.039000000000001</v>
       </c>
       <c r="Y45" s="9">
         <f t="shared" ref="Y45" si="290">ROUND(G45/P45,3)</f>
-        <v>30.611000000000001</v>
+        <v>30.556000000000001</v>
       </c>
       <c r="Z45" s="9">
         <f t="shared" ref="Z45" si="291">ROUND(H45/Q45,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="292">ROUND(I45/R45,3)</f>
-        <v>21.844999999999999</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5141,33 +5145,33 @@
       </c>
       <c r="C46" s="5">
         <f t="shared" ref="C46" si="294">D45/D46</f>
-        <v>0.99902104747919729</v>
+        <v>0.99559471365638752</v>
       </c>
       <c r="D46" s="4">
         <f t="shared" ref="D46" si="295">SUM(F46:H46)</f>
         <v>20.43</v>
       </c>
       <c r="E46" s="9">
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
       <c r="F46" s="9">
-        <v>8.7799999999999994</v>
+        <v>8.76</v>
       </c>
       <c r="G46" s="9">
-        <v>11.01</v>
+        <v>11.03</v>
       </c>
       <c r="H46" s="9">
         <v>0.64</v>
       </c>
       <c r="I46" s="14">
-        <v>9.81</v>
+        <v>9.73</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="271"/>
-        <v>45.835164835164825</v>
+        <v>46.344444444444434</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="272"/>
@@ -5175,13 +5179,13 @@
       </c>
       <c r="M46" s="4">
         <f t="shared" si="273"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N46" s="9">
         <v>0.09</v>
       </c>
       <c r="O46" s="9">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="P46" s="9">
         <v>0.36</v>
@@ -5197,27 +5201,27 @@
       </c>
       <c r="T46" s="5">
         <f t="shared" ref="T46" si="296">ROUND(B46/K46,3)</f>
-        <v>0.53700000000000003</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" ref="U46" si="297">ROUND(C46/L46,3)</f>
-        <v>0.999</v>
+        <v>0.996</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" ref="V46" si="298">ROUND(D46/M46,3)</f>
-        <v>22.451000000000001</v>
+        <v>22.7</v>
       </c>
       <c r="W46" s="9">
         <f t="shared" ref="W46" si="299">ROUND(E46/N46,3)</f>
-        <v>8.6669999999999998</v>
+        <v>9</v>
       </c>
       <c r="X46" s="9">
         <f t="shared" ref="X46" si="300">ROUND(F46/O46,3)</f>
-        <v>16.885000000000002</v>
+        <v>17.175999999999998</v>
       </c>
       <c r="Y46" s="9">
         <f t="shared" ref="Y46" si="301">ROUND(G46/P46,3)</f>
-        <v>30.582999999999998</v>
+        <v>30.638999999999999</v>
       </c>
       <c r="Z46" s="9">
         <f t="shared" ref="Z46" si="302">ROUND(H46/Q46,3)</f>
@@ -5225,7 +5229,7 @@
       </c>
       <c r="AA46" s="14">
         <f t="shared" ref="AA46" si="303">ROUND(I46/R46,3)</f>
-        <v>28.853000000000002</v>
+        <v>28.617999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5234,51 +5238,51 @@
       </c>
       <c r="B47" s="5">
         <f t="shared" ref="B47" si="304">D$2/D47</f>
-        <v>25.128435782108944</v>
+        <v>25.065802592223324</v>
       </c>
       <c r="C47" s="5">
         <f t="shared" ref="C47" si="305">D46/D47</f>
-        <v>1.0209895052473763</v>
+        <v>1.0184446660019939</v>
       </c>
       <c r="D47" s="4">
         <f t="shared" ref="D47" si="306">SUM(F47:H47)</f>
-        <v>20.009999999999998</v>
+        <v>20.060000000000002</v>
       </c>
       <c r="E47" s="9">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="F47" s="9">
-        <v>8.69</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G47" s="13">
-        <v>10.68</v>
+        <v>10.65</v>
       </c>
       <c r="H47" s="9">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="I47" s="14">
-        <v>9.42</v>
+        <v>9.27</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>56</v>
       </c>
       <c r="K47" s="5">
         <f t="shared" ref="K47" si="307">M$2/M47</f>
-        <v>47.397727272727266</v>
+        <v>46.865168539325836</v>
       </c>
       <c r="L47" s="5">
         <f t="shared" ref="L47" si="308">M46/M47</f>
-        <v>1.0340909090909092</v>
+        <v>1.0112359550561798</v>
       </c>
       <c r="M47" s="4">
         <f t="shared" ref="M47" si="309">SUM(O47:Q47)</f>
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="N47" s="9">
         <v>0.08</v>
       </c>
       <c r="O47" s="9">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="P47" s="13">
         <v>0.36</v>
@@ -5294,35 +5298,35 @@
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47" si="310">ROUND(B47/K47,3)</f>
-        <v>0.53</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" ref="U47" si="311">ROUND(C47/L47,3)</f>
-        <v>0.98699999999999999</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="V47" s="4">
         <f t="shared" ref="V47" si="312">ROUND(D47/M47,3)</f>
-        <v>22.739000000000001</v>
+        <v>22.539000000000001</v>
       </c>
       <c r="W47" s="9">
         <f t="shared" ref="W47" si="313">ROUND(E47/N47,3)</f>
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="X47" s="9">
         <f t="shared" ref="X47" si="314">ROUND(F47/O47,3)</f>
-        <v>17.734999999999999</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="Y47" s="13">
         <f t="shared" ref="Y47" si="315">ROUND(G47/P47,3)</f>
-        <v>29.667000000000002</v>
+        <v>29.582999999999998</v>
       </c>
       <c r="Z47" s="9">
         <f t="shared" ref="Z47" si="316">ROUND(H47/Q47,3)</f>
-        <v>21.332999999999998</v>
+        <v>23.667000000000002</v>
       </c>
       <c r="AA47" s="14">
         <f t="shared" ref="AA47" si="317">ROUND(I47/R47,3)</f>
-        <v>28.545000000000002</v>
+        <v>28.091000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5331,30 +5335,30 @@
       </c>
       <c r="B48" s="2">
         <f t="shared" ref="B48" si="318">D$2/D48</f>
-        <v>27.062432723358448</v>
+        <v>27.135456017269295</v>
       </c>
       <c r="C48" s="2">
         <f t="shared" ref="C48" si="319">D47/D48</f>
-        <v>1.0769644779332617</v>
+        <v>1.0825688073394497</v>
       </c>
       <c r="D48" s="6">
         <f t="shared" ref="D48" si="320">SUM(F48:H48)</f>
-        <v>18.579999999999998</v>
+        <v>18.529999999999998</v>
       </c>
       <c r="E48" s="9">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="F48" s="18">
-        <v>8.6300000000000008</v>
+        <v>8.6</v>
       </c>
       <c r="G48" s="13">
-        <v>9.3000000000000007</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="H48" s="9">
         <v>0.65</v>
       </c>
       <c r="I48" s="14">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="J48" s="12" t="s">
         <v>57</v>
@@ -5365,7 +5369,7 @@
       </c>
       <c r="L48" s="2">
         <f t="shared" ref="L48" si="322">M47/M48</f>
-        <v>1.1282051282051282</v>
+        <v>1.141025641025641</v>
       </c>
       <c r="M48" s="6">
         <f t="shared" ref="M48" si="323">SUM(O48:Q48)</f>
@@ -5391,27 +5395,27 @@
       </c>
       <c r="T48" s="2">
         <f t="shared" ref="T48" si="324">ROUND(B48/K48,3)</f>
-        <v>0.50600000000000001</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="U48" s="2">
         <f t="shared" ref="U48" si="325">ROUND(C48/L48,3)</f>
-        <v>0.95499999999999996</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" ref="V48" si="326">ROUND(D48/M48,3)</f>
-        <v>23.821000000000002</v>
+        <v>23.756</v>
       </c>
       <c r="W48" s="9">
         <f t="shared" ref="W48" si="327">ROUND(E48/N48,3)</f>
-        <v>11.375</v>
+        <v>9.875</v>
       </c>
       <c r="X48" s="9">
         <f t="shared" ref="X48" si="328">ROUND(F48/O48,3)</f>
-        <v>17.260000000000002</v>
+        <v>17.2</v>
       </c>
       <c r="Y48" s="13">
         <f t="shared" ref="Y48" si="329">ROUND(G48/P48,3)</f>
-        <v>37.200000000000003</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="Z48" s="9">
         <f t="shared" ref="Z48" si="330">ROUND(H48/Q48,3)</f>
@@ -5419,7 +5423,7 @@
       </c>
       <c r="AA48" s="14">
         <f t="shared" ref="AA48" si="331">ROUND(I48/R48,3)</f>
-        <v>28.44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5428,30 +5432,30 @@
       </c>
       <c r="B49" s="5">
         <f t="shared" ref="B49" si="332">D$2/D49</f>
-        <v>27.312330255296033</v>
+        <v>27.446506550218338</v>
       </c>
       <c r="C49" s="5">
         <f t="shared" ref="C49" si="333">D48/D49</f>
-        <v>1.0092341118957087</v>
+        <v>1.0114628820960698</v>
       </c>
       <c r="D49" s="4">
         <f t="shared" ref="D49" si="334">SUM(F49:H49)</f>
-        <v>18.41</v>
+        <v>18.32</v>
       </c>
       <c r="E49" s="13">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="F49" s="9">
-        <v>8.69</v>
+        <v>8.6</v>
       </c>
       <c r="G49" s="9">
-        <v>9.08</v>
+        <v>9.06</v>
       </c>
       <c r="H49" s="9">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="I49" s="14">
-        <v>6.94</v>
+        <v>7</v>
       </c>
       <c r="J49" s="12" t="s">
         <v>58</v>
@@ -5469,7 +5473,7 @@
         <v>0.77</v>
       </c>
       <c r="N49" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O49" s="9">
         <v>0.5</v>
@@ -5488,35 +5492,35 @@
       </c>
       <c r="T49" s="5">
         <f t="shared" ref="T49" si="338">ROUND(B49/K49,3)</f>
-        <v>0.504</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="U49" s="5">
         <f t="shared" ref="U49" si="339">ROUND(C49/L49,3)</f>
-        <v>0.996</v>
+        <v>0.998</v>
       </c>
       <c r="V49" s="4">
         <f t="shared" ref="V49" si="340">ROUND(D49/M49,3)</f>
-        <v>23.908999999999999</v>
+        <v>23.792000000000002</v>
       </c>
       <c r="W49" s="13">
         <f t="shared" ref="W49" si="341">ROUND(E49/N49,3)</f>
-        <v>8.5709999999999997</v>
+        <v>7.75</v>
       </c>
       <c r="X49" s="18">
         <f t="shared" ref="X49" si="342">ROUND(F49/O49,3)</f>
-        <v>17.38</v>
+        <v>17.2</v>
       </c>
       <c r="Y49" s="18">
         <f t="shared" ref="Y49" si="343">ROUND(G49/P49,3)</f>
-        <v>37.832999999999998</v>
+        <v>37.75</v>
       </c>
       <c r="Z49" s="18">
         <f t="shared" ref="Z49" si="344">ROUND(H49/Q49,3)</f>
-        <v>21.332999999999998</v>
+        <v>22</v>
       </c>
       <c r="AA49" s="14">
         <f t="shared" ref="AA49" si="345">ROUND(I49/R49,3)</f>
-        <v>28.917000000000002</v>
+        <v>29.167000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5525,30 +5529,30 @@
       </c>
       <c r="B50" s="2">
         <f t="shared" ref="B50" si="346">D$2/D50</f>
-        <v>28.699771689497712</v>
+        <v>28.765446224256287</v>
       </c>
       <c r="C50" s="2">
         <f t="shared" ref="C50" si="347">D49/D50</f>
-        <v>1.0507990867579908</v>
+        <v>1.0480549199084668</v>
       </c>
       <c r="D50" s="6">
         <f t="shared" ref="D50" si="348">SUM(F50:H50)</f>
-        <v>17.52</v>
+        <v>17.48</v>
       </c>
       <c r="E50" s="9">
-        <v>0.69</v>
+        <v>0.64</v>
       </c>
       <c r="F50" s="13">
-        <v>7.78</v>
+        <v>7.76</v>
       </c>
       <c r="G50" s="9">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
       <c r="H50" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I50" s="10">
-        <v>6.91</v>
+        <v>6.95</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>59</v>
@@ -5585,35 +5589,132 @@
       </c>
       <c r="T50" s="2">
         <f t="shared" ref="T50" si="352">ROUND(B50/K50,3)</f>
-        <v>0.50900000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="U50" s="2">
         <f t="shared" ref="U50" si="353">ROUND(C50/L50,3)</f>
-        <v>1.01</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="V50" s="6">
         <f t="shared" ref="V50" si="354">ROUND(D50/M50,3)</f>
-        <v>23.675999999999998</v>
+        <v>23.622</v>
       </c>
       <c r="W50" s="18">
         <f t="shared" ref="W50" si="355">ROUND(E50/N50,3)</f>
-        <v>9.8569999999999993</v>
+        <v>9.1430000000000007</v>
       </c>
       <c r="X50" s="13">
         <f t="shared" ref="X50" si="356">ROUND(F50/O50,3)</f>
-        <v>16.553000000000001</v>
+        <v>16.510999999999999</v>
       </c>
       <c r="Y50" s="18">
         <f t="shared" ref="Y50" si="357">ROUND(G50/P50,3)</f>
-        <v>37.875</v>
+        <v>37.832999999999998</v>
       </c>
       <c r="Z50" s="18">
         <f t="shared" ref="Z50" si="358">ROUND(H50/Q50,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA50" s="19">
         <f t="shared" ref="AA50" si="359">ROUND(I50/R50,3)</f>
-        <v>28.792000000000002</v>
+        <v>28.957999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="2">
+        <f t="shared" ref="B51" si="360">D$2/D51</f>
+        <v>32.885546108567688</v>
+      </c>
+      <c r="C51" s="2">
+        <f t="shared" ref="C51" si="361">D50/D51</f>
+        <v>1.143230869849575</v>
+      </c>
+      <c r="D51" s="6">
+        <f t="shared" ref="D51" si="362">SUM(F51:H51)</f>
+        <v>15.29</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="F51" s="9">
+        <v>7.72</v>
+      </c>
+      <c r="G51" s="13">
+        <v>6.93</v>
+      </c>
+      <c r="H51" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="I51" s="14">
+        <v>4.88</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="K51" s="2">
+        <f t="shared" ref="K51" si="363">M$2/M51</f>
+        <v>62.253731343283569</v>
+      </c>
+      <c r="L51" s="2">
+        <f t="shared" ref="L51" si="364">M50/M51</f>
+        <v>1.1044776119402984</v>
+      </c>
+      <c r="M51" s="6">
+        <f t="shared" ref="M51" si="365">SUM(O51:Q51)</f>
+        <v>0.67</v>
+      </c>
+      <c r="N51" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O51" s="9">
+        <v>0.47</v>
+      </c>
+      <c r="P51" s="13">
+        <v>0.17</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R51" s="14">
+        <v>0.18</v>
+      </c>
+      <c r="S51" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="T51" s="2">
+        <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="U51" s="2">
+        <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="V51" s="6">
+        <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
+        <v>22.821000000000002</v>
+      </c>
+      <c r="W51" s="9">
+        <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
+        <v>9.2859999999999996</v>
+      </c>
+      <c r="X51" s="9">
+        <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
+        <v>16.425999999999998</v>
+      </c>
+      <c r="Y51" s="13">
+        <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
+        <v>40.765000000000001</v>
+      </c>
+      <c r="Z51" s="9">
+        <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
+        <v>21.332999999999998</v>
+      </c>
+      <c r="AA51" s="14">
+        <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
+        <v>27.111000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F1F8E4-B6B9-42C8-887A-E398519E3391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA929256-E440-45E4-A04D-B012F5452188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="63">
   <si>
     <t>H23</t>
   </si>
@@ -249,6 +249,14 @@
   </si>
   <si>
     <t>H71</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H72</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H73</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB53"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5649,56 +5657,56 @@
         <v>0.64</v>
       </c>
       <c r="I51" s="14">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="2">
-        <f t="shared" ref="K51" si="363">M$2/M51</f>
-        <v>62.253731343283569</v>
+        <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
+        <v>63.196969696969681</v>
       </c>
       <c r="L51" s="2">
-        <f t="shared" ref="L51" si="364">M50/M51</f>
-        <v>1.1044776119402984</v>
+        <f t="shared" ref="L51:L53" si="364">M50/M51</f>
+        <v>1.1212121212121211</v>
       </c>
       <c r="M51" s="6">
-        <f t="shared" ref="M51" si="365">SUM(O51:Q51)</f>
-        <v>0.67</v>
+        <f t="shared" ref="M51:M53" si="365">SUM(O51:Q51)</f>
+        <v>0.66</v>
       </c>
       <c r="N51" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.12</v>
       </c>
       <c r="O51" s="9">
         <v>0.47</v>
       </c>
       <c r="P51" s="13">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Q51" s="9">
         <v>0.03</v>
       </c>
       <c r="R51" s="14">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="T51" s="2">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
-        <v>0.52800000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="U51" s="2">
         <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
-        <v>1.0349999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="V51" s="6">
         <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
-        <v>22.821000000000002</v>
+        <v>23.167000000000002</v>
       </c>
       <c r="W51" s="9">
         <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
-        <v>9.2859999999999996</v>
+        <v>5.4169999999999998</v>
       </c>
       <c r="X51" s="9">
         <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
@@ -5706,7 +5714,7 @@
       </c>
       <c r="Y51" s="13">
         <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
-        <v>40.765000000000001</v>
+        <v>43.313000000000002</v>
       </c>
       <c r="Z51" s="9">
         <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
@@ -5714,7 +5722,201 @@
       </c>
       <c r="AA51" s="14">
         <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
-        <v>27.111000000000001</v>
+        <v>28.882000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="5">
+        <f t="shared" ref="B52:B53" si="374">D$2/D52</f>
+        <v>32.885546108567688</v>
+      </c>
+      <c r="C52" s="5">
+        <f t="shared" ref="C52:C53" si="375">D51/D52</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="D52" s="4">
+        <f t="shared" ref="D52:D53" si="376">SUM(F52:H52)</f>
+        <v>15.290000000000001</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="F52" s="9">
+        <v>7.69</v>
+      </c>
+      <c r="G52" s="9">
+        <v>6.94</v>
+      </c>
+      <c r="H52" s="9">
+        <v>0.66</v>
+      </c>
+      <c r="I52" s="14">
+        <v>4.92</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K52" s="5">
+        <f t="shared" si="363"/>
+        <v>62.253731343283569</v>
+      </c>
+      <c r="L52" s="5">
+        <f t="shared" si="364"/>
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="M52" s="4">
+        <f t="shared" si="365"/>
+        <v>0.67</v>
+      </c>
+      <c r="N52" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="O52" s="9">
+        <v>0.47</v>
+      </c>
+      <c r="P52" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="Q52" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R52" s="14">
+        <v>0.18</v>
+      </c>
+      <c r="S52" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="T52" s="5">
+        <f t="shared" ref="T52:T53" si="377">ROUND(B52/K52,3)</f>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="U52" s="5">
+        <f t="shared" ref="U52:U53" si="378">ROUND(C52/L52,3)</f>
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="V52" s="4">
+        <f t="shared" ref="V52:V53" si="379">ROUND(D52/M52,3)</f>
+        <v>22.821000000000002</v>
+      </c>
+      <c r="W52" s="18">
+        <f t="shared" ref="W52:W53" si="380">ROUND(E52/N52,3)</f>
+        <v>8.1110000000000007</v>
+      </c>
+      <c r="X52" s="18">
+        <f t="shared" ref="X52:X53" si="381">ROUND(F52/O52,3)</f>
+        <v>16.361999999999998</v>
+      </c>
+      <c r="Y52" s="18">
+        <f t="shared" ref="Y52:Y53" si="382">ROUND(G52/P52,3)</f>
+        <v>40.823999999999998</v>
+      </c>
+      <c r="Z52" s="18">
+        <f t="shared" ref="Z52:Z53" si="383">ROUND(H52/Q52,3)</f>
+        <v>22</v>
+      </c>
+      <c r="AA52" s="14">
+        <f t="shared" ref="AA52:AA53" si="384">ROUND(I52/R52,3)</f>
+        <v>27.332999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="5">
+        <f t="shared" si="374"/>
+        <v>33.365627073656263</v>
+      </c>
+      <c r="C53" s="5">
+        <f t="shared" si="375"/>
+        <v>1.0145985401459854</v>
+      </c>
+      <c r="D53" s="4">
+        <f t="shared" si="376"/>
+        <v>15.07</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.66</v>
+      </c>
+      <c r="F53" s="9">
+        <v>7.74</v>
+      </c>
+      <c r="G53" s="13">
+        <v>6.67</v>
+      </c>
+      <c r="H53" s="9">
+        <v>0.66</v>
+      </c>
+      <c r="I53" s="14">
+        <v>4.82</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K53" s="5">
+        <f t="shared" si="363"/>
+        <v>63.196969696969681</v>
+      </c>
+      <c r="L53" s="5">
+        <f t="shared" si="364"/>
+        <v>1.0151515151515151</v>
+      </c>
+      <c r="M53" s="4">
+        <f t="shared" si="365"/>
+        <v>0.66</v>
+      </c>
+      <c r="N53" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="O53" s="9">
+        <v>0.48</v>
+      </c>
+      <c r="P53" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R53" s="14">
+        <v>0.16</v>
+      </c>
+      <c r="S53" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="T53" s="5">
+        <f t="shared" si="377"/>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="U53" s="5">
+        <f t="shared" si="378"/>
+        <v>0.999</v>
+      </c>
+      <c r="V53" s="4">
+        <f t="shared" si="379"/>
+        <v>22.832999999999998</v>
+      </c>
+      <c r="W53" s="18">
+        <f t="shared" si="380"/>
+        <v>7.3330000000000002</v>
+      </c>
+      <c r="X53" s="18">
+        <f t="shared" si="381"/>
+        <v>16.125</v>
+      </c>
+      <c r="Y53" s="13">
+        <f t="shared" si="382"/>
+        <v>44.466999999999999</v>
+      </c>
+      <c r="Z53" s="18">
+        <f t="shared" si="383"/>
+        <v>22</v>
+      </c>
+      <c r="AA53" s="14">
+        <f t="shared" si="384"/>
+        <v>30.125</v>
       </c>
     </row>
   </sheetData>
